--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -859,12 +859,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.638635257181679</t>
+          <t>2.5981405273103704</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18.9836587075729</t>
+          <t>6.340143618711291</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.760274721729822</t>
+          <t>6.700318009418449</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.232862236659514</t>
+          <t>6.174846922880504</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.30841221509625</t>
+          <t>24.5361137729174</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.22786744179030108</t>
+          <t>0.22524511508327283</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.009134110098822</t>
+          <t>4.987294873018898</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.434107271888706</t>
+          <t>2.436084356157824</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.912999153255683</t>
+          <t>5.872994721186625</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.7816415441490632</t>
+          <t>1.7754355027562563</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.986616158351691</t>
+          <t>6.90708693944848</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.291370222973141</t>
+          <t>6.256022477132891</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.280053020305841</t>
+          <t>2.270028385485256</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.921791047627531</t>
+          <t>13.93170034817312</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.98503671026167</t>
+          <t>0.987383348258116</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.151185860761057</t>
+          <t>3.148422216374719</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.829271069902287</t>
+          <t>10.769365918362272</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.5981405273103704</t>
+          <t>2.5858163230728692</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.436791924002724</t>
+          <t>15.47832829135311</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.392661081167598</t>
+          <t>7.461115286622892</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.497393237318983</t>
+          <t>7.548964954004653</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.099069434987248</t>
+          <t>12.19341123670982</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.621997342089316</t>
+          <t>6.571398091513861</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.3352419142926424</t>
+          <t>1.3338239010332873</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.239211207410388</t>
+          <t>8.174187930838599</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.284989258237668</t>
+          <t>2.2696857718515107</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.217559166718882</t>
+          <t>5.18588172645788</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.275361229957005</t>
+          <t>4.246760860588047</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.340143618711291</t>
+          <t>6.27137089011487</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.840091041381093</t>
+          <t>12.73754563168697</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.75515946446135</t>
+          <t>13.758540373546456</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.670742032729976</t>
+          <t>4.651326509700397</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.2718019980693036</t>
+          <t>2.259304390746392</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.0373792303197398</t>
+          <t>1.0271157457038314</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.463088543969292</t>
+          <t>6.4337539031073305</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15.95309183775399</t>
+          <t>16.00366986669341</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.7457353169071563</t>
+          <t>2.7326118789783473</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.06243614864972</t>
+          <t>1.0583029721334114</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6.065133947899204</t>
+          <t>6.02521970055686</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5.0485007383393725</t>
+          <t>5.0012357424470615</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.677606198285478</t>
+          <t>5.654444655541488</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.496539346440308</t>
+          <t>13.390447914928998</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.4131896980298184</t>
+          <t>2.399281189350071</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.0451659300868457</t>
+          <t>2.0363148489338627</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.88456998735829</t>
+          <t>3.868110239951818</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.884321969724375</t>
+          <t>20.72485830835255</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13.348384998923507</t>
+          <t>13.21421982771804</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.316107828020975</t>
+          <t>2.3053266076277765</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.876451540255105</t>
+          <t>4.907531178925237</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6.54446359732755</t>
+          <t>6.57717985616226</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.9331606681317295</t>
+          <t>4.968523301089293</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6.31332635488007</t>
+          <t>6.355062281904547</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9.328732475084857</t>
+          <t>9.355122472610143</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6.563479958149072</t>
+          <t>6.5992925583707605</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.367509180659466</t>
+          <t>4.397094906312757</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7.633680743254937</t>
+          <t>7.669586259356665</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9.907272610394536</t>
+          <t>9.92044967400905</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.987329914004904</t>
+          <t>6.026563663586785</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.7602002535262095</t>
+          <t>0.753905645982132</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.352750133250495</t>
+          <t>16.269471607094363</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.066490332154502</t>
+          <t>6.9858547099223385</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.8405144326972618</t>
+          <t>1.804717903291177</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>44.89406252030112</t>
+          <t>45.50184407565176</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.45853698198145</t>
+          <t>11.81828642756114</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.860606877861268</t>
+          <t>5.9100845093697405</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3.0162223897810447</t>
+          <t>2.9877043050018584</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.557888051647077</t>
+          <t>0.5565331341442086</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.772190705448623</t>
+          <t>2.7407444536423022</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.36304224171373</t>
+          <t>1.3650579270037793</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.868406533657254</t>
+          <t>4.8598033129489835</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.817825864425341</t>
+          <t>3.79821748479986</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>23.59838827856617</t>
+          <t>23.630917957421435</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5.74348901584178</t>
+          <t>5.711596164256358</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.54078552439831</t>
+          <t>11.417061143025974</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7.18631390247827</t>
+          <t>7.1552792611967835</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.759239928008284</t>
+          <t>23.631293383284095</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.102026616988564</t>
+          <t>4.071969426496703</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.87337000965512</t>
+          <t>5.912378714646996</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.572506547713267</t>
+          <t>20.08691857130095</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.8244117756400685</t>
+          <t>0.8257714720572105</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.4561287019688819</t>
+          <t>0.4502461185473621</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.3004302579046403</t>
+          <t>2.298784538857351</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5.406889016044112</t>
+          <t>5.339078597391985</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9.55628799552732</t>
+          <t>9.486994448271009</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2.0923245131189194</t>
+          <t>2.0874322498671614</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.35465754994139936</t>
+          <t>0.35143697067845836</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4.788790893463395</t>
+          <t>4.790981394979021</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.29058049951933485</t>
+          <t>0.2884627141241816</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.022045997480461</t>
+          <t>3.0054028500134784</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.9467682099698749</t>
+          <t>1.9276398685421796</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.9664205101166097</t>
+          <t>1.9660991900054692</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.636600713788263</t>
+          <t>2.6128922698571033</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>5.066819196980822</t>
+          <t>5.059077787538641</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.8373828130784253</t>
+          <t>3.826068532630722</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.6519269812510586</t>
+          <t>2.6286644124238894</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.5334503141331517</t>
+          <t>2.510275722540145</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>23.850065394217</t>
+          <t>23.86244656182332</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>8.946848293769957</t>
+          <t>8.94399088404601</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.662556970335089</t>
+          <t>4.63173100774457</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8.486845570757211</t>
+          <t>8.384981754886027</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.75362696867485</t>
+          <t>18.64061483903884</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>15.14187829510006</t>
+          <t>15.25138102825298</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>18.13864096693182</t>
+          <t>18.19672581038954</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.299879935588188</t>
+          <t>3.283125606903752</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>5.233713881592763</t>
+          <t>5.193180841859121</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.272531536588561</t>
+          <t>1.2743186445761996</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.5963905560601996</t>
+          <t>2.583669908283161</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.657760859494921</t>
+          <t>2.651733230418671</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.625472518697629</t>
+          <t>2.602020203315531</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.5751191764874655</t>
+          <t>2.6204122555178557</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.36491140901251684</t>
+          <t>0.36262190704136593</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.49147826299464015</t>
+          <t>0.48352192711084996</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1.3238334835504784</t>
+          <t>1.3230326825127108</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.6828296399119593</t>
+          <t>1.66873079264374</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.39473174830150165</t>
+          <t>0.38667733889350475</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>0.9233646445708961</t>
+          <t>1.877401556860063</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>13.22859188391509</t>
+          <t>13.173926517659467</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>83.03327276339687</t>
+          <t>83.09199914474924</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>18.13971237975958</t>
+          <t>18.15947202935728</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>17.143725360403476</t>
+          <t>17.187966782562814</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>96.37925693459492</t>
+          <t>96.38616442074554</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>7.0430696068819225</t>
+          <t>6.979747957767756</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1.1528541956449319</t>
+          <t>1.1531937807623027</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1.309261333385109</t>
+          <t>1.3048444786316062</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>3.919736822128936</t>
+          <t>3.926726092123735</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>65.86812553901537</t>
+          <t>65.84530612035675</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.7117403359601884</t>
+          <t>3.7263351157359756</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>24.76796842779927</t>
+          <t>25.00964528925075</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>27.00769806149956</t>
+          <t>27.21787373326672</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.9800445957712542</t>
+          <t>0.9008205750454873</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.7844245237079464</t>
+          <t>3.7577029201400762</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.3951384841540753</t>
+          <t>3.456641205378878</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>17.28761517524549</t>
+          <t>17.30318163805743</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.695344670302546</t>
+          <t>6.669964672201859</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>4.007320835733975</t>
+          <t>3.9727299715044637</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.657572614177667</t>
+          <t>4.636408122535457</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>73.84364524956996</t>
+          <t>74.01382146835664</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9.582818856451716</t>
+          <t>9.677959522644361</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.94586000148862</t>
+          <t>4.9238703078472845</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>8.307494225816125</t>
+          <t>8.317917471616916</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>12.228008037996714</t>
+          <t>12.281308894669378</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>89.07757993960402</t>
+          <t>89.09951175731113</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.171134350945685</t>
+          <t>12.044337653161385</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>11.028932565352392</t>
+          <t>10.982358156522997</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>0.5091898424200524</t>
+          <t>0.5109809967237311</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.279991318692866</t>
+          <t>6.250940574628417</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>3.1180037262350204</t>
+          <t>3.06328904244965</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>59.679496941351985</t>
+          <t>60.2144709978781</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.640967010774379</t>
+          <t>0.6368515588654162</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.7121555167907313</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6403,254 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>15.290659597151109</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>F2PLR_PHY_Version_Z_Goku</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>F2P_AGL_Gohan_Piccolo</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>F2P_INT_Krillin</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>F2P_STR_Yamcha</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Tien</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Chiaotzu</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>LR_AGL_Krillin_Gohan_Namek</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>7.385868241461789</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>LR_INT_Vegeta_Goku_Exchange</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>8.293823529705822</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Oolong_Launch</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>BU_INT_Angila_Medamatcha</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>12.64975125011227</t>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>17.62908753506821</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>DF_STR_Lord_Slug</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>56.69042646380463</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.700318009418449</t>
+          <t>6.710169438402861</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.174846922880504</t>
+          <t>6.250487351827658</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.5361137729174</t>
+          <t>24.364890661968587</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.22524511508327283</t>
+          <t>0.2213703826145963</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.987294873018898</t>
+          <t>4.959425631007489</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.436084356157824</t>
+          <t>2.4021133128372654</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.872994721186625</t>
+          <t>5.843913639745715</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.7754355027562563</t>
+          <t>1.7614090834136757</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.90708693944848</t>
+          <t>6.8872073070984</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.256022477132891</t>
+          <t>6.225033444835019</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.270028385485256</t>
+          <t>2.253845214134712</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.93170034817312</t>
+          <t>13.7344258471216</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.987383348258116</t>
+          <t>0.9689374513612639</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.148422216374719</t>
+          <t>3.120126037962489</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.769365918362272</t>
+          <t>10.765363399967907</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.5858163230728692</t>
+          <t>2.5710486002182193</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.47832829135311</t>
+          <t>15.283460943324119</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.461115286622892</t>
+          <t>7.352876062103215</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.548964954004653</t>
+          <t>7.4688883801955654</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.19341123670982</t>
+          <t>12.00271774770994</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.571398091513861</t>
+          <t>6.52704496569263</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.3338239010332873</t>
+          <t>1.314138018986597</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.174187930838599</t>
+          <t>8.15545637581129</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.2696857718515107</t>
+          <t>2.24588141585562</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.18588172645788</t>
+          <t>5.150460467611904</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.246760860588047</t>
+          <t>4.223409447156719</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.27137089011487</t>
+          <t>6.2376287625546105</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.73754563168697</t>
+          <t>12.781018049662322</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.758540373546456</t>
+          <t>13.711481566199058</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.651326509700397</t>
+          <t>4.663834592330971</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.259304390746392</t>
+          <t>2.2479743816735374</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.0271157457038314</t>
+          <t>1.0253786638897608</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.4337539031073305</t>
+          <t>6.431115187485972</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>16.00366986669341</t>
+          <t>15.93837487416927</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.7326118789783473</t>
+          <t>2.7128098714883633</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.0583029721334114</t>
+          <t>1.0500181537835722</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6.02521970055686</t>
+          <t>6.047192555699015</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5.0012357424470615</t>
+          <t>5.00977531487583</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.654444655541488</t>
+          <t>5.588288811631164</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.390447914928998</t>
+          <t>13.426402547564521</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.399281189350071</t>
+          <t>2.4338752120326967</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.0363148489338627</t>
+          <t>2.030318566447562</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.868110239951818</t>
+          <t>3.87603758738382</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.72485830835255</t>
+          <t>20.858091585375135</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13.21421982771804</t>
+          <t>13.327991076973618</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.3053266076277765</t>
+          <t>2.3018366626358784</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.907531178925237</t>
+          <t>4.8133345928460125</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6.57717985616226</t>
+          <t>6.45440169118831</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.968523301089293</t>
+          <t>4.870302217677346</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6.355062281904547</t>
+          <t>6.234510715488257</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9.355122472610143</t>
+          <t>9.20438392274689</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6.5992925583707605</t>
+          <t>6.476896522128111</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.397094906312757</t>
+          <t>4.3113740502784035</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7.669586259356665</t>
+          <t>7.525992172301534</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9.92044967400905</t>
+          <t>9.771393059083344</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6.026563663586785</t>
+          <t>5.91139396382413</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.753905645982132</t>
+          <t>0.7485449787084626</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.269471607094363</t>
+          <t>16.189428931646336</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.9858547099223385</t>
+          <t>6.954525591849043</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.804717903291177</t>
+          <t>1.8116604345981528</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>45.50184407565176</t>
+          <t>44.93481436055274</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.81828642756114</t>
+          <t>11.47684053795683</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.9100845093697405</t>
+          <t>5.826907229333289</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.9877043050018584</t>
+          <t>2.972232495563658</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.5565331341442086</t>
+          <t>0.5502964154305472</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.7407444536423022</t>
+          <t>2.729064924702873</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.3650579270037793</t>
+          <t>1.3446854465295726</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.8598033129489835</t>
+          <t>4.860082247823231</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.79821748479986</t>
+          <t>3.7587778007763393</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>23.630917957421435</t>
+          <t>23.33923071186017</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5.711596164256358</t>
+          <t>5.655007959774631</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.417061143025974</t>
+          <t>11.49448154929891</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7.1552792611967835</t>
+          <t>7.105908258883158</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.631293383284095</t>
+          <t>23.674390117887413</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.071969426496703</t>
+          <t>4.03991196896193</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.912378714646996</t>
+          <t>5.822974190511893</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20.08691857130095</t>
+          <t>19.5744061738142</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.8257714720572105</t>
+          <t>0.8297186322460114</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.4502461185473621</t>
+          <t>0.4452059404717892</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.298784538857351</t>
+          <t>2.27420084974154</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5.339078597391985</t>
+          <t>5.315117737543922</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9.486994448271009</t>
+          <t>9.473667376351171</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2.0874322498671614</t>
+          <t>2.0502035198193393</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.35143697067845836</t>
+          <t>0.345300487688598</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4.790981394979021</t>
+          <t>4.726287976625767</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.2884627141241816</t>
+          <t>0.2861172961882032</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.0054028500134784</t>
+          <t>2.993469211223491</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.9276398685421796</t>
+          <t>1.9355903066315108</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.9660991900054692</t>
+          <t>1.937904177582702</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.6128922698571033</t>
+          <t>2.584427918710461</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>5.059077787538641</t>
+          <t>5.001910768553161</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.826068532630722</t>
+          <t>3.7912376633562515</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.6286644124238894</t>
+          <t>2.60076177416207</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.510275722540145</t>
+          <t>2.512571071896411</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>23.86244656182332</t>
+          <t>23.40215859622587</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>8.94399088404601</t>
+          <t>8.875263342571031</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.63173100774457</t>
+          <t>4.629079015870879</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8.384981754886027</t>
+          <t>8.401750331573837</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.64061483903884</t>
+          <t>18.687836447916368</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>15.25138102825298</t>
+          <t>15.09840377904399</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>18.19672581038954</t>
+          <t>17.81705688132557</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.283125606903752</t>
+          <t>3.274505665469978</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>5.193180841859121</t>
+          <t>5.194341109658438</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.2743186445761996</t>
+          <t>1.252882451079084</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.583669908283161</t>
+          <t>2.5533710542034256</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.651733230418671</t>
+          <t>2.634842472814249</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.602020203315531</t>
+          <t>2.5804038322734453</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.6204122555178557</t>
+          <t>2.5498487112729054</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.36262190704136593</t>
+          <t>0.35973079377358275</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.48352192711084996</t>
+          <t>0.4784972263833698</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1.3230326825127108</t>
+          <t>1.2965441172606909</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.66873079264374</t>
+          <t>1.6568620024546488</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.38667733889350475</t>
+          <t>0.38565346767612746</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.877401556860063</t>
+          <t>1.8542145568509831</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>13.173926517659467</t>
+          <t>12.977846611425573</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>83.09199914474924</t>
+          <t>82.78328082248092</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>18.15947202935728</t>
+          <t>17.8914036046166</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>17.187966782562814</t>
+          <t>16.8317024853996</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>96.38616442074554</t>
+          <t>96.38549527601138</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>6.979747957767756</t>
+          <t>7.090377680695642</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1.1531937807623027</t>
+          <t>1.1298056223015265</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1.3048444786316062</t>
+          <t>1.2896454643181932</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>3.926726092123735</t>
+          <t>3.8825413834626623</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>65.84530612035675</t>
+          <t>65.70461057107299</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.7263351157359756</t>
+          <t>3.7342026943604396</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>25.00964528925075</t>
+          <t>24.64613846215316</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>27.21787373326672</t>
+          <t>26.86792556758759</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.9008205750454873</t>
+          <t>0.882333082871352</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.7577029201400762</t>
+          <t>3.7482060645283974</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.456641205378878</t>
+          <t>3.366124801917439</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>17.30318163805743</t>
+          <t>17.04487788960992</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.669964672201859</t>
+          <t>6.73842594960097</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>3.9727299715044637</t>
+          <t>3.966067909749329</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.636408122535457</t>
+          <t>4.668082846678345</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>74.01382146835664</t>
+          <t>73.4790718485486</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9.677959522644361</t>
+          <t>9.492157791420743</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.9238703078472845</t>
+          <t>4.949394820364144</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>8.317917471616916</t>
+          <t>8.196928410207905</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>12.281308894669378</t>
+          <t>12.39986253758984</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>89.09951175731113</t>
+          <t>89.04707695455203</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.044337653161385</t>
+          <t>12.191133730087282</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10.982358156522997</t>
+          <t>10.99799656050481</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>0.5109809967237311</t>
+          <t>0.5133450653043496</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.250940574628417</t>
+          <t>6.287161120483546</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>3.06328904244965</t>
+          <t>3.0582580832169697</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>60.2144709978781</t>
+          <t>59.45166945317083</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6368515588654162</t>
+          <t>0.6258755715442348</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.7121555167907313</t>
+          <t>0.7050314920320766</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>15.290659597151109</t>
+          <t>15.06587031895554</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>7.385868241461789</t>
+          <t>7.352836603880098</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>8.293823529705822</t>
+          <t>8.268784975598743</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>17.62908753506821</t>
+          <t>17.17803981589618</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,227 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>56.69042646380463</t>
+          <t>34.44131816344349</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>DF_STR_Boujack</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>4.507983801118237</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>BU_AGL_Mechikabura</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>6.129905606148073</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>BU_TEQ_God_Trunks</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>5.494292142452406</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>BU_INT_Xeno_Pan</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>11.819941506406067</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>BU_STR_SS_Vegeks</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2.2009089356743803</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>BU_AGL_SS3_Gotenks_Xeno</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>BU_INT_SS3_Gohanks_Xeno</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>BU_PHY_SS_Goku_Xeno</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2.6657302465116683</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>BU_INT_SS_Vegeta_Xeno</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2.3964831476222637</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>F2P_STR_Towa</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D293"/>
+  <dimension ref="A1:D299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.710169438402861</t>
+          <t>6.707675774887321</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.250487351827658</t>
+          <t>6.243738263394036</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.364890661968587</t>
+          <t>24.31517547224307</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.2213703826145963</t>
+          <t>0.21850259991979826</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.959425631007489</t>
+          <t>4.92642951229023</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.4021133128372654</t>
+          <t>2.381656876145414</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.843913639745715</t>
+          <t>5.813518128004508</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.7614090834136757</t>
+          <t>1.7472056125228237</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.8872073070984</t>
+          <t>6.8662574325352</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.225033444835019</t>
+          <t>6.213518047478541</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.253845214134712</t>
+          <t>2.2405276584784124</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.7344258471216</t>
+          <t>13.7095512354569</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.9689374513612639</t>
+          <t>0.9541176821583139</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.120126037962489</t>
+          <t>3.1135223387951214</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.765363399967907</t>
+          <t>10.766547077277227</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.5710486002182193</t>
+          <t>2.5692859012003098</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.283460943324119</t>
+          <t>15.204291598545918</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.352876062103215</t>
+          <t>7.301074330663739</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.4688883801955654</t>
+          <t>7.43514922008295</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.00271774770994</t>
+          <t>11.91447474883704</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.52704496569263</t>
+          <t>6.503737333979715</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.314138018986597</t>
+          <t>1.2997812876072392</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.15545637581129</t>
+          <t>8.149697368169988</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.24588141585562</t>
+          <t>2.225446573192631</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.150460467611904</t>
+          <t>5.12350879459084</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.223409447156719</t>
+          <t>4.209403276860943</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.2376287625546105</t>
+          <t>6.185113589113001</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.781018049662322</t>
+          <t>12.792071619538532</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.711481566199058</t>
+          <t>13.723843202102689</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.663834592330971</t>
+          <t>4.662343997949193</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.2479743816735374</t>
+          <t>2.2350226841000786</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.0253786638897608</t>
+          <t>1.0247162102138212</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.431115187485972</t>
+          <t>6.434948493678299</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15.93837487416927</t>
+          <t>15.84664953729777</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.7128098714883633</t>
+          <t>2.6885360742208735</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.0500181537835722</t>
+          <t>1.0462380105651512</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6.047192555699015</t>
+          <t>6.056592439143602</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5.00977531487583</t>
+          <t>4.995672126322402</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.588288811631164</t>
+          <t>5.537186752189132</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.426402547564521</t>
+          <t>13.42477676490958</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.4338752120326967</t>
+          <t>2.4486966241524004</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.030318566447562</t>
+          <t>2.0254274049366927</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.87603758738382</t>
+          <t>3.8781392499533354</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.858091585375135</t>
+          <t>20.868636304355427</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13.327991076973618</t>
+          <t>13.332848096645309</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.3018366626358784</t>
+          <t>2.296717897226472</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.8133345928460125</t>
+          <t>4.772633262184832</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6.45440169118831</t>
+          <t>6.403980562082072</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.870302217677346</t>
+          <t>4.831813714141345</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6.234510715488257</t>
+          <t>6.188113194511192</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9.20438392274689</t>
+          <t>9.187680870315747</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6.476896522128111</t>
+          <t>6.431788471359994</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.3113740502784035</t>
+          <t>4.271609976161072</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7.525992172301534</t>
+          <t>7.475234213931008</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9.771393059083344</t>
+          <t>9.755721414667038</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.91139396382413</t>
+          <t>5.86022881334741</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.7485449787084626</t>
+          <t>0.744388280024873</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.189428931646336</t>
+          <t>16.1307037626479</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.954525591849043</t>
+          <t>6.928763087866292</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.8116604345981528</t>
+          <t>1.8040314183456874</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>44.93481436055274</t>
+          <t>45.08316116131187</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.47684053795683</t>
+          <t>11.43851076769352</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.826907229333289</t>
+          <t>5.815893197350017</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.972232495563658</t>
+          <t>2.972893001837227</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.5502964154305472</t>
+          <t>0.5477025185509667</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.729064924702873</t>
+          <t>2.717742887862514</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.3446854465295726</t>
+          <t>1.3322833230772413</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.860082247823231</t>
+          <t>4.8676308851559345</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.7587778007763393</t>
+          <t>3.7519370021377303</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>23.33923071186017</t>
+          <t>23.24577448886881</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5.655007959774631</t>
+          <t>5.64276875095298</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.49448154929891</t>
+          <t>11.488943310483814</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7.105908258883158</t>
+          <t>7.0753632470510555</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.674390117887413</t>
+          <t>23.71711089670277</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.03991196896193</t>
+          <t>4.0050877012048325</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.822974190511893</t>
+          <t>5.749980077012244</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.5744061738142</t>
+          <t>19.57757673656546</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.8297186322460114</t>
+          <t>0.836366757058812</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.4452059404717892</t>
+          <t>0.4409984875287865</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.27420084974154</t>
+          <t>2.2731071960834868</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5.315117737543922</t>
+          <t>5.295295947947905</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9.473667376351171</t>
+          <t>9.470444551482325</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2.0502035198193393</t>
+          <t>2.0325979962244496</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.345300487688598</t>
+          <t>0.34069277806359893</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4.726287976625767</t>
+          <t>4.700627082700172</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.2861172961882032</t>
+          <t>0.28407430223842817</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2.993469211223491</t>
+          <t>2.98672443446436</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.9355903066315108</t>
+          <t>1.9393909303562253</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.937904177582702</t>
+          <t>1.9327660641987416</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.584427918710461</t>
+          <t>2.5615793111577805</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>5.001910768553161</t>
+          <t>4.960912121093161</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.7912376633562515</t>
+          <t>3.7618902919151602</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.60076177416207</t>
+          <t>2.5895600352312798</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.512571071896411</t>
+          <t>2.5097067898970438</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>23.40215859622587</t>
+          <t>23.28681199678681</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>8.875263342571031</t>
+          <t>8.823483231294741</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.629079015870879</t>
+          <t>4.638126093373359</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8.401750331573837</t>
+          <t>8.386834094356033</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.687836447916368</t>
+          <t>18.71799556536353</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>15.09840377904399</t>
+          <t>15.02774965655256</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>17.81705688132557</t>
+          <t>17.69178744258118</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.274505665469978</t>
+          <t>3.2744806728383122</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>5.194341109658438</t>
+          <t>5.188778875099732</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.252882451079084</t>
+          <t>1.2429490474418792</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.5533710542034256</t>
+          <t>2.5319828308794734</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.634842472814249</t>
+          <t>2.625927569342643</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.5804038322734453</t>
+          <t>2.5564213456670277</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.5498487112729054</t>
+          <t>2.5459452811582945</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.35973079377358275</t>
+          <t>0.35863606543679083</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.4784972263833698</t>
+          <t>0.4734540822987796</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1.2965441172606909</t>
+          <t>1.28581538178614</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.6568620024546488</t>
+          <t>1.6420867061377453</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.38565346767612746</t>
+          <t>0.38441723201655564</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.8542145568509831</t>
+          <t>1.8458507599267309</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>12.977846611425573</t>
+          <t>12.950141710800711</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>82.78328082248092</t>
+          <t>82.61768252588116</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>17.8914036046166</t>
+          <t>17.67602404717408</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>16.8317024853996</t>
+          <t>16.682271089044686</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>96.38549527601138</t>
+          <t>96.41509158260794</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>7.090377680695642</t>
+          <t>7.110067050571152</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1.1298056223015265</t>
+          <t>1.1203557153353814</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1.2896454643181932</t>
+          <t>1.2879495883534458</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>3.8825413834626623</t>
+          <t>3.8689640930355047</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>65.70461057107299</t>
+          <t>65.56698552277162</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.7342026943604396</t>
+          <t>3.7384963628089976</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>24.64613846215316</t>
+          <t>24.50692462395185</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>26.86792556758759</t>
+          <t>26.79647868695914</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.882333082871352</t>
+          <t>0.876037791101456</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.7482060645283974</t>
+          <t>3.7548719667840635</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.366124801917439</t>
+          <t>3.3217545560574115</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>17.04487788960992</t>
+          <t>16.88883194970754</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.73842594960097</t>
+          <t>6.743171717552206</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>3.966067909749329</t>
+          <t>3.969147364665791</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.668082846678345</t>
+          <t>4.670532874420161</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>73.4790718485486</t>
+          <t>73.47135456160727</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9.492157791420743</t>
+          <t>9.421724935537114</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.949394820364144</t>
+          <t>4.952810971780004</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>8.196928410207905</t>
+          <t>8.124915917311508</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>12.39986253758984</t>
+          <t>12.358976809319188</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>89.04707695455203</t>
+          <t>89.03310693429542</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.191133730087282</t>
+          <t>12.214024604043436</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10.99799656050481</t>
+          <t>10.999797356806399</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>0.5133450653043496</t>
+          <t>0.5093289791528223</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.287161120483546</t>
+          <t>6.299612144345972</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>3.0582580832169697</t>
+          <t>3.0466592245801287</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>59.45166945317083</t>
+          <t>59.36058623404001</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6258755715442348</t>
+          <t>0.6188337596281512</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.7050314920320766</t>
+          <t>0.6990886778077713</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>15.06587031895554</t>
+          <t>15.01807863755248</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>7.352836603880098</t>
+          <t>7.3409445002020925</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>8.268784975598743</t>
+          <t>8.250753526006372</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>17.17803981589618</t>
+          <t>17.03091790885008</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>34.44131816344349</t>
+          <t>34.47974622739623</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>4.507983801118237</t>
+          <t>4.537820894366587</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>6.129905606148073</t>
+          <t>6.102319113977811</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>5.494292142452406</t>
+          <t>6.6433100358647375</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>11.819941506406067</t>
+          <t>11.828991639019325</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2.2009089356743803</t>
+          <t>2.1921411162518822</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2.6657302465116683</t>
+          <t>2.657374150252235</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2.3964831476222637</t>
+          <t>2.3877698963307927</t>
         </is>
       </c>
     </row>
@@ -6869,6 +6869,138 @@
         </is>
       </c>
       <c r="D293" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>BU_PHY_Warrior_In_Black</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>6.034390480590761</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>BU_TEQ_Dark_King_Demigra</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>7.617510628062733</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>BU_INT_Aeos</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>10.69104355352848</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>BU_AGL_Fu_Dogidogi</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>20.14790224913269</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>BU_STR_SSGSS_Goku_Universe_Tree</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>29.851070415772785</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>DF_TEQ_Beerus</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -6887,12 +6887,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>6.034390480590761</t>
+          <t>1.88544557395457</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>7.617510628062733</t>
+          <t>3.6628969779364304</t>
         </is>
       </c>
     </row>
@@ -6931,12 +6931,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>10.69104355352848</t>
+          <t>6.545089824377829</t>
         </is>
       </c>
     </row>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>29.851070415772785</t>
+          <t>11.947750172070457</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.707675774887321</t>
+          <t>6.51706329965489</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.243738263394036</t>
+          <t>6.28766678749426</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.31517547224307</t>
+          <t>23.70762890337214</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.21850259991979826</t>
+          <t>0.21363957749889906</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.92642951229023</t>
+          <t>4.794609998325191</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.381656876145414</t>
+          <t>2.3357960521611734</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.813518128004508</t>
+          <t>5.653504767082904</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.7472056125228237</t>
+          <t>1.6984874658958375</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.8662574325352</t>
+          <t>6.7172448571724</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.213518047478541</t>
+          <t>2.3921632652842106</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.2405276584784124</t>
+          <t>2.930640013658255</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.7095512354569</t>
+          <t>13.41503943510381</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.9541176821583139</t>
+          <t>0.9397568614945941</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.1135223387951214</t>
+          <t>3.037366043070559</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.766547077277227</t>
+          <t>10.461474834130879</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.5692859012003098</t>
+          <t>2.498118197846111</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.204291598545918</t>
+          <t>14.863851150417442</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.301074330663739</t>
+          <t>7.552918898089299</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.43514922008295</t>
+          <t>7.220942838049563</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11.91447474883704</t>
+          <t>11.67007172453612</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.503737333979715</t>
+          <t>6.322407350906433</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.2997812876072392</t>
+          <t>1.276001553127939</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.149697368169988</t>
+          <t>7.955765476311171</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.225446573192631</t>
+          <t>2.1709238598237146</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.12350879459084</t>
+          <t>4.9821299536356225</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.209403276860943</t>
+          <t>4.088757296296276</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.185113589113001</t>
+          <t>6.041903030870259</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.792071619538532</t>
+          <t>12.67755582017579</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.723843202102689</t>
+          <t>13.401778635386933</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.662343997949193</t>
+          <t>4.629480649513901</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.2350226841000786</t>
+          <t>2.1684967225653455</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.0247162102138212</t>
+          <t>0.9963272378082023</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.434948493678299</t>
+          <t>6.4972914851446495</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15.84664953729777</t>
+          <t>16.24607532326751</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.6885360742208735</t>
+          <t>2.6184158485094535</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.0462380105651512</t>
+          <t>1.0181464671694194</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6.056592439143602</t>
+          <t>6.052206789538796</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.995672126322402</t>
+          <t>4.848500403667931</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.537186752189132</t>
+          <t>5.424295860167784</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.42477676490958</t>
+          <t>13.261112553732495</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.4486966241524004</t>
+          <t>2.541214191609425</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.0254274049366927</t>
+          <t>1.9996756045809292</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.8781392499533354</t>
+          <t>3.921839864604948</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.868636304355427</t>
+          <t>20.602498954106835</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13.332848096645309</t>
+          <t>13.574023044152993</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.296717897226472</t>
+          <t>2.435789147728741</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.772633262184832</t>
+          <t>4.7112079065280845</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6.403980562082072</t>
+          <t>6.309161170714883</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.831813714141345</t>
+          <t>4.768820502879404</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6.188113194511192</t>
+          <t>6.098003992272922</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9.187680870315747</t>
+          <t>8.983059909852196</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6.431788471359994</t>
+          <t>6.3366643385963854</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.271609976161072</t>
+          <t>4.220055780730234</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7.475234213931008</t>
+          <t>7.35749424360559</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9.755721414667038</t>
+          <t>9.537789392090104</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.86022881334741</t>
+          <t>5.776148907921769</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.744388280024873</t>
+          <t>0.7212348531668837</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.1307037626479</t>
+          <t>15.78436164586176</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.928763087866292</t>
+          <t>6.777571412043232</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.8040314183456874</t>
+          <t>1.775675745243106</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>45.08316116131187</t>
+          <t>17.19398839654491</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.43851076769352</t>
+          <t>11.2297464538747</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.815893197350017</t>
+          <t>5.656938601131561</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.972893001837227</t>
+          <t>2.90381274255149</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.5477025185509667</t>
+          <t>0.5315936115486375</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.717742887862514</t>
+          <t>2.647227552122082</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.3322833230772413</t>
+          <t>1.3042130992903336</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.8676308851559345</t>
+          <t>4.868172252781685</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.7519370021377303</t>
+          <t>3.668803883988449</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>23.24577448886881</t>
+          <t>22.766446252680424</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5.64276875095298</t>
+          <t>2.293002647868118</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.488943310483814</t>
+          <t>11.56670822869274</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>7.0753632470510555</t>
+          <t>6.865261146634921</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.71711089670277</t>
+          <t>23.365229762253982</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.0050877012048325</t>
+          <t>3.887767790711851</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.749980077012244</t>
+          <t>5.654592704074722</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.57757673656546</t>
+          <t>19.12922811549033</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.836366757058812</t>
+          <t>0.8806698351257986</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.4409984875287865</t>
+          <t>0.4305130715661975</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.2731071960834868</t>
+          <t>2.2183696922492615</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5.295295947947905</t>
+          <t>5.1728201961720774</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9.470444551482325</t>
+          <t>9.265361177972116</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2.0325979962244496</t>
+          <t>2.067695922969099</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.34069277806359893</t>
+          <t>0.33363380948670873</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4.700627082700172</t>
+          <t>4.594765524117737</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.28407430223842817</t>
+          <t>0.2758166530710702</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2.98672443446436</t>
+          <t>2.9189944010495377</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.9393909303562253</t>
+          <t>1.917880275836879</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.9327660641987416</t>
+          <t>1.8708329312606846</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.5615793111577805</t>
+          <t>2.5028947622756808</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>4.960912121093161</t>
+          <t>4.84121998714282</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.7618902919151602</t>
+          <t>3.6564895589234547</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.5895600352312798</t>
+          <t>2.5279141989346297</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.5097067898970438</t>
+          <t>2.464992654380913</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>23.28681199678681</t>
+          <t>22.82220220730381</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>8.823483231294741</t>
+          <t>8.870214147336885</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.638126093373359</t>
+          <t>4.582419847242676</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8.386834094356033</t>
+          <t>8.229727339435243</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.71799556536353</t>
+          <t>18.79375684635334</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>15.02774965655256</t>
+          <t>15.51320437807864</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>17.69178744258118</t>
+          <t>17.30670703151151</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.2744806728383122</t>
+          <t>3.258666897440398</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>5.188778875099732</t>
+          <t>5.088140347745661</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.2429490474418792</t>
+          <t>1.2828500663958815</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.5319828308794734</t>
+          <t>2.4764857132105846</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.625927569342643</t>
+          <t>2.5905168967825034</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.5564213456670277</t>
+          <t>2.4919502724571387</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.5459452811582945</t>
+          <t>2.4914453785283426</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.35863606543679083</t>
+          <t>0.34733499599448175</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.4734540822987796</t>
+          <t>0.46294609679999077</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1.28581538178614</t>
+          <t>1.2560805091100509</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.6420867061377453</t>
+          <t>1.601424508003974</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.38441723201655564</t>
+          <t>0.3756508064883011</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.8458507599267309</t>
+          <t>1.8858277945408104</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>12.950141710800711</t>
+          <t>12.652499594310855</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>82.61768252588116</t>
+          <t>81.82907539039323</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>17.67602404717408</t>
+          <t>17.30575053537497</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>16.682271089044686</t>
+          <t>16.324747416620742</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>96.41509158260794</t>
+          <t>96.04791537391952</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5325,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>7.110067050571152</t>
+          <t>4.181328972677574</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1.1203557153353814</t>
+          <t>1.096975890722898</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1.2879495883534458</t>
+          <t>1.2544604910470396</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>3.8689640930355047</t>
+          <t>3.7567004818813796</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>65.56698552277162</t>
+          <t>64.441909445714</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.7384963628089976</t>
+          <t>3.7846072445502035</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>24.50692462395185</t>
+          <t>23.92549043802777</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>26.79647868695914</t>
+          <t>26.14757802172822</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.876037791101456</t>
+          <t>0.8572533223755286</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.7548719667840635</t>
+          <t>3.6944038822282375</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.3217545560574115</t>
+          <t>3.283025477770322</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>16.88883194970754</t>
+          <t>16.55438087679658</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.743171717552206</t>
+          <t>6.785341319473773</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>3.969147364665791</t>
+          <t>3.9177353024566868</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.670532874420161</t>
+          <t>4.896603590429848</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>73.47135456160727</t>
+          <t>72.38603525352714</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9.421724935537114</t>
+          <t>9.216705366218543</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.952810971780004</t>
+          <t>4.960249201644641</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>8.124915917311508</t>
+          <t>7.9737355999244315</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>12.358976809319188</t>
+          <t>12.6737468869582</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>89.03310693429542</t>
+          <t>89.1304184867396</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.214024604043436</t>
+          <t>12.283506669243524</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10.999797356806399</t>
+          <t>10.942281116472145</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>0.5093289791528223</t>
+          <t>0.5435371767622306</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.299612144345972</t>
+          <t>6.451274243685461</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>3.0466592245801287</t>
+          <t>2.983088468477799</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>59.36058623404001</t>
+          <t>58.33312407274794</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6188337596281512</t>
+          <t>0.6064766508535137</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.6990886778077713</t>
+          <t>0.683012742484954</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>15.01807863755248</t>
+          <t>14.627691832197913</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>7.3409445002020925</t>
+          <t>7.262979564286615</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>8.250753526006372</t>
+          <t>8.17488642090283</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>17.03091790885008</t>
+          <t>16.70703545855166</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>34.47974622739623</t>
+          <t>33.79527526545628</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>4.537820894366587</t>
+          <t>4.664643330185235</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>6.102319113977811</t>
+          <t>5.991087558084239</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>6.6433100358647375</t>
+          <t>6.60704548941731</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>11.828991639019325</t>
+          <t>11.647848952565862</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2.1921411162518822</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2.657374150252235</t>
+          <t>2.5971410275988385</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2.3877698963307927</t>
+          <t>2.3331109826337</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1.88544557395457</t>
+          <t>1.8334061096422012</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>3.6628969779364304</t>
+          <t>3.5771219432811314</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>6.545089824377829</t>
+          <t>6.38784866969956</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20.14790224913269</t>
+          <t>19.72661687443596</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>11.947750172070457</t>
+          <t>11.956376916138339</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:D311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.51706329965489</t>
+          <t>6.477129110508621</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.28766678749426</t>
+          <t>6.289449049162556</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.70762890337214</t>
+          <t>23.763581597770745</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.21363957749889906</t>
+          <t>0.21330400969099905</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.794609998325191</t>
+          <t>4.766547617847699</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.3357960521611734</t>
+          <t>2.6815750627136277</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.653504767082904</t>
+          <t>5.638912377060916</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.6984874658958375</t>
+          <t>1.6893119495978244</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.7172448571724</t>
+          <t>6.671880415231552</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.3921632652842106</t>
+          <t>2.388183735129232</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.930640013658255</t>
+          <t>2.916762797498585</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.41503943510381</t>
+          <t>13.46254633802256</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.9397568614945941</t>
+          <t>0.21974488940947</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.037366043070559</t>
+          <t>3.0349638139476482</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.461474834130879</t>
+          <t>10.41473185251072</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.498118197846111</t>
+          <t>2.5042724739760693</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14.863851150417442</t>
+          <t>14.854748637093433</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.552918898089299</t>
+          <t>7.530228068431555</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.220942838049563</t>
+          <t>7.18670875953034</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11.67007172453612</t>
+          <t>11.70856344955158</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.322407350906433</t>
+          <t>6.280059275937025</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.276001553127939</t>
+          <t>1.2741675378803055</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.955765476311171</t>
+          <t>7.9163863691185306</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.1709238598237146</t>
+          <t>2.155838585250404</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.9821299536356225</t>
+          <t>4.965907564957238</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.088757296296276</t>
+          <t>0.6410066078449503</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.041903030870259</t>
+          <t>6.009714524395129</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.67755582017579</t>
+          <t>12.67844220103072</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.401778635386933</t>
+          <t>13.340986131569618</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.629480649513901</t>
+          <t>4.6329335613371825</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.1684967225653455</t>
+          <t>2.1584015169155624</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.9963272378082023</t>
+          <t>0.9924510677500002</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.4972914851446495</t>
+          <t>6.379223312931984</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>16.24607532326751</t>
+          <t>16.20935780951293</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.6184158485094535</t>
+          <t>2.6048612785561236</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.0181464671694194</t>
+          <t>1.0189245946799588</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6.052206789538796</t>
+          <t>6.0482867754115155</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.848500403667931</t>
+          <t>4.816915329063578</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.424295860167784</t>
+          <t>5.414969820684189</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.261112553732495</t>
+          <t>13.212845098303298</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.541214191609425</t>
+          <t>2.5285768755140094</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.9996756045809292</t>
+          <t>2.002882999161841</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.921839864604948</t>
+          <t>3.9344012490219598</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.602498954106835</t>
+          <t>20.5840276798885</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13.574023044152993</t>
+          <t>13.53497056772369</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.435789147728741</t>
+          <t>2.433225742819886</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.7112079065280845</t>
+          <t>4.718005798743534</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6.309161170714883</t>
+          <t>6.305348256600577</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.768820502879404</t>
+          <t>4.776795337364632</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6.098003992272922</t>
+          <t>6.104160084298101</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8.983059909852196</t>
+          <t>8.958896175865956</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6.3366643385963854</t>
+          <t>6.33700466880849</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.220055780730234</t>
+          <t>4.227390525553644</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7.35749424360559</t>
+          <t>7.101296726025452</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9.537789392090104</t>
+          <t>9.506687575681191</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.776148907921769</t>
+          <t>5.7870064842026085</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.7212348531668837</t>
+          <t>0.7536128865165418</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>15.78436164586176</t>
+          <t>15.765287402748642</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.777571412043232</t>
+          <t>6.747141625146917</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.775675745243106</t>
+          <t>1.7783694372294292</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>17.19398839654491</t>
+          <t>17.167535198296065</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.2297464538747</t>
+          <t>10.93581200527113</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.656938601131561</t>
+          <t>5.62535525435272</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.90381274255149</t>
+          <t>2.8882526930313333</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.5315936115486375</t>
+          <t>0.5306132651791522</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.647227552122082</t>
+          <t>2.6323022279430766</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.3042130992903336</t>
+          <t>1.3001748605020498</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.868172252781685</t>
+          <t>4.876081205316631</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.668803883988449</t>
+          <t>3.6613489203632987</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22.766446252680424</t>
+          <t>22.772242137113032</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2.293002647868118</t>
+          <t>2.2903111655382595</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.56670822869274</t>
+          <t>11.585660570212895</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6.865261146634921</t>
+          <t>6.846534642304445</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.365229762253982</t>
+          <t>23.25311600765082</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.887767790711851</t>
+          <t>3.8709809155046555</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.654592704074722</t>
+          <t>5.624675867869639</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.12922811549033</t>
+          <t>19.10782885658841</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.8806698351257986</t>
+          <t>0.8875407996636397</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.4305130715661975</t>
+          <t>0.427507637303793</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.2183696922492615</t>
+          <t>2.211063460809978</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5.1728201961720774</t>
+          <t>5.140017795037406</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9.265361177972116</t>
+          <t>9.24000414621572</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2.067695922969099</t>
+          <t>2.0617373959315</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.33363380948670873</t>
+          <t>0.3330645846953202</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4.594765524117737</t>
+          <t>4.56144892440435</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.2758166530710702</t>
+          <t>0.2750575674421507</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2.9189944010495377</t>
+          <t>2.9056944575809602</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.917880275836879</t>
+          <t>1.9113676864071036</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.8708329312606846</t>
+          <t>1.8542837956794038</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.5028947622756808</t>
+          <t>2.490671370955553</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>4.84121998714282</t>
+          <t>4.8244612953724495</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.6564895589234547</t>
+          <t>3.656768882774747</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.5279141989346297</t>
+          <t>2.4876680466910006</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.464992654380913</t>
+          <t>2.4252689418851365</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>22.82220220730381</t>
+          <t>22.82905453656924</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>8.870214147336885</t>
+          <t>3.3780949404791443</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.582419847242676</t>
+          <t>4.565641842658579</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8.229727339435243</t>
+          <t>8.234697242259571</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.79375684635334</t>
+          <t>18.72669336248009</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>15.51320437807864</t>
+          <t>15.503168114156091</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>17.30670703151151</t>
+          <t>17.27543544034278</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.258666897440398</t>
+          <t>3.262683477361705</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>5.088140347745661</t>
+          <t>5.073473116789241</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.2828500663958815</t>
+          <t>1.2785593903810701</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.4764857132105846</t>
+          <t>2.4506563428114823</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.5905168967825034</t>
+          <t>2.5943518193253325</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.4919502724571387</t>
+          <t>2.473136976529368</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.4914453785283426</t>
+          <t>2.473549348619626</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.34733499599448175</t>
+          <t>0.34500823217081233</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.46294609679999077</t>
+          <t>0.45925995502483014</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1.2560805091100509</t>
+          <t>1.2503633707203008</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.601424508003974</t>
+          <t>1.584256871019242</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.3756508064883011</t>
+          <t>0.3727693358974012</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.8858277945408104</t>
+          <t>1.874993754310238</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>12.652499594310855</t>
+          <t>12.622033258237492</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>81.82907539039323</t>
+          <t>81.92060290561311</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>17.30575053537497</t>
+          <t>17.20336160694842</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>16.324747416620742</t>
+          <t>16.364820933312185</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>96.04791537391952</t>
+          <t>96.02606207978904</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>4.181328972677574</t>
+          <t>4.228770083888926</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1.096975890722898</t>
+          <t>1.0896170030401615</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1.2544604910470396</t>
+          <t>1.2474397317633417</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>3.7567004818813796</t>
+          <t>3.739777758956647</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>64.441909445714</t>
+          <t>64.27971971536492</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.7846072445502035</t>
+          <t>3.8077094286692312</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>23.92549043802777</t>
+          <t>23.83946054572517</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>26.14757802172822</t>
+          <t>26.20843959127437</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.8572533223755286</t>
+          <t>0.8502648859373844</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.6944038822282375</t>
+          <t>3.676377183216187</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.283025477770322</t>
+          <t>3.291664472390658</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>16.55438087679658</t>
+          <t>16.51881922998306</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.785341319473773</t>
+          <t>6.775546204317055</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>3.9177353024566868</t>
+          <t>3.909224822048074</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.896603590429848</t>
+          <t>4.9361176810371745</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>72.38603525352714</t>
+          <t>72.2318114593817</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9.216705366218543</t>
+          <t>9.227411501459864</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.960249201644641</t>
+          <t>4.972541646119022</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>7.9737355999244315</t>
+          <t>7.969054970894657</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>12.6737468869582</t>
+          <t>12.68238797466208</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>89.1304184867396</t>
+          <t>89.15486684697831</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.283506669243524</t>
+          <t>12.002892439446258</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10.942281116472145</t>
+          <t>10.94424765107618</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>0.5435371767622306</t>
+          <t>0.5493087963761077</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.451274243685461</t>
+          <t>6.478559910386551</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2.983088468477799</t>
+          <t>2.9630001356942692</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>58.33312407274794</t>
+          <t>58.32074996464482</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6064766508535137</t>
+          <t>0.600484797465835</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.683012742484954</t>
+          <t>0.678569385632056</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>14.627691832197913</t>
+          <t>14.688734877978668</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>7.262979564286615</t>
+          <t>7.279738320004261</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>8.17488642090283</t>
+          <t>8.203453468365016</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>16.70703545855166</t>
+          <t>16.64158355127985</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>33.79527526545628</t>
+          <t>48.08977432571688</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>4.664643330185235</t>
+          <t>4.6631025839726545</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>5.991087558084239</t>
+          <t>6.0175384415966935</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>6.60704548941731</t>
+          <t>6.590224121763268</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>11.647848952565862</t>
+          <t>11.620350069508364</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2.5971410275988385</t>
+          <t>2.5969947555842054</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2.3331109826337</t>
+          <t>2.3306637268292065</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1.8334061096422012</t>
+          <t>1.8281163715287985</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>3.5771219432811314</t>
+          <t>3.550461650529691</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>6.38784866969956</t>
+          <t>6.354866261362462</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>19.72661687443596</t>
+          <t>19.72672956433617</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>11.956376916138339</t>
+          <t>11.96025417574598</t>
         </is>
       </c>
     </row>
@@ -7001,6 +7001,270 @@
         </is>
       </c>
       <c r="D299" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Frieza_Cooler</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Hit</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Saonel_Pirina</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>F2P_STR_Champa</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>BU_INT_Piccolo_ToP</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>BU_TEQ_ToP_Android_17</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>BU_TEQ_ToP_Android_18</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>BU_AGL_Skinny_Buu</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>DF_TEQ_Buuhan</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>83.3211023567777</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>BU_STR_Grand_Supreme_Kai</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>5.49884022082834</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>F2PLR_STR_Anilaza</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>3.734608390790508</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>DF_INT_Ultimate_Gohan</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D311"/>
+  <dimension ref="A1:D314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.477129110508621</t>
+          <t>4.95527422025744</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.289449049162556</t>
+          <t>6.324036319088684</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.763581597770745</t>
+          <t>18.18632988906396</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.21330400969099905</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.766547617847699</t>
+          <t>3.6036400594945857</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.6815750627136277</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.638912377060916</t>
+          <t>4.233136497189059</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.6893119495978244</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.671880415231552</t>
+          <t>5.130159958443368</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.388183735129232</t>
+          <t>1.7865767766864398</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.916762797498585</t>
+          <t>2.265199530282638</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.46254633802256</t>
+          <t>10.89058321107735</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.21974488940947</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.0349638139476482</t>
+          <t>2.260311763106859</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.41473185251072</t>
+          <t>7.957400543894079</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.5042724739760693</t>
+          <t>1.8878445270066209</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11.666666666666664</t>
+          <t>35.0</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14.854748637093433</t>
+          <t>10.978033171484261</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.530228068431555</t>
+          <t>6.261298019418218</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.18670875953034</t>
+          <t>5.406990404692509</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11.70856344955158</t>
+          <t>9.40959872489692</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.280059275937025</t>
+          <t>4.707175531855792</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.2741675378803055</t>
+          <t>1.0518165956879701</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.9163863691185306</t>
+          <t>6.04654250131396</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.155838585250404</t>
+          <t>1.6861910556608546</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.965907564957238</t>
+          <t>3.798920226010871</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.6410066078449503</t>
+          <t>0.47723438600805856</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.009714524395129</t>
+          <t>4.548858028402352</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.67844220103072</t>
+          <t>11.390252659865247</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.340986131569618</t>
+          <t>10.306529770145918</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.6329335613371825</t>
+          <t>3.9867847791539153</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.1584015169155624</t>
+          <t>1.7011803450268337</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.9924510677500002</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.379223312931984</t>
+          <t>6.374551931444415</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>16.20935780951293</t>
+          <t>13.06232239546589</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.6048612785561236</t>
+          <t>2.034003210795623</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.0189245946799588</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6.0482867754115155</t>
+          <t>5.519632295695495</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.816915329063578</t>
+          <t>3.673506488357239</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.414969820684189</t>
+          <t>4.637318639559511</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.212845098303298</t>
+          <t>11.05531975352115</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.5285768755140094</t>
+          <t>3.42472248725174</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.002882999161841</t>
+          <t>1.6347637917001663</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.9344012490219598</t>
+          <t>3.9434572909026997</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.5840276798885</t>
+          <t>20.137881630878063</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13.53497056772369</t>
+          <t>15.052389892576954</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.433225742819886</t>
+          <t>4.055364874961555</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.718005798743534</t>
+          <t>4.072589500628397</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6.305348256600577</t>
+          <t>5.329408916193561</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.776795337364632</t>
+          <t>4.120032740836277</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6.104160084298101</t>
+          <t>5.16731037449605</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8.958896175865956</t>
+          <t>6.808684003632609</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6.33700466880849</t>
+          <t>5.3610205861227</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4.227390525553644</t>
+          <t>3.6781535606168303</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7.101296726025452</t>
+          <t>5.944476348199434</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9.506687575681191</t>
+          <t>7.2306568657842405</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.7870064842026085</t>
+          <t>4.901933341064457</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.7536128865165418</t>
+          <t>0.5722165140008791</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>15.765287402748642</t>
+          <t>12.02864640427574</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.747141625146917</t>
+          <t>5.158505558935595</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.7783694372294292</t>
+          <t>3.1683784117296767</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>17.167535198296065</t>
+          <t>15.233788092356264</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10.93581200527113</t>
+          <t>8.580728997937063</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.62535525435272</t>
+          <t>4.270956070635581</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.8882526930313333</t>
+          <t>2.2221837844141885</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.5306132651791522</t>
+          <t>0.4100515882081943</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.6323022279430766</t>
+          <t>2.0166444510802797</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.3001748605020498</t>
+          <t>1.0662835686295122</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.876081205316631</t>
+          <t>4.440574840293863</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.6613489203632987</t>
+          <t>2.784507952986981</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22.772242137113032</t>
+          <t>20.827664799631737</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2.2903111655382595</t>
+          <t>1.7393888134926225</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.585660570212895</t>
+          <t>11.415443841782782</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6.846534642304445</t>
+          <t>5.103847903734153</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.25311600765082</t>
+          <t>19.18345490697965</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.8709809155046555</t>
+          <t>2.954158398482279</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.624675867869639</t>
+          <t>4.833364629950692</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.10782885658841</t>
+          <t>14.76617433367126</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.8875407996636397</t>
+          <t>1.5030639864433675</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>2.5</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.427507637303793</t>
+          <t>0.33532973378555475</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.211063460809978</t>
+          <t>1.6572595237880492</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5.140017795037406</t>
+          <t>3.9167255258306217</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9.24000414621572</t>
+          <t>7.248820384763904</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2.0617373959315</t>
+          <t>1.5221577410158993</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.3330645846953202</t>
+          <t>0.25963322624653656</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4.56144892440435</t>
+          <t>3.5046475953848404</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.2750575674421507</t>
+          <t>0.2101644020790765</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2.9056944575809602</t>
+          <t>2.2517872217263992</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.9113676864071036</t>
+          <t>1.6244689407318518</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.8542837956794038</t>
+          <t>1.408222391715574</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2.490671370955553</t>
+          <t>1.9581136101008074</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>4.8244612953724495</t>
+          <t>3.6005840204985504</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.656768882774747</t>
+          <t>2.7858038327897434</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2.4876680466910006</t>
+          <t>1.8959137209957255</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.4252689418851365</t>
+          <t>1.9865972966553875</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>22.82905453656924</t>
+          <t>17.80033048580944</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>3.3780949404791443</t>
+          <t>2.6236893477347927</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.565641842658579</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8.234697242259571</t>
+          <t>9.005221349181582</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.72669336248009</t>
+          <t>17.995158639120945</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>15.503168114156091</t>
+          <t>12.32982562476224</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>17.27543544034278</t>
+          <t>13.78700366900498</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.262683477361705</t>
+          <t>2.723652339534571</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>5.073473116789241</t>
+          <t>4.0180459618376325</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.2785593903810701</t>
+          <t>0.974415566375967</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.4506563428114823</t>
+          <t>1.9157127554707867</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.5943518193253325</t>
+          <t>2.0759233798007415</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2.473136976529368</t>
+          <t>1.8880759058332501</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2.473549348619626</t>
+          <t>1.9156531855539507</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.34500823217081233</t>
+          <t>0.26337880873536634</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.45925995502483014</t>
+          <t>0.3485784203335509</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1.2503633707203008</t>
+          <t>0.936181783569806</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.584256871019242</t>
+          <t>1.2315294673107209</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.3727693358974012</t>
+          <t>0.28576830795540026</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.874993754310238</t>
+          <t>1.4315391822619727</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>12.622033258237492</t>
+          <t>9.551460971752345</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>81.92060290561311</t>
+          <t>71.38000698152224</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>17.20336160694842</t>
+          <t>13.57897811698593</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>16.364820933312185</t>
+          <t>12.68793106417679</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>96.02606207978904</t>
+          <t>91.38364151981533</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>4.228770083888926</t>
+          <t>4.99646262822232</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1.0896170030401615</t>
+          <t>0.8423237686752945</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1.2474397317633417</t>
+          <t>0.9473784196049653</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>3.739777758956647</t>
+          <t>2.8687310171911875</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>64.27971971536492</t>
+          <t>52.78138870077601</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.8077094286692312</t>
+          <t>3.8764240645076007</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>23.83946054572517</t>
+          <t>18.45105439829826</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>26.20843959127437</t>
+          <t>20.34835572893854</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.8502648859373844</t>
+          <t>0.6522486296830411</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.676377183216187</t>
+          <t>2.959999169722594</t>
         </is>
       </c>
     </row>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.291664472390658</t>
+          <t>3.425805384115664</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>16.51881922998306</t>
+          <t>3.682575448279541</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.775546204317055</t>
+          <t>6.7549192230087245</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>3.909224822048074</t>
+          <t>3.223284522085541</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.9361176810371745</t>
+          <t>7.4411912518969245</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>72.2318114593817</t>
+          <t>60.10426668268437</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9.227411501459864</t>
+          <t>7.567468742791884</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.972541646119022</t>
+          <t>4.661100095886076</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>7.969054970894657</t>
+          <t>6.72458475215906</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>12.68238797466208</t>
+          <t>14.749184635593288</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>89.15486684697831</t>
+          <t>80.92482040820138</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.002892439446258</t>
+          <t>12.170436617272305</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10.94424765107618</t>
+          <t>9.603099419284847</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>0.5493087963761077</t>
+          <t>0.981046884432873</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.478559910386551</t>
+          <t>7.662911798188318</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2.9630001356942692</t>
+          <t>2.2834902942850874</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>58.32074996464482</t>
+          <t>46.205592631747905</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.600484797465835</t>
+          <t>0.47208670965797084</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.678569385632056</t>
+          <t>0.5143463954604245</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>14.688734877978668</t>
+          <t>10.96112280813499</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>7.279738320004261</t>
+          <t>6.025592397810618</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>8.203453468365016</t>
+          <t>6.893021248016676</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>16.64158355127985</t>
+          <t>13.34747672796021</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>48.08977432571688</t>
+          <t>33.31723947755024</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>4.6631025839726545</t>
+          <t>6.132351322171022</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>6.0175384415966935</t>
+          <t>4.6138972524987585</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>6.590224121763268</t>
+          <t>4.860362685089655</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>11.620350069508364</t>
+          <t>9.418883276542505</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2.5969947555842054</t>
+          <t>1.9479749093534133</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2.3306637268292065</t>
+          <t>1.7478204091073926</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1.8281163715287985</t>
+          <t>1.3587425125322312</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>3.550461650529691</t>
+          <t>2.63348230575569</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>6.354866261362462</t>
+          <t>4.870802692583487</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>19.72672956433617</t>
+          <t>15.20190735396171</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>11.96025417574598</t>
+          <t>10.918290368651228</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7195,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>83.3211023567777</t>
+          <t>7.970552577171773</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>5.49884022082834</t>
+          <t>4.1659821803736</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.734608390790508</t>
+          <t>2.909656679511464</t>
         </is>
       </c>
     </row>
@@ -7267,6 +7267,72 @@
       <c r="D311" t="inlineStr">
         <is>
           <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>DF_INT_SS3_Angel_Goku</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>DF_TEQ_Majin_Vegeta</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>CLR_TEQ_SS3_Gotenks</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.6607137911252465</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tyler\Documents\DokkanAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DECF04-3EF9-49E1-95EC-745382D9A08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091BF60D-B326-4D24-B774-8F08461DD1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="647">
   <si>
     <t>ID</t>
   </si>
@@ -1949,6 +1949,18 @@
   </si>
   <si>
     <t>BU_TEQ_SS_Goten</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>DF_INT_SS_Goku_Mini_Daima</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>DF_PHY_Glorio</t>
   </si>
 </sst>
 </file>
@@ -2133,16 +2145,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{62659D99-13CE-4711-BA56-3CCEF6633E08}" name="Table1" displayName="Table1" ref="A1:D320" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
-  <autoFilter ref="A1:D320" xr:uid="{62659D99-13CE-4711-BA56-3CCEF6633E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D320">
-    <sortCondition descending="1" ref="D1:D320"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C524D4BA-B685-4617-9B4A-8E17852C3639}" name="Table1" displayName="Table1" ref="A1:D322" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+  <autoFilter ref="A1:D322" xr:uid="{C524D4BA-B685-4617-9B4A-8E17852C3639}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D322">
+    <sortCondition descending="1" ref="D1:D322"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5B441BD7-E752-42A0-9BC3-E1E6CFB14E92}" name="ID" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{F5F6E05D-1ABF-43E9-BE09-5D30452A5EF1}" name="common_name"/>
-    <tableColumn id="3" xr3:uid="{2E4A62A3-8CB5-49C8-9217-3DD8D5EF2110}" name="num_copies"/>
-    <tableColumn id="4" xr3:uid="{D5250B62-ACA1-4411-BF14-3DCCA3494C14}" name="Summon Rating"/>
+    <tableColumn id="1" xr3:uid="{40F00575-F0F0-49A1-BCEA-7834848DE35B}" name="ID" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{0DCB8F03-8050-4309-A854-343274141900}" name="common_name"/>
+    <tableColumn id="3" xr3:uid="{759960C5-55CC-4DD2-81CF-294B0A8518B0}" name="num_copies"/>
+    <tableColumn id="4" xr3:uid="{38FB1B61-A60B-46E7-A3FB-640B64D52CFC}" name="Summon Rating"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2433,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D320"/>
+  <dimension ref="A1:D322"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -2466,147 +2478,147 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>91.487176203201798</v>
+        <v>90.748138175909602</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>511</v>
+        <v>645</v>
       </c>
       <c r="B3" t="s">
-        <v>512</v>
+        <v>646</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3">
-        <v>81.138367079445004</v>
+        <v>80.177810405533904</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>431</v>
+        <v>511</v>
       </c>
       <c r="B4" t="s">
-        <v>432</v>
+        <v>512</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4">
-        <v>71.353533380727498</v>
+        <v>79.810198949329504</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>495</v>
+        <v>431</v>
       </c>
       <c r="B5" t="s">
-        <v>496</v>
+        <v>432</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
       </c>
       <c r="D5">
-        <v>60.446944795291103</v>
+        <v>69.873145564913997</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>463</v>
+        <v>643</v>
       </c>
       <c r="B6" t="s">
-        <v>464</v>
+        <v>644</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6">
-        <v>53.089270808271301</v>
+        <v>61.955586836118698</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>535</v>
+        <v>495</v>
       </c>
       <c r="B7" t="s">
-        <v>536</v>
+        <v>496</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7">
-        <v>45.925306718376397</v>
+        <v>58.933789279474901</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>567</v>
+        <v>463</v>
       </c>
       <c r="B8" t="s">
-        <v>568</v>
+        <v>464</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
       </c>
       <c r="D8">
-        <v>40.139105807377298</v>
+        <v>55.033255474703402</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>197</v>
+        <v>535</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>536</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D9">
-        <v>20.895496139812</v>
+        <v>43.841067221542097</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>469</v>
+        <v>567</v>
       </c>
       <c r="B10" t="s">
-        <v>470</v>
+        <v>568</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
       </c>
       <c r="D10">
-        <v>20.4577200763236</v>
+        <v>37.6684782234477</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>20.215826199059901</v>
+        <v>20.999702943693801</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="B12" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
       </c>
       <c r="D12">
-        <v>20.215011216913201</v>
+        <v>20.559037266602701</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
@@ -2620,91 +2632,91 @@
         <v>4</v>
       </c>
       <c r="D13">
-        <v>19.267979676524899</v>
+        <v>19.8184313359017</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>467</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>468</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>18.6031672641749</v>
+        <v>19.769695702322998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>467</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>468</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D15">
-        <v>18.293851860178901</v>
+        <v>18.324010921192102</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>325</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>326</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16">
-        <v>18.0335626802825</v>
+        <v>18.116608922269801</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B17" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>17.785260833653499</v>
+        <v>17.156800288985</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>437</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>438</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
       </c>
       <c r="D18">
-        <v>15.354196817779</v>
+        <v>17.111813686212301</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>169</v>
+        <v>317</v>
       </c>
       <c r="B19" t="s">
-        <v>170</v>
+        <v>318</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D19">
-        <v>15.232015887071</v>
+        <v>16.690535202773599</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
@@ -2718,119 +2730,119 @@
         <v>4</v>
       </c>
       <c r="D20">
-        <v>15.038839577151901</v>
+        <v>15.697895518213601</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>223</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>34</v>
       </c>
       <c r="D21">
-        <v>14.61906768167</v>
+        <v>15.354196817779</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>595</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s">
-        <v>596</v>
+        <v>224</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
       </c>
       <c r="D22">
-        <v>14.406141094076601</v>
+        <v>15.2536410446641</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>509</v>
+        <v>169</v>
       </c>
       <c r="B23" t="s">
-        <v>510</v>
+        <v>170</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
       </c>
       <c r="D23">
-        <v>14.3125054795018</v>
+        <v>14.907300305364</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>333</v>
+        <v>595</v>
       </c>
       <c r="B24" t="s">
-        <v>334</v>
+        <v>596</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24">
-        <v>13.7562527743899</v>
+        <v>14.0998297943596</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>565</v>
+        <v>509</v>
       </c>
       <c r="B25" t="s">
-        <v>566</v>
+        <v>510</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>13.4068684793596</v>
+        <v>14.0264472733429</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>91</v>
+        <v>435</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>436</v>
       </c>
       <c r="C26" t="s">
         <v>34</v>
       </c>
       <c r="D26">
-        <v>13.142618960516099</v>
+        <v>12.911697927992501</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>435</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>436</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
       </c>
       <c r="D27">
-        <v>12.987685618269699</v>
+        <v>12.8965664797022</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>327</v>
+        <v>565</v>
       </c>
       <c r="B28" t="s">
-        <v>328</v>
+        <v>566</v>
       </c>
       <c r="C28" t="s">
         <v>34</v>
       </c>
       <c r="D28">
-        <v>12.3749702655373</v>
+        <v>12.550239792620699</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
@@ -2844,147 +2856,147 @@
         <v>4</v>
       </c>
       <c r="D29">
-        <v>12.2017936881676</v>
+        <v>12.3703827651363</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>161</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>334</v>
       </c>
       <c r="C30" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D30">
-        <v>12.0327875350812</v>
+        <v>12.2598384223356</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s">
-        <v>204</v>
+        <v>328</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D31">
-        <v>11.430987727410001</v>
+        <v>11.8678488459416</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D32">
-        <v>11.4087008106606</v>
+        <v>11.279848387541801</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>109</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>204</v>
       </c>
       <c r="C33" t="s">
         <v>6</v>
       </c>
       <c r="D33">
-        <v>11.1012624387045</v>
+        <v>11.237542872237601</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>545</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s">
-        <v>546</v>
+        <v>162</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
       </c>
       <c r="D34">
-        <v>10.9753726932845</v>
+        <v>10.9744535618205</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>545</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>546</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>10.9301671377474</v>
+        <v>10.909793126138799</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>10.9166118325137</v>
+        <v>10.9043100456399</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>597</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>598</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>10.6343535794934</v>
+        <v>10.4094404899885</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>75</v>
+        <v>597</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>598</v>
       </c>
       <c r="C38" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D38">
-        <v>10.356491345055</v>
+        <v>10.384212645231401</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>519</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>520</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>9.6223383234908102</v>
+        <v>10.054713850657301</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
@@ -2998,77 +3010,77 @@
         <v>4</v>
       </c>
       <c r="D40">
-        <v>9.5717145542321198</v>
+        <v>9.7233141706210997</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>575</v>
+        <v>519</v>
       </c>
       <c r="B41" t="s">
-        <v>576</v>
+        <v>520</v>
       </c>
       <c r="C41" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>9.4324478384712407</v>
+        <v>9.4043138283569601</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>9.4310708725381893</v>
+        <v>9.1205485051190696</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>323</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>324</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>8.9811730622500807</v>
+        <v>9.0460421051408204</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>171</v>
+        <v>575</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>576</v>
       </c>
       <c r="C44" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>8.4858233217913295</v>
+        <v>8.9001841588713901</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D45">
-        <v>8.0096300179511193</v>
+        <v>8.6505909864079396</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
@@ -3082,483 +3094,483 @@
         <v>4</v>
       </c>
       <c r="D46">
-        <v>7.9469638923894097</v>
+        <v>7.8845503563070301</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>523</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>524</v>
+        <v>40</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>7.7047787716002798</v>
+        <v>7.8783791071210301</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="B48" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D48">
-        <v>7.5568683095839901</v>
+        <v>7.6576918120259503</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B49" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D49">
-        <v>7.3754009446050102</v>
+        <v>7.6526939607227602</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D50">
-        <v>7.2793503669519604</v>
+        <v>7.6464542400742603</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>155</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>494</v>
       </c>
       <c r="C51" t="s">
         <v>4</v>
       </c>
       <c r="D51">
-        <v>7.2248115338163101</v>
+        <v>7.30245148212218</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>561</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>562</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52">
-        <v>6.8586146985741099</v>
+        <v>7.2582298810982797</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="C53" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53">
-        <v>6.8013891148742101</v>
+        <v>6.901179767895</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="B54" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D54">
-        <v>6.7642974797649797</v>
+        <v>6.87449422195286</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>507</v>
+        <v>147</v>
       </c>
       <c r="B55" t="s">
-        <v>508</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D55">
-        <v>6.7525929414622796</v>
+        <v>6.8091890858353201</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>87</v>
+        <v>561</v>
       </c>
       <c r="B56" t="s">
-        <v>88</v>
+        <v>562</v>
       </c>
       <c r="C56" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D56">
-        <v>6.5561609826152898</v>
+        <v>6.8004984435153997</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>11</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>488</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D57">
-        <v>6.3521393373143802</v>
+        <v>6.6429484722862</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>47</v>
+        <v>569</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>570</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D58">
-        <v>6.2658234227651901</v>
+        <v>6.6004069125941003</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B59" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C59" t="s">
         <v>11</v>
       </c>
       <c r="D59">
-        <v>6.1210295874127301</v>
+        <v>6.5950248263801301</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C60" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D60">
-        <v>6.0463418363319601</v>
+        <v>6.3227049951271903</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>559</v>
+        <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>560</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
         <v>6</v>
       </c>
       <c r="D61">
-        <v>6.0317399811034598</v>
+        <v>6.2009578454724901</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="C62" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D62">
-        <v>5.9624697379945903</v>
+        <v>6.0934476434114</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D63">
-        <v>5.4906477488242098</v>
+        <v>6.0835344217948002</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>154</v>
       </c>
       <c r="C64" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D64">
-        <v>5.4023092206819303</v>
+        <v>6.0194394813424097</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>149</v>
+        <v>559</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>560</v>
       </c>
       <c r="C65" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D65">
-        <v>5.37864671987787</v>
+        <v>5.95156050637158</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>141</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>448</v>
       </c>
       <c r="C66" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D66">
-        <v>5.3464907871970198</v>
+        <v>5.5939863252652398</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D67">
-        <v>5.1853620004597003</v>
+        <v>5.5379163981044996</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D68">
-        <v>5.1681468548548901</v>
+        <v>5.4529388518120996</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="C69" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D69">
-        <v>5.1527795537929704</v>
+        <v>5.4071843111909201</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>205</v>
+        <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="C70" t="s">
         <v>6</v>
       </c>
       <c r="D70">
-        <v>5.1022962233848004</v>
+        <v>5.38746322321688</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>447</v>
+        <v>145</v>
       </c>
       <c r="B71" t="s">
-        <v>448</v>
+        <v>146</v>
       </c>
       <c r="C71" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D71">
-        <v>5.01638590835777</v>
+        <v>5.2360743780091097</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="C72" t="s">
         <v>6</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>5.0640711088346704</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>4</v>
+        <v>205</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>206</v>
       </c>
       <c r="C73" t="s">
         <v>6</v>
       </c>
       <c r="D73">
-        <v>4.9817525019907896</v>
+        <v>5.0040568062157904</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D74">
-        <v>4.9175375196388904</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>593</v>
+        <v>157</v>
       </c>
       <c r="B75" t="s">
-        <v>594</v>
+        <v>158</v>
       </c>
       <c r="C75" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D75">
-        <v>4.8874698597304196</v>
+        <v>4.9952560875329404</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>573</v>
+        <v>26</v>
       </c>
       <c r="B76" t="s">
-        <v>574</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D76">
-        <v>4.8623354813482802</v>
+        <v>4.97797564533853</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>221</v>
+        <v>593</v>
       </c>
       <c r="B77" t="s">
-        <v>222</v>
+        <v>594</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D77">
-        <v>4.8319145401126899</v>
+        <v>4.9148069946472601</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>55</v>
+        <v>221</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="C78" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D78">
-        <v>4.7201831504976104</v>
+        <v>4.7582256745120102</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>499</v>
+        <v>163</v>
       </c>
       <c r="B79" t="s">
-        <v>500</v>
+        <v>164</v>
       </c>
       <c r="C79" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D79">
-        <v>4.6567950958061504</v>
+        <v>4.7374078953141501</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>107</v>
+        <v>499</v>
       </c>
       <c r="B80" t="s">
-        <v>108</v>
+        <v>500</v>
       </c>
       <c r="C80" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D80">
-        <v>4.6325242804258799</v>
+        <v>4.6393037984580197</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
@@ -3572,553 +3584,553 @@
         <v>6</v>
       </c>
       <c r="D81">
-        <v>4.6164674846346303</v>
+        <v>4.5332669665897702</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C82" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D82">
-        <v>4.5451924779097999</v>
+        <v>4.4875272709963303</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>68</v>
       </c>
       <c r="C83" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>4.4498698357627902</v>
+        <v>4.4396163752218003</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C84" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D84">
-        <v>4.2845034280215604</v>
+        <v>4.35614684950938</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="C85" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D85">
-        <v>4.2503168711297103</v>
+        <v>4.3548196456992603</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>619</v>
+        <v>55</v>
       </c>
       <c r="B86" t="s">
-        <v>620</v>
+        <v>56</v>
       </c>
       <c r="C86" t="s">
         <v>4</v>
       </c>
       <c r="D86">
-        <v>4.16588564380866</v>
+        <v>4.2756590103229399</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B87" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C87" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D87">
-        <v>4.1302718317276703</v>
+        <v>4.2324540339648404</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C88" t="s">
         <v>34</v>
       </c>
       <c r="D88">
-        <v>4.08291603962323</v>
+        <v>4.1817640231055</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>347</v>
+        <v>139</v>
       </c>
       <c r="B89" t="s">
-        <v>348</v>
+        <v>140</v>
       </c>
       <c r="C89" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D89">
-        <v>4.0434228061502999</v>
+        <v>4.1352906612939702</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>137</v>
+        <v>347</v>
       </c>
       <c r="B90" t="s">
-        <v>138</v>
+        <v>348</v>
       </c>
       <c r="C90" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D90">
-        <v>4.0040809252695899</v>
+        <v>4.0908052736952802</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>77</v>
+        <v>619</v>
       </c>
       <c r="B91" t="s">
-        <v>78</v>
+        <v>620</v>
       </c>
       <c r="C91" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D91">
-        <v>3.9998133298713698</v>
+        <v>4.0780317574601996</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>129</v>
+        <v>465</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>466</v>
       </c>
       <c r="C92" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D92">
-        <v>3.94754461049896</v>
+        <v>3.9059523744087201</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="B93" t="s">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D93">
-        <v>3.9194163393383401</v>
+        <v>3.8835175104692601</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>465</v>
+        <v>77</v>
       </c>
       <c r="B94" t="s">
-        <v>466</v>
+        <v>78</v>
       </c>
       <c r="C94" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D94">
-        <v>3.87411902868369</v>
+        <v>3.8821835090303098</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>63</v>
+        <v>639</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>640</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D95">
-        <v>3.8187338976466201</v>
+        <v>3.8343824864076201</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
         <v>6</v>
       </c>
       <c r="D96">
-        <v>3.7021775546253002</v>
+        <v>3.7837490541547099</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>485</v>
+        <v>239</v>
       </c>
       <c r="B97" t="s">
-        <v>486</v>
+        <v>240</v>
       </c>
       <c r="C97" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D97">
-        <v>3.6904489590247298</v>
+        <v>3.7719895073274401</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="C98" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D98">
-        <v>3.6859817248614299</v>
+        <v>3.7624957873918898</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>301</v>
+        <v>151</v>
       </c>
       <c r="B99" t="s">
-        <v>302</v>
+        <v>152</v>
       </c>
       <c r="C99" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D99">
-        <v>3.6080656971919498</v>
+        <v>3.7380334625925999</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>251</v>
+        <v>117</v>
       </c>
       <c r="B100" t="s">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D100">
-        <v>3.5112530381437299</v>
+        <v>3.7143105783982899</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C101" t="s">
         <v>6</v>
       </c>
       <c r="D101">
-        <v>3.5034216566365801</v>
+        <v>3.6802199316423598</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>117</v>
+        <v>301</v>
       </c>
       <c r="B102" t="s">
-        <v>118</v>
+        <v>302</v>
       </c>
       <c r="C102" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D102">
-        <v>3.4296372357806799</v>
+        <v>3.55233812032851</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>639</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>640</v>
+        <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D103">
-        <v>3.4211830064398701</v>
+        <v>3.4725857250655601</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B104" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C104" t="s">
         <v>4</v>
       </c>
       <c r="D104">
-        <v>3.4209754497751899</v>
+        <v>3.4526419373461099</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>491</v>
+        <v>251</v>
       </c>
       <c r="B105" t="s">
-        <v>492</v>
+        <v>252</v>
       </c>
       <c r="C105" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D105">
-        <v>3.2284011115681701</v>
+        <v>3.4456356663250398</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>165</v>
+        <v>483</v>
       </c>
       <c r="B106" t="s">
-        <v>166</v>
+        <v>484</v>
       </c>
       <c r="C106" t="s">
         <v>4</v>
       </c>
       <c r="D106">
-        <v>3.1242385971971198</v>
+        <v>3.3968951470892002</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>479</v>
+        <v>165</v>
       </c>
       <c r="B107" t="s">
-        <v>480</v>
+        <v>166</v>
       </c>
       <c r="C107" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D107">
-        <v>2.9620103924558299</v>
+        <v>3.1033251584098398</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>213</v>
+        <v>591</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
+        <v>592</v>
       </c>
       <c r="C108" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D108">
-        <v>2.9583759598038601</v>
+        <v>3.0472632403324198</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>621</v>
+        <v>491</v>
       </c>
       <c r="B109" t="s">
-        <v>622</v>
+        <v>492</v>
       </c>
       <c r="C109" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D109">
-        <v>2.9033395932168999</v>
+        <v>2.9408648360606602</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="B110" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="C110" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D110">
-        <v>2.88435322476737</v>
+        <v>2.9185384938978598</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>195</v>
+        <v>629</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>630</v>
       </c>
       <c r="C111" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D111">
-        <v>2.75251534773775</v>
+        <v>2.8154257017431599</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>343</v>
+        <v>461</v>
       </c>
       <c r="B112" t="s">
-        <v>344</v>
+        <v>462</v>
       </c>
       <c r="C112" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D112">
-        <v>2.7271385561558601</v>
+        <v>2.7455836213595499</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="B113" t="s">
-        <v>304</v>
+        <v>196</v>
       </c>
       <c r="C113" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D113">
-        <v>2.6922038010487501</v>
+        <v>2.6883733779795902</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>591</v>
+        <v>343</v>
       </c>
       <c r="B114" t="s">
-        <v>592</v>
+        <v>344</v>
       </c>
       <c r="C114" t="s">
         <v>9</v>
       </c>
       <c r="D114">
-        <v>2.6704428168862999</v>
+        <v>2.6875634023312198</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>629</v>
+        <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>630</v>
+        <v>214</v>
       </c>
       <c r="C115" t="s">
         <v>4</v>
       </c>
       <c r="D115">
-        <v>2.65458032644423</v>
+        <v>2.66609841337208</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B116" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C116" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D116">
-        <v>2.5686478706156302</v>
+        <v>2.6146464535083802</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="B117" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="C117" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D117">
-        <v>2.5259927469379599</v>
+        <v>2.5621236267138698</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>99</v>
+        <v>631</v>
       </c>
       <c r="B118" t="s">
-        <v>100</v>
+        <v>632</v>
       </c>
       <c r="C118" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D118">
-        <v>2.5</v>
+        <v>2.54504748775615</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>525</v>
+        <v>99</v>
       </c>
       <c r="B119" t="s">
-        <v>526</v>
+        <v>100</v>
       </c>
       <c r="C119" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D119">
-        <v>2.2800530777463401</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>30</v>
+        <v>319</v>
       </c>
       <c r="B120" t="s">
-        <v>31</v>
+        <v>320</v>
       </c>
       <c r="C120" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D120">
-        <v>2.2765773172650099</v>
+        <v>2.42066461745216</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
@@ -4132,757 +4144,757 @@
         <v>9</v>
       </c>
       <c r="D121">
-        <v>2.2565564587245399</v>
+        <v>2.2722008557421498</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>637</v>
+        <v>525</v>
       </c>
       <c r="B122" t="s">
-        <v>638</v>
+        <v>526</v>
       </c>
       <c r="C122" t="s">
         <v>4</v>
       </c>
       <c r="D122">
-        <v>2.2323334473957299</v>
+        <v>2.27098054779812</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B123" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C123" t="s">
         <v>6</v>
       </c>
       <c r="D123">
-        <v>2.19345668825415</v>
+        <v>2.2019824786426199</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="B124" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="C124" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D124">
-        <v>2.1635365956506898</v>
+        <v>2.19345668825415</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>375</v>
+        <v>637</v>
       </c>
       <c r="B125" t="s">
-        <v>376</v>
+        <v>638</v>
       </c>
       <c r="C125" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D125">
-        <v>2.0715951716248102</v>
+        <v>2.1884004511058999</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="C126" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D126">
-        <v>2.0708758847295701</v>
+        <v>2.0741267208815399</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>93</v>
+        <v>375</v>
       </c>
       <c r="B127" t="s">
-        <v>94</v>
+        <v>376</v>
       </c>
       <c r="C127" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D127">
-        <v>2.0429256796461401</v>
+        <v>2.00950224550972</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="B128" t="s">
-        <v>180</v>
+        <v>316</v>
       </c>
       <c r="C128" t="s">
         <v>6</v>
       </c>
       <c r="D128">
-        <v>2.0262231708179801</v>
+        <v>2.0034205192340702</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>315</v>
+        <v>37</v>
       </c>
       <c r="B129" t="s">
-        <v>316</v>
+        <v>38</v>
       </c>
       <c r="C129" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D129">
-        <v>1.99428577147575</v>
+        <v>2.0014901566596501</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>295</v>
+        <v>93</v>
       </c>
       <c r="B130" t="s">
-        <v>296</v>
+        <v>94</v>
       </c>
       <c r="C130" t="s">
         <v>6</v>
       </c>
       <c r="D130">
-        <v>1.9630203245606599</v>
+        <v>1.9932706053809699</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>583</v>
+        <v>383</v>
       </c>
       <c r="B131" t="s">
-        <v>584</v>
+        <v>384</v>
       </c>
       <c r="C131" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D131">
-        <v>1.9497960946891699</v>
+        <v>1.9697751977719999</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>371</v>
+        <v>305</v>
       </c>
       <c r="B132" t="s">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="C132" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D132">
-        <v>1.91964170347658</v>
+        <v>1.9253776777663201</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>383</v>
+        <v>175</v>
       </c>
       <c r="B133" t="s">
-        <v>384</v>
+        <v>176</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133">
-        <v>1.90384108298119</v>
+        <v>1.9225801890897001</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>305</v>
+        <v>583</v>
       </c>
       <c r="B134" t="s">
-        <v>306</v>
+        <v>584</v>
       </c>
       <c r="C134" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D134">
-        <v>1.9024867241263701</v>
+        <v>1.8905659476477299</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>41</v>
+        <v>371</v>
       </c>
       <c r="B135" t="s">
-        <v>42</v>
+        <v>372</v>
       </c>
       <c r="C135" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D135">
-        <v>1.8976008456071201</v>
+        <v>1.88519500687701</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>381</v>
+        <v>41</v>
       </c>
       <c r="B136" t="s">
-        <v>382</v>
+        <v>42</v>
       </c>
       <c r="C136" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D136">
-        <v>1.8910346847813699</v>
+        <v>1.8566688327821901</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>28</v>
+        <v>381</v>
       </c>
       <c r="B137" t="s">
-        <v>29</v>
+        <v>382</v>
       </c>
       <c r="C137" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D137">
-        <v>1.7908712077928199</v>
+        <v>1.8535257114252399</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>585</v>
+        <v>28</v>
       </c>
       <c r="B138" t="s">
-        <v>586</v>
+        <v>29</v>
       </c>
       <c r="C138" t="s">
         <v>9</v>
       </c>
       <c r="D138">
-        <v>1.74913504499818</v>
+        <v>1.80266776176747</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="B139" t="s">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="C139" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D139">
-        <v>1.7433748647502101</v>
+        <v>1.74458661813256</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="B140" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="C140" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D140">
-        <v>1.7151569967923399</v>
+        <v>1.7437513964731199</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="B141" t="s">
-        <v>62</v>
+        <v>230</v>
       </c>
       <c r="C141" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D141">
-        <v>1.69270833086968</v>
+        <v>1.73886639776759</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>237</v>
+        <v>585</v>
       </c>
       <c r="B142" t="s">
-        <v>238</v>
+        <v>586</v>
       </c>
       <c r="C142" t="s">
         <v>9</v>
       </c>
       <c r="D142">
-        <v>1.67020904076592</v>
+        <v>1.70095527116226</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>125</v>
+        <v>295</v>
       </c>
       <c r="B143" t="s">
-        <v>126</v>
+        <v>296</v>
       </c>
       <c r="C143" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D143">
-        <v>1.6367542752953399</v>
+        <v>1.67491910027264</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>283</v>
+        <v>61</v>
       </c>
       <c r="B144" t="s">
-        <v>284</v>
+        <v>62</v>
       </c>
       <c r="C144" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D144">
-        <v>1.63249432668392</v>
+        <v>1.6287545160700601</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B145" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C145" t="s">
         <v>9</v>
       </c>
       <c r="D145">
-        <v>1.51971130661406</v>
+        <v>1.6267805120221099</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>243</v>
+        <v>125</v>
       </c>
       <c r="B146" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="C146" t="s">
         <v>9</v>
       </c>
       <c r="D146">
-        <v>1.51654623058464</v>
+        <v>1.56897578756786</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>421</v>
+        <v>283</v>
       </c>
       <c r="B147" t="s">
-        <v>422</v>
+        <v>284</v>
       </c>
       <c r="C147" t="s">
         <v>11</v>
       </c>
       <c r="D147">
-        <v>1.4342160592975901</v>
+        <v>1.54427300440302</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="B148" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="C148" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D148">
-        <v>1.4093039474487401</v>
+        <v>1.4664436067728801</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>589</v>
+        <v>291</v>
       </c>
       <c r="B149" t="s">
-        <v>590</v>
+        <v>292</v>
       </c>
       <c r="C149" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D149">
-        <v>1.35909578512677</v>
+        <v>1.43078361961539</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B150" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C150" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D150">
-        <v>1.2350569305544701</v>
+        <v>1.41783790652026</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>231</v>
+        <v>589</v>
       </c>
       <c r="B151" t="s">
-        <v>232</v>
+        <v>590</v>
       </c>
       <c r="C151" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D151">
-        <v>1.0967283441270701</v>
+        <v>1.35277955297054</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>181</v>
+        <v>521</v>
       </c>
       <c r="B152" t="s">
-        <v>182</v>
+        <v>522</v>
       </c>
       <c r="C152" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D152">
-        <v>1.06681300052315</v>
+        <v>1.32378137129099</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>57</v>
+        <v>413</v>
       </c>
       <c r="B153" t="s">
-        <v>58</v>
+        <v>414</v>
       </c>
       <c r="C153" t="s">
         <v>6</v>
       </c>
       <c r="D153">
-        <v>1.05533761619488</v>
+        <v>1.2661621866519499</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>349</v>
+        <v>231</v>
       </c>
       <c r="B154" t="s">
-        <v>350</v>
+        <v>232</v>
       </c>
       <c r="C154" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D154">
-        <v>0.97343787631830003</v>
+        <v>1.0967283441270701</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>521</v>
+        <v>181</v>
       </c>
       <c r="B155" t="s">
-        <v>522</v>
+        <v>182</v>
       </c>
       <c r="C155" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D155">
-        <v>0.97005666316422401</v>
+        <v>1.09520200721075</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>457</v>
+        <v>57</v>
       </c>
       <c r="B156" t="s">
-        <v>458</v>
+        <v>58</v>
       </c>
       <c r="C156" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D156">
-        <v>0.950383403041826</v>
+        <v>1.0347245077194001</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>411</v>
+        <v>349</v>
       </c>
       <c r="B157" t="s">
-        <v>412</v>
+        <v>350</v>
       </c>
       <c r="C157" t="s">
         <v>9</v>
       </c>
       <c r="D157">
-        <v>0.93332379926854003</v>
+        <v>0.97504729504642795</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B158" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C158" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D158">
-        <v>0.84189768685657695</v>
+        <v>0.96576653313320404</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>95</v>
+        <v>411</v>
       </c>
       <c r="B159" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="C159" t="s">
         <v>9</v>
       </c>
       <c r="D159">
-        <v>0.76362765673789201</v>
+        <v>0.91281492088703498</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>81</v>
+        <v>453</v>
       </c>
       <c r="B160" t="s">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="C160" t="s">
         <v>9</v>
       </c>
       <c r="D160">
-        <v>0.75818365590435999</v>
+        <v>0.77913581407588295</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="B161" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C161" t="s">
         <v>9</v>
       </c>
       <c r="D161">
-        <v>0.69390264804633695</v>
+        <v>0.77153563950325199</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>473</v>
+        <v>95</v>
       </c>
       <c r="B162" t="s">
-        <v>474</v>
+        <v>96</v>
       </c>
       <c r="C162" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D162">
-        <v>0.65180180989045899</v>
+        <v>0.74544151708686002</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="B163" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C163" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D163">
-        <v>0.63319640470965999</v>
+        <v>0.69390264804633695</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>159</v>
+        <v>473</v>
       </c>
       <c r="B164" t="s">
-        <v>160</v>
+        <v>474</v>
       </c>
       <c r="C164" t="s">
         <v>11</v>
       </c>
       <c r="D164">
-        <v>0.55793135165974495</v>
+        <v>0.68001866646278397</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B165" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C165" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D165">
-        <v>0.47866079286672097</v>
+        <v>0.63319640470965999</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>539</v>
+        <v>159</v>
       </c>
       <c r="B166" t="s">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="C166" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D166">
-        <v>0.47197890553640298</v>
+        <v>0.56967380947909896</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>177</v>
+        <v>539</v>
       </c>
       <c r="B167" t="s">
-        <v>178</v>
+        <v>540</v>
       </c>
       <c r="C167" t="s">
         <v>9</v>
       </c>
       <c r="D167">
-        <v>0.41151770970755502</v>
+        <v>0.48157114535773898</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>409</v>
+        <v>65</v>
       </c>
       <c r="B168" t="s">
-        <v>410</v>
+        <v>66</v>
       </c>
       <c r="C168" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D168">
-        <v>0.34786472880599201</v>
+        <v>0.47112661380468801</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="B169" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="C169" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D169">
-        <v>0.33510146088415999</v>
+        <v>0.407521540254769</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>415</v>
+        <v>235</v>
       </c>
       <c r="B170" t="s">
-        <v>416</v>
+        <v>236</v>
       </c>
       <c r="C170" t="s">
         <v>11</v>
       </c>
       <c r="D170">
-        <v>0.28616061606954002</v>
+        <v>0.34282497419504099</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="B171" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="C171" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D171">
-        <v>0.26341368230411</v>
+        <v>0.34135189601152499</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>249</v>
+        <v>415</v>
       </c>
       <c r="B172" t="s">
-        <v>250</v>
+        <v>416</v>
       </c>
       <c r="C172" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D172">
-        <v>0.25871547013733798</v>
+        <v>0.28783635190249601</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>257</v>
+        <v>389</v>
       </c>
       <c r="B173" t="s">
-        <v>258</v>
+        <v>390</v>
       </c>
       <c r="C173" t="s">
         <v>9</v>
       </c>
       <c r="D173">
-        <v>0.21045271187561099</v>
+        <v>0.268995083455351</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>6</v>
+        <v>249</v>
       </c>
       <c r="B174" t="s">
-        <v>7</v>
+        <v>250</v>
       </c>
       <c r="C174" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D174">
-        <v>0.2</v>
+        <v>0.26103584423750098</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C175" t="s">
         <v>8</v>
@@ -4893,13 +4905,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C176" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D176">
         <v>0.2</v>
@@ -4907,13 +4919,13 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B177" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C177" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D177">
         <v>0.2</v>
@@ -4921,13 +4933,13 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B178" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C178" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D178">
         <v>0.2</v>
@@ -4935,13 +4947,13 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B179" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C179" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D179">
         <v>0.2</v>
@@ -4949,10 +4961,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B180" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C180" t="s">
         <v>8</v>
@@ -4963,10 +4975,10 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B181" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C181" t="s">
         <v>8</v>
@@ -4977,10 +4989,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B182" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C182" t="s">
         <v>8</v>
@@ -4991,10 +5003,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B183" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C183" t="s">
         <v>8</v>
@@ -5005,10 +5017,10 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B184" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C184" t="s">
         <v>8</v>
@@ -5019,10 +5031,10 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B185" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C185" t="s">
         <v>8</v>
@@ -5033,10 +5045,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B186" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C186" t="s">
         <v>8</v>
@@ -5047,10 +5059,10 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B187" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C187" t="s">
         <v>8</v>
@@ -5061,10 +5073,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B188" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C188" t="s">
         <v>8</v>
@@ -5075,10 +5087,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B189" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C189" t="s">
         <v>8</v>
@@ -5089,10 +5101,10 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B190" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C190" t="s">
         <v>8</v>
@@ -5103,10 +5115,10 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B191" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C191" t="s">
         <v>8</v>
@@ -5117,10 +5129,10 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B192" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C192" t="s">
         <v>8</v>
@@ -5131,10 +5143,10 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="B193" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="C193" t="s">
         <v>8</v>
@@ -5145,10 +5157,10 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="B194" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C194" t="s">
         <v>8</v>
@@ -5159,10 +5171,10 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B195" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C195" t="s">
         <v>8</v>
@@ -5173,10 +5185,10 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B196" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C196" t="s">
         <v>8</v>
@@ -5187,10 +5199,10 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B197" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C197" t="s">
         <v>8</v>
@@ -5201,10 +5213,10 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B198" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C198" t="s">
         <v>8</v>
@@ -5215,10 +5227,10 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B199" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C199" t="s">
         <v>8</v>
@@ -5229,10 +5241,10 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C200" t="s">
         <v>8</v>
@@ -5243,10 +5255,10 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B201" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C201" t="s">
         <v>8</v>
@@ -5257,10 +5269,10 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B202" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C202" t="s">
         <v>8</v>
@@ -5271,10 +5283,10 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B203" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C203" t="s">
         <v>8</v>
@@ -5285,10 +5297,10 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B204" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C204" t="s">
         <v>8</v>
@@ -5299,10 +5311,10 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B205" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C205" t="s">
         <v>8</v>
@@ -5313,10 +5325,10 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B206" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C206" t="s">
         <v>8</v>
@@ -5327,10 +5339,10 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B207" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C207" t="s">
         <v>8</v>
@@ -5341,10 +5353,10 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B208" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C208" t="s">
         <v>8</v>
@@ -5355,10 +5367,10 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B209" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C209" t="s">
         <v>8</v>
@@ -5369,10 +5381,10 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B210" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C210" t="s">
         <v>8</v>
@@ -5383,10 +5395,10 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B211" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C211" t="s">
         <v>8</v>
@@ -5397,10 +5409,10 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B212" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C212" t="s">
         <v>8</v>
@@ -5411,13 +5423,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B213" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C213" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D213">
         <v>0.2</v>
@@ -5425,10 +5437,10 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B214" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C214" t="s">
         <v>8</v>
@@ -5439,10 +5451,10 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B215" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C215" t="s">
         <v>8</v>
@@ -5453,10 +5465,10 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B216" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C216" t="s">
         <v>8</v>
@@ -5467,10 +5479,10 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B217" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C217" t="s">
         <v>8</v>
@@ -5481,10 +5493,10 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A218" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B218" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C218" t="s">
         <v>8</v>
@@ -5495,10 +5507,10 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A219" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B219" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C219" t="s">
         <v>8</v>
@@ -5509,10 +5521,10 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A220" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B220" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C220" t="s">
         <v>8</v>
@@ -5523,10 +5535,10 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A221" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B221" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C221" t="s">
         <v>8</v>
@@ -5537,10 +5549,10 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B222" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C222" t="s">
         <v>8</v>
@@ -5551,10 +5563,10 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A223" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B223" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C223" t="s">
         <v>8</v>
@@ -5565,10 +5577,10 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A224" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B224" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C224" t="s">
         <v>8</v>
@@ -5579,10 +5591,10 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B225" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C225" t="s">
         <v>8</v>
@@ -5593,10 +5605,10 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B226" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C226" t="s">
         <v>8</v>
@@ -5607,10 +5619,10 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A227" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B227" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C227" t="s">
         <v>8</v>
@@ -5621,10 +5633,10 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A228" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B228" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C228" t="s">
         <v>8</v>
@@ -5635,10 +5647,10 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A229" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B229" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C229" t="s">
         <v>8</v>
@@ -5649,10 +5661,10 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A230" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B230" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C230" t="s">
         <v>8</v>
@@ -5663,10 +5675,10 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A231" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B231" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C231" t="s">
         <v>8</v>
@@ -5677,10 +5689,10 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A232" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B232" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C232" t="s">
         <v>8</v>
@@ -5691,10 +5703,10 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A233" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B233" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C233" t="s">
         <v>8</v>
@@ -5705,10 +5717,10 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A234" s="1" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B234" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="C234" t="s">
         <v>8</v>
@@ -5719,10 +5731,10 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" s="1" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B235" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C235" t="s">
         <v>8</v>
@@ -5733,10 +5745,10 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A236" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B236" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C236" t="s">
         <v>8</v>
@@ -5747,10 +5759,10 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A237" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B237" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C237" t="s">
         <v>8</v>
@@ -5761,10 +5773,10 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A238" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B238" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C238" t="s">
         <v>8</v>
@@ -5775,10 +5787,10 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A239" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B239" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C239" t="s">
         <v>8</v>
@@ -5789,10 +5801,10 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A240" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B240" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C240" t="s">
         <v>8</v>
@@ -5803,10 +5815,10 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" s="1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B241" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C241" t="s">
         <v>8</v>
@@ -5817,10 +5829,10 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A242" s="1" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B242" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C242" t="s">
         <v>8</v>
@@ -5831,10 +5843,10 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A243" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B243" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C243" t="s">
         <v>8</v>
@@ -5845,10 +5857,10 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B244" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C244" t="s">
         <v>8</v>
@@ -5859,10 +5871,10 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A245" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B245" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C245" t="s">
         <v>8</v>
@@ -5873,10 +5885,10 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A246" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B246" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C246" t="s">
         <v>8</v>
@@ -5887,10 +5899,10 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A247" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B247" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C247" t="s">
         <v>8</v>
@@ -5901,13 +5913,13 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A248" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B248" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C248" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D248">
         <v>0.2</v>
@@ -5915,10 +5927,10 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B249" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C249" t="s">
         <v>8</v>
@@ -5929,13 +5941,13 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B250" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C250" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D250">
         <v>0.2</v>
@@ -5943,10 +5955,10 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A251" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B251" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C251" t="s">
         <v>8</v>
@@ -5957,10 +5969,10 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A252" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B252" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C252" t="s">
         <v>8</v>
@@ -5971,10 +5983,10 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B253" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C253" t="s">
         <v>8</v>
@@ -5985,10 +5997,10 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A254" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B254" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C254" t="s">
         <v>8</v>
@@ -5999,10 +6011,10 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A255" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B255" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C255" t="s">
         <v>8</v>
@@ -6013,10 +6025,10 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A256" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B256" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C256" t="s">
         <v>8</v>
@@ -6027,10 +6039,10 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B257" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C257" t="s">
         <v>8</v>
@@ -6041,10 +6053,10 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A258" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B258" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C258" t="s">
         <v>8</v>
@@ -6055,10 +6067,10 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B259" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C259" t="s">
         <v>8</v>
@@ -6069,10 +6081,10 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A260" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B260" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C260" t="s">
         <v>8</v>
@@ -6083,10 +6095,10 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A261" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B261" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C261" t="s">
         <v>8</v>
@@ -6097,10 +6109,10 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B262" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C262" t="s">
         <v>8</v>
@@ -6111,10 +6123,10 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A263" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B263" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C263" t="s">
         <v>8</v>
@@ -6125,10 +6137,10 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A264" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B264" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C264" t="s">
         <v>8</v>
@@ -6139,10 +6151,10 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" s="1" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B265" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C265" t="s">
         <v>8</v>
@@ -6153,10 +6165,10 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A266" s="1" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="B266" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C266" t="s">
         <v>8</v>
@@ -6167,10 +6179,10 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A267" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B267" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C267" t="s">
         <v>8</v>
@@ -6181,10 +6193,10 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B268" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C268" t="s">
         <v>8</v>
@@ -6195,10 +6207,10 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A269" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B269" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C269" t="s">
         <v>8</v>
@@ -6209,10 +6221,10 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A270" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B270" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C270" t="s">
         <v>8</v>
@@ -6223,10 +6235,10 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" s="1" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B271" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C271" t="s">
         <v>8</v>
@@ -6237,10 +6249,10 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A272" s="1" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B272" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C272" t="s">
         <v>8</v>
@@ -6251,10 +6263,10 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B273" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C273" t="s">
         <v>8</v>
@@ -6265,10 +6277,10 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A274" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B274" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C274" t="s">
         <v>8</v>
@@ -6279,10 +6291,10 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A275" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B275" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C275" t="s">
         <v>8</v>
@@ -6293,10 +6305,10 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A276" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B276" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C276" t="s">
         <v>8</v>
@@ -6307,10 +6319,10 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B277" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C277" t="s">
         <v>8</v>
@@ -6321,10 +6333,10 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A278" s="1" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="B278" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="C278" t="s">
         <v>8</v>
@@ -6335,10 +6347,10 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A279" s="1" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B279" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C279" t="s">
         <v>8</v>
@@ -6349,10 +6361,10 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B280" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C280" t="s">
         <v>8</v>
@@ -6363,10 +6375,10 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B281" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C281" t="s">
         <v>8</v>
@@ -6377,10 +6389,10 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A282" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B282" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C282" t="s">
         <v>8</v>
@@ -6391,10 +6403,10 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A283" s="1" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="B283" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C283" t="s">
         <v>8</v>
@@ -6405,10 +6417,10 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A284" s="1" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="B284" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="C284" t="s">
         <v>8</v>
@@ -6419,10 +6431,10 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A285" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B285" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C285" t="s">
         <v>8</v>
@@ -6433,10 +6445,10 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" s="1" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="B286" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C286" t="s">
         <v>8</v>
@@ -6447,10 +6459,10 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A287" s="1" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B287" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C287" t="s">
         <v>8</v>
@@ -6461,10 +6473,10 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A288" s="1" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="B288" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="C288" t="s">
         <v>8</v>
@@ -6475,10 +6487,10 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" s="1" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="B289" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="C289" t="s">
         <v>8</v>
@@ -6489,10 +6501,10 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A290" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B290" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C290" t="s">
         <v>8</v>
@@ -6503,10 +6515,10 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A291" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B291" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C291" t="s">
         <v>8</v>
@@ -6517,10 +6529,10 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A292" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B292" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C292" t="s">
         <v>8</v>
@@ -6531,10 +6543,10 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A293" s="1" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="B293" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C293" t="s">
         <v>8</v>
@@ -6545,10 +6557,10 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A294" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B294" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C294" t="s">
         <v>8</v>
@@ -6559,10 +6571,10 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" s="1" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B295" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C295" t="s">
         <v>8</v>
@@ -6573,10 +6585,10 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A296" s="1" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B296" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C296" t="s">
         <v>8</v>
@@ -6587,10 +6599,10 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B297" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C297" t="s">
         <v>8</v>
@@ -6601,10 +6613,10 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B298" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C298" t="s">
         <v>8</v>
@@ -6615,10 +6627,10 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A299" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B299" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C299" t="s">
         <v>8</v>
@@ -6629,10 +6641,10 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A300" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B300" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C300" t="s">
         <v>8</v>
@@ -6643,10 +6655,10 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A301" s="1" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B301" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C301" t="s">
         <v>8</v>
@@ -6657,10 +6669,10 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A302" s="1" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
       <c r="B302" t="s">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="C302" t="s">
         <v>8</v>
@@ -6671,10 +6683,10 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A303" s="1" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="B303" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="C303" t="s">
         <v>8</v>
@@ -6685,10 +6697,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B304" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C304" t="s">
         <v>8</v>
@@ -6699,10 +6711,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" s="1" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B305" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C305" t="s">
         <v>8</v>
@@ -6713,10 +6725,10 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A306" s="1" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="B306" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="C306" t="s">
         <v>8</v>
@@ -6727,10 +6739,10 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" s="1" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="B307" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="C307" t="s">
         <v>8</v>
@@ -6741,10 +6753,10 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A308" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B308" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C308" t="s">
         <v>8</v>
@@ -6755,10 +6767,10 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A309" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B309" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C309" t="s">
         <v>8</v>
@@ -6769,10 +6781,10 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A310" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B310" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C310" t="s">
         <v>8</v>
@@ -6783,10 +6795,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A311" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B311" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C311" t="s">
         <v>8</v>
@@ -6797,10 +6809,10 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A312" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B312" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C312" t="s">
         <v>8</v>
@@ -6811,10 +6823,10 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B313" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C313" t="s">
         <v>8</v>
@@ -6825,10 +6837,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B314" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C314" t="s">
         <v>8</v>
@@ -6839,10 +6851,10 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" s="1" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="B315" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="C315" t="s">
         <v>8</v>
@@ -6853,10 +6865,10 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" s="1" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="B316" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C316" t="s">
         <v>8</v>
@@ -6867,10 +6879,10 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B317" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C317" t="s">
         <v>8</v>
@@ -6881,10 +6893,10 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" s="1" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B318" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C318" t="s">
         <v>8</v>
@@ -6895,10 +6907,10 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" s="1" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="B319" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C319" t="s">
         <v>8</v>
@@ -6909,15 +6921,43 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A320" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B320" t="s">
+        <v>634</v>
+      </c>
+      <c r="C320" t="s">
+        <v>8</v>
+      </c>
+      <c r="D320">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A321" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B321" t="s">
+        <v>636</v>
+      </c>
+      <c r="C321" t="s">
+        <v>8</v>
+      </c>
+      <c r="D321">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A322" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B322" t="s">
         <v>642</v>
       </c>
-      <c r="C320" t="s">
-        <v>8</v>
-      </c>
-      <c r="D320">
+      <c r="C322" t="s">
+        <v>8</v>
+      </c>
+      <c r="D322">
         <v>0.2</v>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>1.0408539720695054</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.193456688254154</t>
+          <t>3.290185032381231</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.2019032392273283</t>
+          <t>2.7396817278381107</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.354196817779076</t>
+          <t>23.031295226668618</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.47111349970925964</t>
+          <t>0.5483641720635385</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.9497946070644906</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.05456407624061</t>
+          <t>6.910114073114488</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.7715230141773901</t>
+          <t>0.9497946070644906</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.5</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.7454277833780303</t>
+          <t>0.9497946070644906</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.6450925161906156</t>
         </is>
       </c>
     </row>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>17.156902479115324</t>
+          <t>7.997720155403101</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.0094888305897243</t>
+          <t>2.5534930050244</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1.8534675961545544</t>
+          <t>0.3344215141407467</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>80.5003179969023</t>
+          <t>9.04813010939371</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0639740643077005</t>
+          <t>5.133629820345758</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.201014887024684</t>
+          <t>6.311965175196768</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.1160659009356</t>
+          <t>18.63423667815604</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.4724860641729514</t>
+          <t>3.53535234265245</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.783659748195369</t>
+          <t>3.8509131546954856</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.977885639349839</t>
+          <t>5.050299810830412</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.8026249410430708</t>
+          <t>1.7113917697967995</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.279397522399732</t>
+          <t>10.77020820601579</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.0014526848676795</t>
+          <t>1.9436161385808894</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.878239831267251</t>
+          <t>6.446747524345021</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.8566324046023404</t>
+          <t>1.4812344024448405</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9.045829942221769</t>
+          <t>8.548627021991578</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6.322422915549722</t>
+          <t>5.883739351590575</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.53774687038907</t>
+          <t>4.733804726662532</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.65021940143634</t>
+          <t>7.940115468734638</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.275553350822473</t>
+          <t>4.0275482685158925</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.034682028803835</t>
+          <t>1.057076985958365</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.083417780291118</t>
+          <t>6.121311684243718</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.6286967224106892</t>
+          <t>1.646948633257536</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.680102282956146</t>
+          <t>3.2974398465700556</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.439528554345751</t>
+          <t>4.62498467374853</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10.409491767918574</t>
+          <t>10.270649215942775</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6.910114073114488</t>
+          <t>7.056112711267345</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.8821730321244203</t>
+          <t>3.7674583264236645</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.744519463485565</t>
+          <t>1.846563586895664</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.093509860898287</t>
+          <t>5.98791648785982</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12.89608604670573</t>
+          <t>13.33454837764203</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.9931981715190246</t>
+          <t>2.102264387794558</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.3874810838686455</t>
+          <t>5.373745799717781</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3.762401540016601</t>
+          <t>3.9331089352926814</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.487322721595731</t>
+          <t>4.735790517442211</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.904251551088738</t>
+          <t>10.905083784457336</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3.71437534845908</t>
+          <t>4.224085265782004</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.5689681986882604</t>
+          <t>1.5941958216236358</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.8835476532058593</t>
+          <t>3.8582543803639955</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19.769836383544323</t>
+          <t>20.183131593989238</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15.698106640163424</t>
+          <t>16.7361406519366</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.23253730593683</t>
+          <t>4.209236597147822</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.135094349101541</t>
+          <t>4.043133674665377</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.406934516739013</t>
+          <t>5.2744189091902225</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.181560630385394</t>
+          <t>4.159803195494077</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5.2358390335433</t>
+          <t>5.081279659511366</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6.80897642298328</t>
+          <t>6.105435629983042</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5.452694200861386</t>
+          <t>5.265024340549225</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3.73785141362323</t>
+          <t>3.8584742389077356</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6.019173428656923</t>
+          <t>5.816536158485467</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>7.258008028512196</t>
+          <t>6.438632356338654</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.995027748098905</t>
+          <t>4.91013918804361</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.5696566590052267</t>
+          <t>0.3823555783665645</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10.974275173360091</t>
+          <t>11.00671732931579</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.7373113148432</t>
+          <t>4.724971371128469</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3.103381051531642</t>
+          <t>3.3267279851573472</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>14.907312384692524</t>
+          <t>14.582615788593614</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.646115826697297</t>
+          <t>7.2074459858020035</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4.354663764685473</t>
+          <t>3.987225432010584</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.9225417513835033</t>
+          <t>1.8715331106811814</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.4075074166159336</t>
+          <t>0.41006106261296704</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.074074054257759</t>
+          <t>2.1134618317034324</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.0951541349965912</t>
+          <t>1.1637584361929352</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.356151250160252</t>
+          <t>4.273655406940542</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2.6883211014767916</t>
+          <t>2.54694185254745</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20.999719416516054</t>
+          <t>20.79540373807589</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.7437140779538698</t>
+          <t>1.7649304822825407</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.237627438048188</t>
+          <t>10.909182199510326</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5.003946508528087</t>
+          <t>5.0184165247225465</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>19.81834015555607</t>
+          <t>20.770251757696677</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.6660038368045056</t>
+          <t>2.631716901415027</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4.75799919083927</t>
+          <t>5.038437158956202</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>15.25308862943588</t>
+          <t>13.39169307044152</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1.7389009436870586</t>
+          <t>1.693112981690161</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.34281189071182155</t>
+          <t>0.27103930228763695</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1.626747254659131</t>
+          <t>1.6080360299086003</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>3.771924136812275</t>
+          <t>3.881494363024722</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6.9010895185729035</t>
+          <t>6.746909173979117</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1.4664058806665992</t>
+          <t>1.3688619479542474</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.2610258725150911</t>
+          <t>0.2597371646463313</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>3.4455165034502855</t>
+          <t>3.291386803864336</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2.2721672936812283</t>
+          <t>2.178854658996549</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.54426525827623</t>
+          <t>1.5011711939700034</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.4307382926147074</t>
+          <t>1.348498530131189</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1.6748544391544107</t>
+          <t>1.5946255641519465</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3.5522428347721497</t>
+          <t>3.802096685352211</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.6145542211542043</t>
+          <t>2.7294066999974573</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1.9253191404361927</t>
+          <t>1.9631134912983494</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.003404882923103</t>
+          <t>2.041427081834195</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>16.68998339141745</t>
+          <t>15.605223720903039</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2.420643162171423</t>
+          <t>2.4929233969313813</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>9.120672374359621</t>
+          <t>10.472427296448066</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7.997720155403101</t>
+          <t>7.983781354105177</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>11.86739558655097</t>
+          <t>11.04946658485552</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>12.25936058126739</t>
+          <t>11.6682784237647</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.6875550434723334</t>
+          <t>2.7701506341537043</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4.09075781100627</t>
+          <t>4.199510984798888</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.9750119691038064</t>
+          <t>0.7845459579504102</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1.8851279223383846</t>
+          <t>1.8790564119467172</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2.5534930050244</t>
+          <t>1.997477213295575</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.3344215141407467</t>
+          <t>0.35169694648809013</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1.9696996170862588</t>
+          <t>1.3901707743130478</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.2689863036621896</t>
+          <t>0.2763556453369372</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.3413412015718844</t>
+          <t>0.3594627758224842</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.9127856184993152</t>
+          <t>0.9644664829408622</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.2661189124090573</t>
+          <t>1.3257471893775845</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.28783024347411257</t>
+          <t>0.29976631214742</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.4177949823943765</t>
+          <t>1.3368107998542242</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>9.723094684700067</t>
+          <t>9.422258795321191</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>69.87267364289399</t>
+          <t>68.41057251449232</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>12.91120286611158</t>
+          <t>13.528928568701819</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>17.11125813351445</t>
+          <t>16.261087209603293</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>90.74798771199073</t>
+          <t>90.88736004056815</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.594058754245476</t>
+          <t>5.494731875911529</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0.7791069319795075</t>
+          <t>0.7167694602299738</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.9657423159148039</t>
+          <t>0.9277362261075695</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2.7454924862703427</t>
+          <t>2.7168135117211936</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>55.03254211916122</t>
+          <t>56.57631378646745</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.905981898975371</t>
+          <t>3.9109581273138696</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>18.32341326986705</t>
+          <t>18.95130385418102</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20.5584071071737</t>
+          <t>20.36475538403137</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.6799964513565673</t>
+          <t>0.790303805379419</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2.9185105362217283</t>
+          <t>2.7341948532785674</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.3967586031608343</t>
+          <t>3.193238201663818</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>3.45255922796861</t>
+          <t>3.3226808377915393</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.643002965144069</t>
+          <t>6.600464299154262</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2.940850170116663</t>
+          <t>2.5823793475340975</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.302590230643546</t>
+          <t>7.563651281401206</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>58.93309982587904</t>
+          <t>56.06335663576398</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>7.652360046369493</t>
+          <t>7.493480722310937</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.639310433505088</t>
+          <t>4.665409764655038</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>6.874188909206063</t>
+          <t>7.27455146609668</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>14.026662651902086</t>
+          <t>13.989112385832605</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>79.80985692137874</t>
+          <t>79.37980440628567</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.370471224462975</t>
+          <t>12.351699819684047</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>9.40432106503125</t>
+          <t>9.441713703653079</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.323806460312986</t>
+          <t>1.271842190795139</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>7.657800714003081</t>
+          <t>7.867856932263585</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2.2709424494410406</t>
+          <t>2.3000652730717484</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>43.84025309582759</t>
+          <t>44.08976579666836</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.48155314013561445</t>
+          <t>0.45719572198636393</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>10.90955882965124</t>
+          <t>10.072217046945735</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>5.951532380786212</t>
+          <t>5.871808504264908</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>6.800480235863873</t>
+          <t>7.295696464584026</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>12.549772509322372</t>
+          <t>13.21967917628702</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>37.66770361978604</t>
+          <t>38.73843436373674</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>6.600515424656862</t>
+          <t>6.785314304133419</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.533217340838095</t>
+          <t>4.676475017951436</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>6.595005788973099</t>
+          <t>7.381496065748709</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>8.900099869101641</t>
+          <t>8.4172333341793</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>1.8905265946588878</t>
+          <t>2.01928877692962</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>1.7009165861205</t>
+          <t>1.8232675119921165</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1.3527451734538403</t>
+          <t>1.3258551990165905</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>3.0472027923262495</t>
+          <t>3.027338627344232</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>4.914675764301016</t>
+          <t>4.187207021857878</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>14.09932577989589</t>
+          <t>14.88979892747012</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>10.384239238315516</t>
+          <t>10.757092689556693</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>7.884699941848781</t>
+          <t>7.730366228530272</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>4.077909553977241</t>
+          <t>4.27753708689226</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.5620187930089315</t>
+          <t>2.292367904836176</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.815469096995386</t>
+          <t>2.9026092706660904</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.544976359711932</t>
+          <t>2.5778830741057184</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2.1883429278697886</t>
+          <t>2.1583097329992693</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>3.8344600828996613</t>
+          <t>3.827810709789974</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>61.954918242042964</t>
+          <t>63.32151495965024</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>9.04813010939371</t>
+          <t>8.721206634387585</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.133629820345758</t>
+          <t>5.106760855733459</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.311965175196768</t>
+          <t>6.3034485578175605</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.63423667815604</t>
+          <t>2.2898346271860213</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.53535234265245</t>
+          <t>0.8509043556650404</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0408539720695054</t>
+          <t>1.1406434434506174</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.8509131546954856</t>
+          <t>3.9193830948577286</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.290185032381231</t>
+          <t>3.605623925768521</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.050299810830412</t>
+          <t>4.942710365200972</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.7113917697967995</t>
+          <t>1.710213706139319</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.7396817278381107</t>
+          <t>3.002342387940007</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.77020820601579</t>
+          <t>10.80716535705717</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.9436161385808894</t>
+          <t>1.9636098969079292</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.446747524345021</t>
+          <t>6.422778228607779</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.4812344024448405</t>
+          <t>1.2873746001238011</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23.031295226668618</t>
+          <t>25.23936748037964</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.548627021991578</t>
+          <t>4.5283260867300825</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.883739351590575</t>
+          <t>5.898390779319075</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.733804726662532</t>
+          <t>4.7377401587601735</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.940115468734638</t>
+          <t>6.403559714390065</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.0275482685158925</t>
+          <t>3.9993274178410205</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.057076985958365</t>
+          <t>1.075278946048834</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.121311684243718</t>
+          <t>5.079492758476391</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.646948633257536</t>
+          <t>1.6357838934475382</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.2974398465700556</t>
+          <t>3.3154010358208756</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.5483641720635385</t>
+          <t>0.6009373209614203</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.62498467374853</t>
+          <t>4.6067889422623995</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.9497946070644906</t>
+          <t>1.0408539720695054</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10.270649215942775</t>
+          <t>10.254860336918142</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.056112711267345</t>
+          <t>7.013988726245884</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.7674583264236645</t>
+          <t>3.763595432749121</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.846563586895664</t>
+          <t>1.8995892141289812</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.9497946070644906</t>
+          <t>1.0408539720695054</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.219045183514332</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.98791648785982</t>
+          <t>5.998875707712465</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.33454837764203</t>
+          <t>13.34544908976272</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.102264387794558</t>
+          <t>2.09547389220487</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.9497946070644906</t>
+          <t>1.0408539720695054</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.109522591757166</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.373745799717781</t>
+          <t>5.353240576361516</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3.9331089352926814</t>
+          <t>3.9151307467612106</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.735790517442211</t>
+          <t>4.745322983057517</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.905083784457336</t>
+          <t>10.853545010989887</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.224085265782004</t>
+          <t>4.525259970323061</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.5941958216236358</t>
+          <t>1.5471527008601313</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.8582543803639955</t>
+          <t>3.8568586918725742</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.183131593989238</t>
+          <t>20.106848935985056</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>16.7361406519366</t>
+          <t>16.70593453430589</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.209236597147822</t>
+          <t>4.240025259904726</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.043133674665377</t>
+          <t>4.057366480645557</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.2744189091902225</t>
+          <t>5.289165677193682</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.159803195494077</t>
+          <t>4.317723948459807</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5.081279659511366</t>
+          <t>5.092632848742794</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6.105435629983042</t>
+          <t>6.1045025423440435</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5.265024340549225</t>
+          <t>5.27391962299201</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3.8584742389077356</t>
+          <t>3.871483908100057</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5.816536158485467</t>
+          <t>5.826855101739504</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6.438632356338654</t>
+          <t>6.434572116543064</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.91013918804361</t>
+          <t>5.090705543188559</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.3823555783665645</t>
+          <t>0.3907698589301063</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11.00671732931579</t>
+          <t>10.65405371412179</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.724971371128469</t>
+          <t>4.706748311059482</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3.3267279851573472</t>
+          <t>3.369981125231632</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>14.582615788593614</t>
+          <t>14.55770449228303</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.2074459858020035</t>
+          <t>7.591381556604848</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.987225432010584</t>
+          <t>3.9938398055501105</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.8715331106811814</t>
+          <t>1.865205404095235</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.41006106261296704</t>
+          <t>0.4094741841668128</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.1134618317034324</t>
+          <t>2.0967726545419723</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.1637584361929352</t>
+          <t>1.1619195325231022</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.273655406940542</t>
+          <t>4.271870949755012</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2.54694185254745</t>
+          <t>2.537679162941929</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20.79540373807589</t>
+          <t>4.061664223324982</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.7649304822825407</t>
+          <t>1.7263891097903787</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10.909182199510326</t>
+          <t>11.72205959142498</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5.0184165247225465</t>
+          <t>2.2894298861818627</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20.770251757696677</t>
+          <t>4.417216300121261</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.631716901415027</t>
+          <t>1.02311457587186</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.038437158956202</t>
+          <t>1.666179903653175</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>13.39169307044152</t>
+          <t>13.46711058678533</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1.693112981690161</t>
+          <t>1.702620618192863</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1.6450925161906156</t>
+          <t>1.8028119628842605</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.27103930228763695</t>
+          <t>0.6417733367788604</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1.6080360299086003</t>
+          <t>1.6087972667815311</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>3.881494363024722</t>
+          <t>3.8585139043854424</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6.746909173979117</t>
+          <t>6.722389146749922</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1.3688619479542474</t>
+          <t>1.3685276335420795</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.2597371646463313</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>3.291386803864336</t>
+          <t>3.283388614725382</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2.178854658996549</t>
+          <t>2.1716975202363002</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.5011711939700034</t>
+          <t>1.6450925161906156</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.348498530131189</t>
+          <t>1.345896568004517</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1.5946255641519465</t>
+          <t>1.5911403726015974</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3.802096685352211</t>
+          <t>3.7869757366020487</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.7294066999974573</t>
+          <t>3.1980268189557073</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1.9631134912983494</t>
+          <t>1.9418391658543042</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.041427081834195</t>
+          <t>2.0295968474360158</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>15.605223720903039</t>
+          <t>8.771631716820409</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2.4929233969313813</t>
+          <t>2.4968155834561685</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10.472427296448066</t>
+          <t>10.506442875864757</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7.983781354105177</t>
+          <t>7.917247916334581</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>11.04946658485552</t>
+          <t>9.30045711428055</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>11.6682784237647</t>
+          <t>12.045081018239562</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.7701506341537043</t>
+          <t>4.952928154885152</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4.199510984798888</t>
+          <t>4.175098205808009</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.7845459579504102</t>
+          <t>0.7853750537906965</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1.8790564119467172</t>
+          <t>1.8697348939400107</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1.997477213295575</t>
+          <t>1.8510659297872039</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.35169694648809013</t>
+          <t>0.3506627107087894</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1.3901707743130478</t>
+          <t>1.3962938354731715</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.2763556453369372</t>
+          <t>0.27565202861934174</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.3594627758224842</t>
+          <t>0.3584964751461577</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.9644664829408622</t>
+          <t>0.9622408297238838</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.3257471893775845</t>
+          <t>1.3147456909817492</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.29976631214742</t>
+          <t>0.2984030756340863</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.3368107998542242</t>
+          <t>1.3345206379312444</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>9.422258795321191</t>
+          <t>2.603889535896377</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>68.41057251449232</t>
+          <t>68.384975027314</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>13.528928568701819</t>
+          <t>13.46649034981179</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>16.261087209603293</t>
+          <t>16.272873307687146</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>90.88736004056815</t>
+          <t>90.8598354587483</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.494731875911529</t>
+          <t>5.5064559757110665</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0.7167694602299738</t>
+          <t>0.7130846624900848</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.9277362261075695</t>
+          <t>0.9229022955793283</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2.7168135117211936</t>
+          <t>2.701136743557967</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>56.57631378646745</t>
+          <t>56.53172769036435</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.9109581273138696</t>
+          <t>3.559163934909575</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>18.95130385418102</t>
+          <t>18.90467223905086</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20.36475538403137</t>
+          <t>20.38595159587068</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.790303805379419</t>
+          <t>0.7011195136179875</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2.7341948532785674</t>
+          <t>2.723204167883055</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.193238201663818</t>
+          <t>3.194061935352062</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>3.3226808377915393</t>
+          <t>2.8780204745867977</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.600464299154262</t>
+          <t>6.583058890084688</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2.5823793475340975</t>
+          <t>2.2413878665082</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.563651281401206</t>
+          <t>7.568862629096073</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>56.06335663576398</t>
+          <t>55.93280572880043</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>7.493480722310937</t>
+          <t>7.518236151299324</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.665409764655038</t>
+          <t>4.668714147804753</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>7.27455146609668</t>
+          <t>1.9121920057156248</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>13.989112385832605</t>
+          <t>13.943878674262644</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>79.37980440628567</t>
+          <t>79.3991917326151</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.351699819684047</t>
+          <t>9.193224297153941</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>9.441713703653079</t>
+          <t>9.436249469861622</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.271842190795139</t>
+          <t>1.286914627431307</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>7.867856932263585</t>
+          <t>7.864796419950402</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2.3000652730717484</t>
+          <t>1.6552346410856202</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>44.08976579666836</t>
+          <t>44.06209112105566</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.45719572198636393</t>
+          <t>0.455606340631742</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>10.072217046945735</t>
+          <t>10.49242316137087</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>5.871808504264908</t>
+          <t>5.7971726291867025</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>7.295696464584026</t>
+          <t>7.288484078107734</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>13.21967917628702</t>
+          <t>2.683232966951021</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>38.73843436373674</t>
+          <t>38.6925361595361</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>6.785314304133419</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.676475017951436</t>
+          <t>4.6909160491912365</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>7.381496065748709</t>
+          <t>6.300848933217064</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>8.4172333341793</t>
+          <t>8.390385893517223</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2.01928877692962</t>
+          <t>2.0130310073965876</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>1.8232675119921165</t>
+          <t>1.8168332826034466</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1.3258551990165905</t>
+          <t>1.32397634149733</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>3.027338627344232</t>
+          <t>3.3142357491424725</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>4.187207021857878</t>
+          <t>4.127900841355631</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>14.88979892747012</t>
+          <t>14.90771088371332</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>10.757092689556693</t>
+          <t>10.294606217627724</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>7.730366228530272</t>
+          <t>7.784124963985917</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>4.27753708689226</t>
+          <t>4.263045639939591</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.292367904836176</t>
+          <t>2.3470633337378586</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.9026092706660904</t>
+          <t>2.9033869146013274</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5778830741057184</t>
+          <t>2.5622470197007785</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2.1583097329992693</t>
+          <t>2.15946438831293</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>3.827810709789974</t>
+          <t>3.8428264745136733</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>63.32151495965024</t>
+          <t>63.15154862340032</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>8.721206634387585</t>
+          <t>8.78377881722487</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.106760855733459</t>
+          <t>1.4433756729740643</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.3034485578175605</t>
+          <t>3.8315856827956516</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.2898346271860213</t>
+          <t>0.37049174364188264</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.8509043556650404</t>
+          <t>0.38021448115020573</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.9193830948577286</t>
+          <t>0.3147744932624183</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.942710365200972</t>
+          <t>0.5272519943537441</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.710213706139319</t>
+          <t>0.5003903979900011</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.80716535705717</t>
+          <t>2.8043741644866276</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.9636098969079292</t>
+          <t>0.34695132402316853</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.422778228607779</t>
+          <t>0.7604289623004115</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.2873746001238011</t>
+          <t>0.6009373209614203</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.5283260867300825</t>
+          <t>0.5067807888762054</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.898390779319075</t>
+          <t>5.833333333333332</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.7377401587601735</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.403559714390065</t>
+          <t>0.40930011810409317</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.9993274178410205</t>
+          <t>0.3054626683083246</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.075278946048834</t>
+          <t>0.23130088268211232</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.079492758476391</t>
+          <t>0.692127162153197</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.6357838934475382</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.3154010358208756</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.6067889422623995</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10.254860336918142</t>
+          <t>4.717602726921022</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.013988726245884</t>
+          <t>1.2014798145840209</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.763595432749121</t>
+          <t>0.8344960168122482</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.998875707712465</t>
+          <t>4.166424863988899</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.34544908976272</t>
+          <t>7.005465571860014</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.09547389220487</t>
+          <t>1.5817559830612322</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.353240576361516</t>
+          <t>2.1794089044126794</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3.9151307467612106</t>
+          <t>1.3171015982511909</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.745322983057517</t>
+          <t>4.044607433712034</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.853545010989887</t>
+          <t>2.1266332316247567</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.525259970323061</t>
+          <t>6.921858845594372</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.5471527008601313</t>
+          <t>1.3698408639190554</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.8568586918725742</t>
+          <t>1.946076891031236</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.106848935985056</t>
+          <t>10.427301145948132</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>16.70593453430589</t>
+          <t>15.408265119679609</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.240025259904726</t>
+          <t>13.993169421959792</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.057366480645557</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.289165677193682</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4.317723948459807</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5.092632848742794</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6.1045025423440435</t>
+          <t>0.3194783495112404</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5.27391962299201</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3.871483908100057</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5.826855101739504</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6.434572116543064</t>
+          <t>0.3527209445716921</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.090705543188559</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.3907698589301063</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10.65405371412179</t>
+          <t>1.207231315369677</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.706748311059482</t>
+          <t>0.4306794675390997</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3.369981125231632</t>
+          <t>11.000438787530385</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>14.55770449228303</t>
+          <t>4.548537523772909</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.591381556604848</t>
+          <t>1.619106178774786</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.9938398055501105</t>
+          <t>1.733403185876587</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.865205404095235</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.4094741841668128</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.0967726545419723</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.1619195325231022</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.271870949755012</t>
+          <t>1.284026265426592</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2.537679162941929</t>
+          <t>0.23433266072009618</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4.061664223324982</t>
+          <t>3.41039337680412</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.7263891097903787</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>11.72205959142498</t>
+          <t>6.658766671177399</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2.2894298861818627</t>
+          <t>0.2537641061248578</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4.417216300121261</t>
+          <t>3.209674629674881</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.02311457587186</t>
+          <t>0.7908779915306161</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1.666179903653175</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>13.46711058678533</t>
+          <t>1.5033780612921988</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1.702620618192863</t>
+          <t>5.615202818334916</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.6417733367788604</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1.6087972667815311</t>
+          <t>1.25</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>3.8585139043854424</t>
+          <t>0.3771788599082533</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6.722389146749922</t>
+          <t>0.83642401962363</t>
         </is>
       </c>
     </row>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1.3685276335420795</t>
+          <t>0.34695132402316853</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>3.283388614725382</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2.1716975202363002</t>
+          <t>0.6009373209614203</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.345896568004517</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1.5911403726015974</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3.7869757366020487</t>
+          <t>0.26303249048250205</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.1980268189557073</t>
+          <t>1.4433756729740643</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1.9418391658543042</t>
+          <t>0.24056261216234406</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.0295968474360158</t>
+          <t>0.39648497749678946</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>8.771631716820409</t>
+          <t>0.9597738102390321</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2.4968155834561685</t>
+          <t>0.4678396196778478</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10.506442875864757</t>
+          <t>9.62612522673948</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7.917247916334581</t>
+          <t>6.6768458343079296</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>9.30045711428055</t>
+          <t>0.8033668676971861</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>12.045081018239562</t>
+          <t>1.477458277655874</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4.952928154885152</t>
+          <t>1.5081722901323624</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4.175098205808009</t>
+          <t>0.6252684993337903</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.7853750537906965</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1.8697348939400107</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1.8510659297872039</t>
+          <t>0.42873867904681484</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.3506627107087894</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1.3962938354731715</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.27565202861934174</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.3584964751461577</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.9622408297238838</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1.3147456909817492</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.2984030756340863</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1.3345206379312444</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2.603889535896377</t>
+          <t>0.39918667479354514</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>68.384975027314</t>
+          <t>23.07484559429439</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>13.46649034981179</t>
+          <t>0.5810942076799046</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>16.272873307687146</t>
+          <t>0.917241423058644</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>90.8598354587483</t>
+          <t>73.25793524352409</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.5064559757110665</t>
+          <t>5.192621977965413</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0.7130846624900848</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.9229022955793283</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2.701136743557967</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>56.53172769036435</t>
+          <t>12.47108892582653</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.559163934909575</t>
+          <t>2.8846725909179654</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>18.90467223905086</t>
+          <t>1.061820575124136</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20.38595159587068</t>
+          <t>1.2302546534920695</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.7011195136179875</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2.723204167883055</t>
+          <t>0.4309693399108413</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>3.194061935352062</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2.8780204745867977</t>
+          <t>0.283509554710371</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.583058890084688</t>
+          <t>7.042407236577326</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2.2413878665082</t>
+          <t>0.438276820359319</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.568862629096073</t>
+          <t>21.82212294095504</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>55.93280572880043</t>
+          <t>11.965758906772441</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>7.518236151299324</t>
+          <t>0.37420850780809073</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4.668714147804753</t>
+          <t>1.6402745764253097</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>1.9121920057156248</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>13.943878674262644</t>
+          <t>19.149144591923193</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>79.3991917326151</t>
+          <t>41.23068539651286</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>9.193224297153941</t>
+          <t>9.569294067353205</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>9.436249469861622</t>
+          <t>2.7328637071264397</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.286914627431307</t>
+          <t>4.302266142481382</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>7.864796419950402</t>
+          <t>8.33269484608762</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>1.6552346410856202</t>
+          <t>0.20786901634898713</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>44.06209112105566</t>
+          <t>6.250569009745783</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.455606340631742</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>10.49242316137087</t>
+          <t>0.8965952414479735</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>5.7971726291867025</t>
+          <t>1.2715819235853518</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>7.288484078107734</t>
+          <t>1.8436698954755606</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2.683232966951021</t>
+          <t>0.21366096239331467</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>38.6925361595361</t>
+          <t>4.566547055989128</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.6909160491912365</t>
+          <t>0.7713937200103896</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>6.300848933217064</t>
+          <t>1.5160197967508124</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>8.390385893517223</t>
+          <t>1.4112487804235425</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2.0130310073965876</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>1.8168332826034466</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1.32397634149733</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>3.3142357491424725</t>
+          <t>0.3202892787021886</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>4.127900841355631</t>
+          <t>0.28987016646647434</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>14.90771088371332</t>
+          <t>0.6936518776479348</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>10.294606217627724</t>
+          <t>3.7687579112523557</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>7.784124963985917</t>
+          <t>15.673794701454877</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>4.263045639939591</t>
+          <t>0.23216137540579487</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.3470633337378586</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.9033869146013274</t>
+          <t>8.229541321019411</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5622470197007785</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2.15946438831293</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>3.8428264745136733</t>
+          <t>11.4095166975838</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>63.15154862340032</t>
+          <t>17.52191206655069</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>8.78377881722487</t>
+          <t>25.09186239626196</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.4433756729740643</t>
+          <t>5.106760855733459</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.8315856827956516</t>
+          <t>6.3034485578175605</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.37049174364188264</t>
+          <t>2.2898346271860213</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.38021448115020573</t>
+          <t>0.8509043556650404</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3147744932624183</t>
+          <t>3.9193830948577286</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.5272519943537441</t>
+          <t>4.942710365200972</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.5003903979900011</t>
+          <t>1.710213706139319</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.8043741644866276</t>
+          <t>10.80716535705717</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.34695132402316853</t>
+          <t>1.9636098969079292</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.7604289623004115</t>
+          <t>6.422778228607779</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.6009373209614203</t>
+          <t>1.2873746001238011</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.5067807888762054</t>
+          <t>4.5283260867300825</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.833333333333332</t>
+          <t>5.898390779319075</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>4.7377401587601735</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.40930011810409317</t>
+          <t>6.403559714390065</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.3054626683083246</t>
+          <t>3.9993274178410205</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.23130088268211232</t>
+          <t>1.075278946048834</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.692127162153197</t>
+          <t>5.079492758476391</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.6357838934475382</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>3.3154010358208756</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>4.6067889422623995</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.717602726921022</t>
+          <t>10.254860336918142</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.2014798145840209</t>
+          <t>7.013988726245884</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.8344960168122482</t>
+          <t>3.763595432749121</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.166424863988899</t>
+          <t>5.998875707712465</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.005465571860014</t>
+          <t>13.34544908976272</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.5817559830612322</t>
+          <t>2.09547389220487</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.1794089044126794</t>
+          <t>5.353240576361516</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.3171015982511909</t>
+          <t>3.9151307467612106</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.044607433712034</t>
+          <t>4.745322983057517</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.1266332316247567</t>
+          <t>10.853545010989887</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6.921858845594372</t>
+          <t>4.525259970323061</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.3698408639190554</t>
+          <t>1.5471527008601313</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.946076891031236</t>
+          <t>3.8568586918725742</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10.427301145948132</t>
+          <t>20.106848935985056</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15.408265119679609</t>
+          <t>16.70593453430589</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13.993169421959792</t>
+          <t>4.240025259904726</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>4.057366480645557</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>5.289165677193682</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>4.317723948459807</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>5.092632848742794</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.3194783495112404</t>
+          <t>6.1045025423440435</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>5.27391962299201</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.871483908100057</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>5.826855101739504</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.3527209445716921</t>
+          <t>6.434572116543064</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>5.090705543188559</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.207231315369677</t>
+          <t>10.65405371412179</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4306794675390997</t>
+          <t>4.706748311059482</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>11.000438787530385</t>
+          <t>3.369981125231632</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4.548537523772909</t>
+          <t>14.55770449228303</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.619106178774786</t>
+          <t>7.591381556604848</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.733403185876587</t>
+          <t>3.9938398055501105</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.865205404095235</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4094741841668128</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.0967726545419723</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.1619195325231022</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.284026265426592</t>
+          <t>4.271870949755012</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.23433266072009618</t>
+          <t>2.537679162941929</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3.41039337680412</t>
+          <t>4.061664223324982</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.7263891097903787</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.658766671177399</t>
+          <t>11.72205959142498</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.2537641061248578</t>
+          <t>2.2894298861818627</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3.209674629674881</t>
+          <t>4.417216300121261</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.7908779915306161</t>
+          <t>1.02311457587186</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.666179903653175</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.5033780612921988</t>
+          <t>13.46711058678533</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5.615202818334916</t>
+          <t>1.702620618192863</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6417733367788604</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.6087972667815311</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.3771788599082533</t>
+          <t>3.8585139043854424</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.83642401962363</t>
+          <t>6.722389146749922</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.34695132402316853</t>
+          <t>2.337713137615461</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.283388614725382</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.6009373209614203</t>
+          <t>2.1716975202363002</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.345896568004517</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.5911403726015974</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.26303249048250205</t>
+          <t>3.7869757366020487</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1.4433756729740643</t>
+          <t>3.1980268189557073</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.24056261216234406</t>
+          <t>1.9418391658543042</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.39648497749678946</t>
+          <t>2.0295968474360158</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.9597738102390321</t>
+          <t>8.771631716820409</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.4678396196778478</t>
+          <t>2.4968155834561685</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>9.62612522673948</t>
+          <t>10.506442875864757</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.6768458343079296</t>
+          <t>7.917247916334581</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.8033668676971861</t>
+          <t>9.30045711428055</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.477458277655874</t>
+          <t>12.045081018239562</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1.5081722901323624</t>
+          <t>4.952928154885152</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.6252684993337903</t>
+          <t>4.175098205808009</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.7853750537906965</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.8697348939400107</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.42873867904681484</t>
+          <t>1.8510659297872039</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3506627107087894</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.3962938354731715</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.27565202861934174</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3584964751461577</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.9622408297238838</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.3147456909817492</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2984030756340863</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.3345206379312444</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.39918667479354514</t>
+          <t>2.603889535896377</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>23.07484559429439</t>
+          <t>68.384975027314</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>0.5810942076799046</t>
+          <t>13.46649034981179</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.917241423058644</t>
+          <t>16.272873307687146</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>73.25793524352409</t>
+          <t>90.8598354587483</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.192621977965413</t>
+          <t>5.5064559757110665</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.7130846624900848</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.9229022955793283</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.701136743557967</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.47108892582653</t>
+          <t>13.241025122046523</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2.8846725909179654</t>
+          <t>3.559163934909575</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.061820575124136</t>
+          <t>18.90467223905086</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.2302546534920695</t>
+          <t>20.38595159587068</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.7011195136179875</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.4309693399108413</t>
+          <t>2.723204167883055</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.194061935352062</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.283509554710371</t>
+          <t>2.8780204745867977</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>7.042407236577326</t>
+          <t>7.5957414002642425</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.438276820359319</t>
+          <t>2.2413878665082</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>21.82212294095504</t>
+          <t>7.568862629096073</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>11.965758906772441</t>
+          <t>55.93280572880043</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.37420850780809073</t>
+          <t>7.518236151299324</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>1.6402745764253097</t>
+          <t>4.668714147804753</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.9121920057156248</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>19.149144591923193</t>
+          <t>13.943878674262644</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>41.23068539651286</t>
+          <t>79.3991917326151</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>9.569294067353205</t>
+          <t>9.193224297153941</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2.7328637071264397</t>
+          <t>9.436249469861622</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>4.302266142481382</t>
+          <t>1.286914627431307</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>8.33269484608762</t>
+          <t>7.864796419950402</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.20786901634898713</t>
+          <t>1.6552346410856202</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>6.250569009745783</t>
+          <t>44.06209112105566</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.455606340631742</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.8965952414479735</t>
+          <t>10.49242316137087</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>1.2715819235853518</t>
+          <t>5.7971726291867025</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>1.8436698954755606</t>
+          <t>7.288484078107734</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.21366096239331467</t>
+          <t>2.683232966951021</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>4.566547055989128</t>
+          <t>38.6925361595361</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.7713937200103896</t>
+          <t>4.6909160491912365</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>1.5160197967508124</t>
+          <t>6.300848933217064</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.4112487804235425</t>
+          <t>8.390385893517223</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.0130310073965876</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.8168332826034466</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.32397634149733</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.3202892787021886</t>
+          <t>3.3142357491424725</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.28987016646647434</t>
+          <t>4.127900841355631</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.6936518776479348</t>
+          <t>14.90771088371332</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>3.7687579112523557</t>
+          <t>10.294606217627724</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>15.673794701454877</t>
+          <t>7.784124963985917</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.23216137540579487</t>
+          <t>4.263045639939591</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.3470633337378586</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>8.229541321019411</t>
+          <t>2.9033869146013274</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.5622470197007785</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.15946438831293</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>11.4095166975838</t>
+          <t>3.8428264745136733</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>17.52191206655069</t>
+          <t>63.15154862340032</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>25.09186239626196</t>
+          <t>8.78377881722487</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.13035243497669</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.687166908878922</t>
+          <t>4.342045710791501</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6763382793410448</t>
+          <t>0.3953354735858779</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.7273981480951476</t>
+          <t>0.37972838858737</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.1607258857190328</t>
+          <t>0.6338296412257199</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.4497687650439972</t>
+          <t>0.24521502121384797</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.479457202414675</t>
+          <t>0.8118512094156047</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.9195049003918658</t>
+          <t>0.4991767897119047</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.5723323881399061</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.9636363836562498</t>
+          <t>0.48046017102042543</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.6998326178037755</t>
+          <t>0.36091376273641906</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.4464161067266033</t>
+          <t>0.828721712832946</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.423608940401042</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.9456853491746132</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.040713360595911</t>
+          <t>4.999084995730655</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.324169321382072</t>
+          <t>1.3812978562310492</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.5630522834301912</t>
+          <t>0.9737779346916476</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.812687726030049</t>
+          <t>4.576340802425589</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.4671557950874483</t>
+          <t>2.411137889872512</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.064491929470826</t>
+          <t>2.4868311017164832</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.757458938528724</t>
+          <t>7.520674054328197</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.0255043311146177</t>
+          <t>2.2208254241038006</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15.98991650341617</t>
+          <t>11.922740160760736</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.474789851488108</t>
+          <t>16.52125128067391</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11.10260636679942</t>
+          <t>13.939410246169388</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.2467152746633819</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.36616293015606644</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.2673594280547849</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.3512138775199222</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.8041805562575471</t>
+          <t>0.3878668903912969</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.3745990584132196</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.22924405978254223</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.4331538676973064</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.8832334829444907</t>
+          <t>0.4299441886243924</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.3423581159750052</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.550682610299318</t>
+          <t>1.413951141061644</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.9784306532026353</t>
+          <t>0.5225681382126862</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7.8705396123937135</t>
+          <t>10.075412458458345</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7.67259754386958</t>
+          <t>5.092253580364981</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.4363377027486233</t>
+          <t>0.23652425821716255</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.3621660072766329</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2.185739268533088</t>
+          <t>1.4377630006974043</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.570410048452261</t>
+          <t>0.3067060356747502</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4.51471423833809</t>
+          <t>3.6970792968836914</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.3753303867223179</t>
+          <t>0.20083125009975278</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10.082130485281871</t>
+          <t>7.668569463790311</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.5184846252728982</t>
+          <t>0.28485488970007716</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4.60800512602901</t>
+          <t>3.694187189432139</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.20294887292889363</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3.2563889897573697</t>
+          <t>1.8082893378883762</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>4.057772379809442</t>
+          <t>5.1219867006205755</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.8438075495851147</t>
+          <t>0.4566464740200867</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.7469445579159992</t>
+          <t>0.9823201801210706</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.3862564811011311</t>
+          <t>0.23130088268211232</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.39540686349247156</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.5808333396296068</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.6358738213023891</t>
+          <t>0.3238865577238284</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2969663962880267</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.7957293638397427</t>
+          <t>0.4891345027892857</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.1608886148029627</t>
+          <t>1.1970754661452816</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.7739844184695102</t>
+          <t>0.4613680669038098</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>12.657290892932515</t>
+          <t>10.71777168709035</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>9.04579917265669</t>
+          <t>7.541977052152761</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.8889006654743001</t>
+          <t>1.001190568665706</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.290880752205205</t>
+          <t>0.9849721851039159</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.8105355051028598</t>
+          <t>1.8831840220330058</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.2262094060492763</t>
+          <t>0.7093081478178842</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.2082141241812305</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.7724559615456688</t>
+          <t>0.4832589025331533</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.8287301751596179</t>
+          <t>0.48694868758564613</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>35.09037587964151</t>
+          <t>25.54986538051179</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.472180751253519</t>
+          <t>0.6923774397133089</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2.1473907166201855</t>
+          <t>1.0636285448632121</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>79.23473227296435</t>
+          <t>73.95126253128637</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>6.645773008929873</t>
+          <t>5.721761286212494</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0.3332190687035447</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>16.08654859925314</t>
+          <t>13.928229664903663</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.9677372466116134</t>
+          <t>3.2801321746669823</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2.254240374970384</t>
+          <t>1.104858409808856</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2.896098981414223</t>
+          <t>1.45570369442252</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.8750731377407015</t>
+          <t>0.5121226742473157</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.2803396845646927</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.6304795994556969</t>
+          <t>0.34095116205005327</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>9.126195600115603</t>
+          <t>7.799577162910593</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.8943137479411818</t>
+          <t>0.548380312495463</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>17.500045059571995</t>
+          <t>20.951710305018132</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20.12823422293119</t>
+          <t>13.03909814425472</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5959099391754378</t>
+          <t>0.2578443263709956</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2.778459023786683</t>
+          <t>1.9112817559265243</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.2427627632524697</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>21.55760770297422</t>
+          <t>20.52247829191431</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>53.7949416742517</t>
+          <t>44.07029818486402</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>11.658684886290935</t>
+          <t>10.021335583598374</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>4.7515106649514545</t>
+          <t>3.116958502658347</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>3.0990526094544055</t>
+          <t>3.970854774127795</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>10.188187338372611</t>
+          <t>8.978613961864628</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.4563781145206107</t>
+          <t>0.258976741950957</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>12.39103246916242</t>
+          <t>7.415552913345212</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2.0295192869055074</t>
+          <t>1.070626853391384</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2.4046652098732744</t>
+          <t>1.5076420851176353</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>3.4067090557193715</t>
+          <t>2.199395756501703</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.4769185751491569</t>
+          <t>0.2482044371852905</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>9.652528583273355</t>
+          <t>5.576882766842663</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1.546580029501185</t>
+          <t>0.9236372922475216</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2.9763319915404813</t>
+          <t>1.897403895551504</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2.5725602644416954</t>
+          <t>1.508961320276801</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>0.3874158721189018</t>
+          <t>0.20245051461732713</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>0.3341889439279662</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.22783326035598894</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.7343951737968348</t>
+          <t>0.39819888247219903</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6789455150943496</t>
+          <t>0.34447478728723535</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1.844658373955503</t>
+          <t>0.8865254422510852</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>6.344429447475912</t>
+          <t>4.3882802625126365</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>15.083271283263501</t>
+          <t>15.929520204745108</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.6225005855869545</t>
+          <t>0.3039933650932868</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>0.21538254896119302</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>6.376912643056755</t>
+          <t>7.993784059209929</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.37834117088036473</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.361530496176804</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>8.959757520829507</t>
+          <t>10.795079637392085</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>29.68969956122453</t>
+          <t>20.79334522714615</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20.143508262641348</t>
+          <t>23.929752317313536</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.124441370296634</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.342045710791501</t>
+          <t>5.675788972523023</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3953354735858779</t>
+          <t>0.6732760002958607</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.37972838858737</t>
+          <t>0.7233373989994243</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.6338296412257199</t>
+          <t>1.154728682206246</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.24521502121384797</t>
+          <t>0.44743860006644415</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.8118512094156047</t>
+          <t>1.471880159463147</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.4991767897119047</t>
+          <t>0.9147042326284731</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.5686776564175712</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.48046017102042543</t>
+          <t>0.9578515317006229</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.36091376273641906</t>
+          <t>0.6958475423866107</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.828721712832946</t>
+          <t>1.43959343660655</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.940630444623042</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.999084995730655</t>
+          <t>7.02182006166832</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.3812978562310492</t>
+          <t>2.3140090106469433</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.9737779346916476</t>
+          <t>1.5569208938202115</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.576340802425589</t>
+          <t>5.802711268250739</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.411137889872512</t>
+          <t>3.4571811999921853</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.4868311017164832</t>
+          <t>4.047837462048418</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.520674054328197</t>
+          <t>7.758455806153715</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2.2208254241038006</t>
+          <t>3.0183454990473297</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11.922740160760736</t>
+          <t>15.95408800937209</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>16.52125128067391</t>
+          <t>19.45418431146278</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13.939410246169388</t>
+          <t>11.126550965973195</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.24477508018104926</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3633958283217983</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.26527351420922346</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.34854829339911103</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.3878668903912969</t>
+          <t>0.799110489599748</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3717748876275772</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.22742825614930617</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.42993767907758373</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.4299441886243924</t>
+          <t>0.8777383267343062</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3397529123862247</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.413951141061644</t>
+          <t>2.537855575218365</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5225681382126862</t>
+          <t>0.9731739727437042</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10.075412458458345</t>
+          <t>7.888229341763279</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.092253580364981</t>
+          <t>7.647073347372748</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.23652425821716255</t>
+          <t>0.43405372873140086</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.36008382201028205</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.4377630006974043</t>
+          <t>2.178296851294403</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.3067060356747502</t>
+          <t>0.5673814186742281</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3.6970792968836914</t>
+          <t>4.508596219157749</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.20083125009975278</t>
+          <t>0.37332065638138</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7.668569463790311</t>
+          <t>10.06154948022761</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.28485488970007716</t>
+          <t>0.5158354122136073</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3.694187189432139</t>
+          <t>4.600867175447419</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.8082893378883762</t>
+          <t>3.2400595612612646</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5.1219867006205755</t>
+          <t>4.066677632166805</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.4566464740200867</t>
+          <t>0.839377421658433</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.9823201801210706</t>
+          <t>1.7383950362093186</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.23130088268211232</t>
+          <t>0.3839877849516608</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.392809093067169</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.5779873703579028</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.3238865577238284</t>
+          <t>0.6321810568427588</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.29517036870115687</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.4891345027892857</t>
+          <t>0.7925065494497072</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1.1970754661452816</t>
+          <t>2.150010254123576</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.4613680669038098</t>
+          <t>0.7706236606071899</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10.71777168709035</t>
+          <t>12.643859477691539</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7.541977052152761</t>
+          <t>9.034980223330752</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.001190568665706</t>
+          <t>1.8786157630277232</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.9849721851039159</t>
+          <t>1.2822759515097457</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1.8831840220330058</t>
+          <t>2.8014584479562363</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.7093081478178842</t>
+          <t>1.2205362593098732</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.4832589025331533</t>
+          <t>0.7694569392266688</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.48694868758564613</t>
+          <t>0.8250187361271202</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>25.54986538051179</t>
+          <t>34.9997062552446</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>0.6923774397133089</t>
+          <t>1.46253048138868</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1.0636285448632121</t>
+          <t>2.1343133526326974</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>73.95126253128637</t>
+          <t>79.19189246592778</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.721761286212494</t>
+          <t>6.639752648318337</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3310603993055736</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>13.928229664903663</t>
+          <t>16.0725973125051</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.2801321746669823</t>
+          <t>3.9627019796096636</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.104858409808856</t>
+          <t>2.24029826333001</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.45570369442252</t>
+          <t>2.878846825163033</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.5121226742473157</t>
+          <t>0.8711209574782511</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.27832716171543437</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.34095116205005327</t>
+          <t>0.6271654514443719</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>7.799577162910593</t>
+          <t>9.11729640413187</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.548380312495463</t>
+          <t>0.8906706231432799</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20.951710305018132</t>
+          <t>17.531806014972908</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>13.03909814425472</t>
+          <t>20.05520571791057</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.2578443263709956</t>
+          <t>0.5915629962219479</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>1.9112817559265243</t>
+          <t>2.7701804175457543</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.24121088401802407</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20.52247829191431</t>
+          <t>21.556637448725862</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>44.07029818486402</t>
+          <t>53.709798710791695</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>10.021335583598374</t>
+          <t>11.647866205765629</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>3.116958502658347</t>
+          <t>4.735192052853999</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>3.970854774127795</t>
+          <t>3.1061074213233035</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>8.978613961864628</t>
+          <t>10.181046682367175</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.258976741950957</t>
+          <t>0.4541843818255549</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>7.415552913345212</t>
+          <t>12.33706606063009</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>1.070626853391384</t>
+          <t>2.0183783136395994</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>1.5076420851176353</t>
+          <t>2.3953757348375295</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2.199395756501703</t>
+          <t>3.3944970322471564</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.2482044371852905</t>
+          <t>0.47424293009349117</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>5.576882766842663</t>
+          <t>9.607352248140325</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.9236372922475216</t>
+          <t>1.5398910877009373</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>1.897403895551504</t>
+          <t>2.9653052281241186</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.508961320276801</t>
+          <t>2.5609911516632726</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>0.20245051461732713</t>
+          <t>0.38525691865339035</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.332295463461318</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.226508533909614</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.39819888247219903</t>
+          <t>0.7305527592087238</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.34447478728723535</t>
+          <t>0.6749783130345265</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.8865254422510852</t>
+          <t>1.8329236910574052</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>4.3882802625126365</t>
+          <t>6.325835301318699</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>15.929520204745108</t>
+          <t>15.095872302861409</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.3039933650932868</t>
+          <t>0.6186473237698054</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21384670445630807</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>7.993784059209929</t>
+          <t>6.389848731834391</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3760679050285543</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.35943593323950984</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>10.795079637392085</t>
+          <t>8.976480401511711</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20.79334522714615</t>
+          <t>29.602822267697942</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>23.929752317313536</t>
+          <t>20.178849467581784</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.124441370296634</t>
+          <t>1.1632203356842548</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.675788972523023</t>
+          <t>5.74914246859203</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6732760002958607</t>
+          <t>0.6933100900325817</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.7233373989994243</t>
+          <t>0.7500114526089093</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.154728682206246</t>
+          <t>1.194063560225489</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.44743860006644415</t>
+          <t>0.4627225502833369</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.471880159463147</t>
+          <t>1.5215687500986799</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.9147042326284731</t>
+          <t>0.9461974690558669</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.5686776564175712</t>
+          <t>0.5927488367852094</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.9578515317006229</t>
+          <t>0.9959055712866902</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.6958475423866107</t>
+          <t>0.7220346966656827</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.43959343660655</t>
+          <t>1.4842640127144664</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.4385645394024833</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.940630444623042</t>
+          <t>0.9738067157559511</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.02182006166832</t>
+          <t>7.144263707438208</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.3140090106469433</t>
+          <t>2.3804367128963033</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.5569208938202115</t>
+          <t>1.5969258863961242</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.802711268250739</t>
+          <t>5.86684962909143</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.4571811999921853</t>
+          <t>3.5218995493540364</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.047837462048418</t>
+          <t>4.15659423618686</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.758455806153715</t>
+          <t>7.750998428569606</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.0183454990473297</t>
+          <t>3.0646338968258195</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15.95408800937209</t>
+          <t>16.18565127955781</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.45418431146278</t>
+          <t>19.58546463280412</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11.126550965973195</t>
+          <t>10.97188176045917</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.24477508018104926</t>
+          <t>0.2576126727706408</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.3633958283217983</t>
+          <t>0.3816886267129263</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.26527351420922346</t>
+          <t>0.2790728234418501</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.34854829339911103</t>
+          <t>0.3661716361554796</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.799110489599748</t>
+          <t>0.8324955761800378</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.3717748876275772</t>
+          <t>0.39044399570676713</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.22742825614930617</t>
+          <t>0.23944474634897922</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.42993767907758373</t>
+          <t>0.4511911813137516</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.8777383267343062</t>
+          <t>0.9139129435792932</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.3397529123862247</t>
+          <t>0.3569780444684485</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.537855575218365</t>
+          <t>2.6219446000856785</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.9731739727437042</t>
+          <t>1.0076780739436955</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7.888229341763279</t>
+          <t>7.7741926485242345</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7.647073347372748</t>
+          <t>7.813128561000995</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.43405372873140086</t>
+          <t>0.4490377014074145</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.36008382201028205</t>
+          <t>0.37376900294907506</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2.178296851294403</t>
+          <t>2.226730392159442</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.5673814186742281</t>
+          <t>0.5872562045786811</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4.508596219157749</t>
+          <t>4.547746126274898</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.37332065638138</t>
+          <t>0.38651126366711397</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10.06154948022761</t>
+          <t>10.194302984017652</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.5158354122136073</t>
+          <t>0.5332074076287597</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4.600867175447419</t>
+          <t>4.646666071876432</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3.2400595612612646</t>
+          <t>3.347105324426791</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>4.066677632166805</t>
+          <t>4.0091754532504025</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.839377421658433</t>
+          <t>0.8684430277247774</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.7383950362093186</t>
+          <t>1.7944121567399174</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.3839877849516608</t>
+          <t>0.398905088747936</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.392809093067169</t>
+          <t>0.40992857944695044</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.5779873703579028</t>
+          <t>0.5966344830830783</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.6321810568427588</t>
+          <t>0.656456667643524</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.29517036870115687</t>
+          <t>0.30698657442059646</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.7925065494497072</t>
+          <t>0.8135466312285242</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.150010254123576</t>
+          <t>2.221325310804554</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.7706236606071899</t>
+          <t>0.7925930191586267</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>12.643859477691539</t>
+          <t>12.729381185862785</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>9.034980223330752</t>
+          <t>9.104039564777292</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.8786157630277232</t>
+          <t>1.9461433583296</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.2822759515097457</t>
+          <t>1.339011167886784</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.8014584479562363</t>
+          <t>2.8604741155293727</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.2205362593098732</t>
+          <t>1.2576666381066102</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.7694569392266688</t>
+          <t>0.7890205857781263</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.8250187361271202</t>
+          <t>0.8492947561020858</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>34.9997062552446</t>
+          <t>35.58871430050539</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.46253048138868</t>
+          <t>1.526137445039931</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2.1343133526326974</t>
+          <t>2.2203837165334566</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>79.19189246592778</t>
+          <t>79.46819379893032</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>6.639752648318337</t>
+          <t>6.677922298443082</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0.3310603993055736</t>
+          <t>0.3452820652378276</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>16.0725973125051</t>
+          <t>16.16100728365175</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.9627019796096636</t>
+          <t>3.994878973839855</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2.24029826333001</t>
+          <t>2.332087798595968</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2.878846825163033</t>
+          <t>2.992345594700509</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.8711209574782511</t>
+          <t>0.8969757909078236</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.27832716171543437</t>
+          <t>0.2916144138971628</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.6271654514443719</t>
+          <t>0.6489096635721943</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>9.11729640413187</t>
+          <t>9.173835535794307</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.8906706231432799</t>
+          <t>0.9144572818147054</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>17.531806014972908</t>
+          <t>17.325912253283136</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20.05520571791057</t>
+          <t>20.53159736229587</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5915629962219479</t>
+          <t>0.6202779401872459</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2.7701804175457543</t>
+          <t>2.8239274093078373</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.24121088401802407</t>
+          <t>0.25143213720713353</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>21.556637448725862</t>
+          <t>21.560197939339552</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>53.709798710791695</t>
+          <t>54.260745622118804</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>11.647866205765629</t>
+          <t>11.716529834381301</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>4.735192052853999</t>
+          <t>4.8414122341093195</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>3.1061074213233035</t>
+          <t>3.060614417989638</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>10.181046682367175</t>
+          <t>10.225985825863326</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.4541843818255549</t>
+          <t>0.468552665607584</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>12.33706606063009</t>
+          <t>12.6901030696256</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2.0183783136395994</t>
+          <t>2.091538766545579</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2.3953757348375295</t>
+          <t>2.4559696598505494</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>3.3944970322471564</t>
+          <t>3.474046199102666</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.47424293009349117</t>
+          <t>0.49182019672414</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>9.607352248140325</t>
+          <t>9.903246178687269</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1.5398910877009373</t>
+          <t>1.5836139504558506</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2.9653052281241186</t>
+          <t>3.0371764186419536</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2.5609911516632726</t>
+          <t>2.6366712128308056</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>0.38525691865339035</t>
+          <t>0.3994379847761073</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>0.332295463461318</t>
+          <t>0.34473680751808716</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.226508533909614</t>
+          <t>0.23521722733873496</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.7305527592087238</t>
+          <t>0.7557606804612691</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6749783130345265</t>
+          <t>0.701061217451547</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1.8329236910574052</t>
+          <t>1.9102232153798058</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>6.325835301318699</t>
+          <t>6.446525834735647</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>15.095872302861409</t>
+          <t>15.012770254768562</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.6186473237698054</t>
+          <t>0.6440101804612461</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>0.21384670445630807</t>
+          <t>0.22398523729625683</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>6.389848731834391</t>
+          <t>6.306455587443907</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.3760679050285543</t>
+          <t>0.39102199088865663</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.35943593323950984</t>
+          <t>0.37320453901835404</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>8.976480401511711</t>
+          <t>8.868120651660051</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>29.602822267697942</t>
+          <t>30.16796949021078</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20.178849467581784</t>
+          <t>19.949606788869488</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.1632203356842548</t>
+          <t>1.0491344499275668</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.74914246859203</t>
+          <t>4.91911958947221</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6933100900325817</t>
+          <t>0.7575305364633911</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.7500114526089093</t>
+          <t>0.8947948165783295</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.194063560225489</t>
+          <t>0.870027040520301</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.4627225502833369</t>
+          <t>0.37778710682941896</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.5215687500986799</t>
+          <t>1.6167196805330453</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.9461974690558669</t>
+          <t>0.7892017907472955</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.5927488367852094</t>
+          <t>0.6366095495548054</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.9959055712866902</t>
+          <t>0.631148730999064</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.7220346966656827</t>
+          <t>0.7358047908330718</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.4842640127144664</t>
+          <t>1.5114677929462919</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.4385645394024833</t>
+          <t>0.5676069659720463</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.9738067157559511</t>
+          <t>1.168370703883813</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.144263707438208</t>
+          <t>7.465188252147819</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.3804367128963033</t>
+          <t>2.2591356001118754</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.5969258863961242</t>
+          <t>0.632638458353207</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.86684962909143</t>
+          <t>6.55353247046364</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.5218995493540364</t>
+          <t>3.5218343341973037</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9500928858883221</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.15659423618686</t>
+          <t>2.1428130926831703</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.750998428569606</t>
+          <t>5.059201245034552</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.0646338968258195</t>
+          <t>1.6614286173001709</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16.18565127955781</t>
+          <t>6.841962765151133</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.58546463280412</t>
+          <t>15.448036460632839</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10.97188176045917</t>
+          <t>8.806524182428788</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.2576126727706408</t>
+          <t>0.3634574449933109</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.3816886267129263</t>
+          <t>0.42771252395482945</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.2790728234418501</t>
+          <t>0.3853812200944283</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.3661716361554796</t>
+          <t>0.37402054343542773</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.8324955761800378</t>
+          <t>0.3958941324195353</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.39044399570676713</t>
+          <t>0.3629511439674982</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.23944474634897922</t>
+          <t>0.3339428591063688</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.4511911813137516</t>
+          <t>0.4166982272878613</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.9139129435792932</t>
+          <t>0.46005518184814886</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.3569780444684485</t>
+          <t>0.4809008211261408</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.6219446000856785</t>
+          <t>2.71889904145002</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.0076780739436955</t>
+          <t>0.6341590446312532</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7.7741926485242345</t>
+          <t>14.463489109251228</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7.813128561000995</t>
+          <t>9.759852897489475</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.4490377014074145</t>
+          <t>0.35267377229104396</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.37376900294907506</t>
+          <t>0.48266088198606605</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2.226730392159442</t>
+          <t>1.542502888154288</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.5872562045786811</t>
+          <t>0.48769846641677983</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4.547746126274898</t>
+          <t>4.72408960238358</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.38651126366711397</t>
+          <t>0.22985714095333412</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10.194302984017652</t>
+          <t>7.441117382639778</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.5332074076287597</t>
+          <t>0.481007838938688</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4.646666071876432</t>
+          <t>2.061007663948031</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3.347105324426791</t>
+          <t>2.469757185115035</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>4.0091754532504025</t>
+          <t>5.4384218846036845</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.8684430277247774</t>
+          <t>0.869242827296952</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.7944121567399174</t>
+          <t>1.4431372370396995</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.398905088747936</t>
+          <t>0.23130088268211232</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.40992857944695044</t>
+          <t>0.3225412869681684</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.5966344830830783</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.656456667643524</t>
+          <t>0.6028243272819518</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.30698657442059646</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8135466312285242</t>
+          <t>0.9357543952797719</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.221325310804554</t>
+          <t>1.7093665636572242</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.7925930191586267</t>
+          <t>1.012002258115979</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>12.729381185862785</t>
+          <t>9.793816760980878</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>9.104039564777292</t>
+          <t>7.01286919996388</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1.9461433583296</t>
+          <t>0.8252515749526593</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.339011167886784</t>
+          <t>0.9849721851039159</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.8604741155293727</t>
+          <t>2.96746498958057</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.2576666381066102</t>
+          <t>1.3446977685042416</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.7890205857781263</t>
+          <t>0.46085787254729915</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.8492947561020858</t>
+          <t>0.665999781011232</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>35.58871430050539</t>
+          <t>20.44241548487502</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.526137445039931</t>
+          <t>2.109243658126877</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2.2203837165334566</t>
+          <t>1.4330656750316193</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>79.46819379893032</t>
+          <t>69.96231073210255</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>6.677922298443082</t>
+          <t>3.5340248681753383</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0.3452820652378276</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>16.16100728365175</t>
+          <t>11.54293567298227</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.994878973839855</t>
+          <t>3.4724767753813124</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2.332087798595968</t>
+          <t>2.697320859173856</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2.992345594700509</t>
+          <t>2.415249968006912</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.8969757909078236</t>
+          <t>0.3771401033088265</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.2916144138971628</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.6489096635721943</t>
+          <t>0.7734579890462778</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>9.173835535794307</t>
+          <t>2.7166735028756506</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.9144572818147054</t>
+          <t>0.5300187499137251</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>17.325912253283136</t>
+          <t>13.686308859965566</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20.53159736229587</t>
+          <t>24.64782357807381</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6202779401872459</t>
+          <t>0.39132603841434344</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2.8239274093078373</t>
+          <t>2.2442907367257177</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.25143213720713353</t>
+          <t>0.476297788445569</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>21.560197939339552</t>
+          <t>13.07649002630421</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>54.260745622118804</t>
+          <t>44.30158139339529</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>11.716529834381301</t>
+          <t>11.886226648190423</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>4.8414122341093195</t>
+          <t>3.728548479588924</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>3.060614417989638</t>
+          <t>2.685203859347256</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>10.225985825863326</t>
+          <t>10.01684481187386</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.468552665607584</t>
+          <t>0.5331645916603636</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>12.6901030696256</t>
+          <t>5.608208929578404</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2.091538766545579</t>
+          <t>1.0177089506770187</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2.4559696598505494</t>
+          <t>1.5516608567895978</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>3.474046199102666</t>
+          <t>2.3341311039900625</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.49182019672414</t>
+          <t>0.69052309562882</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>9.903246178687269</t>
+          <t>6.863787632059095</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1.5836139504558506</t>
+          <t>1.7289216269738583</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>3.0371764186419536</t>
+          <t>1.048317827190461</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2.6366712128308056</t>
+          <t>2.040220302692428</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>0.3994379847761073</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>0.34473680751808716</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.23521722733873496</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.7557606804612691</t>
+          <t>0.41485960317701</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.701061217451547</t>
+          <t>0.6932416726053439</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1.9102232153798058</t>
+          <t>1.518341072413619</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>6.446525834735647</t>
+          <t>4.566698213702369</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>15.012770254768562</t>
+          <t>19.25982428601712</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.6440101804612461</t>
+          <t>0.5265321764685291</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>0.22398523729625683</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>6.306455587443907</t>
+          <t>11.955185570640921</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.39102199088865663</t>
+          <t>0.504828490388032</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.37320453901835404</t>
+          <t>0.4806614224131358</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>8.868120651660051</t>
+          <t>8.351002358055275</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>30.16796949021078</t>
+          <t>31.837171582418595</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>19.949606788869488</t>
+          <t>22.322077570922957</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0491344499275668</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.91911958947221</t>
+          <t>6.40613162704345</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.7575305364633911</t>
+          <t>0.5436670056775945</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.8947948165783295</t>
+          <t>0.8270988884878415</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.870027040520301</t>
+          <t>0.7269450475321183</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.37778710682941896</t>
+          <t>0.370724171654574</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.6167196805330453</t>
+          <t>1.2486279405423</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.7892017907472955</t>
+          <t>0.36471136413336946</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.6366095495548054</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.631148730999064</t>
+          <t>0.3327763201137081</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.7358047908330718</t>
+          <t>0.90631498806767</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.5114677929462919</t>
+          <t>1.100649031113079</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.5676069659720463</t>
+          <t>0.4617696594750791</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.168370703883813</t>
+          <t>1.2508587266700282</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.465188252147819</t>
+          <t>7.96066281124526</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.2591356001118754</t>
+          <t>2.155766187102445</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.632638458353207</t>
+          <t>0.4645330898451175</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6.55353247046364</t>
+          <t>5.854180159455012</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.5218343341973037</t>
+          <t>4.01743976247084</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.9500928858883221</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.1428130926831703</t>
+          <t>1.658276003929078</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5.059201245034552</t>
+          <t>4.942587327773091</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.6614286173001709</t>
+          <t>1.3312293369609804</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6.841962765151133</t>
+          <t>4.230440314261502</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15.448036460632839</t>
+          <t>17.21345282136048</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8.806524182428788</t>
+          <t>10.663909096831446</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.3634574449933109</t>
+          <t>0.23998812715926332</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.42771252395482945</t>
+          <t>0.29741987966991446</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.3853812200944283</t>
+          <t>0.2566041154177858</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.37402054343542773</t>
+          <t>0.259446344096453</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.3958941324195353</t>
+          <t>0.45638955007497056</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.3629511439674982</t>
+          <t>0.2549190928216798</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.3339428591063688</t>
+          <t>0.21577032086213255</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.4166982272878613</t>
+          <t>0.2884072666444276</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.46005518184814886</t>
+          <t>0.5496598299815102</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.4809008211261408</t>
+          <t>0.332046402083238</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.71889904145002</t>
+          <t>1.2982851328546623</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.6341590446312532</t>
+          <t>0.6912679759729408</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14.463489109251228</t>
+          <t>15.017849352827968</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>9.759852897489475</t>
+          <t>2.4343429521951885</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.35267377229104396</t>
+          <t>0.4236876510003378</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.48266088198606605</t>
+          <t>0.6825468109172736</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.542502888154288</t>
+          <t>1.0254437533567706</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.48769846641677983</t>
+          <t>0.870555228163242</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4.72408960238358</t>
+          <t>9.695916205634743</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.22985714095333412</t>
+          <t>0.2768394294536419</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7.441117382639778</t>
+          <t>7.758732607651211</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.481007838938688</t>
+          <t>0.2667779427292586</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2.061007663948031</t>
+          <t>1.6248588943473719</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2.469757185115035</t>
+          <t>3.4219935496548732</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5.4384218846036845</t>
+          <t>5.3957998356830545</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.869242827296952</t>
+          <t>1.2127189817125412</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.4431372370396995</t>
+          <t>1.1315551872180933</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.3225412869681684</t>
+          <t>0.32280422906378475</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.6028243272819518</t>
+          <t>0.6510651607238674</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.9357543952797719</t>
+          <t>1.3916201186999138</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1.7093665636572242</t>
+          <t>1.9943661624562201</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1.012002258115979</t>
+          <t>1.1739678468702603</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>9.793816760980878</t>
+          <t>12.85795458355327</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7.01286919996388</t>
+          <t>10.304030361375922</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.8252515749526593</t>
+          <t>0.5699162990210787</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.96746498958057</t>
+          <t>5.083904525285538</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.3446977685042416</t>
+          <t>1.7186979934750368</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.46085787254729915</t>
+          <t>0.58633022617866</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.665999781011232</t>
+          <t>0.4302524507807909</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20.44241548487502</t>
+          <t>18.15834492588299</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.109243658126877</t>
+          <t>3.127566373476804</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1.4330656750316193</t>
+          <t>0.7676723632636353</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>69.96231073210255</t>
+          <t>69.84969407798386</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>3.5340248681753383</t>
+          <t>5.77159354746433</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.33245518100005705</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>11.54293567298227</t>
+          <t>18.556372537008833</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.4724767753813124</t>
+          <t>4.296040302150362</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2.697320859173856</t>
+          <t>3.858004029611924</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2.415249968006912</t>
+          <t>1.583984513807338</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.3771401033088265</t>
+          <t>0.2390702350859313</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.7734579890462778</t>
+          <t>1.0979661791593482</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.7166735028756506</t>
+          <t>4.126676395608076</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.5300187499137251</t>
+          <t>0.36850001286790146</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>13.686308859965566</t>
+          <t>13.131693803158354</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>24.64782357807381</t>
+          <t>14.06349245479493</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.39132603841434344</t>
+          <t>0.3342790864762784</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2.2442907367257177</t>
+          <t>3.2061725066568347</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.476297788445569</t>
+          <t>0.618722896431944</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>13.07649002630421</t>
+          <t>13.531474201782814</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>44.30158139339529</t>
+          <t>34.5296547562633</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>11.886226648190423</t>
+          <t>16.311484323499084</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>3.728548479588924</t>
+          <t>3.332821781149728</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.685203859347256</t>
+          <t>2.333155289310172</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>10.01684481187386</t>
+          <t>8.102984688826972</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.5331645916603636</t>
+          <t>0.9198895865542349</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>5.608208929578404</t>
+          <t>8.013297490104382</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>1.0177089506770187</t>
+          <t>0.4040930160476631</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>1.5516608567895978</t>
+          <t>1.6152871351608538</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2.3341311039900625</t>
+          <t>2.8423773739271043</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.69052309562882</t>
+          <t>1.0703407507219307</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>6.863787632059095</t>
+          <t>10.31107202962487</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1.7289216269738583</t>
+          <t>3.4370302789930234</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>1.048317827190461</t>
+          <t>0.4656803996648664</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2.040220302692428</t>
+          <t>2.065291470483428</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.27020266150139904</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.41485960317701</t>
+          <t>0.5489650279838301</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6932416726053439</t>
+          <t>0.7755286469168579</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1.518341072413619</t>
+          <t>3.16812301098128</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>4.566698213702369</t>
+          <t>6.084441286925006</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>19.25982428601712</t>
+          <t>24.6219897178622</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.5265321764685291</t>
+          <t>0.8686692488001093</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>11.955185570640921</t>
+          <t>20.013188769091556</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.504828490388032</t>
+          <t>0.7412269232260577</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.4806614224131358</t>
+          <t>0.70009538571506</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>8.351002358055275</t>
+          <t>7.23059446227222</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>31.837171582418595</t>
+          <t>21.754699950106534</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>22.322077570922957</t>
+          <t>26.736108969275545</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D322"/>
+  <dimension ref="A1:D328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.40613162704345</t>
+          <t>4.909558293807898</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.5436670056775945</t>
+          <t>0.30421525271958005</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.8270988884878415</t>
+          <t>0.6083393539571412</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.7269450475321183</t>
+          <t>0.7226316927759698</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.370724171654574</t>
+          <t>0.2862952103943379</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.2486279405423</t>
+          <t>0.8463023237547902</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.36471136413336946</t>
+          <t>0.2514153694540111</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.8888888888888884</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.3327763201137081</t>
+          <t>0.2670832537606312</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.90631498806767</t>
+          <t>0.5996429526135719</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.100649031113079</t>
+          <t>0.8573017651763901</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.4617696594750791</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.2508587266700282</t>
+          <t>0.8459946682788368</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.96066281124526</t>
+          <t>4.996927462056149</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.155766187102445</t>
+          <t>1.6849013215444963</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.4645330898451175</t>
+          <t>0.3335935986600007</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.854180159455012</t>
+          <t>3.976178950692489</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4.01743976247084</t>
+          <t>2.3998232891685762</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.6964049558080228</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.658276003929078</t>
+          <t>0.6215699887406969</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.942587327773091</t>
+          <t>5.418251122582801</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.3312293369609804</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.230440314261502</t>
+          <t>3.941830703022425</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>17.21345282136048</t>
+          <t>12.017672181475355</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10.663909096831446</t>
+          <t>11.927919491019885</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.23998812715926332</t>
+          <t>0.22461217210683504</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.29741987966991446</t>
+          <t>0.27425920605489384</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.2566041154177858</t>
+          <t>0.23816916584042036</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.259446344096453</t>
+          <t>0.24226186630458924</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.45638955007497056</t>
+          <t>0.3767129997820668</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.2549190928216798</t>
+          <t>0.24035078045507663</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.21577032086213255</t>
+          <t>0.20294898883472937</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2884072666444276</t>
+          <t>0.27038182988241627</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.5496598299815102</t>
+          <t>0.43156184612361487</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.332046402083238</t>
+          <t>0.3064672286984422</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.2982851328546623</t>
+          <t>1.232779322817346</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.6912679759729408</t>
+          <t>0.4568539621534216</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>15.017849352827968</t>
+          <t>14.281713329270183</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2.4343429521951885</t>
+          <t>4.896374006544114</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.4236876510003378</t>
+          <t>0.38012696977537186</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.6825468109172736</t>
+          <t>0.5042273088296477</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.0254437533567706</t>
+          <t>0.5398060080636155</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.870555228163242</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>9.695916205634743</t>
+          <t>6.41985055534561</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.2768394294536419</t>
+          <t>0.36047955827061506</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7.758732607651211</t>
+          <t>5.755364480494822</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.2667779427292586</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1.6248588943473719</t>
+          <t>1.9347794908073617</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3.4219935496548732</t>
+          <t>2.7438946145284144</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5.3957998356830545</t>
+          <t>7.140955264614027</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.2127189817125412</t>
+          <t>0.21584475250145665</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.1315551872180933</t>
+          <t>0.7115566154590928</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.23130088268211232</t>
+          <t>0.291149726691148</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.32280422906378475</t>
+          <t>0.3376971390819318</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.6510651607238674</t>
+          <t>0.512300253357509</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.3916201186999138</t>
+          <t>0.8920192195332045</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1.9943661624562201</t>
+          <t>1.791646536979793</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1.1739678468702603</t>
+          <t>0.40093814877214484</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>12.85795458355327</t>
+          <t>9.628473785976409</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10.304030361375922</t>
+          <t>7.6920653288006005</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.5699162990210787</t>
+          <t>0.8385138516424451</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>5.083904525285538</t>
+          <t>3.3049940080926175</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.7186979934750368</t>
+          <t>1.1713685698513743</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.58633022617866</t>
+          <t>0.4644688308913558</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.4302524507807909</t>
+          <t>0.6705263756255058</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>18.15834492588299</t>
+          <t>15.79036606787081</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>3.127566373476804</t>
+          <t>2.233848332385374</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.7676723632636353</t>
+          <t>0.8837502252446245</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>69.84969407798386</t>
+          <t>55.04180563723715</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.77159354746433</t>
+          <t>3.811411963683153</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.33245518100005705</t>
+          <t>0.2993396152929419</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>18.556372537008833</t>
+          <t>6.090076985253597</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>4.296040302150362</t>
+          <t>2.7979367505389647</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>3.858004029611924</t>
+          <t>1.153979412168309</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.583984513807338</t>
+          <t>1.6836706162694757</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.2390702350859313</t>
+          <t>0.28280701992542917</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>1.0979661791593482</t>
+          <t>0.7443893846406251</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>4.126676395608076</t>
+          <t>1.571214663013003</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.36850001286790146</t>
+          <t>0.23530266027014765</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>13.131693803158354</t>
+          <t>13.83268042679417</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>14.06349245479493</t>
+          <t>13.37722097988723</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.3342790864762784</t>
+          <t>0.4093141102689524</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>3.2061725066568347</t>
+          <t>1.8344245117853675</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.618722896431944</t>
+          <t>0.6327543470176672</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>13.531474201782814</t>
+          <t>10.180133334053014</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>34.5296547562633</t>
+          <t>9.190378011760288</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>16.311484323499084</t>
+          <t>12.090701250822901</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>3.332821781149728</t>
+          <t>2.7435315723589198</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.333155289310172</t>
+          <t>3.397419860360713</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>8.102984688826972</t>
+          <t>6.446978094924653</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.9198895865542349</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>8.013297490104382</t>
+          <t>6.970014314994211</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.4040930160476631</t>
+          <t>0.3158849285852084</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>1.6152871351608538</t>
+          <t>0.9392222441507888</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2.8423773739271043</t>
+          <t>2.268045023738182</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.0703407507219307</t>
+          <t>0.8267037412964751</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>10.31107202962487</t>
+          <t>7.704225494636596</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>3.4370302789930234</t>
+          <t>4.10964196345328</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.4656803996648664</t>
+          <t>0.9757994539451424</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2.065291470483428</t>
+          <t>1.250085721238284</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.27020266150139904</t>
+          <t>0.23889539707129392</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.5489650279838301</t>
+          <t>0.5313553089490173</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7755286469168579</t>
+          <t>0.5456347107398372</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>3.16812301098128</t>
+          <t>3.5318666859946792</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>6.084441286925006</t>
+          <t>4.299645808861484</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>24.6219897178622</t>
+          <t>26.37968401041447</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.8686692488001093</t>
+          <t>0.9116283685127535</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20.013188769091556</t>
+          <t>24.67180802331191</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.7412269232260577</t>
+          <t>0.5105484507094079</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.70009538571506</t>
+          <t>0.4865191541420848</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>7.23059446227222</t>
+          <t>5.884308222598272</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>21.754699950106534</t>
+          <t>24.99600852017211</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,139 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>26.736108969275545</t>
+          <t>26.70999351706555</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>DF_AGL_Super_Vegito</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>3.1445916824696227</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>DF_INT_Buuhan</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>BU_STR_Hercule</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>7.28508599540455</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>CLR_STR_Evolution_Blue_Vegeta</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>8.738311645233402</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>CLR_AGL_SS4_Goku</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>48.84284928427354</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>DFLR_TEQ_Super_Vegito</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>5.039928813817795</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.909558293807898</t>
+          <t>5.531237293629751</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.30421525271958005</t>
+          <t>0.32659489096026917</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.25347632076680376</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.6083393539571412</t>
+          <t>0.645812050360615</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.4037492838456807</t>
+          <t>2.634203196502382</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.7226316927759698</t>
+          <t>0.7646805987204524</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.0015615919600047</t>
+          <t>2.193456688254154</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.8695827763244182</t>
+          <t>2.0488247083907414</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.2862952103943379</t>
+          <t>0.304927282070133</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.8463023237547902</t>
+          <t>0.9093488269814942</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16.826244986919765</t>
+          <t>2.634203196502382</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.2514153694540111</t>
+          <t>0.27395607025130664</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.2670832537606312</t>
+          <t>0.2926892440558202</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.5996429526135719</t>
+          <t>0.6350161762822725</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8573017651763901</t>
+          <t>0.9025125515155519</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.46260176536422465</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.8459946682788368</t>
+          <t>0.9152355044432129</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.996927462056149</t>
+          <t>5.664406444885321</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6849013215444963</t>
+          <t>1.8341237462058286</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.36574580461168477</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.2663928094193209</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.479363455676221</t>
+          <t>6.004684775880015</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.976178950692489</t>
+          <t>4.544488730384067</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.670310381240009</t>
+          <t>5.1180656059263585</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.054503988707488</t>
+          <t>1.1556021239177248</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.7396817278381107</t>
+          <t>3.0023423879400073</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.3998232891685762</t>
+          <t>2.778496935410148</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.3852007079725748</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.6215699887406969</t>
+          <t>0.697928356587505</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5.418251122582801</t>
+          <t>6.219961622686318</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3.941830703022425</t>
+          <t>4.528713946351106</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12.017672181475355</t>
+          <t>14.139494919904942</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11.927919491019885</t>
+          <t>12.187914512515357</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.22461217210683504</t>
+          <t>0.20690839246694862</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.27425920605489384</t>
+          <t>0.25583238835924843</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.23816916584042036</t>
+          <t>0.21991979781498516</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.24226186630458924</t>
+          <t>0.22490884712487266</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.3767129997820668</t>
+          <t>0.38748245674504744</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.24035078045507663</t>
+          <t>0.2232245297481526</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.20294898883472937</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.27038182988241627</t>
+          <t>0.25266700868845726</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.43156184612361487</t>
+          <t>0.4468078298741132</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.3064672286984422</t>
+          <t>0.28666432904984435</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.232779322817346</t>
+          <t>1.319794484067121</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4568539621534216</t>
+          <t>0.47671583561314107</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14.281713329270183</t>
+          <t>13.036693538749645</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4.896374006544114</t>
+          <t>5.163763782422933</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.0794041191831907</t>
+          <t>1.1828894969117507</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.1556021239177248</t>
+          <t>1.2663928094193209</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.38012696977537186</t>
+          <t>0.4079030870860707</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.5042273088296477</t>
+          <t>0.5339154389200457</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.5398060080636155</t>
+          <t>0.6069066103759343</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6.41985055534561</t>
+          <t>7.64248265916461</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.36047955827061506</t>
+          <t>0.38417518387155103</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.755364480494822</t>
+          <t>6.51728044730611</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1.9347794908073617</t>
+          <t>2.2673467042797846</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2.7438946145284144</t>
+          <t>3.102517461060962</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>7.140955264614027</t>
+          <t>6.467400048080358</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1.2018746419228403</t>
+          <t>1.317101598251191</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.21584475250145665</t>
+          <t>0.23597993287030708</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.7115566154590928</t>
+          <t>0.7545674418231051</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.291149726691148</t>
+          <t>0.30672632109356</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.3376971390819318</t>
+          <t>0.339193934311656</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.2018746419228403</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.512300253357509</t>
+          <t>0.5397989383483542</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8920192195332045</t>
+          <t>1.0021109064356706</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1.791646536979793</t>
+          <t>2.5200297782960464</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.40093814877214484</t>
+          <t>0.47413850389291134</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>9.628473785976409</t>
+          <t>11.10278833271194</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>7.6920653288006005</t>
+          <t>8.75174561492608</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.8385138516424451</t>
+          <t>0.866408862058502</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.9849721851039159</t>
+          <t>1.0794041191831907</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.3049940080926175</t>
+          <t>3.875195899324561</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.1713685698513743</t>
+          <t>1.2728291775588847</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.4644688308913558</t>
+          <t>0.5269330624384887</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.6705263756255058</t>
+          <t>0.7247214518284827</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>15.79036606787081</t>
+          <t>18.30065745055701</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.233848332385374</t>
+          <t>2.27739359530318</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.8837502252446245</t>
+          <t>0.8850216617509928</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>55.04180563723715</t>
+          <t>60.5878570688421</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>3.811411963683153</t>
+          <t>4.4376645030091195</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.2993396152929419</t>
+          <t>0.3226651218080246</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>6.090076985253597</t>
+          <t>6.105887626095928</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2.7979367505389647</t>
+          <t>3.2092464183882328</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.153979412168309</t>
+          <t>1.167583397572037</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.6836706162694757</t>
+          <t>1.737281691689796</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.28280701992542917</t>
+          <t>0.31373833297928827</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.7443893846406251</t>
+          <t>0.8090810317337711</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1.571214663013003</t>
+          <t>1.7822002026236317</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.23530266027014765</t>
+          <t>0.26296947986888974</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>13.83268042679417</t>
+          <t>13.039312924212268</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>13.37722097988723</t>
+          <t>23.268908598073565</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.4093141102689524</t>
+          <t>0.3907680173688625</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>1.8344245117853675</t>
+          <t>2.1589995096480425</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.6327543470176672</t>
+          <t>0.666073527927173</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>10.180133334053014</t>
+          <t>11.495781783960517</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.190378011760288</t>
+          <t>8.528735454948986</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>12.090701250822901</t>
+          <t>5.737679644947775</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2.7435315723589198</t>
+          <t>3.0595362556534127</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>3.397419860360713</t>
+          <t>3.0215855792876876</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.446978094924653</t>
+          <t>7.432905786412363</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20296637826436292</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>6.970014314994211</t>
+          <t>8.040051075640736</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.3158849285852084</t>
+          <t>0.31614186935508326</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.9392222441507888</t>
+          <t>1.0460173271591484</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2.268045023738182</t>
+          <t>2.563487524826303</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.8267037412964751</t>
+          <t>0.8993489348901536</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>7.704225494636596</t>
+          <t>8.904141380620871</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4.10964196345328</t>
+          <t>4.825627436780165</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.9757994539451424</t>
+          <t>1.0734914103271618</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.250085721238284</t>
+          <t>1.3652911608570018</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.23889539707129392</t>
+          <t>0.255573396122595</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.5313553089490173</t>
+          <t>0.6566460049132969</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.5456347107398372</t>
+          <t>0.5758683196192629</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>3.5318666859946792</t>
+          <t>3.857119529487165</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>4.299645808861484</t>
+          <t>4.847275595476553</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>26.37968401041447</t>
+          <t>27.802850968776152</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.9116283685127535</t>
+          <t>0.9670268790320983</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>24.67180802331191</t>
+          <t>21.746088668537098</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.5105484507094079</t>
+          <t>0.43023456483930766</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.4865191541420848</t>
+          <t>0.517223889367306</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>5.884308222598272</t>
+          <t>6.246041011364872</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>24.99600852017211</t>
+          <t>18.94799341058981</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>26.70999351706555</t>
+          <t>27.811959941070995</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.1445916824696227</t>
+          <t>3.654530578351891</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.28508599540455</t>
+          <t>8.268193696474272</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>8.738311645233402</t>
+          <t>10.07194230594015</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>48.84284928427354</t>
+          <t>55.296539491226106</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>5.039928813817795</t>
+          <t>4.715271823076364</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D328"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.054503988707488</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.530860175034061</t>
+          <t>4.361949032591559</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.33524171825218024</t>
+          <t>0.23574617776442475</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.6421910187283718</t>
+          <t>0.5444660522597279</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.7341485092978091</t>
+          <t>0.640702474809646</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.302280806132716</t>
+          <t>0.25347632076680376</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.8853924709908902</t>
+          <t>0.7574550940708971</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.28620894686401366</t>
+          <t>0.2032737737321053</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.6295595247919629</t>
+          <t>0.5870932792370066</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9129750512610001</t>
+          <t>0.853498303881991</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.9185591099221271</t>
+          <t>0.884234533433046</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.93048262518319</t>
+          <t>6.36096509062256</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.8748072884322817</t>
+          <t>1.4390696962073428</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.567069058296742</t>
+          <t>4.087806639014289</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.833348895935714</t>
+          <t>1.2758951062796666</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.8563345777772597</t>
+          <t>0.6658023883024011</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6.5203681092741945</t>
+          <t>4.709333292528688</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.295068795451804</t>
+          <t>3.170928701564671</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14.318659071896288</t>
+          <t>10.817521314724294</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12.200920852053876</t>
+          <t>6.691560799527345</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.20236994602990807</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2482946980630048</t>
+          <t>0.21351661822480747</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.214986139035276</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.21950924776208539</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.3748920765173877</t>
+          <t>0.3151653027179109</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.25370407699906994</t>
+          <t>0.21760374407851518</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.4299796046327436</t>
+          <t>0.3683803402623974</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2825280243742441</t>
+          <t>0.24254382847170267</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.3313771002332726</t>
+          <t>1.0185835570913166</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4519797053827856</t>
+          <t>0.41663353864491204</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20.447350071414398</t>
+          <t>5.481245719791488</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.918751135571405</t>
+          <t>6.6877308732739715</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.42319382932921096</t>
+          <t>0.3521739869560535</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.5195022941207033</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.6439291288542631</t>
+          <t>0.4857808718316848</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>8.349217814182651</t>
+          <t>6.269821995987515</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.3646202810065069</t>
+          <t>0.3155473336779959</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.639868695998623</t>
+          <t>5.02504347848755</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2.235245119783216</t>
+          <t>1.849211317656974</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3.0690146869626322</t>
+          <t>2.30798425687627</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6.205998012225202</t>
+          <t>6.304683545084495</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.2523740888370487</t>
+          <t>0.21445714866870777</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.7445128928456889</t>
+          <t>0.3886901286240877</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.4602636581799371</t>
+          <t>0.37938916268570144</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.33458277763677147</t>
+          <t>0.28201684292622164</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.5401356488602246</t>
+          <t>0.4438586829440962</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.9890143280291415</t>
+          <t>0.9759374150367902</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.4588439255455494</t>
+          <t>2.0371923636241966</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.5082645603725817</t>
+          <t>0.4185592393068056</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>11.00839510514396</t>
+          <t>8.998560924674821</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>8.554253920920349</t>
+          <t>6.800840951423201</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.8446599883440677</t>
+          <t>0.7471447865075329</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.6005891470680855</t>
+          <t>2.8964425916799597</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.2223695908925558</t>
+          <t>1.760487608073925</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.5626032332804041</t>
+          <t>0.6048980187830395</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.7216009582392864</t>
+          <t>0.587591927214329</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>17.99015657891317</t>
+          <t>12.22705876560277</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.361921960094894</t>
+          <t>2.205519333945238</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.7051221191560039</t>
+          <t>0.9555647180379135</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>60.0907559934362</t>
+          <t>52.53703389101396</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.024068186084601</t>
+          <t>2.6747024223347737</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.3075172232975743</t>
+          <t>0.2649244524493756</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>6.047100676420733</t>
+          <t>6.243052438524984</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>3.487740587444185</t>
+          <t>2.90587840903614</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.0883899995358188</t>
+          <t>1.632163020169057</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.658274416003498</t>
+          <t>1.342458798290673</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.32471897430055635</t>
+          <t>0.28709437588717807</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.8140970926724749</t>
+          <t>0.22705927031518014</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1.8071175059677163</t>
+          <t>1.491381877905745</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.26092757733862876</t>
+          <t>0.24371716954058212</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>13.32122932992533</t>
+          <t>5.478692359782769</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>22.826603460413057</t>
+          <t>17.813946906387375</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.3923142367329503</t>
+          <t>0.335556355552918</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2.248762123240217</t>
+          <t>2.0180768093303287</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.656699365342837</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>12.13576047658956</t>
+          <t>5.2077314916527015</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>8.577602169705301</t>
+          <t>9.53223544517617</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>6.022366633752269</t>
+          <t>4.696001942963229</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>3.07017787788702</t>
+          <t>2.234226659006703</t>
         </is>
       </c>
     </row>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>3.0414459213636906</t>
+          <t>2.503292608221715</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>7.814819103039379</t>
+          <t>6.0508738972152685</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.21163104681600053</t>
+          <t>0.20962493103719204</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>8.030965911603506</t>
+          <t>6.414917950036044</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.3153946600914156</t>
+          <t>0.2515007720514022</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>1.0714192394976862</t>
+          <t>0.8474154512779297</t>
         </is>
       </c>
     </row>
@@ -6579,12 +6579,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2.547906389679379</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.8995106518280123</t>
+          <t>1.00317494048871</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>8.362484699022628</t>
+          <t>6.755142769102023</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>3.339120000809444</t>
+          <t>2.6032275927244135</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>1.0932430020604087</t>
+          <t>0.8467153665882885</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.386222123489415</t>
+          <t>1.5827626370724364</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.25139255137154803</t>
+          <t>0.2006487348882513</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.6409017719029362</t>
+          <t>0.4970895183802982</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.5581704967474692</t>
+          <t>0.5859291292878581</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>3.816346946994098</t>
+          <t>3.00259134006887</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>4.805979061197458</t>
+          <t>3.708361847259125</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>31.501364947143163</t>
+          <t>26.09117957317322</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.9357899564347253</t>
+          <t>0.7894701166027333</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20.236362440796597</t>
+          <t>28.441856260873077</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.5665462687332092</t>
+          <t>0.742554864501276</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5185693194572787</t>
+          <t>0.5013459053481271</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.5065755781949095</t>
+          <t>5.754743187802573</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>18.4069255820103</t>
+          <t>19.82671989211166</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>28.572182760867378</t>
+          <t>25.76613502069712</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.734173322371305</t>
+          <t>3.191122613070496</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>8.4156126858001</t>
+          <t>6.72272974787775</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>9.696056013261876</t>
+          <t>6.678260223991702</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>51.39986624238975</t>
+          <t>43.48545620117249</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,227 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>5.265189493447437</t>
+          <t>6.1745635938019205</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>DF_INT_Super_Janemba</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>DF_STR_Super_Gogeta</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>DFLR_AGL_Full_Power_Frieza</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>DFLR_INT_Super_Saiyan_Goku</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>7.804904195241505</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>DF_TEQ_Perfect_Cell</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>4.803419409659969</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>LR_INT_SS2_Gohan</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>5.4848703177516995</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>BU_AGL_Beerus</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>4.122127814960759</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>CLR_INT_Goku_Frieza</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>34.30228673596306</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>CLR_PHY_SS2_Gohan</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>6.013127318312613</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>DFLR_AGL_Super_Gogeta</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>96.0249786545603</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.361949032591559</t>
+          <t>5.147151951407842</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.23574617776442475</t>
+          <t>0.2514861654743399</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.5444660522597279</t>
+          <t>0.6185115447768779</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.640702474809646</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.7574550940708971</t>
+          <t>0.8305678974962332</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.2032737737321053</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.6088181617418025</t>
+          <t>0.30440908087090124</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.5870932792370066</t>
+          <t>0.6249144108027461</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.853498303881991</t>
+          <t>0.780015877729443</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.884234533433046</t>
+          <t>0.854527206960871</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6.36096509062256</t>
+          <t>4.3755703331991995</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.4390696962073428</t>
+          <t>1.31768415351112</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.087806639014289</t>
+          <t>3.4003029950827397</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.2758951062796666</t>
+          <t>1.7739422867197543</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.6658023883024011</t>
+          <t>0.37633598531839096</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.709333292528688</t>
+          <t>1.4560343301113907</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3.170928701564671</t>
+          <t>1.8382241710713654</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10.817521314724294</t>
+          <t>5.958233802081503</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6.691560799527345</t>
+          <t>5.1601351607319685</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.21351661822480747</t>
+          <t>0.3089593851688409</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.24384577650036013</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.3151653027179109</t>
+          <t>0.40517236063483547</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.261267344493279</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.21760374407851518</t>
+          <t>0.28120418872615055</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.3683803402623974</t>
+          <t>0.46370370555211504</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.24254382847170267</t>
+          <t>0.3564428860868816</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.0185835570913166</t>
+          <t>0.6553688053305415</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.41663353864491204</t>
+          <t>0.4837682722766091</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5.481245719791488</t>
+          <t>7.369267468604704</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6.6877308732739715</t>
+          <t>8.958224320187643</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.3521739869560535</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.4857808718316848</t>
+          <t>0.491439493571427</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6.269821995987515</t>
+          <t>3.516138009917059</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.3155473336779959</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.02504347848755</t>
+          <t>5.751336936139</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1.849211317656974</t>
+          <t>0.8460619514923551</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2.30798425687627</t>
+          <t>1.3127006439134168</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6.304683545084495</t>
+          <t>5.299292343968347</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.21445714866870777</t>
+          <t>0.3001388460521803</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.3886901286240877</t>
+          <t>0.5017533944495435</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.37938916268570144</t>
+          <t>0.25347632076680376</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.28201684292622164</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.4438586829440962</t>
+          <t>0.345543576982281</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.9759374150367902</t>
+          <t>0.8809925543567287</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.0371923636241966</t>
+          <t>1.1370510020497602</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.4185592393068056</t>
+          <t>0.36928158244274556</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8.998560924674821</t>
+          <t>7.664627398907729</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.800840951423201</t>
+          <t>4.453073512039786</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.7471447865075329</t>
+          <t>0.3563959877323074</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.8964425916799597</t>
+          <t>1.9500517555017227</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.760487608073925</t>
+          <t>1.3166382408761903</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6048980187830395</t>
+          <t>0.36121892262945554</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.587591927214329</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>12.22705876560277</t>
+          <t>11.50271850717192</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.205519333945238</t>
+          <t>2.372677889027049</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.9555647180379135</t>
+          <t>0.4640873660557289</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>52.53703389101396</t>
+          <t>56.87342871578694</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2.6747024223347737</t>
+          <t>3.392658374337549</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.2649244524493756</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>6.243052438524984</t>
+          <t>9.131986764198928</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2.90587840903614</t>
+          <t>3.935911033002274</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.632163020169057</t>
+          <t>1.0903414444951376</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.342458798290673</t>
+          <t>0.8988016519360076</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.28709437588717807</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.22705927031518014</t>
+          <t>0.21003086090337852</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1.491381877905745</t>
+          <t>6.366836286823892</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.24371716954058212</t>
+          <t>0.23512769880574474</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>5.478692359782769</t>
+          <t>7.886748860894485</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>17.813946906387375</t>
+          <t>8.009437520771026</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.335556355552918</t>
+          <t>0.6397888351014138</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2.0180768093303287</t>
+          <t>1.550610968743939</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>5.2077314916527015</t>
+          <t>3.094788066995569</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.53223544517617</t>
+          <t>13.26245623401097</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>4.696001942963229</t>
+          <t>5.147495365459464</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2.234226659006703</t>
+          <t>0.6360664067784588</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.503292608221715</t>
+          <t>2.8979755096283464</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.0508738972152685</t>
+          <t>6.154296379344521</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.20962493103719204</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>6.414917950036044</t>
+          <t>1.9861074812826018</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.2515007720514022</t>
+          <t>0.3433187417469352</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.8474154512779297</t>
+          <t>0.9538117935943325</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.00317494048871</t>
+          <t>0.8730243497598953</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>6.755142769102023</t>
+          <t>6.295817148787153</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2.6032275927244135</t>
+          <t>0.7594599559910206</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.8467153665882885</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.5827626370724364</t>
+          <t>1.3586051278019424</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.2006487348882513</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.4970895183802982</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.5859291292878581</t>
+          <t>0.6499645485430372</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>3.00259134006887</t>
+          <t>0.7869266552145665</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>3.708361847259125</t>
+          <t>2.6110252083728884</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>26.09117957317322</t>
+          <t>8.85072764255467</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.7894701166027333</t>
+          <t>0.3458311366242411</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>28.441856260873077</t>
+          <t>34.32310560524295</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.742554864501276</t>
+          <t>0.4625256143195366</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5013459053481271</t>
+          <t>0.5163334304244711</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>5.754743187802573</t>
+          <t>8.74088292277886</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>19.82671989211166</t>
+          <t>14.07665325481563</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>25.76613502069712</t>
+          <t>19.174355031292478</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.191122613070496</t>
+          <t>5.347467576922535</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>6.72272974787775</t>
+          <t>7.68575862084333</t>
         </is>
       </c>
     </row>
@@ -7591,12 +7591,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.678260223991702</t>
+          <t>17.55069144050915</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>43.48545620117249</t>
+          <t>47.81727955742368</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>6.1745635938019205</t>
+          <t>13.843388130662065</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>7.804904195241505</t>
+          <t>7.485716831580664</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>4.803419409659969</t>
+          <t>13.138712910077244</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>5.4848703177516995</t>
+          <t>8.00962100680775</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>4.122127814960759</t>
+          <t>5.628099406303551</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>34.30228673596306</t>
+          <t>34.7634032788478</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>6.013127318312613</t>
+          <t>7.685074535361351</t>
         </is>
       </c>
     </row>
@@ -7855,12 +7855,78 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>96.0249786545603</t>
+          <t>4.053138781884925</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Trunks_Goten</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>F2PLR_AGL_Demon_King_Piccolo</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>LR_STR_Kaioken_Goku</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>3.9793022549399226</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D344"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.5562517044001005</t>
+          <t>5.148350354764268</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.23139506153692224</t>
+          <t>0.21106546823655348</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.47399619125802356</t>
+          <t>0.45023294336197556</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.735905186943651</t>
+          <t>0.756471486759053</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>2.5965708291023617</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.6022510761673919</t>
+          <t>0.6476002595255947</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.7721404369011502</t>
+          <t>0.8472367604537439</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.8785048196846343</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.980533563575431</t>
+          <t>3.5020743146828295</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.2062214990020066</t>
+          <t>1.4481632545294802</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.9065228982470295</t>
+          <t>3.0571957995350694</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.3949243258229431</t>
+          <t>0.5594279192143468</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.30401282996775403</t>
+          <t>0.26361372900287794</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.107591801789285</t>
+          <t>1.4357798047714738</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.2088034999499264</t>
+          <t>1.2161002018432159</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4.013132722398248</t>
+          <t>3.0901408927102922</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.78100619857382</t>
+          <t>4.741383723023766</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.35199827864523187</t>
+          <t>0.3306436611283617</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.30277755360542297</t>
+          <t>0.2610572506404627</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2895908021940786</t>
+          <t>0.2908312992409778</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.29592521763106033</t>
+          <t>0.27829116285590055</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.31973775499847457</t>
+          <t>0.2971784419796575</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.2957801603411678</t>
+          <t>0.29206138974924295</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.39888620254778034</t>
+          <t>0.3729676997640233</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.5102240953767903</t>
+          <t>0.42501697999329396</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.46129289826141334</t>
+          <t>0.48342007519484126</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6.503322933582631</t>
+          <t>8.94473387189344</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.597973018904362</t>
+          <t>5.746678807640219</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.40390189964538514</t>
+          <t>0.3587297537959491</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1.212871421482764</t>
+          <t>1.103324400362609</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.4168701909545796</t>
+          <t>5.10434937495214</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.48213270238788514</t>
+          <t>0.5149921126125698</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.1813117454528599</t>
+          <t>1.230534146315152</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.445702855335761</t>
+          <t>3.743898240591197</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.24366352667659513</t>
+          <t>0.273126333350474</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.47149848725687826</t>
+          <t>0.3957702516231805</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.29217730932975106</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.780302548315472</t>
+          <t>0.8721788409453686</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.7339983649567281</t>
+          <t>0.7128192420100414</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.319561085640256</t>
+          <t>0.32354049091618986</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.0447704801067905</t>
+          <t>6.823573839528946</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.086212801637891</t>
+          <t>3.271486721758933</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.34508740585007125</t>
+          <t>0.34244193077931295</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.8036774783524663</t>
+          <t>0.842819541173392</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.202787912494725</t>
+          <t>1.4852255091698625</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.3414537103185964</t>
+          <t>0.30832865869755466</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>8.809572220731086</t>
+          <t>8.734982021158638</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.45776187437344</t>
+          <t>2.50396934157678</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.44823430391141583</t>
+          <t>0.37729316215769426</t>
         </is>
       </c>
     </row>
@@ -5237,12 +5237,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>51.37565967783792</t>
+          <t>10.002290985425383</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.9132158476023973</t>
+          <t>1.5981894637358895</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>11.755107870476685</t>
+          <t>12.079221465633246</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2.4697645174609812</t>
+          <t>2.180421494649069</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.9649133536484661</t>
+          <t>1.0496328812652562</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.698430058990514</t>
+          <t>2.7585753808601363</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.20597803639427398</t>
+          <t>0.20333168742934404</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>8.865999782557118</t>
+          <t>8.931643074437595</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>5.314861775410902</t>
+          <t>4.658203191359647</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.7088639199955747</t>
+          <t>0.6982086851636129</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.6516709151317407</t>
+          <t>0.4756128886333354</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>7.404073566308405</t>
+          <t>7.755281366001679</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.635942505152329</t>
+          <t>10.479058710929323</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.799841401704286</t>
+          <t>2.773782377370461</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.47895758849744735</t>
+          <t>0.3844972138262874</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.54156955898681</t>
+          <t>6.057199802326575</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>5.079079116235052</t>
+          <t>5.115815482106296</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>3.439320104741448</t>
+          <t>3.5577018954856525</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.3351177383038719</t>
+          <t>0.33528272828819466</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.8513658327188445</t>
+          <t>0.8576182274988603</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.8175122424577106</t>
+          <t>0.932363220173678</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.804378565679117</t>
+          <t>2.645881877065856</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.5094693936177713</t>
+          <t>0.48988068475454455</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.2162602776039624</t>
+          <t>1.2058009496953161</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6342319457873602</t>
+          <t>0.7245083337127021</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.4432073994266871</t>
+          <t>0.3675723993896604</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.7549044708295563</t>
+          <t>1.4653682710362572</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.822636352995126</t>
+          <t>5.297166377248052</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.20260057280264362</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.24598562235419</t>
+          <t>15.99757819784864</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.5581795217137148</t>
+          <t>0.6149994264397224</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.49949346023655306</t>
+          <t>0.5481018068821593</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.005649403279681</t>
+          <t>6.172338856837851</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.57972794438178</t>
+          <t>9.495536926182734</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>19.143637583624027</t>
+          <t>18.491211434882004</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.3171555586094756</t>
+          <t>3.3546679722384667</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>6.508687904394648</t>
+          <t>7.656131784053651</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>10.767991401434756</t>
+          <t>7.202091358693308</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>14.419912465236685</t>
+          <t>17.025676863311</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>13.805671081157072</t>
+          <t>8.656687595712967</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>5.565762362355044</t>
+          <t>4.375848467056815</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.755149317860688</t>
+          <t>7.860432173319486</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>5.655974423308284</t>
+          <t>6.219300086838104</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.97723921654271</t>
+          <t>2.1979854125729386</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>27.00451298964859</t>
+          <t>28.31897990225758</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.207990712201346</t>
+          <t>10.31028174623647</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>6.3509603583106005</t>
+          <t>5.641720633859251</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.2660070225724582</t>
+          <t>2.436854571670405</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>3.974592608472599</t>
+          <t>4.252801047097823</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,51 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2.347151088584613</t>
+          <t>1.787654880691924</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>BU_INT_Chichi</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>1.5036398406563283</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>DF_AGL_Kid_Goku</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>17.22485524094945</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.148350354764268</t>
+          <t>5.1097911767253485</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.21106546823655348</t>
+          <t>0.23130088268211232</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.30440908087090124</t>
+          <t>0.3335935986600007</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.45023294336197556</t>
+          <t>0.43320612230368494</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.886751345948129</t>
+          <t>3.163511966122465</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.46260176536422465</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.4037492838456807</t>
+          <t>2.634203196502382</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.2452510468485443</t>
+          <t>2.4605093069841395</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.2777777777777778</t>
+          <t>0.30440908087090124</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.756471486759053</t>
+          <t>0.7320087445396901</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.5965708291023617</t>
+          <t>2.5748454376806587</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.886751345948129</t>
+          <t>3.163511966122465</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.6671871973200014</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.3207501495497921</t>
+          <t>0.3515013295691628</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.6476002595255947</t>
+          <t>0.6279245769581694</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8472367604537439</t>
+          <t>0.8188014344283372</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.8785048196846343</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.5020743146828295</t>
+          <t>3.45959617828694</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.4481632545294802</t>
+          <t>1.4160270041296572</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>3.763376538332825</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.290185032381231</t>
+          <t>3.605623925768521</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.0571957995350694</t>
+          <t>3.0117094647045413</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5.608748328973255</t>
+          <t>6.146474125172224</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.2663928094193209</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>4.995514570902137</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.290185032381231</t>
+          <t>3.605623925768521</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5594279192143468</t>
+          <t>0.5517554967238465</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.46260176536422465</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.26361372900287794</t>
+          <t>0.25538197943196894</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.4357798047714738</t>
+          <t>1.3924896197617855</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.2161002018432159</t>
+          <t>1.1860652118028128</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3.0901408927102922</t>
+          <t>2.997376534362459</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.741383723023766</t>
+          <t>4.752921356981709</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.3306436611283617</t>
+          <t>0.31890474157610726</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.2610572506404627</t>
+          <t>0.2514525966694305</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2908312992409778</t>
+          <t>0.2819949401837128</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.27829116285590055</t>
+          <t>0.268076833119676</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2971784419796575</t>
+          <t>0.28628884687773315</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.29206138974924295</t>
+          <t>0.2835964317900078</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.3729676997640233</t>
+          <t>0.35994189560178724</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.42501697999329396</t>
+          <t>0.41151924765781644</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.48342007519484126</t>
+          <t>0.4671399140430351</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8.94473387189344</t>
+          <t>8.972337885708328</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.746678807640219</t>
+          <t>5.657342790315582</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.2962962962962958</t>
+          <t>1.4205757107308723</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3587297537959491</t>
+          <t>0.34826447889590206</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1.103324400362609</t>
+          <t>1.0651329781457262</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.10434937495214</t>
+          <t>5.025816885146192</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.5149921126125698</t>
+          <t>0.505472241279256</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.230534146315152</t>
+          <t>1.190715762305378</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.743898240591197</t>
+          <t>3.763485849263174</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>1.5817559830612324</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.273126333350474</t>
+          <t>0.2639679692713095</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.3957702516231805</t>
+          <t>0.3839434633864113</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.2777777777777778</t>
+          <t>0.30440908087090124</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.317101598251191</t>
+          <t>1.4433756729740645</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1.1556021239177248</t>
+          <t>1.2663928094193209</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8721788409453686</t>
+          <t>0.8511366464695271</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.7128192420100414</t>
+          <t>0.6900714965953486</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.32354049091618986</t>
+          <t>0.31371671969226345</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.823573839528946</t>
+          <t>6.740318442152397</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.271486721758933</t>
+          <t>3.1922104565367464</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.34244193077931295</t>
+          <t>0.3303574641958599</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.1828894969117507</t>
+          <t>1.2962962962962958</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.842819541173392</t>
+          <t>0.8229642314553349</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.4852255091698625</t>
+          <t>1.4565396715513828</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.30832865869755466</t>
+          <t>0.30620160017605613</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>8.734982021158638</t>
+          <t>8.57062206126565</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.50396934157678</t>
+          <t>2.41012547033572</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.37729316215769426</t>
+          <t>0.3651033410292895</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10.002290985425383</t>
+          <t>10.017300796207039</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.5981894637358895</t>
+          <t>1.5476209612012324</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.079221465633246</t>
+          <t>12.107348771453786</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2.180421494649069</t>
+          <t>2.13326486134147</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.0496328812652562</t>
+          <t>1.0256680540909953</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.9849721851039159</t>
+          <t>1.0794041191831907</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.7585753808601363</t>
+          <t>2.6815339594133625</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.20333168742934404</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>8.931643074437595</t>
+          <t>8.95894895693003</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>4.658203191359647</t>
+          <t>4.564176907467944</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6982086851636129</t>
+          <t>0.6712914952897368</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.4756128886333354</t>
+          <t>0.4596174046687628</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>7.755281366001679</t>
+          <t>7.70981098670779</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>10.479058710929323</t>
+          <t>10.368483019247691</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.773782377370461</t>
+          <t>2.7274117143083902</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.3844972138262874</t>
+          <t>0.3730357624404607</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.057199802326575</t>
+          <t>6.100933938412704</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>5.115815482106296</t>
+          <t>5.021011510341831</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>3.5577018954856525</t>
+          <t>3.457388044172497</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.33528272828819466</t>
+          <t>0.24139226948829218</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.8576182274988603</t>
+          <t>0.8316178029087808</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.932363220173678</t>
+          <t>0.9066866778031439</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.645881877065856</t>
+          <t>2.563191353737057</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.48988068475454455</t>
+          <t>0.4723600248920257</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.2058009496953161</t>
+          <t>1.1802073634222567</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7245083337127021</t>
+          <t>0.7057767394895853</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.3675723993896604</t>
+          <t>0.3538007180231855</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.4653682710362572</t>
+          <t>1.420274550089951</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.297166377248052</t>
+          <t>5.206855091072776</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>15.99757819784864</t>
+          <t>16.00937791198877</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.6149994264397224</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5481018068821593</t>
+          <t>0.6434067289567031</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.172338856837851</t>
+          <t>6.087189867972359</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>9.495536926182734</t>
+          <t>9.287431137906683</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18.491211434882004</t>
+          <t>18.323099028269553</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.3546679722384667</t>
+          <t>3.3073746963071144</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.656131784053651</t>
+          <t>7.643918580158791</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>7.202091358693308</t>
+          <t>7.02218280725348</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.025676863311</t>
+          <t>16.970831032029174</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>8.656687595712967</t>
+          <t>8.533964789315064</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.375848467056815</t>
+          <t>4.339862976320477</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.860432173319486</t>
+          <t>7.892596162422837</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.219300086838104</t>
+          <t>6.15083844164785</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.1979854125729386</t>
+          <t>2.150690785447379</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>28.31897990225758</t>
+          <t>27.74655359406637</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.31028174623647</t>
+          <t>10.411118020271978</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>5.641720633859251</t>
+          <t>5.619778795139041</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.436854571670405</t>
+          <t>2.378676272218593</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.252801047097823</t>
+          <t>4.1664278715909235</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.787654880691924</t>
+          <t>1.774113964407824</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.5036398406563283</t>
+          <t>1.459513189176923</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,161 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>17.22485524094945</t>
+          <t>16.78897592422427</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>F2P_STR_Goku_Black</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>0.975139350229086</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Gotenks</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Jackie_Chun</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>F2PLR_AGL_SS_Bardock</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>BU_PHY_Android_18</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>5.010623465139139</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>DF_STR_Cell_Perfect_Form</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>15.71384425906206</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Para_Para_Bros</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D353"/>
+  <dimension ref="A1:D361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.1097911767253485</t>
+          <t>5.064508719172281</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.43320612230368494</t>
+          <t>0.38346037001470584</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.7320087445396901</t>
+          <t>0.6786465660021828</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.5748454376806587</t>
+          <t>4.175550618586431</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.6279245769581694</t>
+          <t>0.58217942169996</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8188014344283372</t>
+          <t>0.7505795728184741</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.45959617828694</t>
+          <t>3.2400493314217</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.4160270041296572</t>
+          <t>1.3334682859748073</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.763376538332825</t>
+          <t>5.496473049264533</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.605623925768521</t>
+          <t>6.179575255637341</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.0117094647045413</t>
+          <t>2.9518955804034412</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.995514570902137</t>
+          <t>4.911890486509735</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.605623925768521</t>
+          <t>2.4627890622114257</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5517554967238465</t>
+          <t>0.5229736565604937</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.25538197943196894</t>
+          <t>0.2255309713110849</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.3924896197617855</t>
+          <t>1.227696399101349</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.1860652118028128</t>
+          <t>1.13075885376783</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.997376534362459</t>
+          <t>2.7452662063221283</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.752921356981709</t>
+          <t>4.870147912049184</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.31890474157610726</t>
+          <t>0.2662230503627709</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.2514525966694305</t>
+          <t>0.20821378390405748</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2819949401837128</t>
+          <t>0.24565671356849042</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.268076833119676</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.28628884687773315</t>
+          <t>0.23848970482277812</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.2835964317900078</t>
+          <t>0.24871050969145506</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.35994189560178724</t>
+          <t>0.2999107552556894</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.41151924765781644</t>
+          <t>0.35101343464386525</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4671399140430351</t>
+          <t>0.43021078393206597</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8.972337885708328</t>
+          <t>9.26037733728218</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.657342790315582</t>
+          <t>5.6031036623021375</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.34826447889590206</t>
+          <t>0.3171940153404691</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1.0651329781457262</t>
+          <t>0.9218338537781517</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.025816885146192</t>
+          <t>5.07409369519522</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.505472241279256</t>
+          <t>0.3771135361347633</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.190715762305378</t>
+          <t>1.097181060957338</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.763485849263174</t>
+          <t>3.852799370971762</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.2639679692713095</t>
+          <t>0.23533333467836112</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.3839434633864113</t>
+          <t>0.34258376490753334</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8511366464695271</t>
+          <t>0.8410929678079326</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.6900714965953486</t>
+          <t>0.6291336671747167</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.31371671969226345</t>
+          <t>0.29474172675266885</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.740318442152397</t>
+          <t>6.619820832658048</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.1922104565367464</t>
+          <t>3.156732334402836</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.3303574641958599</t>
+          <t>0.3207501495497921</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.8229642314553349</t>
+          <t>0.7105174489561629</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.4565396715513828</t>
+          <t>1.4324931367873273</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.30620160017605613</t>
+          <t>0.2793025161978706</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>8.57062206126565</t>
+          <t>7.747501325241572</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.41012547033572</t>
+          <t>2.172624219253894</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.3651033410292895</t>
+          <t>0.29470283086379645</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10.017300796207039</t>
+          <t>10.52585599392259</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.5476209612012324</t>
+          <t>1.4750199503836559</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.107348771453786</t>
+          <t>12.357524727778177</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2.13326486134147</t>
+          <t>2.1338643957085117</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.0256680540909953</t>
+          <t>1.1743280809287082</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.6815339594133625</t>
+          <t>2.572506361528603</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>8.95894895693003</t>
+          <t>9.066639437090629</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>4.564176907467944</t>
+          <t>4.253797215511758</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6712914952897368</t>
+          <t>0.581017346078505</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.4596174046687628</t>
+          <t>0.4055706726573892</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>7.70981098670779</t>
+          <t>7.895415655537128</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>10.368483019247691</t>
+          <t>9.913556435035101</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.7274117143083902</t>
+          <t>2.6310049511576747</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.3730357624404607</t>
+          <t>0.3128879659773654</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.100933938412704</t>
+          <t>6.416561547585242</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>5.021011510341831</t>
+          <t>4.863064306950799</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>3.457388044172497</t>
+          <t>3.03758520938641</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.24139226948829218</t>
+          <t>0.21114072383807292</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.8316178029087808</t>
+          <t>0.7954363457314444</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.9066866778031439</t>
+          <t>0.8742987529259798</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.563191353737057</t>
+          <t>2.30933010816998</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.4723600248920257</t>
+          <t>0.4248964432514785</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.1802073634222567</t>
+          <t>1.1404700885132921</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7057767394895853</t>
+          <t>0.6585845799537391</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.3538007180231855</t>
+          <t>0.2974224555313996</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.420274550089951</t>
+          <t>1.322145495916371</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.206855091072776</t>
+          <t>5.151761005092862</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.00937791198877</t>
+          <t>16.487115065099374</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.6434067289567031</t>
+          <t>0.61083375986978</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.087189867972359</t>
+          <t>5.993267240635909</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>9.287431137906683</t>
+          <t>8.389755290932648</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18.323099028269553</t>
+          <t>18.205272537419077</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.3073746963071144</t>
+          <t>3.18284939039927</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.643918580158791</t>
+          <t>7.555257772604542</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>7.02218280725348</t>
+          <t>6.599747298265699</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>16.970831032029174</t>
+          <t>17.5239524848022</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>8.533964789315064</t>
+          <t>8.691928538094189</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.339862976320477</t>
+          <t>4.25492248957655</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.892596162422837</t>
+          <t>7.931347340045062</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.15083844164785</t>
+          <t>6.140641633849044</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.150690785447379</t>
+          <t>2.1204673744426703</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>27.74655359406637</t>
+          <t>26.244864296927734</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.411118020271978</t>
+          <t>10.751275187247678</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>5.619778795139041</t>
+          <t>5.869289490370619</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.378676272218593</t>
+          <t>2.2905187797382625</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.1664278715909235</t>
+          <t>4.141091986662926</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.774113964407824</t>
+          <t>1.493159816496397</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.459513189176923</t>
+          <t>1.231863674654132</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>16.78897592422427</t>
+          <t>15.89588174507386</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.975139350229086</t>
+          <t>0.9056354272361974</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.010623465139139</t>
+          <t>4.591148582901005</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>15.71384425906206</t>
+          <t>14.7570831304079</t>
         </is>
       </c>
     </row>
@@ -8189,6 +8189,182 @@
         </is>
       </c>
       <c r="D353" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>BU_PHY_SS_Kaioken_Goku</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>BU_STR_Paikuhan</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>LR_PHY_Paikuhan</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>34.38736678404419</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>BU_AGL_Piccolo</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2.296781222681973</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>BU_PHY_Magetta</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>DF_INT_Hit</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>30.01588952780522</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>DF_TEQ_SSGSS_Kaioken_Goku</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>21.74120759306507</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>DF_AGL_SSGSS_Kaioken_Goku</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.064508719172281</t>
+          <t>5.115465800333862</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.23130088268211232</t>
+          <t>0.25347632076680376</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.38346037001470584</t>
+          <t>0.3644350876632149</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.163511966122465</t>
+          <t>3.466806371753173</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.46260176536422465</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.634203196502382</t>
+          <t>2.886751345948129</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.4605093069841395</t>
+          <t>2.6964049558080228</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.30440908087090124</t>
+          <t>0.3335935986600007</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.6786465660021828</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.175550618586431</t>
+          <t>4.171696068981469</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.163511966122465</t>
+          <t>3.466806371753173</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.3655761147090257</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.8012497612818937</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.3515013295691628</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.58217942169996</t>
+          <t>0.5676110228331634</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.7505795728184741</t>
+          <t>0.7287760928014371</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.2400493314217</t>
+          <t>3.22750693039068</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.3334682859748073</t>
+          <t>1.3180596521288082</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.6666666666666665</t>
+          <t>1.8264544852254074</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.496473049264533</t>
+          <t>5.548913642584572</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.179575255637341</t>
+          <t>6.150416627073601</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.9518955804034412</t>
+          <t>2.9191135239553514</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6.146474125172224</t>
+          <t>6.735753140545633</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.911890486509735</t>
+          <t>4.920070614381428</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.4627890622114257</t>
+          <t>2.458228100066297</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5229736565604937</t>
+          <t>0.5160810086423834</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.2255309713110849</t>
+          <t>0.21580506869300287</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.227696399101349</t>
+          <t>1.1869929854821306</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.13075885376783</t>
+          <t>1.071913391759753</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.7452662063221283</t>
+          <t>2.598464431638534</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.870147912049184</t>
+          <t>4.883013866098651</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2662230503627709</t>
+          <t>0.2500384830923253</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.20821378390405748</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.24565671356849042</t>
+          <t>0.23344357618825323</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.23848970482277812</t>
+          <t>0.22286061669014093</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.24871050969145506</t>
+          <t>0.23787876058242025</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2999107552556894</t>
+          <t>0.28122979011747223</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.35101343464386525</t>
+          <t>0.3312832763265048</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.43021078393206597</t>
+          <t>0.4017834461802574</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>9.26037733728218</t>
+          <t>9.245473650344351</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.6031036623021375</t>
+          <t>5.585466047493879</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.4205757107308723</t>
+          <t>1.5567701270800032</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3171940153404691</t>
+          <t>0.3050232705384787</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.9218338537781517</t>
+          <t>0.86762962456038</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.07409369519522</t>
+          <t>5.088915463590048</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.3771135361347633</t>
+          <t>0.36506578452846195</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.097181060957338</t>
+          <t>1.065784963443189</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.852799370971762</t>
+          <t>3.9012871849860336</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>4.9939565582866425</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.23533333467836112</t>
+          <t>0.228848101167564</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.34258376490753334</t>
+          <t>0.3288134345106524</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.30440908087090124</t>
+          <t>0.3335935986600007</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>1.5817559830612324</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1.2663928094193209</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20817079441390107</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8410929678079326</t>
+          <t>0.8333185018118512</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.6291336671747167</t>
+          <t>0.5958844958632094</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.29474172675266885</t>
+          <t>0.28849617282870454</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.619820832658048</t>
+          <t>6.692553758589616</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.156732334402836</t>
+          <t>2.9879488637227976</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.3207501495497921</t>
+          <t>0.3515013295691628</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.2962962962962958</t>
+          <t>1.4205757107308723</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.7105174489561629</t>
+          <t>0.6932148991050822</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.4324931367873273</t>
+          <t>1.4173205489033176</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2793025161978706</t>
+          <t>0.27927148942983493</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>7.747501325241572</t>
+          <t>7.664778834820622</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.172624219253894</t>
+          <t>2.092121280692673</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.29470283086379645</t>
+          <t>0.27615509956497203</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10.52585599392259</t>
+          <t>10.597562101023712</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.4750199503836559</t>
+          <t>1.4436080553523452</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.357524727778177</t>
+          <t>12.441379099340011</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2.1338643957085117</t>
+          <t>1.6533872191049066</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1.1743280809287082</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.0794041191831907</t>
+          <t>1.1828894969117507</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.572506361528603</t>
+          <t>2.5011246979168136</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9.066639437090629</t>
+          <t>9.114602076706532</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>4.253797215511758</t>
+          <t>4.118051958521447</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.581017346078505</t>
+          <t>0.5465512964263467</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.4055706726573892</t>
+          <t>0.38862347481697446</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>7.895415655537128</t>
+          <t>8.024274299627852</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.913556435035101</t>
+          <t>9.555081452450288</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.6310049511576747</t>
+          <t>2.603659037714796</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.3128879659773654</t>
+          <t>0.29349821001811494</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.416561547585242</t>
+          <t>6.487232644811542</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4.863064306950799</t>
+          <t>4.794027336717848</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>3.03758520938641</t>
+          <t>2.990138839457762</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.21114072383807292</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.7954363457314444</t>
+          <t>0.7762872908308381</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.8742987529259798</t>
+          <t>0.859992256244849</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.30933010816998</t>
+          <t>2.226246633585183</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.4248964432514785</t>
+          <t>0.405996393274927</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.1404700885132921</t>
+          <t>1.113418444305252</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6585845799537391</t>
+          <t>0.6414080804377651</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2974224555313996</t>
+          <t>0.279513903433363</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.322145495916371</t>
+          <t>1.285877399057601</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.151761005092862</t>
+          <t>5.083878818314353</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.487115065099374</t>
+          <t>16.555149670977443</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.61083375986978</t>
+          <t>0.5958575939888231</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>5.993267240635909</t>
+          <t>5.97248086428023</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>8.389755290932648</t>
+          <t>8.165600830294125</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18.205272537419077</t>
+          <t>17.890370273739034</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.18284939039927</t>
+          <t>3.1659159699899044</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.555257772604542</t>
+          <t>7.63690450149447</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.599747298265699</t>
+          <t>6.485873160704825</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.5239524848022</t>
+          <t>17.4664364025448</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>8.691928538094189</t>
+          <t>8.6915975498883</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.25492248957655</t>
+          <t>4.254000640897765</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.931347340045062</t>
+          <t>7.953193048143646</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.140641633849044</t>
+          <t>6.132201281672706</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.1204673744426703</t>
+          <t>2.111952932385</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>26.244864296927734</t>
+          <t>26.1447906964883</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.751275187247678</t>
+          <t>10.885042886306657</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>5.869289490370619</t>
+          <t>5.763346581903036</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.2905187797382625</t>
+          <t>2.141364605665139</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.141091986662926</t>
+          <t>4.132850063831648</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.493159816496397</t>
+          <t>1.474224318428229</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.231863674654132</t>
+          <t>1.183091590976732</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>15.89588174507386</t>
+          <t>15.847789955456882</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.9056354272361974</t>
+          <t>0.8895336582668022</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.591148582901005</t>
+          <t>4.425785480915729</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>14.7570831304079</t>
+          <t>14.61765407928939</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>34.38736678404419</t>
+          <t>33.65071579353501</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2.296781222681973</t>
+          <t>2.192864030300972</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>30.01588952780522</t>
+          <t>58.209040570612274</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>21.74120759306507</t>
+          <t>14.84559696142368</t>
         </is>
       </c>
     </row>
@@ -8367,6 +8367,138 @@
       <c r="D361" t="inlineStr">
         <is>
           <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>F2P_STR_Tien</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>F2PLR_STR_Mercenary_Tao</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>F2P_INT_SS_Future_Gohan</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>0.7307605124613712</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Boujack</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Mecha_Frieza</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CLR_PHY_SS2_Caulifla_Kale</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>14.38824648440677</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.115465800333862</t>
+          <t>5.0606226089739685</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3644350876632149</t>
+          <t>0.3605759356505258</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.171696068981469</t>
+          <t>4.214855077218388</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.466806371753173</t>
+          <t>17.434919509342816</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.5676110228331634</t>
+          <t>0.5586793142970299</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.7287760928014371</t>
+          <t>0.7026007960080971</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.22750693039068</t>
+          <t>3.138430595540349</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.3180596521288082</t>
+          <t>1.2851814653880562</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.548913642584572</t>
+          <t>5.541474699070654</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.150416627073601</t>
+          <t>6.103638792654679</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.9191135239553514</t>
+          <t>2.9472898109265095</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.920070614381428</t>
+          <t>4.9369323810577885</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.458228100066297</t>
+          <t>2.4677187350622063</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5160810086423834</t>
+          <t>0.5169362667957346</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.21580506869300287</t>
+          <t>0.21422835064360005</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.1869929854821306</t>
+          <t>1.1686013209994512</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.071913391759753</t>
+          <t>1.0883584965951858</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.598464431638534</t>
+          <t>2.5930364463617592</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.883013866098651</t>
+          <t>4.820539392994206</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2500384830923253</t>
+          <t>0.2420191886925882</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.23344357618825323</t>
+          <t>0.22702047174595535</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.22286061669014093</t>
+          <t>0.21573068858525893</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.23787876058242025</t>
+          <t>0.2316059319042534</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.28122979011747223</t>
+          <t>0.2723113366998503</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.3312832763265048</t>
+          <t>0.32591454937541564</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4017834461802574</t>
+          <t>0.39270969918746557</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>9.245473650344351</t>
+          <t>9.207796159736823</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.585466047493879</t>
+          <t>5.584871561711122</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3050232705384787</t>
+          <t>0.3009890695541519</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.86762962456038</t>
+          <t>0.854586274491064</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.088915463590048</t>
+          <t>5.094882517071628</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.36506578452846195</t>
+          <t>0.36019455449775806</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.065784963443189</t>
+          <t>1.047395615938452</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.9012871849860336</t>
+          <t>3.9275577291176473</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4.9939565582866425</t>
+          <t>4.730535933042728</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.228848101167564</t>
+          <t>0.21800084596242178</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.3288134345106524</t>
+          <t>0.3243780436059737</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8333185018118512</t>
+          <t>0.8343720142143859</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5958844958632094</t>
+          <t>0.591536981134159</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.28849617282870454</t>
+          <t>0.2831822851814172</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.692553758589616</t>
+          <t>6.633340146564193</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2.9879488637227976</t>
+          <t>3.1022939179357127</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.6932148991050822</t>
+          <t>0.6905285669533175</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.4173205489033176</t>
+          <t>1.412354483737026</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.27927148942983493</t>
+          <t>0.27155013538773876</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>7.664778834820622</t>
+          <t>7.47200190820389</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.092121280692673</t>
+          <t>2.03208685318577</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.27615509956497203</t>
+          <t>0.2672357703032776</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10.597562101023712</t>
+          <t>10.691573249031272</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.4436080553523452</t>
+          <t>1.4259084461702682</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.441379099340011</t>
+          <t>12.554225955914553</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>1.6533872191049066</t>
+          <t>1.441494679199058</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.5011246979168136</t>
+          <t>2.5066184048677584</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9.114602076706532</t>
+          <t>9.130636980433081</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>4.118051958521447</t>
+          <t>4.1644128202390736</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5465512964263467</t>
+          <t>0.5369916917262897</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.38862347481697446</t>
+          <t>0.37922549699852054</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>8.024274299627852</t>
+          <t>8.117796775285477</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.555081452450288</t>
+          <t>9.66278568226636</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.603659037714796</t>
+          <t>2.5716749318750405</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.29349821001811494</t>
+          <t>0.28669020813860774</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.487232644811542</t>
+          <t>6.587737591989622</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4.794027336717848</t>
+          <t>4.768077413527978</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.990138839457762</t>
+          <t>2.874788903235739</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.7762872908308381</t>
+          <t>0.7664270726599696</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.859992256244849</t>
+          <t>0.8483739046786671</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.226246633585183</t>
+          <t>2.186584409775653</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.405996393274927</t>
+          <t>0.40243981924232247</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.113418444305252</t>
+          <t>1.1097785581861839</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6414080804377651</t>
+          <t>0.6316229742739923</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.279513903433363</t>
+          <t>0.2693003429645484</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.285877399057601</t>
+          <t>1.2743295490951623</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.083878818314353</t>
+          <t>5.131792625819012</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.555149670977443</t>
+          <t>16.731723171522226</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5958575939888231</t>
+          <t>0.5871768134646951</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>5.97248086428023</t>
+          <t>6.033096173558272</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>8.165600830294125</t>
+          <t>10.74745035096173</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>17.890370273739034</t>
+          <t>18.07950799062408</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.1659159699899044</t>
+          <t>3.1769025451359765</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.63690450149447</t>
+          <t>7.535455346059519</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.485873160704825</t>
+          <t>6.486811250030035</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.4664364025448</t>
+          <t>17.554906892789354</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>8.6915975498883</t>
+          <t>8.440022438170189</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.254000640897765</t>
+          <t>4.219217474818955</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.953193048143646</t>
+          <t>7.992153454460699</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.132201281672706</t>
+          <t>6.173337844305144</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.111952932385</t>
+          <t>2.0971303315508205</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>26.1447906964883</t>
+          <t>26.15909904575567</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.885042886306657</t>
+          <t>10.874479692685306</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>5.763346581903036</t>
+          <t>5.756985094558729</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.141364605665139</t>
+          <t>2.140581016548841</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.132850063831648</t>
+          <t>4.128768666934561</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.474224318428229</t>
+          <t>1.436276267097917</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.183091590976732</t>
+          <t>1.576132202644427</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>15.847789955456882</t>
+          <t>15.39300492857368</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.8895336582668022</t>
+          <t>0.8742389788016768</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.425785480915729</t>
+          <t>4.345897870004435</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>14.61765407928939</t>
+          <t>14.58097448912503</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>33.65071579353501</t>
+          <t>33.61435211534555</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2.192864030300972</t>
+          <t>2.168424155594008</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>58.209040570612274</t>
+          <t>29.934171664873688</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>14.84559696142368</t>
+          <t>14.827726678464032</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.7307605124613712</t>
+          <t>0.7175744651657553</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>14.38824648440677</t>
+          <t>14.93954707339017</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D367"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0606226089739685</t>
+          <t>5.029637233690881</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3605759356505258</t>
+          <t>0.35460791985559187</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.214855077218388</t>
+          <t>4.215705312342196</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17.434919509342816</t>
+          <t>9.127296037223486</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.5586793142970299</t>
+          <t>0.5505170125199683</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.7026007960080971</t>
+          <t>0.6926913140576241</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.138430595540349</t>
+          <t>3.103754201996164</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.2851814653880562</t>
+          <t>1.2701875758856724</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.541474699070654</t>
+          <t>5.547539883660526</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.103638792654679</t>
+          <t>6.102794885784954</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.9472898109265095</t>
+          <t>2.9145528216265006</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.9369323810577885</t>
+          <t>4.967595019872334</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.4677187350622063</t>
+          <t>2.475229643293604</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5169362667957346</t>
+          <t>0.5120691147954334</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.21422835064360005</t>
+          <t>0.21153268601390107</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.1686013209994512</t>
+          <t>1.159713843508305</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.0883584965951858</t>
+          <t>1.07977110240242</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.5930364463617592</t>
+          <t>2.5702144014947295</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.820539392994206</t>
+          <t>4.832905179121738</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2420191886925882</t>
+          <t>0.23705833784967606</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.22702047174595535</t>
+          <t>0.22291600474572043</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.21573068858525893</t>
+          <t>0.2106891244012182</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.2316059319042534</t>
+          <t>0.22739328862222036</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2723113366998503</t>
+          <t>0.26587702447804235</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.32591454937541564</t>
+          <t>0.3207501495497921</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.39270969918746557</t>
+          <t>0.3855535700591768</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>9.207796159736823</t>
+          <t>9.221331667244492</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.584871561711122</t>
+          <t>5.53644399613817</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3009890695541519</t>
+          <t>0.2984496022696028</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.854586274491064</t>
+          <t>0.8396872445526161</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.094882517071628</t>
+          <t>5.051919945888422</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.36019455449775806</t>
+          <t>0.35589291390942485</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.047395615938452</t>
+          <t>1.035821722191737</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.9275577291176473</t>
+          <t>3.9422159760295115</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4.730535933042728</t>
+          <t>4.74727219617907</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.21800084596242178</t>
+          <t>0.21432431662102122</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.3243780436059737</t>
+          <t>0.3189321180091081</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8343720142143859</t>
+          <t>0.82643571363379</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.591536981134159</t>
+          <t>0.5779452541434835</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2831822851814172</t>
+          <t>0.27980085262951615</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.633340146564193</t>
+          <t>6.619425873249263</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.1022939179357127</t>
+          <t>3.024218214612237</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.6905285669533175</t>
+          <t>0.6805639044929116</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.412354483737026</t>
+          <t>1.383548886201858</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.27155013538773876</t>
+          <t>0.2669626822789617</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>7.47200190820389</t>
+          <t>7.380452710130515</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.03208685318577</t>
+          <t>1.9971729369751183</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2672357703032776</t>
+          <t>0.2612755510866797</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10.691573249031272</t>
+          <t>10.747797153265331</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.4259084461702682</t>
+          <t>1.4151350474775861</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.554225955914553</t>
+          <t>12.637486132097138</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>1.441494679199058</t>
+          <t>1.429583118141326</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.5066184048677584</t>
+          <t>2.476108796950359</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9.130636980433081</t>
+          <t>9.156829453293433</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>4.1644128202390736</t>
+          <t>4.071295337460333</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5369916917262897</t>
+          <t>0.5243744141762279</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.37922549699852054</t>
+          <t>0.3749742509642245</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>8.117796775285477</t>
+          <t>8.096035678342826</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.66278568226636</t>
+          <t>9.62889793319479</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.5716749318750405</t>
+          <t>2.5566804028754992</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.28669020813860774</t>
+          <t>0.2808039693255893</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.587737591989622</t>
+          <t>6.612745754978659</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4.768077413527978</t>
+          <t>4.727374623461534</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.874788903235739</t>
+          <t>2.852537688668249</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.7664270726599696</t>
+          <t>0.7570996997906809</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.8483739046786671</t>
+          <t>0.8324235544451652</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.186584409775653</t>
+          <t>2.135234942226825</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.40243981924232247</t>
+          <t>0.3958859604430158</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.1097785581861839</t>
+          <t>1.090154639984042</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6316229742739923</t>
+          <t>0.6181589576670299</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2693003429645484</t>
+          <t>0.2627536175540617</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.2743295490951623</t>
+          <t>1.2578010735329699</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.131792625819012</t>
+          <t>5.093220262132031</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.731723171522226</t>
+          <t>16.744533548184656</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5871768134646951</t>
+          <t>0.5762524308573722</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.033096173558272</t>
+          <t>6.029791070613891</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>10.74745035096173</t>
+          <t>10.58316497690881</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18.07950799062408</t>
+          <t>18.027256838636482</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.1769025451359765</t>
+          <t>3.1719491437306813</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.535455346059519</t>
+          <t>7.412070969354218</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.486811250030035</t>
+          <t>6.420317102852038</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.554906892789354</t>
+          <t>17.562662222659633</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>8.440022438170189</t>
+          <t>8.430203194793322</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.219217474818955</t>
+          <t>4.223040334237534</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.992153454460699</t>
+          <t>7.97969532326898</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.173337844305144</t>
+          <t>6.156806778772114</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.0971303315508205</t>
+          <t>2.079224865766065</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>26.15909904575567</t>
+          <t>25.97905493261966</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.874479692685306</t>
+          <t>10.935465043934606</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>5.756985094558729</t>
+          <t>5.793123784853961</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.140581016548841</t>
+          <t>2.1359334576673237</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.128768666934561</t>
+          <t>4.121352388747133</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.436276267097917</t>
+          <t>1.4120180645978</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.576132202644427</t>
+          <t>1.538323907633113</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>15.39300492857368</t>
+          <t>15.25066518687007</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.8742389788016768</t>
+          <t>0.8595299250167244</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.345897870004435</t>
+          <t>4.246216139991666</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>14.58097448912503</t>
+          <t>14.46199402155039</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>33.61435211534555</t>
+          <t>33.21244239442409</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2.168424155594008</t>
+          <t>2.135456693435359</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>29.934171664873688</t>
+          <t>29.50119916202205</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>14.827726678464032</t>
+          <t>15.046619085838316</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.7175744651657553</t>
+          <t>0.7112369887225177</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,51 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>14.93954707339017</t>
+          <t>14.84584519363588</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>BU_TEQ_General_Blue</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>8.129376446536565</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>DF_PHY_Mercenary_Tao</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>4.834630458528981</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D369"/>
+  <dimension ref="A1:D371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.029637233690881</t>
+          <t>4.8521676374782</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.25347632076680376</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.3655761147090257</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.2018746419228403</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.35460791985559187</t>
+          <t>0.3397760469484014</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.466806371753173</t>
+          <t>3.7991784282579633</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.886751345948129</t>
+          <t>3.163511966122465</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.6964049558080228</t>
+          <t>2.954916555311748</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.8012497612818937</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.215705312342196</t>
+          <t>3.0607830406604393</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.127296037223486</t>
+          <t>9.216863847973123</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.3852007079725748</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.5505170125199683</t>
+          <t>0.5222711869203575</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.6926913140576241</t>
+          <t>0.6918388324536968</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.6088181617418025</t>
+          <t>0.6671871973200014</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.054503988707488</t>
+          <t>12.396334601423781</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.103754201996164</t>
+          <t>2.9545525828607015</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.2701875758856724</t>
+          <t>1.2104817764579798</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>2.0015615919600047</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.547539883660526</t>
+          <t>5.5482511213539</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.102794885784954</t>
+          <t>6.064478080133986</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.9145528216265006</t>
+          <t>2.8483989604339595</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6.735753140545633</t>
+          <t>7.381527920952416</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.967595019872334</t>
+          <t>5.6871819613714765</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.475229643293604</t>
+          <t>2.4637389775109058</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5120691147954334</t>
+          <t>0.4961068170574896</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.21153268601390107</t>
+          <t>0.23130088268211232</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.159713843508305</t>
+          <t>1.1274319351737374</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.07977110240242</t>
+          <t>1.0837746548340759</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.5702144014947295</t>
+          <t>2.5547835394340286</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.832905179121738</t>
+          <t>4.768451343359651</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.23705833784967606</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.22291600474572043</t>
+          <t>0.21642680699454572</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2106891244012182</t>
+          <t>0.2022561587285118</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.22739328862222036</t>
+          <t>0.22052472189251165</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.26587702447804235</t>
+          <t>0.2585968572045896</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.3207501495497921</t>
+          <t>0.3515013295691628</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.3855535700591768</t>
+          <t>0.39177697918573645</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>9.221331667244492</t>
+          <t>8.96883253814218</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.53644399613817</t>
+          <t>5.75396725250719</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.5567701270800032</t>
+          <t>1.7060218686421196</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.6666666666666665</t>
+          <t>1.8264544852254074</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2984496022696028</t>
+          <t>0.28616177176716917</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.8396872445526161</t>
+          <t>0.8112100922482781</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.051919945888422</t>
+          <t>4.841363793005801</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.35589291390942485</t>
+          <t>0.35173015111792605</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.035821722191737</t>
+          <t>1.0035490902871829</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.9422159760295115</t>
+          <t>3.992885954038373</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4.74727219617907</t>
+          <t>4.734923024941029</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.21432431662102122</t>
+          <t>0.2189390630842381</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.3189321180091081</t>
+          <t>0.30933823954032336</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>1.7334031858765866</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.20817079441390107</t>
+          <t>0.22812868869012348</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.82643571363379</t>
+          <t>0.8035486658456465</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5779452541434835</t>
+          <t>0.5538225688614105</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.27980085262951615</t>
+          <t>0.2576565292219586</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.619425873249263</t>
+          <t>6.923364607276653</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.024218214612237</t>
+          <t>2.5817131447294512</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.3515013295691628</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.4205757107308723</t>
+          <t>1.5567701270800032</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.6805639044929116</t>
+          <t>0.6762114182717297</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.383548886201858</t>
+          <t>1.3590489354895654</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2669626822789617</t>
+          <t>0.25458205339553874</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>7.380452710130515</t>
+          <t>6.991633374802774</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.9971729369751183</t>
+          <t>1.8743017731590432</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2612755510866797</t>
+          <t>0.25277995719301816</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>10.747797153265331</t>
+          <t>9.303196457047441</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.4151350474775861</t>
+          <t>1.4195995936751928</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.637486132097138</t>
+          <t>12.769153489437684</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>1.429583118141326</t>
+          <t>1.3974273039088192</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.1828894969117507</t>
+          <t>1.2962962962962958</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.476108796950359</t>
+          <t>2.449784568228828</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9.156829453293433</t>
+          <t>9.11707297224433</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>4.071295337460333</t>
+          <t>4.055925353170053</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5243744141762279</t>
+          <t>0.4968437264042267</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.3749742509642245</t>
+          <t>0.36479822551582186</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>8.096035678342826</t>
+          <t>8.38932550731278</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.62889793319479</t>
+          <t>9.667015961302141</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.5566804028754992</t>
+          <t>2.465580669066376</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2808039693255893</t>
+          <t>0.2690230308098341</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.612745754978659</t>
+          <t>6.624256610917513</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4.727374623461534</t>
+          <t>4.626750434621737</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.852537688668249</t>
+          <t>2.706336160084895</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.7570996997906809</t>
+          <t>0.7145062658362322</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.8324235544451652</t>
+          <t>0.784899261713575</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.135234942226825</t>
+          <t>2.108856194287287</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3958859604430158</t>
+          <t>0.3756797203473123</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.090154639984042</t>
+          <t>1.1198369204591205</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6181589576670299</t>
+          <t>0.5849690972309789</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2627536175540617</t>
+          <t>0.2696404955808023</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.2578010735329699</t>
+          <t>1.24365405381114</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7195,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.093220262132031</t>
+          <t>5.920180588156882</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.744533548184656</t>
+          <t>16.705728446283985</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5762524308573722</t>
+          <t>0.5819503664771211</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.029791070613891</t>
+          <t>6.099992565516384</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>10.58316497690881</t>
+          <t>7.680737902620337</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18.027256838636482</t>
+          <t>18.20605838442988</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.1719491437306813</t>
+          <t>3.2234887355389192</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.412070969354218</t>
+          <t>7.16676122377081</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.420317102852038</t>
+          <t>6.533930141242295</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.562662222659633</t>
+          <t>17.260681142803904</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>8.430203194793322</t>
+          <t>7.968144156190192</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.223040334237534</t>
+          <t>4.280567628972907</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.97969532326898</t>
+          <t>7.153168473583053</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.156806778772114</t>
+          <t>6.126997457777237</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.079224865766065</t>
+          <t>2.0240203579361413</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>25.97905493261966</t>
+          <t>27.72088296188101</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.935465043934606</t>
+          <t>10.582280317660581</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>5.793123784853961</t>
+          <t>6.232692999349936</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.1359334576673237</t>
+          <t>2.1297028206908686</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.121352388747133</t>
+          <t>4.116522643748734</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.4120180645978</t>
+          <t>1.587589617241351</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.538323907633113</t>
+          <t>1.461455527212997</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>15.25066518687007</t>
+          <t>15.85145844046337</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.8595299250167244</t>
+          <t>0.8523036777253646</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.246216139991666</t>
+          <t>4.033463991694138</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>14.46199402155039</t>
+          <t>19.26216765481304</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>33.21244239442409</t>
+          <t>33.77134617137299</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2.135456693435359</t>
+          <t>0.5365570326868889</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>29.50119916202205</t>
+          <t>28.758711005361402</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>15.046619085838316</t>
+          <t>25.996550250368823</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.7112369887225177</t>
+          <t>0.7079968205592471</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>14.84584519363588</t>
+          <t>15.14826212909517</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>8.129376446536565</t>
+          <t>7.761568124299892</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,51 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>4.834630458528981</t>
+          <t>4.768068741763198</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>BU_INT_Burter_Jeice</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>0.6020162943306347</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>LR_STR_Tien</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>5.842984355011708</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D371"/>
+  <dimension ref="A1:D373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.8521676374782</t>
+          <t>4.925526245728369</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3397760469484014</t>
+          <t>0.3419096495523001</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.0607830406604393</t>
+          <t>3.042297512899862</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.216863847973123</t>
+          <t>9.128717945362556</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.5222711869203575</t>
+          <t>0.528221610355193</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.6918388324536968</t>
+          <t>0.7046705599859742</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12.396334601423781</t>
+          <t>12.400473208132933</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.9545525828607015</t>
+          <t>2.999988346087736</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.2104817764579798</t>
+          <t>1.2324004652256257</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.5482511213539</t>
+          <t>5.55532620910623</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.064478080133986</t>
+          <t>6.060846949401306</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.8483989604339595</t>
+          <t>2.87414369378396</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.6871819613714765</t>
+          <t>5.63993729495337</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.4637389775109058</t>
+          <t>2.444055180377</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.4961068170574896</t>
+          <t>0.49856573425630196</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.1274319351737374</t>
+          <t>1.1213113085547128</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.0837746548340759</t>
+          <t>1.086083818289579</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.5547835394340286</t>
+          <t>2.5605425440362835</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.768451343359651</t>
+          <t>4.750855163659317</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.21642680699454572</t>
+          <t>0.21948996538872007</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2022561587285118</t>
+          <t>0.20524253108416413</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.22052472189251165</t>
+          <t>0.22426716539791092</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2585968572045896</t>
+          <t>0.2621270557406109</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.39177697918573645</t>
+          <t>0.3966649104145783</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8.96883253814218</t>
+          <t>8.873550052605083</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.75396725250719</t>
+          <t>5.785748386516909</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.28616177176716917</t>
+          <t>0.28587472373975076</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.8112100922482781</t>
+          <t>0.8077099557814891</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4.841363793005801</t>
+          <t>5.358381405127737</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.35173015111792605</t>
+          <t>0.35320834806276896</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.0035490902871829</t>
+          <t>1.0181468778177802</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.992885954038373</t>
+          <t>3.980676533207918</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4.734923024941029</t>
+          <t>4.709387265348476</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.2189390630842381</t>
+          <t>0.22028719131074484</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.30933823954032336</t>
+          <t>0.31250323917696676</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8035486658456465</t>
+          <t>0.8133311376751888</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5538225688614105</t>
+          <t>0.5609350589272633</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2576565292219586</t>
+          <t>0.2583391273399265</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.923364607276653</t>
+          <t>7.057954688433551</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2.5817131447294512</t>
+          <t>2.6188049903870274</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.6762114182717297</t>
+          <t>0.6877814666924529</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.3590489354895654</t>
+          <t>1.387393734443715</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.25458205339553874</t>
+          <t>0.2603042840914327</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>6.991633374802774</t>
+          <t>7.039361649490607</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.8743017731590432</t>
+          <t>1.900644451859908</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.25277995719301816</t>
+          <t>0.2556471491708957</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>9.303196457047441</t>
+          <t>9.938154019577105</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.4195995936751928</t>
+          <t>1.4276012820379478</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.769153489437684</t>
+          <t>12.680030212103844</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>1.3974273039088192</t>
+          <t>1.4012804980569422</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.449784568228828</t>
+          <t>2.4620371424529996</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9.11707297224433</t>
+          <t>9.060650542149581</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>4.055925353170053</t>
+          <t>5.057205643953512</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.4968437264042267</t>
+          <t>0.5067638061171399</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.36479822551582186</t>
+          <t>0.3675693318145089</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>8.38932550731278</t>
+          <t>4.952897814828525</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.667015961302141</t>
+          <t>9.589283052939262</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.465580669066376</t>
+          <t>2.4641192639797973</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2690230308098341</t>
+          <t>0.27166894141495534</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.624256610917513</t>
+          <t>6.567323480805774</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4.626750434621737</t>
+          <t>6.015089827652405</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.706336160084895</t>
+          <t>2.735877597109182</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.7145062658362322</t>
+          <t>0.7202409362346669</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.784899261713575</t>
+          <t>0.7982370157461404</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.108856194287287</t>
+          <t>4.820547537574458</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3756797203473123</t>
+          <t>0.3796671239529504</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.1198369204591205</t>
+          <t>1.137460507119968</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.5849690972309789</t>
+          <t>0.59624701306133</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.24365405381114</t>
+          <t>1.2660156890600698</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.920180588156882</t>
+          <t>6.019095471065951</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.705728446283985</t>
+          <t>16.66828016029904</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5819503664771211</t>
+          <t>0.5919989961416121</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.099992565516384</t>
+          <t>6.103873483166561</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>7.680737902620337</t>
+          <t>7.811967389959564</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18.20605838442988</t>
+          <t>18.122741525145564</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.2234887355389192</t>
+          <t>3.2455125146255392</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.16676122377081</t>
+          <t>7.34737054320703</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.533930141242295</t>
+          <t>6.625502439110697</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.260681142803904</t>
+          <t>17.174878678822076</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>7.968144156190192</t>
+          <t>7.736005012077399</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.280567628972907</t>
+          <t>4.272206778748996</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.153168473583053</t>
+          <t>7.150027423208482</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.126997457777237</t>
+          <t>6.148539876287393</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.0240203579361413</t>
+          <t>2.047989264652788</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>27.72088296188101</t>
+          <t>28.23341248214076</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.582280317660581</t>
+          <t>10.524811741194604</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>6.232692999349936</t>
+          <t>6.093755835868677</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.1297028206908686</t>
+          <t>2.1375673507114614</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.116522643748734</t>
+          <t>4.128085947507728</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.587589617241351</t>
+          <t>3.977802087401423</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.461455527212997</t>
+          <t>1.49001155749632</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>15.85145844046337</t>
+          <t>16.24547847912793</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.8523036777253646</t>
+          <t>0.8686433764336741</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.033463991694138</t>
+          <t>4.114128858883518</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>19.26216765481304</t>
+          <t>19.62469913049717</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>33.77134617137299</t>
+          <t>33.94907654506217</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.5365570326868889</t>
+          <t>0.539874707810307</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>28.758711005361402</t>
+          <t>29.117263388585005</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>25.996550250368823</t>
+          <t>25.763048364156987</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.7079968205592471</t>
+          <t>0.7182844613862664</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>15.14826212909517</t>
+          <t>15.25620003290234</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>7.761568124299892</t>
+          <t>7.914952891085331</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>4.768068741763198</t>
+          <t>4.870350634853652</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.6020162943306347</t>
+          <t>0.6074605002989314</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,51 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>5.842984355011708</t>
+          <t>5.738435724587077</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>F2P_INT_Chiaotzu</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>F2PLR_INT_Tien</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D373"/>
+  <dimension ref="A1:D384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.925526245728369</t>
+          <t>3.3808926552247307</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.2777777777777778</t>
+          <t>0.30440908087090124</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.2018746419228403</t>
+          <t>1.317101598251191</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3419096495523001</t>
+          <t>0.31316065983022356</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.7991784282579633</t>
+          <t>4.1634158882780214</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.163511966122465</t>
+          <t>3.466806371753173</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.954916555311748</t>
+          <t>3.238212357549572</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.3655761147090257</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.042297512899862</t>
+          <t>3.0430928996679256</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.128717945362556</t>
+          <t>9.582268595320816</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.46260176536422465</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.528221610355193</t>
+          <t>0.42763269036800144</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.7046705599859742</t>
+          <t>0.579123258192987</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.6671871973200014</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12.400473208132933</t>
+          <t>9.326903256081495</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.2018746419228403</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.999988346087736</t>
+          <t>2.016675277484194</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.2324004652256257</t>
+          <t>0.956248694109017</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.0015615919600047</t>
+          <t>2.193456688254154</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.55532620910623</t>
+          <t>4.031597237161612</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.060846949401306</t>
+          <t>4.170805751633459</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.87414369378396</t>
+          <t>1.9388975429958502</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.381527920952416</t>
+          <t>8.089214867424072</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.6666666666666665</t>
+          <t>1.8264544852254074</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.63993729495337</t>
+          <t>5.589514335727756</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.444055180377</t>
+          <t>2.0069091105995613</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.49856573425630196</t>
+          <t>0.33264625994397984</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.6088181617418025</t>
+          <t>0.6671871973200014</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.23130088268211232</t>
+          <t>0.25347632076680376</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.1213113085547128</t>
+          <t>0.804728620396432</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.086083818289579</t>
+          <t>0.7597590205996774</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.5605425440362835</t>
+          <t>1.870159012649401</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.750855163659317</t>
+          <t>4.096235304538709</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.21948996538872007</t>
+          <t>0.2208942617069901</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.20524253108416413</t>
+          <t>0.2444635805550093</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.22426716539791092</t>
+          <t>0.22301689434978245</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2621270557406109</t>
+          <t>0.2995227309891349</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.3515013295691628</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.3966649104145783</t>
+          <t>0.3403246415354794</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8.873550052605083</t>
+          <t>8.648682570939563</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5.785748386516909</t>
+          <t>4.011400737082411</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.7060218686421196</t>
+          <t>1.8695827763244182</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>2.0015615919600047</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.28587472373975076</t>
+          <t>0.2048487430873061</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.8077099557814891</t>
+          <t>0.6489388245586281</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.358381405127737</t>
+          <t>3.3604082815295317</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.35320834806276896</t>
+          <t>0.3335935986600007</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.0181468778177802</t>
+          <t>0.825454135188999</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.980676533207918</t>
+          <t>3.3466136130134982</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4.709387265348476</t>
+          <t>3.770976039361595</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.22028719131074484</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.31250323917696676</t>
+          <t>0.2680888881711568</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.3655761147090257</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.7334031858765866</t>
+          <t>1.8995892141289816</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.22812868869012348</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8133311376751888</t>
+          <t>0.5753444569981735</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5609350589272633</t>
+          <t>0.5003725397772337</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2583391273399265</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>7.057954688433551</t>
+          <t>4.905872296040986</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2.6188049903870274</t>
+          <t>2.081054852710549</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.3852007079725748</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.5567701270800032</t>
+          <t>1.7060218686421196</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.6877814666924529</t>
+          <t>0.5738886617182192</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.387393734443715</t>
+          <t>1.0175906711745188</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2603042840914327</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>7.039361649490607</t>
+          <t>5.566687168038773</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.900644451859908</t>
+          <t>1.754479411681297</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2556471491708957</t>
+          <t>0.2975170326328406</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>9.938154019577105</t>
+          <t>9.434700110893964</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1.4276012820379478</t>
+          <t>0.9983953479811586</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>12.680030212103844</t>
+          <t>10.902955330674104</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>1.4012804980569422</t>
+          <t>0.9733327174378074</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.2962962962962958</t>
+          <t>1.4205757107308723</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.4620371424529996</t>
+          <t>1.751157987952102</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>9.060650542149581</t>
+          <t>7.708283656197039</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>5.057205643953512</t>
+          <t>3.016521239466615</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5067638061171399</t>
+          <t>0.5542022383496139</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.3675693318145089</t>
+          <t>0.30151567421330183</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.952897814828525</t>
+          <t>6.0126796410899885</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>9.589283052939262</t>
+          <t>6.16927773401051</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.4641192639797973</t>
+          <t>1.652163762642712</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.27166894141495534</t>
+          <t>0.24769862518476513</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.567323480805774</t>
+          <t>6.947936147835601</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>6.015089827652405</t>
+          <t>3.154092293957592</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.735877597109182</t>
+          <t>2.368138434383743</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.7202409362346669</t>
+          <t>0.5404002220861166</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.7982370157461404</t>
+          <t>0.6189439886771102</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>4.820547537574458</t>
+          <t>1.9171101605206218</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3796671239529504</t>
+          <t>0.34943941766748154</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.137460507119968</t>
+          <t>0.8282366700994057</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.59624701306133</t>
+          <t>0.4916507359243558</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2696404955808023</t>
+          <t>0.2990643668816461</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.2660156890600698</t>
+          <t>1.021229512222161</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>6.019095471065951</t>
+          <t>4.056437227954046</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>16.66828016029904</t>
+          <t>13.53438615052502</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5919989961416121</t>
+          <t>0.4680890213240252</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>6.103873483166561</t>
+          <t>4.030012148746476</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>7.811967389959564</t>
+          <t>6.051409592170405</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18.122741525145564</t>
+          <t>13.088147119394549</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.2455125146255392</t>
+          <t>2.095538756452518</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>7.34737054320703</t>
+          <t>4.98035527960406</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.625502439110697</t>
+          <t>4.605709570264343</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.174878678822076</t>
+          <t>13.619118111427088</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>7.736005012077399</t>
+          <t>13.783344804856311</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>4.272206778748996</t>
+          <t>2.8221906126780425</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.150027423208482</t>
+          <t>5.268154274805591</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>6.148539876287393</t>
+          <t>4.141603930827592</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.047989264652788</t>
+          <t>1.4249508621813058</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>28.23341248214076</t>
+          <t>19.30150146959916</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.524811741194604</t>
+          <t>10.36499741498195</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>6.093755835868677</t>
+          <t>10.70421518263133</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2.1375673507114614</t>
+          <t>1.9644893521961442</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>4.128085947507728</t>
+          <t>2.7236087799500908</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>3.977802087401423</t>
+          <t>1.405593033879737</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.49001155749632</t>
+          <t>1.048651743066376</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>16.24547847912793</t>
+          <t>11.91210267904161</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.8686433764336741</t>
+          <t>0.7022659869847747</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.114128858883518</t>
+          <t>3.53244957608655</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>19.62469913049717</t>
+          <t>13.70149876722906</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>33.94907654506217</t>
+          <t>24.1784183689816</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.539874707810307</t>
+          <t>0.4339661197687241</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>29.117263388585005</t>
+          <t>20.92972482061578</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>25.763048364156987</t>
+          <t>26.593557417571898</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.7182844613862664</t>
+          <t>0.5372668003320523</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>15.25620003290234</t>
+          <t>11.11987755197584</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>7.914952891085331</t>
+          <t>6.34878281543224</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>4.870350634853652</t>
+          <t>3.8141883275869284</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.6074605002989314</t>
+          <t>0.40842397268634906</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>5.738435724587077</t>
+          <t>8.28704788293993</t>
         </is>
       </c>
     </row>
@@ -8631,6 +8631,248 @@
       <c r="D373" t="inlineStr">
         <is>
           <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>F2PLR_STR_Goku_Black</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>DFLR_STR_SSGSS_Goku_Vegeta</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>96.32975869763862</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>CLR_STR_Goku_Black_Zamasu</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>52.688534760477246</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>BU_AGL_Champa</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>3.80984454228257</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>F2P_AGL_Goku_Black_Clone</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Goku_Black_Clone</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>F2P_INT_Goku_Black_Clone</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>F2P_STR_Goku_Black_Clone</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Goku_Black_Clone</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>DF_PHY_Vegito_Blue</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>DF_AGL_SSR_Goku_Black</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>5.23549053336625</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -2223,12 +2223,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8.648682570939563</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>3.016521239466615</t>
+          <t>2.7802739065559408</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.605709570264343</t>
+          <t>11.081648053008788</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>19.30150146959916</t>
+          <t>12.23130082452139</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>96.32975869763862</t>
+          <t>2.3187950730306284</t>
         </is>
       </c>
     </row>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>52.688534760477246</t>
+          <t>22.86555967901485</t>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>5.23549053336625</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.3808926552247307</t>
+          <t>3.32037731272111</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.31316065983022356</t>
+          <t>0.31148422563337824</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.0430928996679256</t>
+          <t>2.9891540848139826</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.582268595320816</t>
+          <t>9.54816464967251</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.42763269036800144</t>
+          <t>0.4233716781455701</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.579123258192987</t>
+          <t>0.5735410992671841</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.326903256081495</t>
+          <t>9.177087880872257</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.016675277484194</t>
+          <t>1.980944204399579</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.956248694109017</t>
+          <t>0.9442162660036177</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4.031597237161612</t>
+          <t>3.9601927683363582</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.170805751633459</t>
+          <t>4.090352424371068</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.9388975429958502</t>
+          <t>1.903852940462361</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.589514335727756</t>
+          <t>5.556265882707192</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.0069091105995613</t>
+          <t>1.981007449825325</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.33264625994397984</t>
+          <t>0.3265215318736289</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.804728620396432</t>
+          <t>0.7914569344287923</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.7597590205996774</t>
+          <t>0.7463248179552684</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.870159012649401</t>
+          <t>1.8401236169214812</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.096235304538709</t>
+          <t>4.0464920078700715</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2208942617069901</t>
+          <t>0.22042446645113314</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2444635805550093</t>
+          <t>0.2457572991764916</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.22301689434978245</t>
+          <t>0.2224115103962941</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2995227309891349</t>
+          <t>0.30066302663725986</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.3403246415354794</t>
+          <t>0.33749914284473137</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4.011400737082411</t>
+          <t>3.940973984105001</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2048487430873061</t>
+          <t>0.20158131058719164</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.6489388245586281</t>
+          <t>0.641529666742964</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3.3604082815295317</t>
+          <t>3.302392828498082</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.825454135188999</t>
+          <t>0.817213468482368</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.3466136130134982</t>
+          <t>3.3066697768789624</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3.770976039361595</t>
+          <t>3.7185616329924653</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.2680888881711568</t>
+          <t>0.26581861608282936</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.5753444569981735</t>
+          <t>0.5662323199399428</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5003725397772337</t>
+          <t>0.4967767963239652</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.905872296040986</t>
+          <t>4.817170810315577</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2.081054852710549</t>
+          <t>2.048177042289815</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.5738886617182192</t>
+          <t>0.5686168971284743</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.0175906711745188</t>
+          <t>1.001929756085545</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>5.566687168038773</t>
+          <t>5.497545919402947</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.754479411681297</t>
+          <t>1.746832923116299</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2975170326328406</t>
+          <t>0.2986953100164115</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>9.434700110893964</t>
+          <t>9.339961429003957</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.9983953479811586</t>
+          <t>0.9810441505306873</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>10.902955330674104</t>
+          <t>10.787473972726609</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9733327174378074</t>
+          <t>0.9568700308627374</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1.751157987952102</t>
+          <t>1.7211650261843663</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.708283656197039</t>
+          <t>7.619702200372629</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2.7802739065559408</t>
+          <t>2.7278366264622917</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5542022383496139</t>
+          <t>0.5551738888078468</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.30151567421330183</t>
+          <t>0.29868144782273226</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>6.0126796410899885</t>
+          <t>5.9068899251194225</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>6.16927773401051</t>
+          <t>6.04539727694217</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.652163762642712</t>
+          <t>1.6194748153341505</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.24769862518476513</t>
+          <t>0.24615116771721907</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.947936147835601</t>
+          <t>6.92725638763532</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>3.154092293957592</t>
+          <t>3.0984100412380364</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.368138434383743</t>
+          <t>2.351576797006591</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.5404002220861166</t>
+          <t>0.5332163713195525</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.6189439886771102</t>
+          <t>0.6110436072322387</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.9171101605206218</t>
+          <t>1.905297880224305</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.34943941766748154</t>
+          <t>0.3473906275925513</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>0.8282366700994057</t>
+          <t>0.8155331079814849</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.4916507359243558</t>
+          <t>0.48661744011142294</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2990643668816461</t>
+          <t>0.3003718880750734</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.021229512222161</t>
+          <t>1.009926871255433</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>4.056437227954046</t>
+          <t>3.9812170835278344</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>13.53438615052502</t>
+          <t>13.343873511047871</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.4680890213240252</t>
+          <t>0.4626532618311923</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>4.030012148746476</t>
+          <t>3.9470800741031913</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>6.051409592170405</t>
+          <t>5.982473930186203</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.088147119394549</t>
+          <t>12.857343015466697</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2.095538756452518</t>
+          <t>2.052096518102606</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>4.98035527960406</t>
+          <t>4.891100086088649</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>11.081648053008788</t>
+          <t>10.861484504766311</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>13.619118111427088</t>
+          <t>13.40828773780429</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>13.783344804856311</t>
+          <t>14.076037490896113</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.8221906126780425</t>
+          <t>2.7653656191530476</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>5.268154274805591</t>
+          <t>5.178119777096821</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>4.141603930827592</t>
+          <t>4.060516589662484</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>1.4249508621813058</t>
+          <t>1.3993142275889632</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>12.23130082452139</t>
+          <t>12.102134228447731</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.36499741498195</t>
+          <t>10.298360960082569</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>10.70421518263133</t>
+          <t>10.9216533669602</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>1.9644893521961442</t>
+          <t>1.9243721145040746</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2.7236087799500908</t>
+          <t>2.66941012601286</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.405593033879737</t>
+          <t>1.393313106871701</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.048651743066376</t>
+          <t>1.04686467721479</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>11.91210267904161</t>
+          <t>11.71785824479324</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.7022659869847747</t>
+          <t>0.6947228852978338</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>3.53244957608655</t>
+          <t>3.503359332449826</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>13.70149876722906</t>
+          <t>13.47994722936595</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>24.1784183689816</t>
+          <t>23.77425341367451</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.4339661197687241</t>
+          <t>0.4292326175423479</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20.92972482061578</t>
+          <t>20.59360333340272</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>26.593557417571898</t>
+          <t>26.497170102589234</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.5372668003320523</t>
+          <t>0.5300094176941147</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>11.11987755197584</t>
+          <t>10.94517356531055</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>6.34878281543224</t>
+          <t>6.27800001536675</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>3.8141883275869284</t>
+          <t>3.772802574781843</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.40842397268634906</t>
+          <t>0.40061125165973976</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>8.28704788293993</t>
+          <t>8.372660796578742</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2.3187950730306284</t>
+          <t>2.2068720195395457</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>22.86555967901485</t>
+          <t>21.954134055136123</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>3.80984454228257</t>
+          <t>3.77181029846715</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D384"/>
+  <dimension ref="A1:D388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.32037731272111</t>
+          <t>2.8719388039325224</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.31148422563337824</t>
+          <t>0.28209341017693546</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.6088181617418025</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.9891540848139826</t>
+          <t>3.454764087872958</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.54816464967251</t>
+          <t>9.270863318554191</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.4233716781455701</t>
+          <t>0.39581433261182497</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.5735410992671841</t>
+          <t>0.5354443934593529</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.177087880872257</t>
+          <t>7.262894981374233</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.980944204399579</t>
+          <t>1.6869951904406344</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.9442162660036177</t>
+          <t>0.8772548616916472</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.9601927683363582</t>
+          <t>2.631434749802151</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.090352424371068</t>
+          <t>3.0267242707445576</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.903852940462361</t>
+          <t>1.5902887189156676</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.556265882707192</t>
+          <t>5.561284744260165</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.981007449825325</t>
+          <t>1.595030975019747</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.3265215318736289</t>
+          <t>0.26617520508269416</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.25347632076680376</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.7914569344287923</t>
+          <t>0.5815028349649706</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.7463248179552684</t>
+          <t>0.5675322183722704</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.8401236169214812</t>
+          <t>1.506636851938489</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.0464920078700715</t>
+          <t>3.290576819025482</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.22042446645113314</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2457572991764916</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.2224115103962941</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.30066302663725986</t>
+          <t>0.30611814624777933</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.33749914284473137</t>
+          <t>0.31083065700500906</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3.940973984105001</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.20158131058719164</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.641529666742964</t>
+          <t>0.28867178691677986</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3.302392828498082</t>
+          <t>2.797440280972811</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>7.011605541475897</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.817213468482368</t>
+          <t>0.7251547084493839</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.3066697768789624</t>
+          <t>3.7166194694089354</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3.7185616329924653</t>
+          <t>2.871722352480684</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.26581861608282936</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.5662323199399428</t>
+          <t>0.5030869371653497</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4967767963239652</t>
+          <t>0.43656190393141575</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.817170810315577</t>
+          <t>4.021009107376554</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2.048177042289815</t>
+          <t>1.6786495219500166</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1.7060218686421196</t>
+          <t>0.24371740980601708</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.5686168971284743</t>
+          <t>0.3711302677175175</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.001929756085545</t>
+          <t>0.8830267947641461</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>5.497545919402947</t>
+          <t>4.552808037207205</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.746832923116299</t>
+          <t>1.716771200801538</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2986953100164115</t>
+          <t>0.30073024952741706</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>9.339961429003957</t>
+          <t>7.390692173123882</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.9810441505306873</t>
+          <t>0.701120274218117</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>10.787473972726609</t>
+          <t>9.035878102573161</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9568700308627374</t>
+          <t>0.7190747910129631</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1.7211650261843663</t>
+          <t>1.1058181314089763</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.619702200372629</t>
+          <t>6.010177210844883</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2.7278366264622917</t>
+          <t>1.8410030094974372</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5551738888078468</t>
+          <t>0.5561146303658148</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.29868144782273226</t>
+          <t>0.20951598588080095</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>5.9068899251194225</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>6.04539727694217</t>
+          <t>3.6355050382812504</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.6194748153341505</t>
+          <t>1.1840851441684066</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.24615116771721907</t>
+          <t>0.21275055954882158</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.92725638763532</t>
+          <t>6.686339856151926</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>3.0984100412380364</t>
+          <t>2.3423937247388746</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.351576797006591</t>
+          <t>2.025652110858251</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.5332163713195525</t>
+          <t>0.4742955325358924</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.6110436072322387</t>
+          <t>0.5552413772026057</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.905297880224305</t>
+          <t>1.493207795630802</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3473906275925513</t>
+          <t>0.31510623183993325</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>0.8155331079814849</t>
+          <t>0.7027968997842594</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.48661744011142294</t>
+          <t>0.45024191295639615</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.3003718880750734</t>
+          <t>0.2954916555311748</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1.009926871255433</t>
+          <t>0.8500230974486529</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>3.9812170835278344</t>
+          <t>2.66922976257743</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>13.343873511047871</t>
+          <t>12.268701009979804</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.4626532618311923</t>
+          <t>0.4227963511409802</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>3.9470800741031913</t>
+          <t>2.7762672631887733</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>5.982473930186203</t>
+          <t>6.731581477007603</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>12.857343015466697</t>
+          <t>7.2481215299753226</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2.052096518102606</t>
+          <t>1.3683341220614482</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>4.891100086088649</t>
+          <t>1.0085761396513888</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>10.861484504766311</t>
+          <t>8.197251227506822</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>13.40828773780429</t>
+          <t>11.220228108664962</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>14.076037490896113</t>
+          <t>17.7801213556601</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.7653656191530476</t>
+          <t>2.823193213181641</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>5.178119777096821</t>
+          <t>4.623921006316134</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>4.060516589662484</t>
+          <t>2.835404490331144</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>1.3993142275889632</t>
+          <t>1.0776724279539822</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>12.102134228447731</t>
+          <t>10.435636708130357</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.298360960082569</t>
+          <t>9.72204153606112</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>10.9216533669602</t>
+          <t>15.038921490056737</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>1.9243721145040746</t>
+          <t>1.2874166798238689</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2.66941012601286</t>
+          <t>1.9929458306260013</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.393313106871701</t>
+          <t>0.9055697694633579</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.04686467721479</t>
+          <t>1.337533702346662</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>11.71785824479324</t>
+          <t>8.191510217245062</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.6947228852978338</t>
+          <t>0.5412042687644639</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>3.503359332449826</t>
+          <t>3.236688538673005</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>13.47994722936595</t>
+          <t>13.55601087875316</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>23.77425341367451</t>
+          <t>8.211881626086178</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.4292326175423479</t>
+          <t>0.38473795349386597</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20.59360333340272</t>
+          <t>17.67620164539403</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>26.497170102589234</t>
+          <t>23.729893776369394</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.5300094176941147</t>
+          <t>0.4361686125390163</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>10.94517356531055</t>
+          <t>8.31090661935608</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>6.27800001536675</t>
+          <t>5.661336753450432</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>3.772802574781843</t>
+          <t>2.787914981072819</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.40061125165973976</t>
+          <t>0.31853703071847356</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>8.372660796578742</t>
+          <t>9.273567655333643</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2.2068720195395457</t>
+          <t>3.365739199123027</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>21.954134055136123</t>
+          <t>20.947622085783166</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>3.77181029846715</t>
+          <t>2.3424264556582983</t>
         </is>
       </c>
     </row>
@@ -8873,6 +8873,94 @@
       <c r="D384" t="inlineStr">
         <is>
           <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>F2PLR_STR_Nuova_Shenron</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>BU_STR_Pan_GT</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.103637505293687</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>DFLR_PHY_Omega_Shenron</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>16.07645373413125</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>CLR_AGL_SS4_Gogeta</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>81.03521007976153</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D388"/>
+  <dimension ref="A1:D399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.8719388039325224</t>
+          <t>2.546845902540257</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.30440908087090124</t>
+          <t>0.3335935986600007</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.317101598251191</t>
+          <t>1.4433756729740645</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.28209341017693546</t>
+          <t>0.2588653777429838</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.1634158882780214</t>
+          <t>4.56257377380247</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.466806371753173</t>
+          <t>3.7991784282579633</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.238212357549572</t>
+          <t>3.5486684907352526</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.454764087872958</t>
+          <t>2.9862594049407427</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.270863318554191</t>
+          <t>8.308804637701614</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.46260176536422465</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.39581433261182497</t>
+          <t>0.4654135533305186</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.5354443934593529</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.8012497612818937</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.262894981374233</t>
+          <t>6.003590661594146</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.2018746419228403</t>
+          <t>1.317101598251191</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.6869951904406344</t>
+          <t>1.478148728952813</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.8772548616916472</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.193456688254154</t>
+          <t>2.4037492838456807</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.631434749802151</t>
+          <t>2.264840790504686</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.0267242707445576</t>
+          <t>2.5478177315596975</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.5902887189156676</t>
+          <t>1.3923731997791222</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.089214867424072</t>
+          <t>8.864749665935244</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>2.0015615919600047</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.561284744260165</t>
+          <t>4.932943286197067</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.595030975019747</t>
+          <t>1.4169950864858396</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.26617520508269416</t>
+          <t>0.23281197966985215</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.6671871973200014</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.5815028349649706</t>
+          <t>0.4950331893910344</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.5675322183722704</t>
+          <t>0.48467436452650414</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.506636851938489</t>
+          <t>1.3439536121701492</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.290576819025482</t>
+          <t>2.9803105756864485</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.30611814624777933</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.3852007079725748</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.31083065700500906</t>
+          <t>0.28625534843017225</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.8695827763244182</t>
+          <t>2.0488247083907414</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.0015615919600047</t>
+          <t>11.784592536281089</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.28867178691677986</t>
+          <t>0.3297833657201261</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2.797440280972811</t>
+          <t>2.4456546229092186</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>7.011605541475897</t>
+          <t>6.188709463676639</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.7251547084493839</t>
+          <t>0.6647553793143953</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.7166194694089354</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.871722352480684</t>
+          <t>2.440606153706441</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1.8995892141289816</t>
+          <t>2.0817079441390107</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1.6666666666666665</t>
+          <t>1.8264544852254074</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.2739681727838111</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.5030869371653497</t>
+          <t>0.4491628271557584</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.43656190393141575</t>
+          <t>0.4050393342411643</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.021009107376554</t>
+          <t>3.613411748176585</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.6786495219500166</t>
+          <t>1.4765081141771979</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.46260176536422465</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.24371740980601708</t>
+          <t>0.2670832537606312</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.3711302677175175</t>
+          <t>0.33942192742246596</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.8830267947641461</t>
+          <t>0.8046561920692666</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.552808037207205</t>
+          <t>4.039827056178428</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.716771200801538</t>
+          <t>1.597638347812634</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.30073024952741706</t>
+          <t>0.28665595954342815</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>7.390692173123882</t>
+          <t>6.817638272490747</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.701120274218117</t>
+          <t>0.5940103351592135</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>9.035878102573161</t>
+          <t>8.285284785195639</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.7190747910129631</t>
+          <t>0.6341445595301786</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.4205757107308723</t>
+          <t>1.5567701270800032</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1.1058181314089763</t>
+          <t>0.9517050863207015</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.010177210844883</t>
+          <t>5.3337248217636315</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>1.8410030094974372</t>
+          <t>1.59480578918068</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5561146303658148</t>
+          <t>0.5398140382314854</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.20951598588080095</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>3.6355050382812504</t>
+          <t>4.06923314770224</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.1840851441684066</t>
+          <t>0.9847755906468894</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.21275055954882158</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.686339856151926</t>
+          <t>6.28488825394116</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2.3423937247388746</t>
+          <t>2.083004621525836</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.025652110858251</t>
+          <t>1.857818089476861</t>
         </is>
       </c>
     </row>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.4742955325358924</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.5552413772026057</t>
+          <t>0.5052934577228037</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.493207795630802</t>
+          <t>1.462814797386696</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.31510623183993325</t>
+          <t>0.2925824961827059</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>0.7027968997842594</t>
+          <t>0.6328735047635601</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.45024191295639615</t>
+          <t>0.41676147703491884</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2954916555311748</t>
+          <t>0.32382123575495725</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.8500230974486529</t>
+          <t>0.7648462638916091</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.66922976257743</t>
+          <t>2.36457639762133</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>12.268701009979804</t>
+          <t>10.56740292883843</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.4227963511409802</t>
+          <t>0.38351575111747804</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2.7762672631887733</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>6.731581477007603</t>
+          <t>6.117741992946267</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>7.2481215299753226</t>
+          <t>8.142281648117939</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.3683341220614482</t>
+          <t>1.1450588513577102</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.0085761396513888</t>
+          <t>0.8962595390896286</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>8.197251227506822</t>
+          <t>6.741508363509366</t>
         </is>
       </c>
     </row>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>11.220228108664962</t>
+          <t>4.778112816396849</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>17.7801213556601</t>
+          <t>18.887682052326937</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.823193213181641</t>
+          <t>2.3294738536454225</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>4.623921006316134</t>
+          <t>4.005713582004205</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.835404490331144</t>
+          <t>2.430362055506487</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>1.0776724279539822</t>
+          <t>0.9366142201667724</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>10.435636708130357</t>
+          <t>9.09115693780451</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>9.72204153606112</t>
+          <t>8.071904645476444</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>15.038921490056737</t>
+          <t>15.946266134074492</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>1.2874166798238689</t>
+          <t>1.0751273823141068</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>1.9929458306260013</t>
+          <t>1.6739863036779845</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.9055697694633579</t>
+          <t>0.8229527270557838</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.337533702346662</t>
+          <t>1.252812793078675</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>8.191510217245062</t>
+          <t>7.09454301175179</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.5412042687644639</t>
+          <t>0.4830925667688474</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>3.236688538673005</t>
+          <t>2.988518576306209</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>13.55601087875316</t>
+          <t>11.95043090013553</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>8.211881626086178</t>
+          <t>7.090023123555609</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.38473795349386597</t>
+          <t>0.34605168926271235</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2048824708390741</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>17.67620164539403</t>
+          <t>15.70734236768849</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>23.729893776369394</t>
+          <t>21.512721412830313</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.4361686125390163</t>
+          <t>0.38381047959694276</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>8.31090661935608</t>
+          <t>7.179627053302537</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>5.661336753450432</t>
+          <t>5.178777172345293</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2.787914981072819</t>
+          <t>2.4808849629717455</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.31853703071847356</t>
+          <t>0.39291885081587247</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>9.273567655333643</t>
+          <t>9.277219835839432</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>3.365739199123027</t>
+          <t>4.14786397946601</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20.947622085783166</t>
+          <t>19.981634797408624</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2.3424264556582983</t>
+          <t>2.138999738986051</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2.103637505293687</t>
+          <t>1.898105599083687</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>16.07645373413125</t>
+          <t>7.462950344189366</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,254 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>81.03521007976153</t>
+          <t>14.370342769685038</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>DF_STR_SS4_Goku</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>DF_AGL_SS4_Vegeta</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>10.63781488603764</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>DF_STR_Omega_Shenron</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>5.338802555470234</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>BU_TEQ_Syn_Shenron</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>BU_AGL_SS3_Goku_GT</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>BU_STR_SS3_Goku_GT_GiantApe</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>BU_STR_SS_Trunks_GT</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>BU_PHY_Pan_GT</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>BU_INT_Super_Baby_2</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>F2PLR_INT_Shadow_Dragons</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>DF_INT_SS4_Gogeta</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>4.2515176807740405</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D399"/>
+  <dimension ref="A1:D402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.546845902540257</t>
+          <t>2.5423472441845085</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.2588653777429838</t>
+          <t>0.2537330197797297</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.9862594049407427</t>
+          <t>2.9786295898545183</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.308804637701614</t>
+          <t>8.307002102083835</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.4654135533305186</t>
+          <t>0.4597916277454612</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.003590661594146</t>
+          <t>5.964484368252976</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.478148728952813</t>
+          <t>1.458810846796931</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.264840790504686</t>
+          <t>2.2472305848654606</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.5478177315596975</t>
+          <t>2.5249238187100285</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.3923731997791222</t>
+          <t>1.376246612022955</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.932943286197067</t>
+          <t>4.941569962096486</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.4169950864858396</t>
+          <t>1.4215931523876952</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.23281197966985215</t>
+          <t>0.2293038700092393</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.4950331893910344</t>
+          <t>0.48842210471839387</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.48467436452650414</t>
+          <t>0.4786110919558322</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.3439536121701492</t>
+          <t>1.3275419748146309</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.9803105756864485</t>
+          <t>2.9894579943947406</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.28625534843017225</t>
+          <t>0.28342307577955034</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11.784592536281089</t>
+          <t>14.466145721137472</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.3297833657201261</t>
+          <t>0.32484364583247194</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2.4456546229092186</t>
+          <t>2.4438979782549204</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6.188709463676639</t>
+          <t>6.199022669461144</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6647553793143953</t>
+          <t>0.6546067263196684</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.440606153706441</t>
+          <t>2.4459582569965557</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.4491628271557584</t>
+          <t>0.44585753255766136</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4050393342411643</t>
+          <t>0.40068813951261917</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.613411748176585</t>
+          <t>3.5810037544732944</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.4765081141771979</t>
+          <t>1.454102357231383</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.33942192742246596</t>
+          <t>0.3324387964582936</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.8046561920692666</t>
+          <t>0.8037663959530414</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.039827056178428</t>
+          <t>3.968518719073099</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.597638347812634</t>
+          <t>1.5729734233028143</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.28665595954342815</t>
+          <t>0.27959456380059444</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.817638272490747</t>
+          <t>6.81870195483544</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.5940103351592135</t>
+          <t>0.5859899987283762</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>8.285284785195639</t>
+          <t>8.27068244492525</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.6341445595301786</t>
+          <t>0.6306519175828466</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.9517050863207015</t>
+          <t>0.9449736446753657</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>5.3337248217636315</t>
+          <t>5.31638141654323</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>1.59480578918068</t>
+          <t>1.5734505310840703</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5398140382314854</t>
+          <t>0.5294732219187072</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.06923314770224</t>
+          <t>4.03934572483622</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.9847755906468894</t>
+          <t>0.9787443039282102</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.28488825394116</t>
+          <t>6.305994778777377</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2.083004621525836</t>
+          <t>2.0654678908282085</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.857818089476861</t>
+          <t>1.806829189192417</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.5052934577228037</t>
+          <t>0.5037224639153011</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.462814797386696</t>
+          <t>1.439666919836852</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.2925824961827059</t>
+          <t>0.28810023416094294</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>0.6328735047635601</t>
+          <t>0.6307581628250734</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.41676147703491884</t>
+          <t>0.413629643672456</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.7648462638916091</t>
+          <t>0.7524901419650931</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.36457639762133</t>
+          <t>2.3562039644997546</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>10.56740292883843</t>
+          <t>10.524947631076781</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.38351575111747804</t>
+          <t>0.3811282828223051</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>6.117741992946267</t>
+          <t>6.016242255845177</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>8.142281648117939</t>
+          <t>8.153223652727862</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1450588513577102</t>
+          <t>1.1315135390944393</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0.8962595390896286</t>
+          <t>0.8947843322238213</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.741508363509366</t>
+          <t>6.655852884244747</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>4.778112816396849</t>
+          <t>4.781925135785599</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>18.887682052326937</t>
+          <t>19.04115432715492</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.3294738536454225</t>
+          <t>2.2990971738345594</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>4.005713582004205</t>
+          <t>4.007106022010905</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.430362055506487</t>
+          <t>2.4193412474157387</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9366142201667724</t>
+          <t>0.9336821727242645</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.09115693780451</t>
+          <t>9.03709721645108</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>8.071904645476444</t>
+          <t>8.0756816463714</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>15.946266134074492</t>
+          <t>16.108860748737534</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>1.0751273823141068</t>
+          <t>1.0620302517635718</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>1.6739863036779845</t>
+          <t>1.6637896954003697</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.8229527270557838</t>
+          <t>0.7811033707882434</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.252812793078675</t>
+          <t>1.230190623815638</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>7.09454301175179</t>
+          <t>6.90439753795507</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.4830925667688474</t>
+          <t>0.47576286487873287</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2.988518576306209</t>
+          <t>2.961594927856082</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>11.95043090013553</t>
+          <t>11.71837018502669</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>7.090023123555609</t>
+          <t>7.098772293993131</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.34605168926271235</t>
+          <t>0.34331057692049916</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>15.70734236768849</t>
+          <t>15.601749746604101</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>21.512721412830313</t>
+          <t>21.51667605263761</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.38381047959694276</t>
+          <t>0.37846318245606253</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>7.179627053302537</t>
+          <t>7.018083374564155</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>5.178777172345293</t>
+          <t>5.145199124576654</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2.4808849629717455</t>
+          <t>2.40316073298291</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.39291885081587247</t>
+          <t>0.3901457939798222</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>9.277219835839432</t>
+          <t>9.325363148634594</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.14786397946601</t>
+          <t>4.2073889346430775</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>19.981634797408624</t>
+          <t>20.053616169909837</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2.138999738986051</t>
+          <t>2.0983958668304</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>1.898105599083687</t>
+          <t>1.864025388811892</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>7.462950344189366</t>
+          <t>7.55903136263683</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>14.370342769685038</t>
+          <t>14.555259600530817</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>10.63781488603764</t>
+          <t>10.627535427330633</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>5.338802555470234</t>
+          <t>5.843791610761826</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,73 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.2515176807740405</t>
+          <t>4.224576651953931</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>LR_AGL_Goten_Trunks</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>3.0011734427997685</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>BU_PHY_Spopovich</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>4.156832533038856</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>DFLR_INT_SS_Hybrid_Saiyans</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>20.75501999881234</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.5423472441845085</t>
+          <t>3.48246046439664</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.2537330197797297</t>
+          <t>0.29072719555264886</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.9786295898545183</t>
+          <t>2.777608430529609</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.307002102083835</t>
+          <t>5.2227419997476865</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.4597916277454612</t>
+          <t>0.6312979498820557</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.645795358326648</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5.964484368252976</t>
+          <t>7.763004541435874</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.458810846796931</t>
+          <t>2.0939429055966414</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>1.099868628429304</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.2472305848654606</t>
+          <t>2.2426208044831717</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.5249238187100285</t>
+          <t>2.981925294227106</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.376246612022955</t>
+          <t>1.9621288864307296</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.941569962096486</t>
+          <t>5.492747431509739</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.4215931523876952</t>
+          <t>1.7318463691820205</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.2293038700092393</t>
+          <t>0.32637327205290084</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.48842210471839387</t>
+          <t>0.5395259997512826</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.4786110919558322</t>
+          <t>0.7369231149686373</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.3275419748146309</t>
+          <t>1.124981979661848</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.9894579943947406</t>
+          <t>3.680840605206811</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.28342307577955034</t>
+          <t>0.36889625614058663</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>14.466145721137472</t>
+          <t>14.47246386863075</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.32484364583247194</t>
+          <t>0.262167245931918</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2.4438979782549204</t>
+          <t>3.8608803775576312</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6.199022669461144</t>
+          <t>11.134155822987397</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6546067263196684</t>
+          <t>0.647234071340347</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.4459582569965557</t>
+          <t>2.249509319218861</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.44585753255766136</t>
+          <t>0.6414554362048445</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.40068813951261917</t>
+          <t>0.4185448676455623</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.5810037544732944</t>
+          <t>4.093054720513955</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.454102357231383</t>
+          <t>1.6735101429058146</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.3324387964582936</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.8037663959530414</t>
+          <t>1.132817357322823</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>3.968518719073099</t>
+          <t>4.161420892430288</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.5729734233028143</t>
+          <t>1.978898820160567</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.27959456380059444</t>
+          <t>0.28425204718132857</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.81870195483544</t>
+          <t>8.073683686732942</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.5859899987283762</t>
+          <t>0.46676865661484923</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>8.27068244492525</t>
+          <t>8.322754867653977</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.6306519175828466</t>
+          <t>0.6120519750620169</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.9449736446753657</t>
+          <t>0.3155411814182408</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>5.31638141654323</t>
+          <t>6.018845623838409</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>1.5734505310840703</t>
+          <t>1.2432209669809762</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5294732219187072</t>
+          <t>0.6071908320060513</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.03934572483622</t>
+          <t>2.319112934694532</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.9787443039282102</t>
+          <t>0.9275193920595436</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.22305589356894623</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.305994778777377</t>
+          <t>6.371959940062437</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2.0654678908282085</t>
+          <t>2.3642863209111913</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.806829189192417</t>
+          <t>1.510468606069046</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20808883700317996</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.5037224639153011</t>
+          <t>0.6962160497562877</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.439666919836852</t>
+          <t>1.1828894969117507</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.28810023416094294</t>
+          <t>0.29141350043176906</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>0.6307581628250734</t>
+          <t>0.883732153265012</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.413629643672456</t>
+          <t>0.5537865096919188</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.7524901419650931</t>
+          <t>0.6721804845540089</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.3562039644997546</t>
+          <t>3.596951136956635</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>10.524947631076781</t>
+          <t>14.255886289880529</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.3811282828223051</t>
+          <t>0.5224199666609142</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>6.016242255845177</t>
+          <t>7.609514215614433</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>8.153223652727862</t>
+          <t>13.30413216054449</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1315135390944393</t>
+          <t>1.7903713932015148</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0.8947843322238213</t>
+          <t>0.4832189716328888</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>6.655852884244747</t>
+          <t>4.590120157124332</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>4.781925135785599</t>
+          <t>10.908455922020487</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>19.04115432715492</t>
+          <t>22.212320140429142</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.2990971738345594</t>
+          <t>2.5240660060558726</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>4.007106022010905</t>
+          <t>5.063390153417177</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.4193412474157387</t>
+          <t>1.7033977517623797</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9336821727242645</t>
+          <t>0.9114042342443991</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.03709721645108</t>
+          <t>11.293394715717342</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>8.0756816463714</t>
+          <t>10.15842409492516</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>16.108860748737534</t>
+          <t>16.31342674193428</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>1.0620302517635718</t>
+          <t>0.8303572231547852</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>1.6637896954003697</t>
+          <t>2.0221134570728565</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.7811033707882434</t>
+          <t>0.7484170156161815</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.230190623815638</t>
+          <t>1.377529820833623</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>6.90439753795507</t>
+          <t>9.522640221983327</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.47576286487873287</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2.961594927856082</t>
+          <t>3.8364202975021517</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>11.71837018502669</t>
+          <t>10.81804246168071</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>7.098772293993131</t>
+          <t>6.109990325453619</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.34331057692049916</t>
+          <t>0.4582275693470161</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>15.601749746604101</t>
+          <t>21.33616779915481</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>21.51667605263761</t>
+          <t>22.188499540275</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.37846318245606253</t>
+          <t>0.29599848012167845</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>7.018083374564155</t>
+          <t>3.833079353927842</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>5.145199124576654</t>
+          <t>6.898552816594917</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2.40316073298291</t>
+          <t>2.0879462778347</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.3901457939798222</t>
+          <t>0.5460287236306728</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>9.325363148634594</t>
+          <t>9.066735833421184</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.2073889346430775</t>
+          <t>3.9209666108186525</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20.053616169909837</t>
+          <t>17.04863914110097</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2.0983958668304</t>
+          <t>0.7964166277818737</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>1.864025388811892</t>
+          <t>0.9541252141454664</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>7.55903136263683</t>
+          <t>19.388582490522936</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>14.555259600530817</t>
+          <t>13.17575773818186</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>10.627535427330633</t>
+          <t>4.17779600978341</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>5.843791610761826</t>
+          <t>2.439282775881299</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.224576651953931</t>
+          <t>3.9852282294345946</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.0011734427997685</t>
+          <t>3.0799272588067272</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.156832533038856</t>
+          <t>2.490341460900245</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20.75501999881234</t>
+          <t>12.601451192866804</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D402"/>
+  <dimension ref="A1:D406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.48246046439664</t>
+          <t>5.282736753751919</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.29072719555264886</t>
+          <t>0.34194032529579477</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.777608430529609</t>
+          <t>1.3957761535334205</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.2227419997476865</t>
+          <t>3.3957020268833427</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.6312979498820557</t>
+          <t>1.0017769507309495</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.645795358326648</t>
+          <t>0.9362958087496331</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.763004541435874</t>
+          <t>9.59202158492104</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.0939429055966414</t>
+          <t>3.32493803795305</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.099868628429304</t>
+          <t>1.7687560051701905</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.2426208044831717</t>
+          <t>4.466519100842142</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.981925294227106</t>
+          <t>2.6773874148906254</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.9621288864307296</t>
+          <t>3.1624190508324688</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.492747431509739</t>
+          <t>5.868424583953217</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.7318463691820205</t>
+          <t>3.7504825531854022</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.32637327205290084</t>
+          <t>0.46451627549856916</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.5395259997512826</t>
+          <t>0.7592499250367513</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.7369231149686373</t>
+          <t>0.946088671129556</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.124981979661848</t>
+          <t>0.8625384322917742</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.680840605206811</t>
+          <t>4.199332225960198</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20043998780570407</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21457686017515018</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.36889625614058663</t>
+          <t>0.5198607599174442</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>14.47246386863075</t>
+          <t>15.348074482573859</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2712823900841203</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.262167245931918</t>
+          <t>0.33404131537763715</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3.8608803775576312</t>
+          <t>6.766094198051</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>11.134155822987397</t>
+          <t>6.389936314705482</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.647234071340347</t>
+          <t>0.5581402372037465</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.249509319218861</t>
+          <t>2.675401935845493</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.6414554362048445</t>
+          <t>1.0895964369618933</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4185448676455623</t>
+          <t>0.4970080068402776</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2998232716632314</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.093054720513955</t>
+          <t>3.2176131470277802</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.6735101429058146</t>
+          <t>1.76574913184073</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.132817357322823</t>
+          <t>2.9582045738074974</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.161420892430288</t>
+          <t>1.7060218686421196</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1.978898820160567</t>
+          <t>2.772220624436631</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.28425204718132857</t>
+          <t>0.28330812609209527</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.073683686732942</t>
+          <t>8.669002442563468</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.46676865661484923</t>
+          <t>0.20218994232205978</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>8.322754867653977</t>
+          <t>4.86282441831478</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.6120519750620169</t>
+          <t>0.8838316548877033</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.3155411814182408</t>
+          <t>0.3534338449783347</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2034245369404104</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.018845623838409</t>
+          <t>6.18468062397524</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>1.2432209669809762</t>
+          <t>0.9596095183439681</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6071908320060513</t>
+          <t>0.6563787013949942</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2.319112934694532</t>
+          <t>2.187625560665712</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.9275193920595436</t>
+          <t>1.3922068132457064</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.22305589356894623</t>
+          <t>0.2639587031861148</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>6.371959940062437</t>
+          <t>3.361405360631453</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2.3642863209111913</t>
+          <t>2.2136517224987466</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.510468606069046</t>
+          <t>1.226665800098623</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.20808883700317996</t>
+          <t>0.32504035486776417</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.6962160497562877</t>
+          <t>1.1379317258154815</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.29141350043176906</t>
+          <t>0.395402824041325</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>0.883732153265012</t>
+          <t>1.4273908521004597</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.5537865096919188</t>
+          <t>0.822512712300191</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6721804845540089</t>
+          <t>0.7248405348808276</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>3.596951136956635</t>
+          <t>4.482558101987888</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>14.255886289880529</t>
+          <t>10.86453988969351</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.5224199666609142</t>
+          <t>0.8441196383192744</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>7.609514215614433</t>
+          <t>11.4449459997094</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.30413216054449</t>
+          <t>16.451702580836397</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.7903713932015148</t>
+          <t>1.6208579324815475</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0.4832189716328888</t>
+          <t>0.97092847186215</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.590120157124332</t>
+          <t>4.6492212105199355</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10.908455922020487</t>
+          <t>16.025033483659612</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>22.212320140429142</t>
+          <t>25.448783108483976</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.5240660060558726</t>
+          <t>0.8595366922594957</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>5.063390153417177</t>
+          <t>8.718396649424813</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.7033977517623797</t>
+          <t>1.580418634492396</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9114042342443991</t>
+          <t>0.5982453702859143</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>11.293394715717342</t>
+          <t>10.67921167824929</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>10.15842409492516</t>
+          <t>5.360265517269859</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>16.31342674193428</t>
+          <t>12.219500802183788</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.8303572231547852</t>
+          <t>0.6676008246311237</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2.0221134570728565</t>
+          <t>0.8694888362212813</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.377529820833623</t>
+          <t>1.709594639875005</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>9.522640221983327</t>
+          <t>4.854788224958444</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>3.8364202975021517</t>
+          <t>5.528210907507161</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>10.81804246168071</t>
+          <t>4.18465979669984</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.109990325453619</t>
+          <t>7.0690678242618015</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.4582275693470161</t>
+          <t>0.745004612950737</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>21.33616779915481</t>
+          <t>32.65837719540821</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>22.188499540275</t>
+          <t>16.075077254245407</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.29599848012167845</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>3.833079353927842</t>
+          <t>2.039508598870059</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>6.898552816594917</t>
+          <t>10.48584381666107</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2.0879462778347</t>
+          <t>1.08021037643291</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.5460287236306728</t>
+          <t>0.7921166996164796</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>9.066735833421184</t>
+          <t>18.119761760754578</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>3.9209666108186525</t>
+          <t>4.020239920875511</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>17.04863914110097</t>
+          <t>21.926318567548872</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.7964166277818737</t>
+          <t>0.435726503648778</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.9541252141454664</t>
+          <t>0.6925411725268137</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>19.388582490522936</t>
+          <t>24.313454766835214</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>13.17575773818186</t>
+          <t>18.92665986559888</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>4.17779600978341</t>
+          <t>3.494033280594053</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2.439282775881299</t>
+          <t>2.253449345365709</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>3.9852282294345946</t>
+          <t>6.486076867523357</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.0799272588067272</t>
+          <t>4.032445649726195</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2.490341460900245</t>
+          <t>5.260504774975272</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,95 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>12.601451192866804</t>
+          <t>7.947093099750347</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>LR_TEQ_SS2_Gohan</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>10.34840713840645</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>BU_PHY_Fasha</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>0.506034915012714</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>BU_TEQ_Ranfan</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>7.352576230049309</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>BU_AGL_Videl</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>0.2344412889806784</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.282736753751919</t>
+          <t>5.5765947400608695</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.34194032529579477</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.3957761535334205</t>
+          <t>1.8772250623065965</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.3957020268833427</t>
+          <t>2.935527304789746</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.0017769507309495</t>
+          <t>0.9613101445951078</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9362958087496331</t>
+          <t>0.9334035840696839</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.59202158492104</t>
+          <t>9.737460381687818</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.32493803795305</t>
+          <t>3.431487285259418</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7687560051701905</t>
+          <t>1.7005163678368014</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4.466519100842142</t>
+          <t>7.08033599872199</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.6773874148906254</t>
+          <t>5.706903094102774</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.1624190508324688</t>
+          <t>3.0698051650371205</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.0015615919600047</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.868424583953217</t>
+          <t>4.322806229155444</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.7504825531854022</t>
+          <t>3.744994527801852</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.46451627549856916</t>
+          <t>0.4801573928843139</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.7592499250367513</t>
+          <t>0.6692012815490624</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.946088671129556</t>
+          <t>0.8384523921250074</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.8625384322917742</t>
+          <t>0.741743302139011</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.199332225960198</t>
+          <t>4.156716498455985</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.20043998780570407</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.21457686017515018</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5198607599174442</t>
+          <t>0.4879302695476937</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2.0488247083907414</t>
+          <t>0.2926892440558202</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>15.348074482573859</t>
+          <t>15.242485906199043</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2712823900841203</t>
+          <t>0.2501100096054711</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.33404131537763715</t>
+          <t>0.28577441249509206</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.766094198051</t>
+          <t>6.8149424301242405</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6.389936314705482</t>
+          <t>6.059208390147677</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5581402372037465</t>
+          <t>0.5218570506356909</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.675401935845493</t>
+          <t>2.6225059888481</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0895964369618933</t>
+          <t>1.0677555159141265</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4970080068402776</t>
+          <t>0.4448658739075828</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2998232716632314</t>
+          <t>0.2857363370383226</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.2176131470277802</t>
+          <t>3.693183496693578</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.76574913184073</t>
+          <t>1.4756445545241519</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.9582045738074974</t>
+          <t>2.8531178502610373</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.772220624436631</t>
+          <t>2.62401011437987</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.28330812609209527</t>
+          <t>0.34415340671088296</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.669002442563468</t>
+          <t>8.865838249503085</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.20218994232205978</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.86282441831478</t>
+          <t>4.909628482225408</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.8838316548877033</t>
+          <t>0.834171547994984</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.3534338449783347</t>
+          <t>0.3110748566586753</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2034245369404104</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.18468062397524</t>
+          <t>6.0184232833940285</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.9596095183439681</t>
+          <t>0.8602300325271708</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6563787013949942</t>
+          <t>0.562906210686051</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2.187625560665712</t>
+          <t>2.00443399432778</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.3922068132457064</t>
+          <t>1.4070159756038316</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2639587031861148</t>
+          <t>0.23219650970634914</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>3.361405360631453</t>
+          <t>2.522930536738791</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2.2136517224987466</t>
+          <t>2.0023138458201424</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.226665800098623</t>
+          <t>1.24886068478635</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.32504035486776417</t>
+          <t>0.30295113794431644</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.1379317258154815</t>
+          <t>1.1107571221170414</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.395402824041325</t>
+          <t>0.35129445866580783</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.4273908521004597</t>
+          <t>1.3853250507347394</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.822512712300191</t>
+          <t>0.7832316252016271</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.7248405348808276</t>
+          <t>0.6422528335456902</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>4.482558101987888</t>
+          <t>4.24432357983011</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>10.86453988969351</t>
+          <t>7.08861363835094</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.8441196383192744</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.4449459997094</t>
+          <t>10.7159057886858</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>16.451702580836397</t>
+          <t>15.91944376464247</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.6208579324815475</t>
+          <t>1.538852025272349</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0.97092847186215</t>
+          <t>0.9389433553841791</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.6492212105199355</t>
+          <t>4.220549282187873</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>16.025033483659612</t>
+          <t>15.370732310938193</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>25.448783108483976</t>
+          <t>23.678060791202675</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.8595366922594957</t>
+          <t>0.7686958492712899</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.718396649424813</t>
+          <t>8.544825659211343</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.580418634492396</t>
+          <t>1.4628788924077516</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5982453702859143</t>
+          <t>0.5595192050364757</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>10.67921167824929</t>
+          <t>10.421879519734519</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>5.360265517269859</t>
+          <t>5.003038927106211</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.219500802183788</t>
+          <t>12.778256731219168</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.6676008246311237</t>
+          <t>0.42209629539635307</t>
         </is>
       </c>
     </row>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>0.8694888362212813</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.709594639875005</t>
+          <t>1.581935923466624</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>4.854788224958444</t>
+          <t>4.062037900663307</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.528210907507161</t>
+          <t>5.264671236996373</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.18465979669984</t>
+          <t>3.66952045814922</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>7.0690678242618015</t>
+          <t>6.855101362585138</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.745004612950737</t>
+          <t>0.6982870053242229</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>32.65837719540821</t>
+          <t>32.09475278245678</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>16.075077254245407</t>
+          <t>15.731566972377017</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2.039508598870059</t>
+          <t>1.718795935775477</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.48584381666107</t>
+          <t>10.09148923022982</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>1.08021037643291</t>
+          <t>0.9808314820514329</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.7921166996164796</t>
+          <t>0.7881486774032597</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>18.119761760754578</t>
+          <t>18.45993500263849</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.020239920875511</t>
+          <t>4.041913886373479</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>21.926318567548872</t>
+          <t>22.03509123806623</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.435726503648778</t>
+          <t>0.3824598690291807</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6925411725268137</t>
+          <t>0.6850444273091363</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.313454766835214</t>
+          <t>15.068844984985633</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>18.92665986559888</t>
+          <t>21.60748490916555</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>3.494033280594053</t>
+          <t>3.1963398122945823</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2.253449345365709</t>
+          <t>1.983371886327645</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>6.486076867523357</t>
+          <t>12.039994594163934</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>4.032445649726195</t>
+          <t>3.871552565866407</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>5.260504774975272</t>
+          <t>4.831803262484551</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>7.947093099750347</t>
+          <t>8.759410385974064</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>10.34840713840645</t>
+          <t>10.019416871574691</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>0.506034915012714</t>
+          <t>0.47612245203453174</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.352576230049309</t>
+          <t>7.07519335922703</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,95 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2344412889806784</t>
+          <t>0.2057991983109635</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>F2P_INT_Annin</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>0.282869268194648</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Yamcha</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>1.283809063882794</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>BU_INT_DBS_Broly_Vegeta</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>4.488085382596886</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>DFLR_TEQ_Golden_Frieza_Gogeta</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>81.53173589251217</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.5765947400608695</t>
+          <t>5.69015378187834</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.8772250623065965</t>
+          <t>1.8870698824560512</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.935527304789746</t>
+          <t>2.9140732902403284</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.9613101445951078</t>
+          <t>1.0106456690272152</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9334035840696839</t>
+          <t>1.006333734255793</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.737460381687818</t>
+          <t>10.052329070335858</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.431487285259418</t>
+          <t>3.3103538590854598</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7005163678368014</t>
+          <t>1.8448284714331569</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7.08033599872199</t>
+          <t>6.828038759436825</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.706903094102774</t>
+          <t>5.773567538830492</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.0698051650371205</t>
+          <t>3.0223079824540093</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.322806229155444</t>
+          <t>4.816766407836238</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.744994527801852</t>
+          <t>2.5273856305575566</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.4801573928843139</t>
+          <t>0.4632701075937768</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.6692012815490624</t>
+          <t>0.358903483722558</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.8384523921250074</t>
+          <t>0.5520677268000931</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.741743302139011</t>
+          <t>0.6188368317389679</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.156716498455985</t>
+          <t>4.1409186115715</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4879302695476937</t>
+          <t>0.5012160281224791</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>15.242485906199043</t>
+          <t>13.870642768516017</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2501100096054711</t>
+          <t>0.3101282287899791</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.28577441249509206</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.8149424301242405</t>
+          <t>6.802607032637521</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6.059208390147677</t>
+          <t>7.492976441950576</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5218570506356909</t>
+          <t>0.5409131174477708</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.6225059888481</t>
+          <t>3.4865342486630886</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0677555159141265</t>
+          <t>1.123419334725318</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4448658739075828</t>
+          <t>0.4649716416888545</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2857363370383226</t>
+          <t>0.24936068288057012</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.693183496693578</t>
+          <t>3.749800660500956</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.4756445545241519</t>
+          <t>1.5411328144625875</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.8531178502610373</t>
+          <t>2.977710291111035</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.62401011437987</t>
+          <t>2.7346360113884134</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.34415340671088296</t>
+          <t>0.32073210173046285</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.865838249503085</t>
+          <t>8.472468626708348</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.909628482225408</t>
+          <t>4.776301812490274</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.834171547994984</t>
+          <t>0.9921523266602748</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.3110748566586753</t>
+          <t>0.31968049152965927</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2033100857837449</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.0184232833940285</t>
+          <t>5.574569892672692</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.8602300325271708</t>
+          <t>0.5721379898073078</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.562906210686051</t>
+          <t>0.584073127909485</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2.00443399432778</t>
+          <t>1.864728714705219</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.4070159756038316</t>
+          <t>2.056477491361894</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23219650970634914</t>
+          <t>0.22988016621497734</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.522930536738791</t>
+          <t>2.4588067349725375</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2.0023138458201424</t>
+          <t>2.093907615967797</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.24886068478635</t>
+          <t>1.253467702955686</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20254686095301688</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.30295113794431644</t>
+          <t>0.37363009335911734</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.1107571221170414</t>
+          <t>1.166192296327874</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.35129445866580783</t>
+          <t>0.35106528733822867</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3853250507347394</t>
+          <t>1.4569985690941123</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7832316252016271</t>
+          <t>0.8172207527958082</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6422528335456902</t>
+          <t>0.7158049540125878</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>4.24432357983011</t>
+          <t>4.4110989252051676</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>7.08861363835094</t>
+          <t>9.472610360359718</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>10.7159057886858</t>
+          <t>11.19755957583417</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>15.91944376464247</t>
+          <t>4.693985470461946</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.538852025272349</t>
+          <t>1.756417258815567</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0.9389433553841791</t>
+          <t>1.765982958097391</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.220549282187873</t>
+          <t>4.176384149841818</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.370732310938193</t>
+          <t>15.00164965301541</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>23.678060791202675</t>
+          <t>22.78472953212276</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.7686958492712899</t>
+          <t>0.9674732790967409</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.544825659211343</t>
+          <t>8.955222333075351</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.4628788924077516</t>
+          <t>1.557856630134744</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5595192050364757</t>
+          <t>0.6002901862166494</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>10.421879519734519</t>
+          <t>10.39846375121928</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>5.003038927106211</t>
+          <t>4.6069201402128</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.778256731219168</t>
+          <t>13.10601899241199</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.42209629539635307</t>
+          <t>0.4696605662064821</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.581935923466624</t>
+          <t>1.638973779203208</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>4.062037900663307</t>
+          <t>2.967351183689141</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.264671236996373</t>
+          <t>5.504207089450729</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>3.66952045814922</t>
+          <t>3.481883343844677</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.855101362585138</t>
+          <t>6.429220070400369</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6982870053242229</t>
+          <t>0.7454097214785533</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>32.09475278245678</t>
+          <t>6.746229033936132</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>15.731566972377017</t>
+          <t>10.431200798152794</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.718795935775477</t>
+          <t>1.7989199472305653</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.09148923022982</t>
+          <t>10.57246497839993</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.9808314820514329</t>
+          <t>0.8858983670500793</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.7881486774032597</t>
+          <t>0.8012232592411711</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>18.45993500263849</t>
+          <t>18.331411405504284</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.041913886373479</t>
+          <t>5.105301426779391</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>22.03509123806623</t>
+          <t>22.845713672304182</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.3824598690291807</t>
+          <t>0.3785281559991037</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6850444273091363</t>
+          <t>0.6554684036238608</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>15.068844984985633</t>
+          <t>14.518858940437655</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>21.60748490916555</t>
+          <t>20.045200483517817</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>3.1963398122945823</t>
+          <t>3.490084942542565</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>1.983371886327645</t>
+          <t>2.4022984530406233</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>12.039994594163934</t>
+          <t>11.685143061892054</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.871552565866407</t>
+          <t>4.084654096015793</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.831803262484551</t>
+          <t>4.792686191802906</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>8.759410385974064</t>
+          <t>8.294443941905854</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>10.019416871574691</t>
+          <t>10.856408422182476</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>0.47612245203453174</t>
+          <t>0.4932816079274537</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.07519335922703</t>
+          <t>7.392707005290344</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2057991983109635</t>
+          <t>0.2099316545191594</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.282869268194648</t>
+          <t>0.2988646728923483</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1.283809063882794</t>
+          <t>1.004880584276258</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>4.488085382596886</t>
+          <t>1.412642853677399</t>
         </is>
       </c>
     </row>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>81.53173589251217</t>
+          <t>2.6395805201753575</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D410"/>
+  <dimension ref="A1:D411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.69015378187834</t>
+          <t>5.46610988368306</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>1.5817559830612324</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.56257377380247</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.7991784282579633</t>
+          <t>4.1634158882780214</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.5486684907352526</t>
+          <t>3.8888888888888884</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.8870698824560512</t>
+          <t>1.7984836086212161</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.9140732902403284</t>
+          <t>2.8241642562711076</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.054503988707488</t>
+          <t>1.1556021239177248</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.0106456690272152</t>
+          <t>0.9647525319395724</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.006333734255793</t>
+          <t>0.9301623182525403</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.052329070335858</t>
+          <t>9.70526157884938</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.317101598251191</t>
+          <t>1.4433756729740645</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.3103538590854598</t>
+          <t>3.2067540888567705</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.8448284714331569</t>
+          <t>1.680044525846534</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.4037492838456807</t>
+          <t>2.634203196502382</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6.828038759436825</t>
+          <t>7.06907577148517</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.773567538830492</t>
+          <t>5.59345253407409</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.0223079824540093</t>
+          <t>3.703099312970821</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.864749665935244</t>
+          <t>9.714637072648715</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.816766407836238</t>
+          <t>4.257561312862458</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.5273856305575566</t>
+          <t>3.689936646202552</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.4632701075937768</t>
+          <t>0.4757161768353174</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.8012497612818937</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.358903483722558</t>
+          <t>0.39887313647796696</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.5520677268000931</t>
+          <t>0.5250125978774465</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6188368317389679</t>
+          <t>0.715439215499061</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.1409186115715</t>
+          <t>4.139947420187596</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.46260176536422465</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5012160281224791</t>
+          <t>0.48323997228840426</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.2926892440558202</t>
+          <t>0.3207501495497921</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>13.870642768516017</t>
+          <t>14.827438257957724</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3101282287899791</t>
+          <t>0.4069046373479304</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6.802607032637521</t>
+          <t>6.431558358469779</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.3655761147090257</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>7.492976441950576</t>
+          <t>6.0250053397154915</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5409131174477708</t>
+          <t>0.526900126822226</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3.4865342486630886</t>
+          <t>2.0990168868561585</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2.0817079441390107</t>
+          <t>2.281286886901235</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>2.0015615919600047</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.2739681727838111</t>
+          <t>0.3002342387940007</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.123419334725318</t>
+          <t>1.066192897038514</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4649716416888545</t>
+          <t>0.44455318891689577</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.24936068288057012</t>
+          <t>0.23185826695407744</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.749800660500956</t>
+          <t>3.703075821061237</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.5411328144625875</t>
+          <t>1.3690250538058413</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.46260176536422465</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.2670832537606312</t>
+          <t>0.2926892440558202</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.977710291111035</t>
+          <t>2.8474879065919545</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>1.7060218686421196</t>
+          <t>1.8695827763244182</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.7346360113884134</t>
+          <t>2.6418862330426163</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.32073210173046285</t>
+          <t>0.3366413779805619</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.472468626708348</t>
+          <t>8.209032132944067</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.776301812490274</t>
+          <t>4.7654401147301115</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9921523266602748</t>
+          <t>0.41202823775593644</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.5567701270800032</t>
+          <t>1.7060218686421196</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.31968049152965927</t>
+          <t>0.31222083342156776</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2033100857837449</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>5.574569892672692</t>
+          <t>5.681040043326469</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.5721379898073078</t>
+          <t>0.5687787343526094</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.584073127909485</t>
+          <t>0.5818583022610359</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.864728714705219</t>
+          <t>1.7968387662566292</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2.056477491361894</t>
+          <t>1.3461499203926661</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.22988016621497734</t>
+          <t>0.23906384787778445</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.4588067349725375</t>
+          <t>2.410270144416822</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2.093907615967797</t>
+          <t>1.9768624715750271</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.253467702955686</t>
+          <t>1.2962962962962958</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.20254686095301688</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.37363009335911734</t>
+          <t>0.2980571349226166</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.166192296327874</t>
+          <t>1.107841651272472</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.1828894969117507</t>
+          <t>1.2962962962962958</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.35106528733822867</t>
+          <t>0.33739305831535094</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.4569985690941123</t>
+          <t>1.3913555566388789</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.8172207527958082</t>
+          <t>0.788630685959546</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.32382123575495725</t>
+          <t>0.3548668490735252</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.7158049540125878</t>
+          <t>0.6821302145093782</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>4.4110989252051676</t>
+          <t>4.203072149704472</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>9.472610360359718</t>
+          <t>6.711392495959651</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.19755957583417</t>
+          <t>10.74953945465116</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>4.693985470461946</t>
+          <t>5.745120929948399</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.756417258815567</t>
+          <t>1.5569220974121896</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.765982958097391</t>
+          <t>1.5484824871985712</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.176384149841818</t>
+          <t>4.291377053473606</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.00164965301541</t>
+          <t>16.02914995186372</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>22.78472953212276</t>
+          <t>24.463926343096315</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.9674732790967409</t>
+          <t>0.8273152638951179</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.955222333075351</t>
+          <t>8.678554214500636</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.557856630134744</t>
+          <t>1.4727816119221768</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.6002901862166494</t>
+          <t>0.5620323269019494</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>10.39846375121928</t>
+          <t>11.102151688669382</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>4.6069201402128</t>
+          <t>4.1971649228361905</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>13.10601899241199</t>
+          <t>12.819828579998557</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.4696605662064821</t>
+          <t>0.42410521984373817</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.7484170156161815</t>
+          <t>0.820169768994713</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.638973779203208</t>
+          <t>1.602902542163351</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.967351183689141</t>
+          <t>2.926968956495221</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.504207089450729</t>
+          <t>5.325682119007242</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>3.481883343844677</t>
+          <t>3.453903205736545</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.429220070400369</t>
+          <t>6.3171200018092195</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7454097214785533</t>
+          <t>0.6927937577999659</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>0.2048824708390741</t>
+          <t>0.2245251046848544</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.746229033936132</t>
+          <t>6.595158630500688</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>10.431200798152794</t>
+          <t>7.952385617934205</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.7989199472305653</t>
+          <t>1.755137508685367</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.57246497839993</t>
+          <t>10.18018328492368</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8858983670500793</t>
+          <t>0.9904327386387525</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.8012232592411711</t>
+          <t>0.7681382376068221</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>18.331411405504284</t>
+          <t>18.670832930404124</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.105301426779391</t>
+          <t>4.704578293251188</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>22.845713672304182</t>
+          <t>21.91412091789013</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.3785281559991037</t>
+          <t>0.3870966572795732</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6554684036238608</t>
+          <t>0.645677538820556</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>14.518858940437655</t>
+          <t>15.029384036577483</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20.045200483517817</t>
+          <t>22.072097055977082</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>3.490084942542565</t>
+          <t>3.24680789680146</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2.4022984530406233</t>
+          <t>1.973726251896709</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>11.685143061892054</t>
+          <t>11.88348455161861</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>4.084654096015793</t>
+          <t>3.8174791762904405</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.792686191802906</t>
+          <t>4.958690828358571</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>8.294443941905854</t>
+          <t>8.844434508059365</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>10.856408422182476</t>
+          <t>9.98018565667837</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>0.4932816079274537</t>
+          <t>0.48183704122008075</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.392707005290344</t>
+          <t>7.137478252307672</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2099316545191594</t>
+          <t>0.21778744785993248</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.2988646728923483</t>
+          <t>0.28361235164346915</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1.004880584276258</t>
+          <t>0.9315179293678965</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.412642853677399</t>
+          <t>1.4749083345302445</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,29 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.6395805201753575</t>
+          <t>1.960001227323929</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>CLR_TEQ_Wrathful_Broly</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>6.630025527325625</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D415"/>
+  <dimension ref="A1:D422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.21353445652834</t>
+          <t>6.17064039995385</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3655761147090257</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>1.7334031858765866</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.1634158882780214</t>
+          <t>4.56257377380247</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.8888888888888884</t>
+          <t>4.261727132192617</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.054503988707488</t>
+          <t>1.1556021239177248</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.18573815540885</t>
+          <t>2.132332714079098</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.005018817437332</t>
+          <t>3.006294108422466</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.1556021239177248</t>
+          <t>1.2663928094193209</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.1159278109994588</t>
+          <t>1.0948837394798392</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.111517217183212</t>
+          <t>1.0789216344495691</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.255307538292833</t>
+          <t>9.259738246443591</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>1.5817559830612324</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.5162202478290094</t>
+          <t>3.489123402690609</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.014707830179246</t>
+          <t>1.9745004314946584</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.634203196502382</t>
+          <t>2.886751345948129</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.967050664739151</t>
+          <t>9.89718133764697</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.637572008407244</t>
+          <t>4.585770641651896</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.160636534983439</t>
+          <t>4.132293659608109</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.714637072648715</t>
+          <t>10.646005472205763</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.2018746419228403</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.405215830526797</t>
+          <t>4.430922600600683</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.763405394391926</t>
+          <t>3.783912191635829</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5367061069308079</t>
+          <t>0.5319156235246268</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.4215553039590265</t>
+          <t>0.41030672372375926</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.5168733096205269</t>
+          <t>0.5054736405823124</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6958271901668671</t>
+          <t>0.6764830964548461</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.013990899748329</t>
+          <t>4.0467685003687635</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.20865807245338586</t>
+          <t>0.2014546494593155</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.46260176536422465</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5407120336902049</t>
+          <t>0.5255418642203459</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.613152354337152</t>
+          <t>0.5950932509468597</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.747994170698766</t>
+          <t>10.63026198285205</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.4412375800401994</t>
+          <t>0.4323179227907339</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.381860478054982</t>
+          <t>1.378492060559438</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.371194915947911</t>
+          <t>4.301952432699249</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.4768774548890691</t>
+          <t>0.46326203304283187</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.9947725651819326</t>
+          <t>2.989785064970411</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2.281286886901235</t>
+          <t>2.5</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.0015615919600047</t>
+          <t>2.193456688254154</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.3002342387940007</t>
+          <t>0.32901850323812315</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.2478740394688481</t>
+          <t>1.2345321521337513</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.49092916560376826</t>
+          <t>0.47494312394737837</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2658717065201124</t>
+          <t>0.26153275525536834</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.079235829594733</t>
+          <t>4.030723781999785</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.5906296616918432</t>
+          <t>1.5601793954488485</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.25347632076680376</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.2926892440558202</t>
+          <t>0.3207501495497921</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>3.6011786324443262</t>
+          <t>3.550737820630887</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>1.8695827763244182</t>
+          <t>2.0488247083907414</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.9324574053907666</t>
+          <t>2.8652834809278054</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.33488687004424117</t>
+          <t>0.3223964661073091</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.316463106814872</t>
+          <t>8.360292805198405</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.751680488706221</t>
+          <t>4.771595009013673</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.48715964368596737</t>
+          <t>0.4811427965485804</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.7060218686421196</t>
+          <t>1.8695827763244182</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.22023035346294684</t>
+          <t>0.21590070946234743</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.22191129916567778</t>
+          <t>0.21745812676523862</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.460311342788778</t>
+          <t>6.485396625226969</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.4212636106504534</t>
+          <t>0.4082625583720914</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6039751004045997</t>
+          <t>0.582346657670827</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.7922808576794402</t>
+          <t>1.7640036506954608</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.4910329241596818</t>
+          <t>1.4666307304222534</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2509893023651805</t>
+          <t>0.24198503875064667</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.3827064937538631</t>
+          <t>1.3745854618158242</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.7783394077164241</t>
+          <t>0.7664361569018014</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.2962962962962958</t>
+          <t>1.4205757107308723</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.3345684662529665</t>
+          <t>0.3286866496822063</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.2904211984427105</t>
+          <t>1.2700094760444456</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.2962962962962958</t>
+          <t>1.4205757107308723</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3705392345669769</t>
+          <t>0.36027726841643887</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.6139209621150596</t>
+          <t>1.5824682688713019</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.9005159794251275</t>
+          <t>0.8798538265376852</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.3548668490735252</t>
+          <t>0.3888888888888888</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.7214662104211261</t>
+          <t>0.7022302340283141</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.3277051204733166</t>
+          <t>2.2921093678505216</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>10.81329370105327</t>
+          <t>10.616084387353489</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.561771334276101</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.2130839035753</t>
+          <t>11.98113475792205</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>14.29162910832062</t>
+          <t>14.340948531889481</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.3521437835857069</t>
+          <t>1.3185060307494203</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2.161512428531349</t>
+          <t>2.15802277079038</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.395180127112706</t>
+          <t>4.270794451847028</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10.926735300954723</t>
+          <t>10.774251512055516</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>25.182766834426747</t>
+          <t>25.285504359967018</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.6745393618155344</t>
+          <t>0.6556180847597329</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.259249178478116</t>
+          <t>8.205650959807679</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.5369079326588428</t>
+          <t>1.5097101955851007</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.6110269437736138</t>
+          <t>0.5987826599260506</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.594584836912581</t>
+          <t>9.50783801762075</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.8803613665671013</t>
+          <t>3.8384069229976703</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.404010531937281</t>
+          <t>12.448011017558246</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.7342964365712291</t>
+          <t>0.7151034695332946</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.820169768994713</t>
+          <t>0.8988016519360076</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.735637715581498</t>
+          <t>1.681728273355257</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.315762874486631</t>
+          <t>2.243849723402082</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.983023824356252</t>
+          <t>5.82749457037785</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.062692035920684</t>
+          <t>7.976505514861958</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>7.090835565045619</t>
+          <t>7.029202863861812</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7912246326354264</t>
+          <t>0.7777568958173363</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>0.2245251046848544</t>
+          <t>0.2460509306984139</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.995685992853964</t>
+          <t>6.984255205371589</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>5.810215094152646</t>
+          <t>5.8327914475395275</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.7494873969017288</t>
+          <t>1.690217647020984</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>11.623926422905</t>
+          <t>11.36233160792764</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8414593637060035</t>
+          <t>0.8063261449256588</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.8602292929663286</t>
+          <t>0.8576502721450814</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.92463167609415</t>
+          <t>25.005771438812396</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.291056895144351</t>
+          <t>4.326296969298355</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>25.299591510402337</t>
+          <t>25.4264427408276</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4152800283457145</t>
+          <t>0.3987445773894692</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6713274165488817</t>
+          <t>0.6404029936869543</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20.791890990972675</t>
+          <t>21.1797546035298</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>26.33166088950626</t>
+          <t>26.706200212615283</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>7.7554938253441295</t>
+          <t>7.828960360176979</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>4.148852134742479</t>
+          <t>3.843822811259166</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.936283603090603</t>
+          <t>4.868145581021032</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>7.867125623185571</t>
+          <t>7.987238380834199</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6.691015115636041</t>
+          <t>6.602182049150279</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>8.145422570718578</t>
+          <t>7.961424481551759</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.3019267910113714</t>
+          <t>0.2904264719644244</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.3198226407736543</t>
+          <t>0.3158565079186206</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1.0638075427232003</t>
+          <t>1.046158862809984</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.6225423833181454</t>
+          <t>1.5918408795364727</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.8036800977147605</t>
+          <t>1.840485682696226</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>8.494865498649897</t>
+          <t>8.328513194839285</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>5.749759781410594</t>
+          <t>5.681356922945177</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,161 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.539704395397266</t>
+          <t>14.670245650932145</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>LR_TEQ_Super_17</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>LR_INT_Baby_Possessed_Bros</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>15.74188923701543</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>LR_AGL_Majin_Vegeta</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>5.271436657421702</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Baby_Possessed_Gohan</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Baby_Possessed_Goten</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>F2P_INT_Baby_Possessed_Trunks</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>F2PLR_STR_Chi_Chi</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>4.145062396081411</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D422"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.17064039995385</t>
+          <t>6.27511326988952</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.132332714079098</t>
+          <t>1.9775662158415226</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.006294108422466</t>
+          <t>2.9291078153044845</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.0948837394798392</t>
+          <t>1.0631421963683494</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.0789216344495691</t>
+          <t>1.0391906782086666</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.259738246443591</t>
+          <t>9.367110747355085</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.489123402690609</t>
+          <t>3.118269073713419</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.9745004314946584</t>
+          <t>1.9280085059469263</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.89718133764697</t>
+          <t>9.739934870120434</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.585770641651896</t>
+          <t>5.12042165125668</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.132293659608109</t>
+          <t>4.029721844962268</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.430922600600683</t>
+          <t>4.384776355234135</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.783912191635829</t>
+          <t>3.771262573599267</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5319156235246268</t>
+          <t>0.5126194832447912</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.41030672372375926</t>
+          <t>0.38444710171983026</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.5054736405823124</t>
+          <t>0.4661077054450167</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6764830964548461</t>
+          <t>0.6258342572683173</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.0467685003687635</t>
+          <t>4.071056143039584</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.2014546494593155</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5255418642203459</t>
+          <t>0.5058589227515468</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5950932509468597</t>
+          <t>0.5739851645477984</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.63026198285205</t>
+          <t>10.836362920824051</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.4323179227907339</t>
+          <t>0.41293330944061346</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.378492060559438</t>
+          <t>1.7477988090448449</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.301952432699249</t>
+          <t>4.026590867444948</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.46326203304283187</t>
+          <t>0.7304715850215887</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.989785064970411</t>
+          <t>2.912231472641559</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.2345321521337513</t>
+          <t>1.2001245749042393</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.47494312394737837</t>
+          <t>0.44745841415399623</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.26153275525536834</t>
+          <t>0.2529492017133732</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.030723781999785</t>
+          <t>4.150183438740635</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.5601793954488485</t>
+          <t>1.4332918358276419</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>3.550737820630887</t>
+          <t>3.1987681367485115</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.8652834809278054</t>
+          <t>2.8000360912370645</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.3223964661073091</t>
+          <t>0.3140861821689471</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.360292805198405</t>
+          <t>8.226268541067924</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.771595009013673</t>
+          <t>4.781093223871898</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.4811427965485804</t>
+          <t>0.4551974566870456</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1.8695827763244182</t>
+          <t>0.33123402300463406</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.21590070946234743</t>
+          <t>0.20923415617259672</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.21745812676523862</t>
+          <t>0.21018891583520166</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.485396625226969</t>
+          <t>6.350582581730627</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.4082625583720914</t>
+          <t>0.5154584915772658</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.582346657670827</t>
+          <t>0.5484644119165465</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.7640036506954608</t>
+          <t>1.6536208167695108</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.4666307304222534</t>
+          <t>1.4254510322626892</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.24198503875064667</t>
+          <t>0.22732189077929288</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.3745854618158242</t>
+          <t>1.3276929279594</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.7664361569018014</t>
+          <t>0.7252416682528198</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.3286866496822063</t>
+          <t>0.3162506836926721</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.2700094760444456</t>
+          <t>1.238654079042825</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.36027726841643887</t>
+          <t>0.33965428223127153</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.5824682688713019</t>
+          <t>1.5376245511429605</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.8798538265376852</t>
+          <t>0.8559533914509156</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.7022302340283141</t>
+          <t>0.6554622015032378</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.2921093678505216</t>
+          <t>2.1620571313495622</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>10.616084387353489</t>
+          <t>8.936896996470168</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2.561771334276101</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.98113475792205</t>
+          <t>12.2731404735573</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>14.340948531889481</t>
+          <t>14.16647486551598</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.3185060307494203</t>
+          <t>1.2662528978097105</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2.15802277079038</t>
+          <t>2.1804462100961306</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.270794451847028</t>
+          <t>3.9828812622342875</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10.774251512055516</t>
+          <t>10.306194242436971</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>25.285504359967018</t>
+          <t>24.89234306215721</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.6556180847597329</t>
+          <t>0.6004010642790676</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.205650959807679</t>
+          <t>7.9646503273075435</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.5097101955851007</t>
+          <t>1.441518175360958</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5987826599260506</t>
+          <t>0.5767897513596196</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.50783801762075</t>
+          <t>9.07315417296447</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.8384069229976703</t>
+          <t>3.5623352227785308</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.448011017558246</t>
+          <t>14.380604299557127</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.7151034695332946</t>
+          <t>0.6571466008688598</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.681728273355257</t>
+          <t>1.6451082526088767</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.243849723402082</t>
+          <t>2.041324484845279</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.82749457037785</t>
+          <t>5.684194068920413</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>7.976505514861958</t>
+          <t>7.569283033526993</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>7.029202863861812</t>
+          <t>6.822573015050082</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7777568958173363</t>
+          <t>0.7305164572872074</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.984255205371589</t>
+          <t>6.862899769139162</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>5.8327914475395275</t>
+          <t>7.168612628501322</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.690217647020984</t>
+          <t>1.590053725975505</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>11.36233160792764</t>
+          <t>11.06869849646139</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8063261449256588</t>
+          <t>0.7513653130876512</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.8576502721450814</t>
+          <t>0.8504978112354858</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>25.005771438812396</t>
+          <t>24.92469089920612</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.326296969298355</t>
+          <t>4.245436584318327</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>25.4264427408276</t>
+          <t>25.236748624394572</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.3987445773894692</t>
+          <t>0.4512937372715812</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6404029936869543</t>
+          <t>0.6046391306235978</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>21.1797546035298</t>
+          <t>22.27125982122574</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>26.706200212615283</t>
+          <t>27.863574874677976</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>7.828960360176979</t>
+          <t>7.959432688033303</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.843822811259166</t>
+          <t>3.727517948719715</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.868145581021032</t>
+          <t>4.728704723316338</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>7.987238380834199</t>
+          <t>8.43611539362142</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6.602182049150279</t>
+          <t>6.287953283753065</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.961424481551759</t>
+          <t>7.768236635894428</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2904264719644244</t>
+          <t>0.2823424725783134</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.3158565079186206</t>
+          <t>0.3051944582833101</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1.046158862809984</t>
+          <t>1.0176340658313023</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.5918408795364727</t>
+          <t>1.566174330445139</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.840485682696226</t>
+          <t>1.913538606647677</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>8.328513194839285</t>
+          <t>7.644481925630623</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>5.681356922945177</t>
+          <t>5.362598274447428</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.670245650932145</t>
+          <t>15.183360848716191</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>15.74188923701543</t>
+          <t>14.75301672365481</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>5.271436657421702</t>
+          <t>3.1896805178116003</t>
         </is>
       </c>
     </row>
@@ -9703,12 +9703,78 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2.9330946722245756</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>F2P_INT_Goten_Icarus</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>BU_PHY_Piccolo_Mini_Daima</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>4.145062396081411</t>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>16.3014367892922</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>DF_TEQ_SS4_Goku_Mini_Daima</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>41.21476162219281</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.2018746419228403</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.27511326988952</t>
+          <t>5.748088997903668</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.7334031858765866</t>
+          <t>1.8995892141289816</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.479363455676221</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.56257377380247</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.261727132192617</t>
+          <t>4.670310381240009</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.1556021239177248</t>
+          <t>1.2663928094193209</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.9775662158415226</t>
+          <t>1.787997065189932</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.9291078153044845</t>
+          <t>3.0611974215346778</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.2663928094193209</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.6088181617418025</t>
+          <t>0.6671871973200014</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.0631421963683494</t>
+          <t>1.0042109238237282</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.0391906782086666</t>
+          <t>0.9720695909413792</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.367110747355085</t>
+          <t>8.624583569139748</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>1.7334031858765866</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.118269073713419</t>
+          <t>2.820942365495158</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.9280085059469263</t>
+          <t>1.7750169564883258</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.886751345948129</t>
+          <t>3.163511966122465</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.739934870120434</t>
+          <t>8.813762271863546</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.12042165125668</t>
+          <t>4.5593170998165355</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.029721844962268</t>
+          <t>3.6508522033163975</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.646005472205763</t>
+          <t>11.666666666666664</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.2018746419228403</t>
+          <t>1.317101598251191</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.384776355234135</t>
+          <t>3.4037136518682343</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.771262573599267</t>
+          <t>3.656481436399693</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5126194832447912</t>
+          <t>0.4868714779590252</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.38444710171983026</t>
+          <t>0.3534143467599192</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.4661077054450167</t>
+          <t>0.42789996885077786</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6258342572683173</t>
+          <t>0.587031325119033</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.071056143039584</t>
+          <t>4.040339407132983</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5058589227515468</t>
+          <t>0.4805535909199937</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5739851645477984</t>
+          <t>0.5176550280360541</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.836362920824051</t>
+          <t>9.457042380675874</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.41293330944061346</t>
+          <t>0.3714579080724956</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.7477988090448449</t>
+          <t>1.619706793550531</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.026590867444948</t>
+          <t>3.7189710182489484</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.7304715850215887</t>
+          <t>0.6938773037229238</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.912231472641559</t>
+          <t>2.674105581840749</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.193456688254154</t>
+          <t>2.4037492838456807</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.32901850323812315</t>
+          <t>0.36056239257685213</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.2001245749042393</t>
+          <t>1.0881356925632737</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.44745841415399623</t>
+          <t>0.412131016200882</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2529492017133732</t>
+          <t>0.24431914450643788</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.150183438740635</t>
+          <t>4.111171173847369</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.4332918358276419</t>
+          <t>1.3218853784882558</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.2777777777777778</t>
+          <t>0.30440908087090124</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.3207501495497921</t>
+          <t>0.3515013295691628</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>3.1987681367485115</t>
+          <t>2.9084022134895253</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2.0488247083907414</t>
+          <t>2.2452510468485443</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.8000360912370645</t>
+          <t>2.687941388392448</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.3140861821689471</t>
+          <t>0.31948994186917223</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.226268541067924</t>
+          <t>8.236355730164703</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.781093223871898</t>
+          <t>4.769694904329697</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.4551974566870456</t>
+          <t>0.5418821327221193</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.369299349377167</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.33123402300463406</t>
+          <t>0.39259205332151914</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.20923415617259672</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.21018891583520166</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.350582581730627</t>
+          <t>7.8461932227916344</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.5154584915772658</t>
+          <t>0.46956750776365297</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5484644119165465</t>
+          <t>0.5608748328973255</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.6536208167695108</t>
+          <t>1.4579200184924712</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.4254510322626892</t>
+          <t>1.4110307639832504</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.22732189077929288</t>
+          <t>0.23159256996537927</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.3276929279594</t>
+          <t>1.2101956949325867</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.7252416682528198</t>
+          <t>0.6430393602332796</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.4205757107308723</t>
+          <t>1.5567701270800032</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.3162506836926721</t>
+          <t>0.28310508217238245</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.238654079042825</t>
+          <t>1.1351872789107622</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.4205757107308723</t>
+          <t>1.5567701270800032</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.33965428223127153</t>
+          <t>0.32829504299804774</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.5376245511429605</t>
+          <t>1.3998521747338093</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.8559533914509156</t>
+          <t>0.7994625752254789</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.3888888888888888</t>
+          <t>0.4261727132192617</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6554622015032378</t>
+          <t>0.6246648147092652</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.1620571313495622</t>
+          <t>1.9534183467276032</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>8.936896996470168</t>
+          <t>8.00194449101668</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.2731404735573</t>
+          <t>11.34815178233698</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>14.16647486551598</t>
+          <t>13.3160625853371</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.2662528978097105</t>
+          <t>1.144574592783843</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2.1804462100961306</t>
+          <t>1.9728411121237792</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>3.9828812622342875</t>
+          <t>4.012187382571737</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10.306194242436971</t>
+          <t>14.835373655486109</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>24.89234306215721</t>
+          <t>23.062763670467987</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.6004010642790676</t>
+          <t>0.5473560760530308</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.9646503273075435</t>
+          <t>8.263360064368321</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.441518175360958</t>
+          <t>1.2872025521602763</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5767897513596196</t>
+          <t>0.5204734740406618</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.07315417296447</t>
+          <t>8.168364134925248</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.5623352227785308</t>
+          <t>3.14816213652618</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.380604299557127</t>
+          <t>14.761163997612634</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.6571466008688598</t>
+          <t>0.593577788522314</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.8988016519360076</t>
+          <t>0.9849721851039159</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.6451082526088767</t>
+          <t>1.604974729966987</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.041324484845279</t>
+          <t>1.960803773053153</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.684194068920413</t>
+          <t>5.360585414772254</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>7.569283033526993</t>
+          <t>7.986414002212382</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.822573015050082</t>
+          <t>6.18000518582879</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7305164572872074</t>
+          <t>0.6724082783974001</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>0.2460509306984139</t>
+          <t>0.2696404955808023</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.862899769139162</t>
+          <t>6.310529834015426</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>7.168612628501322</t>
+          <t>7.05038266134396</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.590053725975505</t>
+          <t>1.527979093008438</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>11.06869849646139</t>
+          <t>10.37642258263363</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.7513653130876512</t>
+          <t>0.8591326736801784</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.8504978112354858</t>
+          <t>0.7230016001660147</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.92469089920612</t>
+          <t>24.088625522974546</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.245436584318327</t>
+          <t>5.103868132807406</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>25.236748624394572</t>
+          <t>23.90098500234816</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4512937372715812</t>
+          <t>0.4576969497908571</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6046391306235978</t>
+          <t>0.6057294970241194</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>22.27125982122574</t>
+          <t>23.808549032394026</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>27.863574874677976</t>
+          <t>19.334747194292788</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>7.959432688033303</t>
+          <t>4.4648093391465205</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.727517948719715</t>
+          <t>3.3165961000555453</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.728704723316338</t>
+          <t>4.448163594545014</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>8.43611539362142</t>
+          <t>9.626808237820612</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6.287953283753065</t>
+          <t>5.504527814205558</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.768236635894428</t>
+          <t>7.506014212153447</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2823424725783134</t>
+          <t>0.2902923744133856</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.3051944582833101</t>
+          <t>0.2749398793744641</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>1.0176340658313023</t>
+          <t>0.9330311696731814</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.566174330445139</t>
+          <t>1.4366071672424985</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.913538606647677</t>
+          <t>2.294625627790481</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>7.644481925630623</t>
+          <t>6.874107651739113</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>5.362598274447428</t>
+          <t>4.770888985598127</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.183360848716191</t>
+          <t>16.04369175316961</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>14.75301672365481</t>
+          <t>14.23725204916376</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.1896805178116003</t>
+          <t>2.8076605112078314</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.9330946722245756</t>
+          <t>2.6550837047342157</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>16.3014367892922</t>
+          <t>14.9680547692242</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>41.21476162219281</t>
+          <t>40.23565743591566</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.748088997903668</t>
+          <t>5.772653450953843</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.787997065189932</t>
+          <t>1.7837348063994507</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.0611974215346778</t>
+          <t>3.0627766375594376</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.0042109238237282</t>
+          <t>1.007905355670706</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9720695909413792</t>
+          <t>0.9747320640873163</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.624583569139748</t>
+          <t>8.638772553617304</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.820942365495158</t>
+          <t>2.8291901680256277</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7750169564883258</t>
+          <t>1.7822516487872342</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.813762271863546</t>
+          <t>8.853708615629175</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.5593170998165355</t>
+          <t>4.568340378025192</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.6508522033163975</t>
+          <t>3.66170446988481</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.4037136518682343</t>
+          <t>3.4087850124921846</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.656481436399693</t>
+          <t>3.655779170196786</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.4868714779590252</t>
+          <t>0.48777814930307173</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3534143467599192</t>
+          <t>0.3536825707350435</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.42789996885077786</t>
+          <t>0.42717818399114904</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.587031325119033</t>
+          <t>0.5859687330333005</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.040339407132983</t>
+          <t>4.040981211321274</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4805535909199937</t>
+          <t>0.48087268502932534</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5176550280360541</t>
+          <t>0.517396733080124</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9.457042380675874</t>
+          <t>9.417149272733333</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3714579080724956</t>
+          <t>0.37190877813854123</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.619706793550531</t>
+          <t>1.6234043452534763</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.7189710182489484</t>
+          <t>3.714055442736943</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6938773037229238</t>
+          <t>0.6959012995268222</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.674105581840749</t>
+          <t>2.677854684038477</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0881356925632737</t>
+          <t>1.0933952486154601</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.412131016200882</t>
+          <t>0.41223775944802243</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.24431914450643788</t>
+          <t>0.24504096184973623</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.111171173847369</t>
+          <t>4.121913566550518</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3218853784882558</t>
+          <t>1.323676406469625</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.9084022134895253</t>
+          <t>2.918293377223036</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.687941388392448</t>
+          <t>2.694666211509644</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.31948994186917223</t>
+          <t>0.31829137467799723</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.236355730164703</t>
+          <t>8.251794612237752</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.769694904329697</t>
+          <t>4.776605968205189</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.5418821327221193</t>
+          <t>0.5437142724895979</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.369299349377167</t>
+          <t>0.3704095446429516</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.39259205332151914</t>
+          <t>0.39182248118976415</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.8461932227916344</t>
+          <t>7.856423708697868</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.46956750776365297</t>
+          <t>0.4685161566304945</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.4579200184924712</t>
+          <t>1.45613271601888</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.4110307639832504</t>
+          <t>1.4134023542043161</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23159256996537927</t>
+          <t>0.2311224775182495</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2101956949325867</t>
+          <t>1.2117415238196594</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6430393602332796</t>
+          <t>0.6430419795045932</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.28310508217238245</t>
+          <t>0.28377593555755454</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.1351872789107622</t>
+          <t>1.1402084208316436</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.32829504299804774</t>
+          <t>0.3281680200725084</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3998521747338093</t>
+          <t>1.4048111483111472</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7994625752254789</t>
+          <t>0.801298939065135</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6246648147092652</t>
+          <t>0.6242965143826038</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.9534183467276032</t>
+          <t>1.9552431966840782</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>8.00194449101668</t>
+          <t>8.0014389100003</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.34815178233698</t>
+          <t>11.36958738516831</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.3160625853371</t>
+          <t>13.34337490374677</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.144574592783843</t>
+          <t>1.1443963566430033</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.9728411121237792</t>
+          <t>1.9824754295638412</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.012187382571737</t>
+          <t>3.9980065067431987</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>14.835373655486109</t>
+          <t>14.854705361116052</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>23.062763670467987</t>
+          <t>23.07395442650456</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5473560760530308</t>
+          <t>0.5459410097836628</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.263360064368321</t>
+          <t>8.285152246732524</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.2872025521602763</t>
+          <t>1.2861075168061495</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5204734740406618</t>
+          <t>0.52083427618496</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.168364134925248</t>
+          <t>8.17580806742445</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.14816213652618</t>
+          <t>3.14089938425729</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.761163997612634</t>
+          <t>14.779825771857723</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.593577788522314</t>
+          <t>0.5917289032239177</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.604974729966987</t>
+          <t>1.605708702168416</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.960803773053153</t>
+          <t>1.957235466379031</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.360585414772254</t>
+          <t>5.372546259500848</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>7.986414002212382</t>
+          <t>7.991090651171374</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.18000518582879</t>
+          <t>6.19234553986929</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6724082783974001</t>
+          <t>0.6755735835461798</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.310529834015426</t>
+          <t>6.318642185467169</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>7.05038266134396</t>
+          <t>7.057300892678327</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.527979093008438</t>
+          <t>1.519440388172085</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.37642258263363</t>
+          <t>10.40698309128574</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8591326736801784</t>
+          <t>0.8566717554477196</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.7230016001660147</t>
+          <t>0.7240926851766005</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.088625522974546</t>
+          <t>24.109238146174437</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.103868132807406</t>
+          <t>5.099143537949175</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>23.90098500234816</t>
+          <t>23.93888980398149</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4576969497908571</t>
+          <t>0.4558815311233534</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6057294970241194</t>
+          <t>0.6034057443428419</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.808549032394026</t>
+          <t>23.81318283384283</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.334747194292788</t>
+          <t>19.372284472055185</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.4648093391465205</t>
+          <t>4.464132610567243</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.3165961000555453</t>
+          <t>3.3248194179309976</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.448163594545014</t>
+          <t>4.452504690242627</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.626808237820612</t>
+          <t>9.607077684827601</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.504527814205558</t>
+          <t>5.499889809735308</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.506014212153447</t>
+          <t>7.529886212638512</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2902923744133856</t>
+          <t>0.2886333862688523</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.2749398793744641</t>
+          <t>0.27546898431367695</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.9330311696731814</t>
+          <t>0.9368678150352134</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.4366071672424985</t>
+          <t>1.4416676392882435</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.294625627790481</t>
+          <t>2.288682555972997</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>6.874107651739113</t>
+          <t>6.851043928973827</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.770888985598127</t>
+          <t>4.7650945147594985</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.04369175316961</t>
+          <t>16.047734681074303</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>14.23725204916376</t>
+          <t>14.27699286422908</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.8076605112078314</t>
+          <t>2.802925606900415</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.6550837047342157</t>
+          <t>2.6598050607150716</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>14.9680547692242</t>
+          <t>9.237631522771624</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>40.23565743591566</t>
+          <t>40.26560463158606</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D425"/>
+  <dimension ref="A1:D435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.772653450953843</t>
+          <t>5.3302449585271106</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.7837348063994507</t>
+          <t>1.8716516898579418</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.0627766375594376</t>
+          <t>2.988461169604335</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.007905355670706</t>
+          <t>0.9779957746022129</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9747320640873163</t>
+          <t>0.966757479760932</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.638772553617304</t>
+          <t>8.82335779223691</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.8291901680256277</t>
+          <t>2.921240013122681</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7822516487872342</t>
+          <t>1.7456626393609234</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.853708615629175</t>
+          <t>8.418693051961043</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.568340378025192</t>
+          <t>3.7462772055644056</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.66170446988481</t>
+          <t>3.523889439951571</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.4087850124921846</t>
+          <t>3.3480049564679177</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.655779170196786</t>
+          <t>3.638861298261271</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.48777814930307173</t>
+          <t>0.46273009131762066</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3536825707350435</t>
+          <t>0.363490768887438</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.42717818399114904</t>
+          <t>0.44489584422710493</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5859687330333005</t>
+          <t>0.6240653225312063</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.040981211321274</t>
+          <t>4.022041760704674</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.48087268502932534</t>
+          <t>0.48370844305605076</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.517396733080124</t>
+          <t>0.5265327059118905</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9.417149272733333</t>
+          <t>8.588331087506374</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.37190877813854123</t>
+          <t>0.36783502024326986</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6234043452534763</t>
+          <t>1.5884921678842403</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.714055442736943</t>
+          <t>4.041964438109833</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6959012995268222</t>
+          <t>0.7034810570908788</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.677854684038477</t>
+          <t>2.6653088060257364</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0933952486154601</t>
+          <t>1.054758677734096</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.41223775944802243</t>
+          <t>0.4290554761277068</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.24504096184973623</t>
+          <t>0.23827672924428797</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.121913566550518</t>
+          <t>3.7761384138113963</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.323676406469625</t>
+          <t>1.4037904400957673</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.918293377223036</t>
+          <t>2.841465124208519</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.694666211509644</t>
+          <t>2.662938515690052</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.31829137467799723</t>
+          <t>0.33280984877236147</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.251794612237752</t>
+          <t>8.791051787531103</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.776605968205189</t>
+          <t>4.791347023086814</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.5437142724895979</t>
+          <t>0.5937585943715828</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.3704095446429516</t>
+          <t>0.3618523107151006</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.39182248118976415</t>
+          <t>0.41709374984005365</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.856423708697868</t>
+          <t>7.782723063789639</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.4685161566304945</t>
+          <t>0.4897134025512835</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5608748328973255</t>
+          <t>0.5934880455548311</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.45613271601888</t>
+          <t>1.4675948539878014</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.4134023542043161</t>
+          <t>1.3818808234142483</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2311224775182495</t>
+          <t>0.24164579226036106</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2117415238196594</t>
+          <t>1.2002704453719701</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6430419795045932</t>
+          <t>0.6439814395125705</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.28377593555755454</t>
+          <t>0.27799070939236153</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.1402084208316436</t>
+          <t>1.1049826750880305</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3281680200725084</t>
+          <t>0.34079958863888565</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.4048111483111472</t>
+          <t>1.3703319427938025</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.801298939065135</t>
+          <t>0.7869903961291587</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6242965143826038</t>
+          <t>0.6562869859910475</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.9552431966840782</t>
+          <t>1.9914500892440472</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>8.0014389100003</t>
+          <t>7.979434800884368</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.36958738516831</t>
+          <t>11.19807058757315</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.34337490374677</t>
+          <t>13.235116755239538</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1443963566430033</t>
+          <t>1.1423898193526818</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.9824754295638412</t>
+          <t>1.7953392698949315</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>3.9980065067431987</t>
+          <t>4.143016538857054</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>14.854705361116052</t>
+          <t>14.668292421120741</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>23.07395442650456</t>
+          <t>22.68671004531214</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5459410097836628</t>
+          <t>0.5735483520183936</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.285152246732524</t>
+          <t>8.095432763905492</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.2861075168061495</t>
+          <t>1.294664927650323</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.52083427618496</t>
+          <t>0.5178197257544985</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.17580806742445</t>
+          <t>8.122770295046559</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.14089938425729</t>
+          <t>3.2580509388212597</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.779825771857723</t>
+          <t>14.775874804079699</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.5917289032239177</t>
+          <t>0.6285084486914435</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.605708702168416</t>
+          <t>1.604484373017472</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.957235466379031</t>
+          <t>2.045661651845483</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.372546259500848</t>
+          <t>5.325068310202655</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>7.991090651171374</t>
+          <t>8.03303867198928</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.19234553986929</t>
+          <t>6.081200605544581</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6755735835461798</t>
+          <t>0.681161715866025</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.318642185467169</t>
+          <t>6.191761106523138</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>7.057300892678327</t>
+          <t>7.029515512598131</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.519440388172085</t>
+          <t>1.599121552356608</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.40698309128574</t>
+          <t>10.22871955390339</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8566717554477196</t>
+          <t>0.9010992061283113</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.7240926851766005</t>
+          <t>0.6764880247155247</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.109238146174437</t>
+          <t>23.60662468660984</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.099143537949175</t>
+          <t>5.8120361814273025</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>23.93888980398149</t>
+          <t>23.63124815763126</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4558815311233534</t>
+          <t>0.4912887413647867</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6034057443428419</t>
+          <t>0.6498075504218223</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.81318283384283</t>
+          <t>24.215831656547643</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.372284472055185</t>
+          <t>19.074868282446147</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.464132610567243</t>
+          <t>4.429105789174327</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.3248194179309976</t>
+          <t>3.2590289598352866</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.452504690242627</t>
+          <t>4.408654540297153</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.607077684827601</t>
+          <t>9.708572722376786</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.499889809735308</t>
+          <t>5.506012575412364</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.529886212638512</t>
+          <t>7.388008753175241</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2886333862688523</t>
+          <t>0.3032129132480611</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.27546898431367695</t>
+          <t>0.2718923215556574</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.9368678150352134</t>
+          <t>0.9153770251443437</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.4416676392882435</t>
+          <t>1.363708964660395</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.288682555972997</t>
+          <t>2.418662622625007</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>6.851043928973827</t>
+          <t>3.241464102498444</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.7650945147594985</t>
+          <t>4.838278114921345</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.047734681074303</t>
+          <t>15.881461867616842</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>14.27699286422908</t>
+          <t>13.83246215592572</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.802925606900415</t>
+          <t>2.8939299915603938</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.6598050607150716</t>
+          <t>2.6328069882171206</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.237631522771624</t>
+          <t>9.5625412698179</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,227 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>40.26560463158606</t>
+          <t>40.05506045624512</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Goku_Mini_Daima</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>F2P_INT_Vegeta_Mini_Daima</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>F2P_INT_Masked_Majin_Panzy</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>F2P_STR_Glorio</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>F2P_AGL_Manga_Goku</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>BU_PHY_Manga_Piccolo_Jr</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3706989318842199</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>BU_STR_Manga_Vegeta</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>BU_TEQ_Manga_SS2_Gohan</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>BU_INT_Manga_Final_Form_Frieza</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>9.800042947424899</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>BU_AGL_Manga_Majin_Buu</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.5469621491631673</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.3302449585271106</t>
+          <t>5.2027329778317295</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.8716516898579418</t>
+          <t>1.8849880214560641</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.988461169604335</t>
+          <t>2.9666396525465593</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.9779957746022129</t>
+          <t>0.9570052640091335</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.966757479760932</t>
+          <t>0.9499460069255821</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.82335779223691</t>
+          <t>8.78639696406101</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.921240013122681</t>
+          <t>2.9071452569091196</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7456626393609234</t>
+          <t>1.697130324502792</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.418693051961043</t>
+          <t>8.249346140256</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.7462772055644056</t>
+          <t>3.727416374921888</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.523889439951571</t>
+          <t>3.466605147109138</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.3480049564679177</t>
+          <t>3.3320355584463273</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.638861298261271</t>
+          <t>3.6295387272004405</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.46273009131762066</t>
+          <t>0.45651391623312115</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.363490768887438</t>
+          <t>0.3636189092698047</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.44489584422710493</t>
+          <t>0.44776226861863533</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6240653225312063</t>
+          <t>0.629546179782533</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.022041760704674</t>
+          <t>4.02953193395188</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.48370844305605076</t>
+          <t>0.47874906800521105</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5265327059118905</t>
+          <t>0.5296430884802138</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8.588331087506374</t>
+          <t>9.00066225500236</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.36783502024326986</t>
+          <t>0.3651876975870881</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.5884921678842403</t>
+          <t>1.5633746874533578</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.041964438109833</t>
+          <t>4.05820609923444</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.7034810570908788</t>
+          <t>0.6951692117067205</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.6653088060257364</t>
+          <t>2.633720532974351</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.054758677734096</t>
+          <t>1.0263148401380329</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4290554761277068</t>
+          <t>0.42795102343884783</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.23827672924428797</t>
+          <t>0.23328641470425282</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.7761384138113963</t>
+          <t>3.731745458579123</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.4037904400957673</t>
+          <t>1.3917394505754506</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.841465124208519</t>
+          <t>2.786608798002257</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.662938515690052</t>
+          <t>2.628048424403137</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.33280984877236147</t>
+          <t>0.3400497420140703</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.791051787531103</t>
+          <t>8.715910395183748</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.791347023086814</t>
+          <t>4.78874511744273</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.5937585943715828</t>
+          <t>0.5799553433420819</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.3618523107151006</t>
+          <t>0.3554178462694466</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.41709374984005365</t>
+          <t>0.420851583571064</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.782723063789639</t>
+          <t>7.71917577927396</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.4897134025512835</t>
+          <t>0.4961421554098937</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5934880455548311</t>
+          <t>0.6044071782205962</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.4675948539878014</t>
+          <t>1.4753805841047303</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.3818808234142483</t>
+          <t>1.367375185135723</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.24164579226036106</t>
+          <t>0.24438426669198482</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2002704453719701</t>
+          <t>1.1879189850223029</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6439814395125705</t>
+          <t>0.6422961873157984</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.27799070939236153</t>
+          <t>0.2740016962134819</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.1049826750880305</t>
+          <t>1.0769407044988535</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.34079958863888565</t>
+          <t>0.34056639546148937</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3703319427938025</t>
+          <t>1.3445191901598417</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7869903961291587</t>
+          <t>0.7765671170640762</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6562869859910475</t>
+          <t>0.6562078428800974</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.9914500892440472</t>
+          <t>1.995176119134994</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>7.979434800884368</t>
+          <t>7.91702375818664</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.19807058757315</t>
+          <t>11.08744897933231</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.235116755239538</t>
+          <t>13.11548454600954</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1423898193526818</t>
+          <t>1.146962668722392</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.7953392698949315</t>
+          <t>1.7680808959068397</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.143016538857054</t>
+          <t>4.185217289483502</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>14.668292421120741</t>
+          <t>14.657567762476303</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>22.68671004531214</t>
+          <t>22.67931415542052</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5735483520183936</t>
+          <t>0.5769952138112573</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.095432763905492</t>
+          <t>8.045195350106605</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.294664927650323</t>
+          <t>1.2939011496032657</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5178197257544985</t>
+          <t>0.5149928500604402</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.122770295046559</t>
+          <t>8.081833984170839</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.2580509388212597</t>
+          <t>3.2863710881337287</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.775874804079699</t>
+          <t>14.68118616113729</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.6285084486914435</t>
+          <t>0.6353585617553528</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.604484373017472</t>
+          <t>1.5993921720018363</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.045661651845483</t>
+          <t>2.065797841990911</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.325068310202655</t>
+          <t>5.269330754302135</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.03303867198928</t>
+          <t>8.02255493607357</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.081200605544581</t>
+          <t>6.011408643424151</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.681161715866025</t>
+          <t>0.6624611176490274</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.191761106523138</t>
+          <t>6.1555689521946215</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>7.029515512598131</t>
+          <t>6.986176645508614</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.599121552356608</t>
+          <t>1.637440561130703</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.22871955390339</t>
+          <t>10.07830816468087</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.9010992061283113</t>
+          <t>0.9114280714608566</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.6764880247155247</t>
+          <t>0.6704868418321702</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>23.60662468660984</t>
+          <t>23.429908180170937</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.8120361814273025</t>
+          <t>5.795929158639112</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>23.63124815763126</t>
+          <t>23.51580675789086</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4912887413647867</t>
+          <t>0.5020235133348279</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6498075504218223</t>
+          <t>0.6618049465248543</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.215831656547643</t>
+          <t>24.143970004713474</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.074868282446147</t>
+          <t>18.946236072288386</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.429105789174327</t>
+          <t>4.424885804222876</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.2590289598352866</t>
+          <t>3.205189633639637</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.408654540297153</t>
+          <t>4.456279040105374</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.708572722376786</t>
+          <t>9.848623551543355</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.506012575412364</t>
+          <t>5.547692697363497</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.388008753175241</t>
+          <t>7.268411049796411</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.3032129132480611</t>
+          <t>0.3136495805186424</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.2718923215556574</t>
+          <t>0.2686524383306319</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.9153770251443437</t>
+          <t>0.8945789435082956</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.363708964660395</t>
+          <t>1.3403131956334908</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.418662622625007</t>
+          <t>2.4655654310268886</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>3.241464102498444</t>
+          <t>3.352372122884722</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.838278114921345</t>
+          <t>4.851222282307286</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.881461867616842</t>
+          <t>15.872267535556576</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>13.83246215592572</t>
+          <t>13.58298876857989</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.8939299915603938</t>
+          <t>2.9127391970621987</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.6328069882171206</t>
+          <t>2.6039058840854334</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.5625412698179</t>
+          <t>9.426974025491347</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>40.05506045624512</t>
+          <t>39.75150844149593</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>0.3706989318842199</t>
+          <t>4.319828541227758</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>9.800042947424899</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>0.5469621491631673</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D435"/>
+  <dimension ref="A1:D436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.2027329778317295</t>
+          <t>5.51947381025747</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.8849880214560641</t>
+          <t>1.9080198712311773</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.9666396525465593</t>
+          <t>3.0070846092895804</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.9570052640091335</t>
+          <t>0.9831582771930346</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9499460069255821</t>
+          <t>0.915506640002771</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.78639696406101</t>
+          <t>9.269071639157735</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.9071452569091196</t>
+          <t>2.72366126294831</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.697130324502792</t>
+          <t>1.677323740065269</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.249346140256</t>
+          <t>8.512477367407165</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.727416374921888</t>
+          <t>4.37645741808409</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.466605147109138</t>
+          <t>3.6562581840550195</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.3320355584463273</t>
+          <t>3.411353573195354</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.6295387272004405</t>
+          <t>3.4592323157648446</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.45651391623312115</t>
+          <t>0.4755465687288353</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3636189092698047</t>
+          <t>0.3564344518343316</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.44776226861863533</t>
+          <t>0.44778582179274284</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.629546179782533</t>
+          <t>0.5977283990375013</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.02953193395188</t>
+          <t>4.088741941895833</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.47874906800521105</t>
+          <t>0.47638921274407703</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5296430884802138</t>
+          <t>0.509995560728742</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9.00066225500236</t>
+          <t>9.776305642155833</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3651876975870881</t>
+          <t>0.3657071422302613</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.5633746874533578</t>
+          <t>1.6312236376410993</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.05820609923444</t>
+          <t>4.052137872191629</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6951692117067205</t>
+          <t>0.6831931521868748</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.633720532974351</t>
+          <t>2.6436039864033285</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0263148401380329</t>
+          <t>1.0780191511734352</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.42795102343884783</t>
+          <t>0.41124957956308367</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.23328641470425282</t>
+          <t>0.23747273048261697</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.731745458579123</t>
+          <t>4.016806270139586</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3917394505754506</t>
+          <t>1.3378822409233344</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.786608798002257</t>
+          <t>2.925095526186007</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.628048424403137</t>
+          <t>2.604686291561745</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.3400497420140703</t>
+          <t>0.32126522436491806</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.715910395183748</t>
+          <t>8.503948308711621</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.78874511744273</t>
+          <t>4.75718256078688</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.5799553433420819</t>
+          <t>0.9423751703411816</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.3554178462694466</t>
+          <t>0.3672147584539882</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.420851583571064</t>
+          <t>0.40213455849634494</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.71917577927396</t>
+          <t>7.870629206364362</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.4961421554098937</t>
+          <t>0.49065513993654264</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6044071782205962</t>
+          <t>0.5707851545981285</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.4753805841047303</t>
+          <t>1.4857215584840002</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.367375185135723</t>
+          <t>1.3914302264526173</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.24438426669198482</t>
+          <t>0.21557561203555647</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.1879189850223029</t>
+          <t>1.2376311328047516</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6422961873157984</t>
+          <t>0.6325256362631677</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.2740016962134819</t>
+          <t>0.27410322404276094</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.0769407044988535</t>
+          <t>1.1103075745011184</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.34056639546148937</t>
+          <t>0.31893845417021055</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3445191901598417</t>
+          <t>1.3959087133510149</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7765671170640762</t>
+          <t>0.7865671063096782</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6562078428800974</t>
+          <t>0.6387007176315248</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.995176119134994</t>
+          <t>2.0306355108947383</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>7.91702375818664</t>
+          <t>7.979121398876452</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.08744897933231</t>
+          <t>11.32089631480935</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.11548454600954</t>
+          <t>13.45761945154657</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.146962668722392</t>
+          <t>1.1684616614158174</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.7680808959068397</t>
+          <t>1.9825670707524787</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.185217289483502</t>
+          <t>4.266493379921529</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>14.657567762476303</t>
+          <t>15.088618155558759</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>22.67931415542052</t>
+          <t>18.25781617935084</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5769952138112573</t>
+          <t>0.5486007797357555</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.045195350106605</t>
+          <t>8.41425442886706</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.2939011496032657</t>
+          <t>1.3109801864955544</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5149928500604402</t>
+          <t>0.5193893372902387</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.081833984170839</t>
+          <t>8.46008691608377</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.2863710881337287</t>
+          <t>3.300366604066552</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.68118616113729</t>
+          <t>14.458157199794726</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.6353585617553528</t>
+          <t>0.6148343012428842</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.5993921720018363</t>
+          <t>1.555981818922953</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.065797841990911</t>
+          <t>2.010877589760554</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.269330754302135</t>
+          <t>5.290323125509957</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.02255493607357</t>
+          <t>8.304046006368626</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.011408643424151</t>
+          <t>6.184366558591389</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6624611176490274</t>
+          <t>0.6683467906060123</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.1555689521946215</t>
+          <t>6.1926923917507715</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>6.986176645508614</t>
+          <t>7.001305850531793</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.637440561130703</t>
+          <t>1.556091161867326</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.07830816468087</t>
+          <t>10.27897260831986</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.9114280714608566</t>
+          <t>0.839535195234778</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.6704868418321702</t>
+          <t>0.698704973318296</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>23.429908180170937</t>
+          <t>24.404890270127517</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.795929158639112</t>
+          <t>5.158262937262066</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>23.51580675789086</t>
+          <t>23.992492718910615</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.5020235133348279</t>
+          <t>0.4651600024671658</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6618049465248543</t>
+          <t>0.609119234656515</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.143970004713474</t>
+          <t>24.151086785286438</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>18.946236072288386</t>
+          <t>19.564438201031223</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.424885804222876</t>
+          <t>4.519133737624145</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.205189633639637</t>
+          <t>3.25758156666851</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.456279040105374</t>
+          <t>4.627315650902674</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.848623551543355</t>
+          <t>9.645297921452652</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.547692697363497</t>
+          <t>5.582434005831531</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.268411049796411</t>
+          <t>7.390571860644215</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.3136495805186424</t>
+          <t>0.2918296970817117</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.2686524383306319</t>
+          <t>0.2784865034361335</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8945789435082956</t>
+          <t>0.9132488153600713</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.3403131956334908</t>
+          <t>1.2164324403188091</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.4655654310268886</t>
+          <t>2.3528402743600907</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>3.352372122884722</t>
+          <t>1.490380510375219</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.851222282307286</t>
+          <t>4.907166467406378</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.872267535556576</t>
+          <t>15.891937174249918</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>13.58298876857989</t>
+          <t>13.33643105578798</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.9127391970621987</t>
+          <t>2.894855041171963</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.6039058840854334</t>
+          <t>2.618057741541551</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.426974025491347</t>
+          <t>9.602603914512903</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>39.75150844149593</t>
+          <t>40.05630486466853</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>4.319828541227758</t>
+          <t>4.569652218463067</t>
         </is>
       </c>
     </row>
@@ -9995,6 +9995,28 @@
       <c r="D435" t="inlineStr">
         <is>
           <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>LR_AGL_Third_Eye_Gomah</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>52.362109813514216</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.51947381025747</t>
+          <t>5.4258653543256585</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.9080198712311773</t>
+          <t>1.9016281988364185</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.0070846092895804</t>
+          <t>3.008245978532504</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.9831582771930346</t>
+          <t>0.9752797419847999</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.915506640002771</t>
+          <t>0.904205928098557</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.269071639157735</t>
+          <t>9.270089887946837</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.72366126294831</t>
+          <t>2.6981575667432085</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.677323740065269</t>
+          <t>1.6472331218699974</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.512477367407165</t>
+          <t>8.471314935424944</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.37645741808409</t>
+          <t>4.353782730766046</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.6562581840550195</t>
+          <t>3.6476148675880324</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.411353573195354</t>
+          <t>3.40615724142673</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.4592323157648446</t>
+          <t>3.453072460151434</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.4755465687288353</t>
+          <t>0.47433152796206507</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3564344518343316</t>
+          <t>0.3584774181626552</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.44778582179274284</t>
+          <t>0.4470484771614749</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5977283990375013</t>
+          <t>0.5995886395515215</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.088741941895833</t>
+          <t>4.095356298230861</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.47638921274407703</t>
+          <t>0.47349631506969003</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.509995560728742</t>
+          <t>0.509153447474468</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9.776305642155833</t>
+          <t>9.824046135765393</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3657071422302613</t>
+          <t>0.36704697607707715</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6312236376410993</t>
+          <t>1.6205769645423622</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.052137872191629</t>
+          <t>4.102296337985126</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6831931521868748</t>
+          <t>0.6825272909349405</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.6436039864033285</t>
+          <t>2.6508744231034416</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0780191511734352</t>
+          <t>1.066477334157728</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.41124957956308367</t>
+          <t>0.41116082242878416</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.23747273048261697</t>
+          <t>0.2364652725517713</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.016806270139586</t>
+          <t>3.9377213582960233</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3378822409233344</t>
+          <t>1.333370965090276</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.925095526186007</t>
+          <t>2.891756626682862</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.604686291561745</t>
+          <t>2.597224050529527</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.32126522436491806</t>
+          <t>0.32335884863496184</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.503948308711621</t>
+          <t>8.49810452967047</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.75718256078688</t>
+          <t>4.765252714093577</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9423751703411816</t>
+          <t>0.9347322548563278</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.3672147584539882</t>
+          <t>0.36510362966436016</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.40213455849634494</t>
+          <t>0.40247308814906035</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.870629206364362</t>
+          <t>7.863538622309662</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.49065513993654264</t>
+          <t>0.49445741219918693</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5707851545981285</t>
+          <t>0.5724748585150121</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1.4857215584840002</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.3914302264526173</t>
+          <t>1.396542346028554</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.21557561203555647</t>
+          <t>0.21689196403547636</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2376311328047516</t>
+          <t>1.2319693478305038</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6325256362631677</t>
+          <t>0.632039580699538</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.27410322404276094</t>
+          <t>0.2726827745323642</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.1103075745011184</t>
+          <t>1.0996978503938832</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.31893845417021055</t>
+          <t>0.3189393068227726</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3959087133510149</t>
+          <t>1.3820906994809068</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7865671063096782</t>
+          <t>0.780655089681551</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6387007176315248</t>
+          <t>0.6384307147560466</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.0306355108947383</t>
+          <t>2.020360012630638</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>7.979121398876452</t>
+          <t>7.968604513649901</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.32089631480935</t>
+          <t>11.24063248965591</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.45761945154657</t>
+          <t>13.420149196121521</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1684616614158174</t>
+          <t>1.1674745313117378</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.9825670707524787</t>
+          <t>1.96502054758275</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.266493379921529</t>
+          <t>4.298277808201491</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.088618155558759</t>
+          <t>15.066414696412709</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>18.25781617935084</t>
+          <t>18.23214467742178</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5486007797357555</t>
+          <t>0.5545626553879645</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.41425442886706</t>
+          <t>8.396992154269999</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.3109801864955544</t>
+          <t>1.3083267219123178</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5193893372902387</t>
+          <t>0.5188648826688684</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.46008691608377</t>
+          <t>8.48118966215611</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.300366604066552</t>
+          <t>3.2925059238839203</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.458157199794726</t>
+          <t>14.4705028125438</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.6148343012428842</t>
+          <t>0.618546074003052</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.555981818922953</t>
+          <t>1.556342174681849</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.010877589760554</t>
+          <t>2.02822236325614</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.290323125509957</t>
+          <t>5.261331609800936</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.304046006368626</t>
+          <t>8.266457619200112</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.184366558591389</t>
+          <t>6.159963382621261</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6683467906060123</t>
+          <t>0.663924368623606</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.1926923917507715</t>
+          <t>6.193871514038673</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>7.001305850531793</t>
+          <t>7.000106186788756</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.556091161867326</t>
+          <t>1.560957290805238</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.27897260831986</t>
+          <t>10.19928072729179</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.839535195234778</t>
+          <t>0.8499539820672584</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.698704973318296</t>
+          <t>0.694734138503374</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.404890270127517</t>
+          <t>24.2912236652496</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.158262937262066</t>
+          <t>5.242485648598787</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>23.992492718910615</t>
+          <t>23.95103347365511</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4651600024671658</t>
+          <t>0.4680453687167178</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.609119234656515</t>
+          <t>0.6140556579508238</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.151086785286438</t>
+          <t>24.012815743742898</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.564438201031223</t>
+          <t>19.500172882427876</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.519133737624145</t>
+          <t>4.512556521452442</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.25758156666851</t>
+          <t>3.2673279308691767</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.627315650902674</t>
+          <t>4.623693479181233</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.645297921452652</t>
+          <t>9.632186374335262</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.582434005831531</t>
+          <t>5.596706225083147</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.390571860644215</t>
+          <t>7.333782081559211</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2918296970817117</t>
+          <t>0.2938388419724429</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.2784865034361335</t>
+          <t>0.27594915888678884</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.9132488153600713</t>
+          <t>0.9088879872400972</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.2164324403188091</t>
+          <t>1.2044046650229552</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.3528402743600907</t>
+          <t>2.3989123246881263</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.490380510375219</t>
+          <t>1.501232742924528</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.907166467406378</t>
+          <t>4.959521709473649</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.891937174249918</t>
+          <t>15.940459374918795</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>13.33643105578798</t>
+          <t>13.21559062590587</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.894855041171963</t>
+          <t>2.9144405980961405</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.618057741541551</t>
+          <t>2.624530159787691</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.602603914512903</t>
+          <t>9.52390291896995</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>40.05630486466853</t>
+          <t>40.03340942298237</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>4.569652218463067</t>
+          <t>4.546166003359231</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>52.362109813514216</t>
+          <t>24.66585319606416</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D436"/>
+  <dimension ref="A1:D439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.4258653543256585</t>
+          <t>5.523288333772758</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.670310381240009</t>
+          <t>0.6671871973200014</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.9016281988364185</t>
+          <t>1.9258912922177345</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.008245978532504</t>
+          <t>3.010313651506483</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.9752797419847999</t>
+          <t>0.9824684008871645</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.904205928098557</t>
+          <t>0.9214530598969362</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.270089887946837</t>
+          <t>9.218918178385737</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.6981575667432085</t>
+          <t>2.709875908260541</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6472331218699974</t>
+          <t>1.6865977128541596</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.471314935424944</t>
+          <t>8.609942464440504</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.353782730766046</t>
+          <t>4.336282145857739</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.6476148675880324</t>
+          <t>3.662627630180392</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.40615724142673</t>
+          <t>3.411804537888935</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.453072460151434</t>
+          <t>3.4659407282183747</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.47433152796206507</t>
+          <t>0.4761737182275684</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3584774181626552</t>
+          <t>0.36035869412944965</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.4470484771614749</t>
+          <t>0.45272777820095955</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5995886395515215</t>
+          <t>0.5987832462807359</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.095356298230861</t>
+          <t>4.098113213848009</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.47349631506969003</t>
+          <t>0.47589515502741003</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.509153447474468</t>
+          <t>0.5087299629616816</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9.824046135765393</t>
+          <t>9.848557978410613</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.36704697607707715</t>
+          <t>0.3641569043710687</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6205769645423622</t>
+          <t>1.6362454267791797</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.102296337985126</t>
+          <t>4.06046117494016</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6825272909349405</t>
+          <t>0.6851523718378347</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.6508744231034416</t>
+          <t>2.6464433715798674</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.066477334157728</t>
+          <t>1.0791265903033187</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.41116082242878416</t>
+          <t>0.4117294676241007</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2364652725517713</t>
+          <t>0.23695509413413163</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.9377213582960233</t>
+          <t>4.039743696149515</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.333370965090276</t>
+          <t>1.3440137683271849</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.891756626682862</t>
+          <t>2.9108251089681088</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.597224050529527</t>
+          <t>2.590992051904661</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.32335884863496184</t>
+          <t>0.3222946097810382</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.49810452967047</t>
+          <t>8.576326001958186</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.765252714093577</t>
+          <t>4.788065201422363</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9347322548563278</t>
+          <t>0.9426594219932736</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.36510362966436016</t>
+          <t>0.36704675268573084</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.40247308814906035</t>
+          <t>0.40391097293258715</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.863538622309662</t>
+          <t>7.85279126766011</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.49445741219918693</t>
+          <t>0.49514762414423424</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5724748585150121</t>
+          <t>0.5692715661697995</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.396542346028554</t>
+          <t>1.3879037978991942</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.21689196403547636</t>
+          <t>0.2156833150580725</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2319693478305038</t>
+          <t>1.2256514922872725</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.632039580699538</t>
+          <t>0.6352964405145025</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.2726827745323642</t>
+          <t>0.2736880162267933</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.0996978503938832</t>
+          <t>1.1042857942048965</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3189393068227726</t>
+          <t>0.32025530081852915</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3820906994809068</t>
+          <t>1.3933206341184812</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.780655089681551</t>
+          <t>0.7841400819509121</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6384307147560466</t>
+          <t>0.6418569812192334</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.020360012630638</t>
+          <t>2.0422543505755577</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>7.968604513649901</t>
+          <t>8.0224118494898</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.24063248965591</t>
+          <t>11.34403800003847</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.420149196121521</t>
+          <t>13.449005677085118</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1674745313117378</t>
+          <t>1.1722075447971407</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.96502054758275</t>
+          <t>1.9660401961237302</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.298277808201491</t>
+          <t>4.1989529339203955</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.066414696412709</t>
+          <t>15.147145174266118</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>18.23214467742178</t>
+          <t>18.238798909221934</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5545626553879645</t>
+          <t>0.5510811987690402</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.396992154269999</t>
+          <t>8.443458316211435</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.3083267219123178</t>
+          <t>1.3084202772581712</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5188648826688684</t>
+          <t>0.5185319361248473</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.48118966215611</t>
+          <t>8.551492210543751</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.2925059238839203</t>
+          <t>3.335868997074721</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.4705028125438</t>
+          <t>14.452600846982811</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.618546074003052</t>
+          <t>0.6174361888125667</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.556342174681849</t>
+          <t>1.547284509851166</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2.02822236325614</t>
+          <t>1.987871073392471</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.261331609800936</t>
+          <t>5.258860626964181</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.266457619200112</t>
+          <t>8.34615587164634</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.159963382621261</t>
+          <t>6.17088462727957</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.663924368623606</t>
+          <t>0.6654589518102249</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.193871514038673</t>
+          <t>6.212365530829459</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>7.000106186788756</t>
+          <t>6.995378400445495</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.560957290805238</t>
+          <t>1.5523381573656263</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.19928072729179</t>
+          <t>10.23717998179486</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8499539820672584</t>
+          <t>0.8376360491382426</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.694734138503374</t>
+          <t>0.6987170999662544</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.2912236652496</t>
+          <t>24.355592288015373</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.242485648598787</t>
+          <t>5.147669406380416</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>23.95103347365511</t>
+          <t>24.018374781214924</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4680453687167178</t>
+          <t>0.466519533371276</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6140556579508238</t>
+          <t>0.6081647681510437</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.012815743742898</t>
+          <t>23.991212109437654</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.500172882427876</t>
+          <t>19.599279027517582</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.512556521452442</t>
+          <t>4.517156022490273</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.2673279308691767</t>
+          <t>3.2409593161472916</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.623693479181233</t>
+          <t>4.627931237461654</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.632186374335262</t>
+          <t>9.695315544343899</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.596706225083147</t>
+          <t>5.606575876277777</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.333782081559211</t>
+          <t>7.358697439463536</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2938388419724429</t>
+          <t>0.29156509740737</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.27594915888678884</t>
+          <t>0.27844746628481937</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.9088879872400972</t>
+          <t>0.9095157719129833</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.2044046650229552</t>
+          <t>1.2170618712539518</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.3989123246881263</t>
+          <t>2.350244450209942</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.501232742924528</t>
+          <t>1.46614185261953</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.959521709473649</t>
+          <t>4.911571966378705</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.940459374918795</t>
+          <t>16.024396971129036</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>13.21559062590587</t>
+          <t>13.32950753964379</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.9144405980961405</t>
+          <t>3.549734516910506</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.624530159787691</t>
+          <t>2.6116598894512055</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.52390291896995</t>
+          <t>9.53698829486335</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>40.03340942298237</t>
+          <t>39.84234619366222</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>4.546166003359231</t>
+          <t>5.942937676661159</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,73 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>24.66585319606416</t>
+          <t>51.7759985842511</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>BU_STR_Android_17_ToP</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>9.58991512834453</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>DF_AGL_Android_16</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>4.447409622692827</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>F2PLR_AGL_Garlic_Jr</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.2018746419228403</t>
+          <t>1.317101598251191</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.523288333772758</t>
+          <t>5.3356026821642</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.8995892141289816</t>
+          <t>2.0817079441390107</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.479363455676221</t>
+          <t>5.304360145149349</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.003479206809121</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.6671871973200014</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.2663928094193209</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.9258912922177345</t>
+          <t>2.0614008583474157</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.010313651506483</t>
+          <t>3.0110305976653775</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.6671871973200014</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.9824684008871645</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9214530598969362</t>
+          <t>0.8450024856517123</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.054503988707488</t>
+          <t>1.1556021239177248</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.218918178385737</t>
+          <t>8.942596546362797</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.7334031858765866</t>
+          <t>1.8995892141289816</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.709875908260541</t>
+          <t>3.007499584967011</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6865977128541596</t>
+          <t>1.7114921266887766</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.163511966122465</t>
+          <t>3.466806371753173</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.609942464440504</t>
+          <t>8.9155291752097</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.336282145857739</t>
+          <t>4.12777232536542</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.662627630180392</t>
+          <t>3.8357403093908182</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.666666666666664</t>
+          <t>12.78518139657785</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.317101598251191</t>
+          <t>1.4433756729740645</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.411804537888935</t>
+          <t>3.424147050400991</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.4659407282183747</t>
+          <t>3.6946828206479427</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.4761737182275684</t>
+          <t>0.5006930329182429</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.2018746419228403</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.36035869412944965</t>
+          <t>0.3849622862097024</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.45272777820095955</t>
+          <t>0.49150924832226206</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5987832462807359</t>
+          <t>0.5937131654982567</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.098113213848009</t>
+          <t>4.076831689929811</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.47589515502741003</t>
+          <t>0.4424976149686115</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5087299629616816</t>
+          <t>0.46580238372174054</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9.848557978410613</t>
+          <t>10.448845961093513</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3641569043710687</t>
+          <t>0.3791652655047262</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6362454267791797</t>
+          <t>1.62165231800223</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.06046117494016</t>
+          <t>3.9860527656758884</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6851523718378347</t>
+          <t>0.6481382416961651</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.6464433715798674</t>
+          <t>2.553290373012608</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20015615919600044</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>1.096728344127077</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.34028350213552</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20015615919600044</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.4037492838456807</t>
+          <t>2.634203196502382</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.36056239257685213</t>
+          <t>0.39513047947535734</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0791265903033187</t>
+          <t>1.1243977796511169</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.4117294676241007</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.23695509413413163</t>
+          <t>0.211943592995258</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.039743696149515</t>
+          <t>4.205517610242191</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3440137683271849</t>
+          <t>1.3624777515889923</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.30440908087090124</t>
+          <t>0.3335935986600007</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.3515013295691628</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.9108251089681088</t>
+          <t>0.23038838191942443</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2.2452510468485443</t>
+          <t>2.4605093069841395</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.590992051904661</t>
+          <t>2.340568978789372</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.3222946097810382</t>
+          <t>0.3027204468658454</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.576326001958186</t>
+          <t>8.097804619778884</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.788065201422363</t>
+          <t>4.778962590194347</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9426594219932736</t>
+          <t>0.9430367217537945</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.36704675268573084</t>
+          <t>0.3515532794364562</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.40391097293258715</t>
+          <t>0.3976885464316451</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.85279126766011</t>
+          <t>7.888311819253616</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.49514762414423424</t>
+          <t>0.5216245466963807</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.5692715661697995</t>
+          <t>0.6146474125172223</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.3879037978991942</t>
+          <t>1.3070872094491708</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2156833150580725</t>
+          <t>0.2393860984181974</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2256514922872725</t>
+          <t>1.2674210334402858</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6352964405145025</t>
+          <t>0.6237902801063031</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.5567701270800032</t>
+          <t>1.7060218686421196</t>
         </is>
       </c>
     </row>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.2736880162267933</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.1042857942048965</t>
+          <t>0.9719876118407306</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.5567701270800032</t>
+          <t>1.7060218686421196</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.32025530081852915</t>
+          <t>0.3175781670853322</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3933206341184812</t>
+          <t>1.3301463156134377</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7841400819509121</t>
+          <t>0.7101995758141642</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.4261727132192617</t>
+          <t>0.4670310381240009</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6418569812192334</t>
+          <t>0.6726909916852046</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.0422543505755577</t>
+          <t>2.120341998787347</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>8.0224118494898</t>
+          <t>3.49506728095119</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.34403800003847</t>
+          <t>12.10544263382634</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.449005677085118</t>
+          <t>13.392618567395907</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1722075447971407</t>
+          <t>1.181340997077648</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.9660401961237302</t>
+          <t>1.8264830277306405</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.1989529339203955</t>
+          <t>4.380954941789566</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.147145174266118</t>
+          <t>15.560033032678668</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>18.238798909221934</t>
+          <t>17.112806790797826</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5510811987690402</t>
+          <t>0.5584407400568359</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.443458316211435</t>
+          <t>8.487883939733631</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.3084202772581712</t>
+          <t>1.299920072485215</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.5185319361248473</t>
+          <t>0.47575193596633625</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.551492210543751</t>
+          <t>9.79599499979006</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.335868997074721</t>
+          <t>3.743277284041671</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.452600846982811</t>
+          <t>13.010184714080815</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.6174361888125667</t>
+          <t>0.38232928277723294</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.9849721851039159</t>
+          <t>1.0794041191831907</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.547284509851166</t>
+          <t>1.419048271191924</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.987871073392471</t>
+          <t>1.811694854213578</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.258860626964181</t>
+          <t>4.775106335458797</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.34615587164634</t>
+          <t>8.865383059568588</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.17088462727957</t>
+          <t>5.975815029786009</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6654589518102249</t>
+          <t>0.6457988925761109</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>0.2696404955808023</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.212365530829459</t>
+          <t>6.044128155272347</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>6.995378400445495</t>
+          <t>6.880308614840196</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.5523381573656263</t>
+          <t>1.7119453622031051</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>10.23717998179486</t>
+          <t>9.578617212179257</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8376360491382426</t>
+          <t>0.8988016519360076</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.6987170999662544</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.355592288015373</t>
+          <t>24.110857674304754</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>5.147669406380416</t>
+          <t>4.079749757848603</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.018374781214924</t>
+          <t>24.100011026104642</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.466519533371276</t>
+          <t>0.4400447667842795</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6081647681510437</t>
+          <t>0.5804071135913977</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.991212109437654</t>
+          <t>23.185118943086415</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.599279027517582</t>
+          <t>19.627079769963572</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.517156022490273</t>
+          <t>4.484091720346303</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.2409593161472916</t>
+          <t>2.9714841940716585</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.627931237461654</t>
+          <t>4.367396108608081</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.695315544343899</t>
+          <t>9.873494095339751</t>
         </is>
       </c>
     </row>
@@ -9285,12 +9285,12 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.606575876277777</t>
+          <t>18.040935766396775</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>7.358697439463536</t>
+          <t>6.723176398497506</t>
         </is>
       </c>
     </row>
@@ -9351,12 +9351,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.29156509740737</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.27844746628481937</t>
+          <t>0.2571247849858876</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.9095157719129833</t>
+          <t>0.813649453073825</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.2170618712539518</t>
+          <t>1.225277182896666</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.350244450209942</t>
+          <t>1.9473046993213075</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.46614185261953</t>
+          <t>1.5612493531952343</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.911571966378705</t>
+          <t>4.822275186490415</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.024396971129036</t>
+          <t>16.662385617303222</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>13.32950753964379</t>
+          <t>11.80147383263223</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.549734516910506</t>
+          <t>3.047191784869996</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.6116598894512055</t>
+          <t>2.3733963100492086</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.53698829486335</t>
+          <t>8.949001609974639</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>39.84234619366222</t>
+          <t>42.32532922302563</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.942937676661159</t>
+          <t>5.821591205089637</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>51.7759985842511</t>
+          <t>53.44259384479737</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>9.58991512834453</t>
+          <t>8.828850635620103</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.447409622692827</t>
+          <t>4.330420177683115</t>
         </is>
       </c>
     </row>
@@ -10083,6 +10083,116 @@
       <c r="D439" t="inlineStr">
         <is>
           <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>BU_INT_Androids_19_20</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>F2PLR_INT_Jackie_Chun</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>F2P_AGL_Piccolo_Jr</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>F2P_INT_Broly_Movie_Trunks</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>CLR_INT_Future_Gohan_Trunks</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>73.73078048738537</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -9703,12 +9703,12 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.3733963100492086</t>
+          <t>2.0622497345449142</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>73.73078048738537</t>
+          <t>12.274177075228536</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D444"/>
+  <dimension ref="A1:D446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.3356026821642</t>
+          <t>5.473527238176587</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.304360145149349</t>
+          <t>5.311176355840945</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.003479206809121</t>
+          <t>7.032646613750743</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.0614008583474157</t>
+          <t>2.087082630694401</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.0110305976653775</t>
+          <t>3.0415943197784054</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8450024856517123</t>
+          <t>0.8530575830163791</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.942596546362797</t>
+          <t>8.956762835340434</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.007499584967011</t>
+          <t>3.0422606126902796</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7114921266887766</t>
+          <t>1.7443489708451876</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.9155291752097</t>
+          <t>9.06144234592061</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.12777232536542</t>
+          <t>4.189073453698123</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.8357403093908182</t>
+          <t>3.8917769124068085</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.424147050400991</t>
+          <t>3.4604491633286854</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.6946828206479427</t>
+          <t>3.724468526240514</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5006930329182429</t>
+          <t>0.5104281988623417</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3849622862097024</t>
+          <t>0.3833544606377244</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.49150924832226206</t>
+          <t>0.49607543548344774</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5937131654982567</t>
+          <t>0.5861946171635851</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.076831689929811</t>
+          <t>4.078050690962144</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4424976149686115</t>
+          <t>0.4454203730470037</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.46580238372174054</t>
+          <t>0.46056419557589506</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.448845961093513</t>
+          <t>10.413187508401085</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3791652655047262</t>
+          <t>0.3767870572140275</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.62165231800223</t>
+          <t>1.6513593344579185</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.9860527656758884</t>
+          <t>3.908229522396541</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6481382416961651</t>
+          <t>0.6478199788220182</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.553290373012608</t>
+          <t>2.5636632279152543</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.34028350213552</t>
+          <t>5.28162386448918</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.1243977796511169</t>
+          <t>1.15461079740155</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.211943592995258</t>
+          <t>0.21448482880690187</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.205517610242191</t>
+          <t>4.30795682527773</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3624777515889923</t>
+          <t>1.3714319377921886</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.23038838191942443</t>
+          <t>0.23952110209630156</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.340568978789372</t>
+          <t>2.331493683434772</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.3027204468658454</t>
+          <t>0.29456833803954846</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.097804619778884</t>
+          <t>8.089232335807395</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.778962590194347</t>
+          <t>4.800384942173963</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9430367217537945</t>
+          <t>0.9653491985850933</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.3515532794364562</t>
+          <t>0.3580230813671861</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3976885464316451</t>
+          <t>0.3937003352742413</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.888311819253616</t>
+          <t>7.963978923592869</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.5216245466963807</t>
+          <t>0.5208131435291063</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.3070872094491708</t>
+          <t>1.305775226414863</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2393860984181974</t>
+          <t>0.23549548605391102</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2674210334402858</t>
+          <t>1.2968915620745998</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6237902801063031</t>
+          <t>0.6270249185431762</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.9719876118407306</t>
+          <t>0.9925536855941326</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3175781670853322</t>
+          <t>0.3156888911192743</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3301463156134377</t>
+          <t>1.3659495558535735</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7101995758141642</t>
+          <t>0.7215407882170508</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6726909916852046</t>
+          <t>0.6684758328592033</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.120341998787347</t>
+          <t>2.1572813929433767</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.49506728095119</t>
+          <t>3.4814173360304217</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.10544263382634</t>
+          <t>12.24562135267711</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.392618567395907</t>
+          <t>13.52084994911661</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.181340997077648</t>
+          <t>1.1880486870304994</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.8264830277306405</t>
+          <t>1.882346471153289</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.380954941789566</t>
+          <t>4.324850921284426</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.560033032678668</t>
+          <t>15.68958604840993</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>17.112806790797826</t>
+          <t>17.034011467767876</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5584407400568359</t>
+          <t>0.5439810315410089</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.487883939733631</t>
+          <t>8.59614795884794</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.299920072485215</t>
+          <t>1.311074177584412</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.47575193596633625</t>
+          <t>0.478283456122802</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.79599499979006</t>
+          <t>9.767025316096381</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.743277284041671</t>
+          <t>3.766062789163609</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>13.010184714080815</t>
+          <t>12.934049450237964</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.38232928277723294</t>
+          <t>0.3799492113684699</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.419048271191924</t>
+          <t>1.405824632859204</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.811694854213578</t>
+          <t>1.754852303743439</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.775106335458797</t>
+          <t>4.81358763685753</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.865383059568588</t>
+          <t>8.941239690880497</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>5.975815029786009</t>
+          <t>6.075661839997571</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6457988925761109</t>
+          <t>0.656467090097737</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.044128155272347</t>
+          <t>6.085452753076737</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>6.880308614840196</t>
+          <t>6.892706607441241</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.7119453622031051</t>
+          <t>1.67065464681619</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>9.578617212179257</t>
+          <t>9.741343292399367</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.110857674304754</t>
+          <t>24.319539596638123</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.079749757848603</t>
+          <t>3.9476075517086</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.100011026104642</t>
+          <t>24.276310633049626</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4400447667842795</t>
+          <t>0.4310318365230144</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5804071135913977</t>
+          <t>0.5665195366826327</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.185118943086415</t>
+          <t>23.209672099141386</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.627079769963572</t>
+          <t>19.84737726151606</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.484091720346303</t>
+          <t>4.511781868845617</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.9714841940716585</t>
+          <t>2.968655107646743</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.367396108608081</t>
+          <t>4.356037629224545</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.873494095339751</t>
+          <t>9.825407378797223</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>18.040935766396775</t>
+          <t>18.193361460961412</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.723176398497506</t>
+          <t>6.819465210957303</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.2571247849858876</t>
+          <t>0.26373985646880166</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.813649453073825</t>
+          <t>0.8180132662705097</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.225277182896666</t>
+          <t>1.2444619179508116</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.9473046993213075</t>
+          <t>1.867271135784392</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.5612493531952343</t>
+          <t>1.486829100138507</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.822275186490415</t>
+          <t>4.767637255992635</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.662385617303222</t>
+          <t>16.640067379190903</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>11.80147383263223</t>
+          <t>11.90402632409664</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.047191784869996</t>
+          <t>3.0396535217963745</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.0622497345449142</t>
+          <t>2.06612061886257</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>8.949001609974639</t>
+          <t>9.071240738747928</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>42.32532922302563</t>
+          <t>42.47829928372439</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.821591205089637</t>
+          <t>5.884959778445882</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>53.44259384479737</t>
+          <t>53.344064852407186</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>8.828850635620103</t>
+          <t>8.911361246342734</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.330420177683115</t>
+          <t>4.205017278063393</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,51 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12.274177075228536</t>
+          <t>12.093196356694977</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>DF_AGL_Gohan_Gamma1</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>22.860714566219535</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>DF_STR_Gamma2_Piccolo</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>56.99345644491073</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.473527238176587</t>
+          <t>5.453394090827377</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.311176355840945</t>
+          <t>5.318982377315061</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.032646613750743</t>
+          <t>7.029438614704981</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.087082630694401</t>
+          <t>2.0807333197320954</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.0415943197784054</t>
+          <t>3.0612976586625877</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8530575830163791</t>
+          <t>0.8463578949005178</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.956762835340434</t>
+          <t>8.94698391864735</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.0422606126902796</t>
+          <t>3.030113826664308</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7443489708451876</t>
+          <t>1.735837561684525</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.06144234592061</t>
+          <t>9.046263133321363</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.189073453698123</t>
+          <t>4.178396238344562</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.8917769124068085</t>
+          <t>3.88108025278483</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.4604491633286854</t>
+          <t>3.4652890805666283</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.724468526240514</t>
+          <t>3.7308582438491755</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5104281988623417</t>
+          <t>0.5103634713730715</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3833544606377244</t>
+          <t>0.38063382407725116</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.49607543548344774</t>
+          <t>0.4936236538224028</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5861946171635851</t>
+          <t>0.5814183692497968</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.078050690962144</t>
+          <t>4.085028972119552</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4454203730470037</t>
+          <t>0.44164971827090643</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.46056419557589506</t>
+          <t>0.45640413667261825</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.413187508401085</t>
+          <t>10.3983829227471</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3767870572140275</t>
+          <t>0.37491668414130935</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6513593344579185</t>
+          <t>1.6500176255460026</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.908229522396541</t>
+          <t>3.9004030905676204</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6478199788220182</t>
+          <t>0.6419437281905944</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.5636632279152543</t>
+          <t>2.5642281433111394</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.28162386448918</t>
+          <t>5.298618523148503</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.15461079740155</t>
+          <t>1.149208373712592</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.21448482880690187</t>
+          <t>0.2136892464376645</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.30795682527773</t>
+          <t>4.310880170091618</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3714319377921886</t>
+          <t>1.3620270930951186</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.23952110209630156</t>
+          <t>0.23921146204813834</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.331493683434772</t>
+          <t>2.310133773741166</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.29456833803954846</t>
+          <t>0.29156294680380196</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.089232335807395</t>
+          <t>8.101320149956578</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.800384942173963</t>
+          <t>4.808516354504086</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9653491985850933</t>
+          <t>0.9627819262235657</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.3580230813671861</t>
+          <t>0.3558709057598657</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3937003352742413</t>
+          <t>0.3908524273065783</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.963978923592869</t>
+          <t>7.962322994345996</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.5208131435291063</t>
+          <t>0.5184847789432183</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.305775226414863</t>
+          <t>1.3007987869626005</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23549548605391102</t>
+          <t>0.2338491239936035</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2968915620745998</t>
+          <t>1.2972043291166497</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6270249185431762</t>
+          <t>0.6264919060123111</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.9925536855941326</t>
+          <t>0.9873795661098814</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3156888911192743</t>
+          <t>0.31380707387427614</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3659495558535735</t>
+          <t>1.3576799764822087</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7215407882170508</t>
+          <t>0.7173412092553848</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6684758328592033</t>
+          <t>0.6640907742226697</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.1572813929433767</t>
+          <t>2.1500357203843716</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.4814173360304217</t>
+          <t>3.4783529995709017</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.24562135267711</t>
+          <t>12.16961936230205</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.52084994911661</t>
+          <t>13.520098180079962</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1880486870304994</t>
+          <t>1.1820141861226168</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.882346471153289</t>
+          <t>1.8742076093470799</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.324850921284426</t>
+          <t>4.306124630571519</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.68958604840993</t>
+          <t>15.658963692857037</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>17.034011467767876</t>
+          <t>17.049038678326077</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5439810315410089</t>
+          <t>0.5420689551026929</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.59614795884794</t>
+          <t>8.596845584259283</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.311074177584412</t>
+          <t>1.309358719309192</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.478283456122802</t>
+          <t>0.47701033525097714</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.767025316096381</t>
+          <t>9.759871667775469</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.766062789163609</t>
+          <t>3.760577356024509</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.934049450237964</t>
+          <t>12.960453610750648</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.3799492113684699</t>
+          <t>0.3801953292987706</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.405824632859204</t>
+          <t>1.393376980581201</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.754852303743439</t>
+          <t>1.742494812473059</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.81358763685753</t>
+          <t>4.77418418862251</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.941239690880497</t>
+          <t>8.915881756740017</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.075661839997571</t>
+          <t>6.059952223929109</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.656467090097737</t>
+          <t>0.651647042397018</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.085452753076737</t>
+          <t>6.080642171092613</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>6.892706607441241</t>
+          <t>6.902439585690935</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.67065464681619</t>
+          <t>1.6590991920503388</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>9.741343292399367</t>
+          <t>9.671261344259289</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.319539596638123</t>
+          <t>24.327393246852907</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>3.9476075517086</t>
+          <t>3.952830043398592</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.276310633049626</t>
+          <t>24.277243729223045</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4310318365230144</t>
+          <t>0.4274150019989122</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5665195366826327</t>
+          <t>0.56191528045561</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.209672099141386</t>
+          <t>23.258797230360706</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.84737726151606</t>
+          <t>19.899349921466225</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.511781868845617</t>
+          <t>4.523863216752017</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.968655107646743</t>
+          <t>2.9621379054226447</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.356037629224545</t>
+          <t>4.321543701119355</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.825407378797223</t>
+          <t>9.857995687799075</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>18.193361460961412</t>
+          <t>18.1968201873957</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.819465210957303</t>
+          <t>6.764200935204028</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.26373985646880166</t>
+          <t>0.26299220571393633</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8180132662705097</t>
+          <t>0.8118247267504173</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.2444619179508116</t>
+          <t>1.2373919772146786</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.867271135784392</t>
+          <t>1.8654147709301157</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.486829100138507</t>
+          <t>1.483906731830788</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.767637255992635</t>
+          <t>4.761434365738809</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.640067379190903</t>
+          <t>16.68009896389494</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>11.90402632409664</t>
+          <t>11.83719385850374</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.0396535217963745</t>
+          <t>3.0342734689520476</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.06612061886257</t>
+          <t>2.0534531828093083</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.071240738747928</t>
+          <t>9.006452135502904</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>42.47829928372439</t>
+          <t>42.36683811290101</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.884959778445882</t>
+          <t>5.86588721427542</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>53.344064852407186</t>
+          <t>53.33705166599155</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>8.911361246342734</t>
+          <t>8.84752426805085</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.205017278063393</t>
+          <t>4.17752174675393</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12.093196356694977</t>
+          <t>12.138252969697177</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>22.860714566219535</t>
+          <t>26.34999468340454</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>56.99345644491073</t>
+          <t>54.35374626416631</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.453394090827377</t>
+          <t>5.452020690416141</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.318982377315061</t>
+          <t>5.326720459076871</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.029438614704981</t>
+          <t>7.052916280637967</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.0807333197320954</t>
+          <t>2.0759981060507284</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.0612976586625877</t>
+          <t>2.808578338120519</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8463578949005178</t>
+          <t>0.8191991853626801</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.94698391864735</t>
+          <t>8.990485240478371</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.030113826664308</t>
+          <t>3.04127654196299</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.735837561684525</t>
+          <t>1.7312741762225419</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.046263133321363</t>
+          <t>8.943609982912891</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.178396238344562</t>
+          <t>4.137912225029143</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.88108025278483</t>
+          <t>3.898862518486538</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.4652890805666283</t>
+          <t>3.8294751001729423</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.7308582438491755</t>
+          <t>3.7487671295843286</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5103634713730715</t>
+          <t>0.5138406426044821</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.38063382407725116</t>
+          <t>0.37140075916084125</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.4936236538224028</t>
+          <t>0.48959180667444224</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5814183692497968</t>
+          <t>0.5578871854062714</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.085028972119552</t>
+          <t>4.119013276103878</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.44164971827090643</t>
+          <t>0.44391590871184033</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.45640413667261825</t>
+          <t>0.4491359459719823</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.3983829227471</t>
+          <t>10.369644483685523</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.37491668414130935</t>
+          <t>0.37724338182611766</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6500176255460026</t>
+          <t>1.6509838831038195</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.9004030905676204</t>
+          <t>3.8554829221582763</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6419437281905944</t>
+          <t>0.6329956130398727</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.5642281433111394</t>
+          <t>2.2647690801097093</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.298618523148503</t>
+          <t>5.3386578187937515</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.149208373712592</t>
+          <t>1.1554172248004306</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2136892464376645</t>
+          <t>0.21492692082068474</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.310880170091618</t>
+          <t>4.269174507216054</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3620270930951186</t>
+          <t>1.3675507562895077</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.23921146204813834</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.310133773741166</t>
+          <t>2.317204226887918</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.29156294680380196</t>
+          <t>0.2839832809570614</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.101320149956578</t>
+          <t>7.9925273369091485</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.808516354504086</t>
+          <t>4.8168275509302205</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9627819262235657</t>
+          <t>0.9636748695697119</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.3558709057598657</t>
+          <t>0.2497585725119027</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3908524273065783</t>
+          <t>0.38180463155216554</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.962322994345996</t>
+          <t>7.9800683375087464</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.5184847789432183</t>
+          <t>0.49839213005165117</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.3007987869626005</t>
+          <t>1.2854174618281284</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2338491239936035</t>
+          <t>0.23563881752036017</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2972043291166497</t>
+          <t>1.2990816490292483</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6264919060123111</t>
+          <t>0.6213615858602939</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.9873795661098814</t>
+          <t>0.9892331138182566</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.31380707387427614</t>
+          <t>0.3052613537589305</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3576799764822087</t>
+          <t>1.3667572121072744</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7173412092553848</t>
+          <t>0.7214449370633838</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6640907742226697</t>
+          <t>0.6538519593360621</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.1500357203843716</t>
+          <t>2.122826044759762</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.4783529995709017</t>
+          <t>3.742875349153959</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.16961936230205</t>
+          <t>12.05746286454855</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.520098180079962</t>
+          <t>13.48315319410888</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1820141861226168</t>
+          <t>1.195540592798038</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.8742076093470799</t>
+          <t>1.8826397006382705</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.306124630571519</t>
+          <t>4.3734272341919755</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.658963692857037</t>
+          <t>15.544580234683963</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>17.049038678326077</t>
+          <t>16.389265285688722</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5420689551026929</t>
+          <t>0.5346092678885458</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.596845584259283</t>
+          <t>8.626920940512512</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.309358719309192</t>
+          <t>1.3026796353861332</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.47701033525097714</t>
+          <t>0.44147511906840364</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.759871667775469</t>
+          <t>9.74172767774016</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.760577356024509</t>
+          <t>3.7540403980981374</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.960453610750648</t>
+          <t>12.936624081606283</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.3801953292987706</t>
+          <t>0.5054697175592268</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.393376980581201</t>
+          <t>1.369638004195441</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.742494812473059</t>
+          <t>1.585283610714609</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.77418418862251</t>
+          <t>4.801493820686367</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.915881756740017</t>
+          <t>9.027321910134269</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.059952223929109</t>
+          <t>6.0671552293841815</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.651647042397018</t>
+          <t>0.6528851599960981</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.080642171092613</t>
+          <t>6.095827752127289</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>6.902439585690935</t>
+          <t>6.89888555156638</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.6590991920503388</t>
+          <t>1.6137744083182093</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>9.671261344259289</t>
+          <t>9.716260480771847</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>24.327393246852907</t>
+          <t>25.08121142525726</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>3.952830043398592</t>
+          <t>4.010788743184904</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.277243729223045</t>
+          <t>24.301234532769122</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4274150019989122</t>
+          <t>0.4184997398923854</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.56191528045561</t>
+          <t>0.5565693523909259</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.258797230360706</t>
+          <t>23.406245884558274</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>19.899349921466225</t>
+          <t>20.52627149702751</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.523863216752017</t>
+          <t>4.9810511823537444</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.9621379054226447</t>
+          <t>2.972936961846161</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.321543701119355</t>
+          <t>4.328324504115557</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.857995687799075</t>
+          <t>9.84209418498402</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>18.1968201873957</t>
+          <t>18.5944354649698</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.764200935204028</t>
+          <t>6.734817668622205</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.26299220571393633</t>
+          <t>0.3115155171050356</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8118247267504173</t>
+          <t>0.8059390289958621</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.2373919772146786</t>
+          <t>1.228337921958948</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.8654147709301157</t>
+          <t>1.9070177994300364</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.483906731830788</t>
+          <t>1.423473491453324</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.761434365738809</t>
+          <t>4.749428504757009</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.68009896389494</t>
+          <t>16.66921054744725</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>11.83719385850374</t>
+          <t>11.85587025614679</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.0342734689520476</t>
+          <t>3.0334392024673207</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.0534531828093083</t>
+          <t>2.0554179783299285</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.006452135502904</t>
+          <t>8.96143774226424</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>42.36683811290101</t>
+          <t>41.88776481433148</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.86588721427542</t>
+          <t>5.904788228531778</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>53.33705166599155</t>
+          <t>53.402869196798484</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>8.84752426805085</t>
+          <t>8.783388583721248</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.17752174675393</t>
+          <t>4.189692754102724</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12.138252969697177</t>
+          <t>12.299272853250827</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>26.34999468340454</t>
+          <t>25.99379473761343</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>54.35374626416631</t>
+          <t>54.478497894982674</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -1365,12 +1365,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.898862518486538</t>
+          <t>2.880783432445579</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12.78518139657785</t>
+          <t>1.8264544852254074</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>6.89888555156638</t>
+          <t>3.582889878581966</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.228337921958948</t>
+          <t>1.166685763070424</t>
         </is>
       </c>
     </row>
@@ -10231,12 +10231,12 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>54.478497894982674</t>
+          <t>20.594093582907888</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.317101598251191</t>
+          <t>1.4433756729740645</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.452020690416141</t>
+          <t>5.446866721690121</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.0817079441390107</t>
+          <t>2.281286886901235</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.326720459076871</t>
+          <t>5.332097027102871</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.052916280637967</t>
+          <t>7.051898903836293</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.8012497612818937</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.0759981060507284</t>
+          <t>2.0718352515060245</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.808578338120519</t>
+          <t>2.809215116141685</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.8012497612818937</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20817079441390107</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8191991853626801</t>
+          <t>0.8180743625423681</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.1556021239177248</t>
+          <t>1.2663928094193209</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.096728344127077</t>
+          <t>1.2018746419228403</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.990485240478371</t>
+          <t>8.985804148902648</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.8995892141289816</t>
+          <t>2.0817079441390107</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.04127654196299</t>
+          <t>3.03626892832906</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7312741762225419</t>
+          <t>1.7293408366724834</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>1.0007807959800024</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.466806371753173</t>
+          <t>3.7991784282579633</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.943609982912891</t>
+          <t>8.768621780443937</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.137912225029143</t>
+          <t>3.310400285770183</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.880783432445579</t>
+          <t>2.880545772603739</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>2.0015615919600047</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>1.5817559830612324</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.8294751001729423</t>
+          <t>3.830863797744318</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.7487671295843286</t>
+          <t>3.7498961957776515</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5138406426044821</t>
+          <t>0.5139797199344653</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.2018746419228403</t>
+          <t>1.317101598251191</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.054503988707488</t>
+          <t>1.1556021239177248</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.37140075916084125</t>
+          <t>0.37096525868971547</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.48959180667444224</t>
+          <t>0.4882465942292753</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.5578871854062714</t>
+          <t>0.6088181617418025</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.119013276103878</t>
+          <t>4.118352964106435</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.6088181617418025</t>
+          <t>0.6671871973200014</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.44391590871184033</t>
+          <t>0.44335969943172343</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.4491359459719823</t>
+          <t>0.46260176536422465</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.369644483685523</t>
+          <t>10.509934344174505</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.37724338182611766</t>
+          <t>0.3765304336631434</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6509838831038195</t>
+          <t>1.650218176924529</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.8554829221582763</t>
+          <t>3.856647940548316</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6329956130398727</t>
+          <t>0.631706049168806</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.2647690801097093</t>
+          <t>2.259186032007402</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.20015615919600044</t>
+          <t>0.2193456688254154</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.3386578187937515</t>
+          <t>5.148347433084852</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.20015615919600044</t>
+          <t>0.2193456688254154</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.634203196502382</t>
+          <t>2.886751345948129</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.39513047947535734</t>
+          <t>0.4330127018922193</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.1554172248004306</t>
+          <t>1.1559227860599854</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.46260176536422465</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.21492692082068474</t>
+          <t>0.21513703899881698</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.269174507216054</t>
+          <t>4.259698170583151</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3675507562895077</t>
+          <t>1.3647263780398027</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.3335935986600007</t>
+          <t>0.3655761147090257</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.3852007079725748</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2.4605093069841395</t>
+          <t>2.6964049558080228</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.317204226887918</t>
+          <t>2.313308321412077</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2839832809570614</t>
+          <t>0.28310183911630005</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>7.9925273369091485</t>
+          <t>8.002457065080847</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.8168275509302205</t>
+          <t>4.8175572966244005</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9636748695697119</t>
+          <t>0.9611046100307579</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2497585725119027</t>
+          <t>0.2490520615975722</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.38180463155216554</t>
+          <t>0.3806831702684232</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.9800683375087464</t>
+          <t>7.981209298903792</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.49839213005165117</t>
+          <t>0.4963572871668003</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6146474125172223</t>
+          <t>0.6735753140545633</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.2854174618281284</t>
+          <t>1.2849114320382269</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23563881752036017</t>
+          <t>0.2349305705115658</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.2990816490292483</t>
+          <t>1.3619762130453177</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6213615858602939</t>
+          <t>0.6197677057911424</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.7060218686421196</t>
+          <t>1.8695827763244182</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.9892331138182566</t>
+          <t>0.984833862538129</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.7060218686421196</t>
+          <t>1.8695827763244182</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3052613537589305</t>
+          <t>0.3045632433364596</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3667572121072744</t>
+          <t>1.3666317145421953</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7214449370633838</t>
+          <t>0.720745232851042</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.4670310381240009</t>
+          <t>0.5118065605926359</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6538519593360621</t>
+          <t>0.6525816312670444</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.122826044759762</t>
+          <t>2.1183715454235985</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.742875349153959</t>
+          <t>3.74473467990715</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.05746286454855</t>
+          <t>12.01911015300918</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.48315319410888</t>
+          <t>13.308072646608942</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.195540592798038</t>
+          <t>1.1929800999889126</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.8826397006382705</t>
+          <t>2.051279870460281</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.3734272341919755</t>
+          <t>4.651804564448513</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.544580234683963</t>
+          <t>15.550853907731181</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>16.389265285688722</t>
+          <t>16.29762714015458</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5346092678885458</t>
+          <t>0.5330923575517352</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.626920940512512</t>
+          <t>8.627216580860116</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.3026796353861332</t>
+          <t>1.3038991096993942</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.44147511906840364</t>
+          <t>0.4408527883538307</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.74172767774016</t>
+          <t>9.714159542573672</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.7540403980981374</t>
+          <t>3.752108407402641</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.936624081606283</t>
+          <t>12.252499562136078</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.5054697175592268</t>
+          <t>0.5059487770577432</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.0794041191831907</t>
+          <t>1.1828894969117507</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1.369638004195441</t>
+          <t>0.7289102397586371</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.585283610714609</t>
+          <t>1.575498359004792</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.801493820686367</t>
+          <t>4.793199068655599</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>9.027321910134269</t>
+          <t>9.867226220061273</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.0671552293841815</t>
+          <t>6.068125689815709</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6528851599960981</t>
+          <t>0.6521389098927619</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.095827752127289</t>
+          <t>6.042917200522417</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3.582889878581966</t>
+          <t>3.586589242959704</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.6137744083182093</t>
+          <t>1.6077302192863927</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>9.716260480771847</t>
+          <t>9.691145194310385</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.8988016519360076</t>
+          <t>0.9849721851039159</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>25.08121142525726</t>
+          <t>25.084831262463233</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.010788743184904</t>
+          <t>4.026668275862249</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.301234532769122</t>
+          <t>24.495906904416053</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4184997398923854</t>
+          <t>0.4174128171977745</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5565693523909259</t>
+          <t>0.5546895028478129</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.406245884558274</t>
+          <t>23.429479624870048</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20.52627149702751</t>
+          <t>20.545307950496678</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.9810511823537444</t>
+          <t>4.983729041356958</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.972936961846161</t>
+          <t>2.972206036429585</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.328324504115557</t>
+          <t>4.659622994626416</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.84209418498402</t>
+          <t>9.880765989594991</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>18.5944354649698</t>
+          <t>18.883098593207084</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.734817668622205</t>
+          <t>6.722392870402423</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.3115155171050356</t>
+          <t>0.31108788299078277</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8059390289958621</t>
+          <t>0.805639540960069</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.166685763070424</t>
+          <t>1.1659713670672245</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.9070177994300364</t>
+          <t>1.9101275168396512</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.423473491453324</t>
+          <t>1.419653387583357</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.749428504757009</t>
+          <t>4.878601078277417</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2048824708390741</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.66921054744725</t>
+          <t>16.6231734873967</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>11.85587025614679</t>
+          <t>11.80971984092477</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.0334392024673207</t>
+          <t>3.0321887737120963</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.0554179783299285</t>
+          <t>2.049672109878583</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>8.96143774226424</t>
+          <t>8.942113887518767</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>41.88776481433148</t>
+          <t>41.84119810179821</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.904788228531778</t>
+          <t>5.871852641650472</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>53.402869196798484</t>
+          <t>53.34397450054901</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>8.783388583721248</t>
+          <t>8.76928237792506</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.189692754102724</t>
+          <t>4.18572177163142</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12.299272853250827</t>
+          <t>12.311600908961992</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>25.99379473761343</t>
+          <t>27.13016174565653</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20.594093582907888</t>
+          <t>20.762999072156987</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.259186032007402</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.21106546823655348</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4.8175572966244005</t>
+          <t>1.1874814616453477</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.5059487770577432</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.7289102397586371</t>
+          <t>0.9416231862323259</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>6.068125689815709</t>
+          <t>3.1522512988899436</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>9.691145194310385</t>
+          <t>1.6892085406500001</t>
         </is>
       </c>
     </row>
@@ -8713,12 +8713,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4174128171977745</t>
+          <t>0.5438322006452276</t>
         </is>
       </c>
     </row>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5546895028478129</t>
+          <t>0.5367532386900891</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>1.1659713670672245</t>
+          <t>0.30006228566031456</t>
         </is>
       </c>
     </row>
@@ -9461,12 +9461,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>1.419653387583357</t>
+          <t>14.371367003566315</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.446866721690121</t>
+          <t>5.5336932628717115</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.332097027102871</t>
+          <t>5.31056476799163</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.051898903836293</t>
+          <t>7.016962483264028</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.0718352515060245</t>
+          <t>2.0904354082426453</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.809215116141685</t>
+          <t>2.80064720732174</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8180743625423681</t>
+          <t>0.8279902755352779</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.985804148902648</t>
+          <t>9.016454922261138</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.03626892832906</t>
+          <t>3.07451308126422</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.7293408366724834</t>
+          <t>1.757435019179947</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.768621780443937</t>
+          <t>8.855710344450598</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.310400285770183</t>
+          <t>3.3374622111241976</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.880545772603739</t>
+          <t>2.921304669581989</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.830863797744318</t>
+          <t>3.836422113319565</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.7498961957776515</t>
+          <t>3.7494285068208257</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5139797199344653</t>
+          <t>0.5191914222405934</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.37096525868971547</t>
+          <t>0.3712839154104891</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.4882465942292753</t>
+          <t>0.49266637317618706</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.118352964106435</t>
+          <t>4.101933967051885</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.44335969943172343</t>
+          <t>0.4469977916659971</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.509934344174505</t>
+          <t>10.571838591251813</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3765304336631434</t>
+          <t>0.3758615484863463</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.650218176924529</t>
+          <t>1.6635342605411587</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.856647940548316</t>
+          <t>3.8011118172269622</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.631706049168806</t>
+          <t>0.6367739202095835</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.148347433084852</t>
+          <t>5.128723355630371</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.1559227860599854</t>
+          <t>1.176035304974992</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.21513703899881698</t>
+          <t>0.21649397572005122</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.259698170583151</t>
+          <t>4.33126094499702</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3647263780398027</t>
+          <t>1.3789218443088442</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.313308321412077</t>
+          <t>2.327426614100465</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.28310183911630005</t>
+          <t>0.2816842416441235</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8.002457065080847</t>
+          <t>7.940782916203475</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.1874814616453477</t>
+          <t>1.1716002303752617</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9611046100307579</t>
+          <t>0.9692048961142632</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2490520615975722</t>
+          <t>0.25148878855248213</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3806831702684232</t>
+          <t>0.3818650418494372</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.981209298903792</t>
+          <t>7.980432222132342</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.4963572871668003</t>
+          <t>0.4970784230077392</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.2849114320382269</t>
+          <t>1.2808494218055337</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2349305705115658</t>
+          <t>0.23467854233944574</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.3619762130453177</t>
+          <t>1.371579764233911</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6197677057911424</t>
+          <t>0.6178945855379157</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.984833862538129</t>
+          <t>0.9982310568271151</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.3045632433364596</t>
+          <t>0.30550928945087763</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3666317145421953</t>
+          <t>1.388770035367729</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.720745232851042</t>
+          <t>0.7299017503783611</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6525816312670444</t>
+          <t>0.6563322324939027</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.1183715454235985</t>
+          <t>2.1429467253120498</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.74473467990715</t>
+          <t>3.7357120161354587</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.01911015300918</t>
+          <t>12.1924919954853</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.308072646608942</t>
+          <t>13.333145423126645</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1929800999889126</t>
+          <t>1.1991026717526971</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2.051279870460281</t>
+          <t>2.08644734513166</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.651804564448513</t>
+          <t>4.66829332268038</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.550853907731181</t>
+          <t>15.603329581690017</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>16.29762714015458</t>
+          <t>16.218039632693475</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5330923575517352</t>
+          <t>0.5270326663116488</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.627216580860116</t>
+          <t>8.675644771382212</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.3038991096993942</t>
+          <t>1.3080276837078608</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4408527883538307</t>
+          <t>0.44186886393108</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.714159542573672</t>
+          <t>9.788990319188361</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.752108407402641</t>
+          <t>3.756353997306558</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.252499562136078</t>
+          <t>12.149972886672016</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.9416231862323259</t>
+          <t>0.26844370148362406</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.575498359004792</t>
+          <t>1.571525592125223</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.793199068655599</t>
+          <t>4.843402117619951</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>9.867226220061273</t>
+          <t>9.961290979465197</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.1522512988899436</t>
+          <t>3.2764582377471996</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6521389098927619</t>
+          <t>0.6601359465859549</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.042917200522417</t>
+          <t>6.022442104487683</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3.586589242959704</t>
+          <t>3.577165088482701</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.6077302192863927</t>
+          <t>1.602914972441185</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>1.6892085406500001</t>
+          <t>1.71334774460429</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>25.084831262463233</t>
+          <t>9.514571916837546</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.026668275862249</t>
+          <t>3.926584344704423</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.495906904416053</t>
+          <t>24.503291616694355</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.5438322006452276</t>
+          <t>0.5464572628231532</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5367532386900891</t>
+          <t>0.534282248369515</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.429479624870048</t>
+          <t>23.329340049065912</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20.545307950496678</t>
+          <t>20.831692745437834</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.983729041356958</t>
+          <t>4.994654426836431</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.972206036429585</t>
+          <t>2.9594094820645016</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.659622994626416</t>
+          <t>4.687632515794301</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.880765989594991</t>
+          <t>9.847807205920304</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>18.883098593207084</t>
+          <t>18.88968471048453</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.722392870402423</t>
+          <t>6.810138196628876</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.31108788299078277</t>
+          <t>0.3148766583206733</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.805639540960069</t>
+          <t>0.8112739768389692</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.30006228566031456</t>
+          <t>0.30320812892579596</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.9101275168396512</t>
+          <t>1.4422644624212921</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.371367003566315</t>
+          <t>10.360044970474249</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.878601078277417</t>
+          <t>4.842929145110255</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.6231734873967</t>
+          <t>16.600472896008462</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>11.80971984092477</t>
+          <t>11.92313374448699</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.0321887737120963</t>
+          <t>3.0155140834186547</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.049672109878583</t>
+          <t>2.056251108018504</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>8.942113887518767</t>
+          <t>9.044216938466315</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>41.84119810179821</t>
+          <t>42.02628560856272</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.871852641650472</t>
+          <t>5.964672480746201</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>53.34397450054901</t>
+          <t>53.001756060757224</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>8.76928237792506</t>
+          <t>8.858917113403535</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.18572177163142</t>
+          <t>4.128141306199573</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12.311600908961992</t>
+          <t>12.216264508141917</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>27.13016174565653</t>
+          <t>34.10370772247462</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20.762999072156987</t>
+          <t>24.598671085766817</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.5336932628717115</t>
+          <t>5.502625007437519</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.31056476799163</t>
+          <t>3.630830902540377</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.016962483264028</t>
+          <t>7.2712141614535115</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.0904354082426453</t>
+          <t>2.2732366267291586</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.80064720732174</t>
+          <t>2.996637715990181</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8279902755352779</t>
+          <t>0.825556943856105</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.016454922261138</t>
+          <t>8.82775293903177</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.07451308126422</t>
+          <t>2.94872088775519</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.757435019179947</t>
+          <t>1.680708345066414</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.855710344450598</t>
+          <t>8.684783312486045</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.3374622111241976</t>
+          <t>4.215101085088792</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.921304669581989</t>
+          <t>2.821131685205902</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.836422113319565</t>
+          <t>3.631874501759585</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.7494285068208257</t>
+          <t>3.127418223632538</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.5191914222405934</t>
+          <t>0.49407580334070844</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3712839154104891</t>
+          <t>0.46232869214042827</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.49266637317618706</t>
+          <t>0.49863914969816214</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.101933967051885</t>
+          <t>4.0006424894855215</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4469977916659971</t>
+          <t>0.43097136814109743</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.571838591251813</t>
+          <t>10.973507449633193</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.3758615484863463</t>
+          <t>0.21272299714736648</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.6635342605411587</t>
+          <t>1.563131711501601</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.8011118172269622</t>
+          <t>3.8379755896754735</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6367739202095835</t>
+          <t>0.625254902795363</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.128723355630371</t>
+          <t>5.021238511102463</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.886751345948129</t>
+          <t>5.452464716770817</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.176035304974992</t>
+          <t>1.0985974201797086</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.21649397572005122</t>
+          <t>0.20875949980794942</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.33126094499702</t>
+          <t>4.473647430071436</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3789218443088442</t>
+          <t>1.2799754071138914</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.327426614100465</t>
+          <t>2.206524252059103</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2816842416441235</t>
+          <t>0.275255458886348</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>7.940782916203475</t>
+          <t>7.913665592832928</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.1716002303752617</t>
+          <t>1.151202992574369</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9692048961142632</t>
+          <t>0.9145787216489047</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.25148878855248213</t>
+          <t>0.32776785563660304</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3818650418494372</t>
+          <t>0.3792358624638517</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>7.980432222132342</t>
+          <t>6.316850916736236</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.4970784230077392</t>
+          <t>0.5193942016454196</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.2808494218055337</t>
+          <t>1.2599098970272102</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23467854233944574</t>
+          <t>0.2325761027601518</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.371579764233911</t>
+          <t>1.685593459757861</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6178945855379157</t>
+          <t>0.5095999226273831</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.9982310568271151</t>
+          <t>0.9662502485972282</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.30550928945087763</t>
+          <t>0.29579590902779107</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.388770035367729</t>
+          <t>1.3827234055165172</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7299017503783611</t>
+          <t>0.7100251846058208</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6563322324939027</t>
+          <t>0.6168446718748535</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.1429467253120498</t>
+          <t>2.3666824328339207</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.7357120161354587</t>
+          <t>4.595674904038042</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>12.1924919954853</t>
+          <t>11.41612114082134</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>13.333145423126645</t>
+          <t>12.745498274137937</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1991026717526971</t>
+          <t>1.2097762032757446</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2.08644734513166</t>
+          <t>1.933251867547721</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.66829332268038</t>
+          <t>4.515495124190838</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15.603329581690017</t>
+          <t>17.50370303202532</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>16.218039632693475</t>
+          <t>16.212284047971842</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5270326663116488</t>
+          <t>0.5258183418371587</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.675644771382212</t>
+          <t>8.886773122171137</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.3080276837078608</t>
+          <t>1.2896550652758982</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.44186886393108</t>
+          <t>0.46927351950300444</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.788990319188361</t>
+          <t>8.79646532048605</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.756353997306558</t>
+          <t>3.607091046376871</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>12.149972886672016</t>
+          <t>10.860304922218305</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.26844370148362406</t>
+          <t>0.26339209808640485</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.571525592125223</t>
+          <t>1.721947005827194</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.843402117619951</t>
+          <t>4.700736428234191</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>9.961290979465197</t>
+          <t>10.020802602692921</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.2764582377471996</t>
+          <t>3.2695298650012603</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.6601359465859549</t>
+          <t>0.613220215485748</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.022442104487683</t>
+          <t>6.077361208675601</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3.577165088482701</t>
+          <t>4.503583508912399</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.602914972441185</t>
+          <t>1.527911861657566</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>1.71334774460429</t>
+          <t>1.68930719550195</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>9.514571916837546</t>
+          <t>11.119540402869747</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>3.926584344704423</t>
+          <t>3.8539923680253736</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.503291616694355</t>
+          <t>24.34723950119853</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.5464572628231532</t>
+          <t>0.5493589162946741</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.534282248369515</t>
+          <t>0.5073956859280386</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>23.329340049065912</t>
+          <t>21.96334250776188</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20.831692745437834</t>
+          <t>20.17934067159179</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>4.994654426836431</t>
+          <t>3.0288355009081056</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.9594094820645016</t>
+          <t>2.864721529919631</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.687632515794301</t>
+          <t>4.611269877164721</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.847807205920304</t>
+          <t>9.925955114338024</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>18.88968471048453</t>
+          <t>16.551419848285377</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.810138196628876</t>
+          <t>6.6407855083428355</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2185464690666557</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.3148766583206733</t>
+          <t>0.3114049319349341</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8112739768389692</t>
+          <t>0.7726228730496798</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.30320812892579596</t>
+          <t>0.2945800572038282</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.4422644624212921</t>
+          <t>1.4382103890013127</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>10.360044970474249</t>
+          <t>8.151202408233885</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.842929145110255</t>
+          <t>5.220986276986225</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>16.600472896008462</t>
+          <t>17.430803131744703</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>11.92313374448699</t>
+          <t>11.62585402698755</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.0155140834186547</t>
+          <t>3.072875084294307</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.056251108018504</t>
+          <t>2.059005844565907</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.044216938466315</t>
+          <t>9.03770119883792</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>42.02628560856272</t>
+          <t>40.21383640633514</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.964672480746201</t>
+          <t>5.938145679031909</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>53.001756060757224</t>
+          <t>51.65669825426314</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>8.858917113403535</t>
+          <t>8.728788985763922</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.128141306199573</t>
+          <t>4.025865328340068</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12.216264508141917</t>
+          <t>12.264240509724246</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>34.10370772247462</t>
+          <t>32.73713080552795</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>24.598671085766817</t>
+          <t>20.213394602498084</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.502625007437519</t>
+          <t>6.74685470409246</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.630830902540377</t>
+          <t>3.746578547599808</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.2712141614535115</t>
+          <t>6.120148846985221</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.2732366267291586</t>
+          <t>0.41074376066408486</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.996637715990181</t>
+          <t>2.553480929692398</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.825556943856105</t>
+          <t>1.1110756792947454</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.82775293903177</t>
+          <t>10.108348892956286</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.94872088775519</t>
+          <t>3.8541878979342012</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.680708345066414</t>
+          <t>2.2096780150824857</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.684783312486045</t>
+          <t>5.431745932917669</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.215101085088792</t>
+          <t>2.026099695881819</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.821131685205902</t>
+          <t>3.349128453304129</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.631874501759585</t>
+          <t>6.348507134005853</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.127418223632538</t>
+          <t>2.9162784120789644</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.49407580334070844</t>
+          <t>0.6667798042514477</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.46232869214042827</t>
+          <t>0.4028193093385412</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.49863914969816214</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.0006424894855215</t>
+          <t>3.225815248434344</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.43097136814109743</t>
+          <t>0.5786317057707349</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.973507449633193</t>
+          <t>7.1933328174649604</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.21272299714736648</t>
+          <t>0.2970058480274846</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.563131711501601</t>
+          <t>1.1973513475731963</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.8379755896754735</t>
+          <t>2.804028436292348</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.625254902795363</t>
+          <t>0.6367182846963463</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.021238511102463</t>
+          <t>5.459221258121378</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5.452464716770817</t>
+          <t>4.466649905148204</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0985974201797086</t>
+          <t>1.4088567747256378</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.20875949980794942</t>
+          <t>0.2813551694668952</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.473647430071436</t>
+          <t>4.69375449813549</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.2799754071138914</t>
+          <t>1.809890457298733</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.206524252059103</t>
+          <t>3.0010582092343037</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.275255458886348</t>
+          <t>0.2972965438375014</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>7.913665592832928</t>
+          <t>6.2897554553522355</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.151202992574369</t>
+          <t>1.0223196211463517</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.9145787216489047</t>
+          <t>0.7018384147353943</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.32776785563660304</t>
+          <t>0.27045164480064976</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3792358624638517</t>
+          <t>0.3515013295691628</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.23574334753072737</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.22970090624105716</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.316850916736236</t>
+          <t>6.756842357783903</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.5193942016454196</t>
+          <t>0.3324890266789211</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6735753140545633</t>
+          <t>0.6921524022464949</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.2599098970272102</t>
+          <t>1.2109312163304347</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2325761027601518</t>
+          <t>0.34293080932847814</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.685593459757861</t>
+          <t>2.2184723264434996</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.5095999226273831</t>
+          <t>0.7354743273175259</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20290934983311892</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.9662502485972282</t>
+          <t>1.2453394347904005</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.29579590902779107</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3827234055165172</t>
+          <t>1.837763295943546</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7100251846058208</t>
+          <t>0.9688459459376468</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.6168446718748535</t>
+          <t>0.5596947667989487</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2.3666824328339207</t>
+          <t>1.5538092162323895</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>4.595674904038042</t>
+          <t>4.3632683667832985</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>11.41612114082134</t>
+          <t>14.01262865751433</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>12.745498274137937</t>
+          <t>5.9815085610747225</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.2097762032757446</t>
+          <t>1.1598293820202226</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.933251867547721</t>
+          <t>1.5920871685328812</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>4.515495124190838</t>
+          <t>2.576640664652369</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17.50370303202532</t>
+          <t>10.508137732413362</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>16.212284047971842</t>
+          <t>16.091141756419752</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5258183418371587</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.886773122171137</t>
+          <t>8.826534419787093</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.2896550652758982</t>
+          <t>1.0343845114571855</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.46927351950300444</t>
+          <t>0.3587605762889705</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.79646532048605</t>
+          <t>8.739590386784489</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.607091046376871</t>
+          <t>3.7160877426553203</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>10.860304922218305</t>
+          <t>14.614591485145155</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.26339209808640485</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.721947005827194</t>
+          <t>1.1828894969117507</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.700736428234191</t>
+          <t>6.445610109414459</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>10.020802602692921</t>
+          <t>6.678296985518274</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.2695298650012603</t>
+          <t>3.7741970078434126</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.613220215485748</t>
+          <t>0.7786154385185391</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.077361208675601</t>
+          <t>6.72589050621906</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>4.503583508912399</t>
+          <t>2.1323395769423996</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.527911861657566</t>
+          <t>1.185780290229832</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>1.68930719550195</t>
+          <t>2.1589600062696697</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>11.119540402869747</t>
+          <t>20.010579395819263</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>3.8539923680253736</t>
+          <t>4.446863243902712</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>24.34723950119853</t>
+          <t>28.469050367387727</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.5493589162946741</t>
+          <t>0.528792891653538</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5073956859280386</t>
+          <t>0.6834689290293248</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>21.96334250776188</t>
+          <t>30.558463401570002</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20.17934067159179</t>
+          <t>33.63128744615188</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>3.0288355009081056</t>
+          <t>14.568363014889982</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.864721529919631</t>
+          <t>3.4555583650286485</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>4.611269877164721</t>
+          <t>3.557362172687966</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.925955114338024</t>
+          <t>9.675418843914372</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>16.551419848285377</t>
+          <t>6.4065613125892265</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.6407855083428355</t>
+          <t>8.588059674733625</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2185464690666557</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.3114049319349341</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7726228730496798</t>
+          <t>0.8579949182404283</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2945800572038282</t>
+          <t>0.2721259051571723</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.4382103890013127</t>
+          <t>1.608812127344294</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>8.151202408233885</t>
+          <t>12.545906718640465</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>5.220986276986225</t>
+          <t>2.64716789114593</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>17.430803131744703</t>
+          <t>14.54062445132147</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>11.62585402698755</t>
+          <t>15.97461228453971</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.072875084294307</t>
+          <t>3.1413098524373995</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.059005844565907</t>
+          <t>2.4793509244930414</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.03770119883792</t>
+          <t>10.43461700022867</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>40.21383640633514</t>
+          <t>37.42191907350624</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.938145679031909</t>
+          <t>4.561831213565177</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>51.65669825426314</t>
+          <t>47.10887006162139</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>8.728788985763922</t>
+          <t>10.14218540797087</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>4.025865328340068</t>
+          <t>2.66339067097403</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>12.264240509724246</t>
+          <t>13.377146527766854</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>32.73713080552795</t>
+          <t>18.09009631692509</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20.213394602498084</t>
+          <t>16.45839441379634</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.74685470409246</t>
+          <t>6.4790755214902305</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.746578547599808</t>
+          <t>3.813580451424619</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.120148846985221</t>
+          <t>5.456755624262623</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.41074376066408486</t>
+          <t>0.4102190563199619</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.553480929692398</t>
+          <t>2.557670500177439</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.1110756792947454</t>
+          <t>1.0798292817046762</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.108348892956286</t>
+          <t>10.108706100044593</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.8541878979342012</t>
+          <t>3.750323177956508</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.2096780150824857</t>
+          <t>2.2238982493074166</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.431745932917669</t>
+          <t>5.2447800001205565</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.026099695881819</t>
+          <t>1.6977672773917412</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.349128453304129</t>
+          <t>3.4227682337343914</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.348507134005853</t>
+          <t>6.482759661679495</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.9162784120789644</t>
+          <t>2.4728219323486633</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.6667798042514477</t>
+          <t>0.6619270865372724</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.4028193093385412</t>
+          <t>0.37258589816035104</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.225815248434344</t>
+          <t>3.280171489876416</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5786317057707349</t>
+          <t>0.5623455637768636</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7.1933328174649604</t>
+          <t>5.7046244024045105</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2970058480274846</t>
+          <t>0.2894178264171252</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.1973513475731963</t>
+          <t>1.220846629472831</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.804028436292348</t>
+          <t>3.551027695237188</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.6367182846963463</t>
+          <t>0.5944750627799527</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.459221258121378</t>
+          <t>4.842718355256733</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.466649905148204</t>
+          <t>4.0435210118891565</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.4088567747256378</t>
+          <t>1.4449747191285005</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2813551694668952</t>
+          <t>0.28118495131116816</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.69375449813549</t>
+          <t>4.259738186849946</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.809890457298733</t>
+          <t>1.8818836664031684</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>3.0010582092343037</t>
+          <t>2.901938401316272</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2972965438375014</t>
+          <t>0.24503021055142843</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.2897554553522355</t>
+          <t>6.155336049534539</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0223196211463517</t>
+          <t>0.997018553795499</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.7018384147353943</t>
+          <t>0.7206219889295419</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.27045164480064976</t>
+          <t>0.2753884053453408</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.23574334753072737</t>
+          <t>0.23199220010740565</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.22970090624105716</t>
+          <t>0.22615506563553261</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.756842357783903</t>
+          <t>6.462186613469434</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.3324890266789211</t>
+          <t>0.24284723055388024</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6921524022464949</t>
+          <t>0.6735753140545633</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.2109312163304347</t>
+          <t>1.2106412462811948</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.34293080932847814</t>
+          <t>0.29422892207391355</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.2184723264434996</t>
+          <t>2.2497376803534013</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.7354743273175259</t>
+          <t>0.7192226731128111</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.20290934983311892</t>
+          <t>0.20754694607635926</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.2453394347904005</t>
+          <t>1.2573217496236744</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.837763295943546</t>
+          <t>1.8479885251600223</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.9688459459376468</t>
+          <t>0.9408345137278369</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.5596947667989487</t>
+          <t>0.5250005451171186</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.5538092162323895</t>
+          <t>1.4464646057940163</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>4.3632683667832985</t>
+          <t>4.20035212607937</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>14.01262865751433</t>
+          <t>14.01754246192197</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>5.9815085610747225</t>
+          <t>12.895472437196371</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.1598293820202226</t>
+          <t>1.064588336577166</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.5920871685328812</t>
+          <t>1.5336616199241995</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2.576640664652369</t>
+          <t>2.2715488169532305</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10.508137732413362</t>
+          <t>10.035939744695568</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>16.091141756419752</t>
+          <t>16.758281116424584</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.826534419787093</t>
+          <t>8.986341862668242</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.0343845114571855</t>
+          <t>0.994412450068532</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3587605762889705</t>
+          <t>0.3469167367146362</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>8.739590386784489</t>
+          <t>9.643955514779929</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.7160877426553203</t>
+          <t>3.362997077623609</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.614591485145155</t>
+          <t>14.582728804395188</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.1828894969117507</t>
+          <t>1.401824548813484</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>6.445610109414459</t>
+          <t>6.25920474034274</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>6.678296985518274</t>
+          <t>6.289775808437862</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.7741970078434126</t>
+          <t>3.8400293569609474</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7786154385185391</t>
+          <t>0.793687030569119</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.72589050621906</t>
+          <t>6.821139151785316</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.1323395769423996</t>
+          <t>2.1068092211882714</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.185780290229832</t>
+          <t>1.34737696790514</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2.1589600062696697</t>
+          <t>2.212976469472812</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20.010579395819263</t>
+          <t>20.27706392141487</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.446863243902712</t>
+          <t>4.683648777727598</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>28.469050367387727</t>
+          <t>28.321746267924595</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.528792891653538</t>
+          <t>0.501019275880096</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6834689290293248</t>
+          <t>0.6812457883642304</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>30.558463401570002</t>
+          <t>20.13402112061111</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>33.63128744615188</t>
+          <t>34.25855571805802</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>14.568363014889982</t>
+          <t>14.674789824131759</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.4555583650286485</t>
+          <t>3.7416816683034355</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>3.557362172687966</t>
+          <t>3.3572840362722665</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.675418843914372</t>
+          <t>9.752880416331166</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6.4065613125892265</t>
+          <t>6.053670203804272</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>8.588059674733625</t>
+          <t>8.4700440164383</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8579949182404283</t>
+          <t>0.9272317458652477</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2721259051571723</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.608812127344294</t>
+          <t>1.738086484182361</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>12.545906718640465</t>
+          <t>14.193744439351889</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2.64716789114593</t>
+          <t>2.510869278617837</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.54062445132147</t>
+          <t>14.599855081038044</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>15.97461228453971</t>
+          <t>16.07483934485834</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.1413098524373995</t>
+          <t>3.061625664573515</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.4793509244930414</t>
+          <t>2.461086931352713</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>10.43461700022867</t>
+          <t>10.34395522708624</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>37.42191907350624</t>
+          <t>46.94934283707943</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>4.561831213565177</t>
+          <t>6.402952440250246</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>47.10887006162139</t>
+          <t>46.92291292125338</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>10.14218540797087</t>
+          <t>9.771501636130038</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2.66339067097403</t>
+          <t>2.389230026287074</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>13.377146527766854</t>
+          <t>13.769500968376036</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>18.09009631692509</t>
+          <t>15.89812255279805</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16.45839441379634</t>
+          <t>16.076761729563827</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D446"/>
+  <dimension ref="A1:D447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.4790755214902305</t>
+          <t>6.42615297536145</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.813580451424619</t>
+          <t>3.8335765264910067</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.456755624262623</t>
+          <t>5.291131823734859</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.4102190563199619</t>
+          <t>0.4023146244803508</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.557670500177439</t>
+          <t>2.5456953734455294</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.0798292817046762</t>
+          <t>1.042863680477415</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.108706100044593</t>
+          <t>10.045772744925927</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.750323177956508</t>
+          <t>3.6750935308707695</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.2238982493074166</t>
+          <t>2.171610549545049</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>5.760255102103324</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.2447800001205565</t>
+          <t>5.164020106730408</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.6977672773917412</t>
+          <t>1.6491434275130008</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.4227682337343914</t>
+          <t>3.421139930603008</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.0015615919600047</t>
+          <t>26.378606852534734</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.482759661679495</t>
+          <t>6.525070821703425</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.4728219323486633</t>
+          <t>2.4946506172752607</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.6619270865372724</t>
+          <t>0.6551612017372871</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.37258589816035104</t>
+          <t>0.36122478174114847</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.280171489876416</t>
+          <t>3.3092461724134523</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5623455637768636</t>
+          <t>0.5440489916117015</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.7046244024045105</t>
+          <t>5.4830915226996755</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2894178264171252</t>
+          <t>0.28227250415058386</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.220846629472831</t>
+          <t>1.2222152949848708</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.551027695237188</t>
+          <t>3.4507533896822378</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5944750627799527</t>
+          <t>0.5734752047820725</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4.842718355256733</t>
+          <t>4.915952651400691</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.0435210118891565</t>
+          <t>4.07895519495651</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.4449747191285005</t>
+          <t>1.4293344891211035</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.28118495131116816</t>
+          <t>0.2739844070723887</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.259738186849946</t>
+          <t>4.187885473237749</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.8818836664031684</t>
+          <t>1.8323893543282135</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.901938401316272</t>
+          <t>2.787071958357862</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.24503021055142843</t>
+          <t>0.2315808430948247</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.155336049534539</t>
+          <t>6.228009284928434</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0.997018553795499</t>
+          <t>1.0064448021279162</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.7206219889295419</t>
+          <t>0.7148690982234334</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2753884053453408</t>
+          <t>0.27059843448680887</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.23199220010740565</t>
+          <t>0.22759246151469548</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.22615506563553261</t>
+          <t>0.2218289183146394</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.462186613469434</t>
+          <t>6.479559374358537</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.24284723055388024</t>
+          <t>0.2363752595965174</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.2106412462811948</t>
+          <t>1.1869894707907374</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.29422892207391355</t>
+          <t>0.2831307895481918</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.2497376803534013</t>
+          <t>2.2526445222047458</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.7192226731128111</t>
+          <t>0.697452980617661</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.20754694607635926</t>
+          <t>0.20406420795604063</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.2573217496236744</t>
+          <t>1.2269391912561094</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.8479885251600223</t>
+          <t>1.8237077486622641</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.9408345137278369</t>
+          <t>0.9130618617888904</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.5250005451171186</t>
+          <t>0.5046382062327719</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.4464646057940163</t>
+          <t>1.415401457863526</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>4.20035212607937</t>
+          <t>4.15500567941239</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>14.01754246192197</t>
+          <t>13.69424222519893</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>12.895472437196371</t>
+          <t>12.936232197600923</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.064588336577166</t>
+          <t>1.0359228708185535</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.5336616199241995</t>
+          <t>1.5155708917567594</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2.2715488169532305</t>
+          <t>2.1976402625292804</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10.035939744695568</t>
+          <t>9.87862832132172</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>16.758281116424584</t>
+          <t>16.897474363627268</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.986341862668242</t>
+          <t>8.902779739225354</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.994412450068532</t>
+          <t>0.9696405247681229</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3469167367146362</t>
+          <t>0.3363556919912636</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.643955514779929</t>
+          <t>9.583256182213562</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.362997077623609</t>
+          <t>3.3221467538306406</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.582728804395188</t>
+          <t>14.731965342242683</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.401824548813484</t>
+          <t>1.338853834689929</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>6.25920474034274</t>
+          <t>6.069158648410628</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>6.289775808437862</t>
+          <t>6.168635979486111</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.8400293569609474</t>
+          <t>3.83956455307981</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.793687030569119</t>
+          <t>0.775049198170643</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.821139151785316</t>
+          <t>6.825339426919342</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.1068092211882714</t>
+          <t>2.128503620959222</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.34737696790514</t>
+          <t>1.286196856507119</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2.212976469472812</t>
+          <t>2.192114851256761</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20.27706392141487</t>
+          <t>20.40199745693254</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.683648777727598</t>
+          <t>4.747004414353853</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>28.321746267924595</t>
+          <t>28.327318130090784</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.501019275880096</t>
+          <t>0.48445665772482194</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6812457883642304</t>
+          <t>0.6549000642264231</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20.13402112061111</t>
+          <t>20.331271797015404</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>34.25855571805802</t>
+          <t>34.87960522860293</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>14.674789824131759</t>
+          <t>14.78858184090546</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.7416816683034355</t>
+          <t>3.692631680723639</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>3.3572840362722665</t>
+          <t>3.234671240899309</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.752880416331166</t>
+          <t>9.817740380418144</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6.053670203804272</t>
+          <t>5.923119974603203</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>8.4700440164383</t>
+          <t>8.238620545367597</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.9272317458652477</t>
+          <t>0.8995522045103117</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.738086484182361</t>
+          <t>1.7486953926685231</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.193744439351889</t>
+          <t>14.413734536074273</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2.510869278617837</t>
+          <t>2.4625650487410176</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.599855081038044</t>
+          <t>14.768974715486479</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>16.07483934485834</t>
+          <t>15.61766031403959</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.061625664573515</t>
+          <t>3.0089947735980087</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.461086931352713</t>
+          <t>2.3978857132816422</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>10.34395522708624</t>
+          <t>10.09085633586806</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>46.94934283707943</t>
+          <t>46.49257034709279</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>6.402952440250246</t>
+          <t>6.254476273804688</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>46.92291292125338</t>
+          <t>45.92158381916685</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>9.771501636130038</t>
+          <t>9.50337235124281</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2.389230026287074</t>
+          <t>2.293932364730086</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>13.769500968376036</t>
+          <t>13.951443255578354</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>15.89812255279805</t>
+          <t>15.36495582148302</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,29 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16.076761729563827</t>
+          <t>16.23546510025362</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>F2PLR_STR_Login_Goku</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>68.42421726234998</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.42615297536145</t>
+          <t>6.50629812370353</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.8335765264910067</t>
+          <t>3.820029699286002</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.291131823734859</t>
+          <t>5.308012939886482</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.4023146244803508</t>
+          <t>0.37288312075800534</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.5456953734455294</t>
+          <t>2.500548572828365</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.042863680477415</t>
+          <t>1.0047008131259638</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.045772744925927</t>
+          <t>10.09280428168829</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.6750935308707695</t>
+          <t>3.7647119084402885</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.171610549545049</t>
+          <t>2.049002408355414</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.760255102103324</t>
+          <t>4.8707714080187134</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.164020106730408</t>
+          <t>5.1248353898633985</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.6491434275130008</t>
+          <t>1.669276727776249</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.421139930603008</t>
+          <t>3.3807372224404304</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26.378606852534734</t>
+          <t>10.56598564364404</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.525070821703425</t>
+          <t>6.486706452554311</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.4946506172752607</t>
+          <t>2.5162193558399446</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.6551612017372871</t>
+          <t>0.6364143980533206</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.36122478174114847</t>
+          <t>0.34577904470346404</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.3092461724134523</t>
+          <t>3.3660467426911325</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5440489916117015</t>
+          <t>0.5255700483687927</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5.4830915226996755</t>
+          <t>3.5434152329344926</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.28227250415058386</t>
+          <t>0.27139048083418055</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.2222152949848708</t>
+          <t>1.2080959505300584</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.4507533896822378</t>
+          <t>3.2537146127145085</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5734752047820725</t>
+          <t>0.5510855935534409</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4.915952651400691</t>
+          <t>5.147915549676676</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.07895519495651</t>
+          <t>4.210829913721223</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.4293344891211035</t>
+          <t>1.4044254366429247</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2739844070723887</t>
+          <t>0.26676438026069516</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.187885473237749</t>
+          <t>4.302815575810051</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.8323893543282135</t>
+          <t>1.6751027782628762</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.787071958357862</t>
+          <t>2.733018700644969</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2315808430948247</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.228009284928434</t>
+          <t>5.775148758822553</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0064448021279162</t>
+          <t>1.0023872501712248</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.7148690982234334</t>
+          <t>0.6894086679415352</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.27059843448680887</t>
+          <t>0.2618339301868602</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.22759246151469548</t>
+          <t>0.22098448949347266</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2218289183146394</t>
+          <t>0.2155974206943565</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.479559374358537</t>
+          <t>6.407427502453423</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.2363752595965174</t>
+          <t>0.22000819456148113</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.1869894707907374</t>
+          <t>1.1446056315761142</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2831307895481918</t>
+          <t>0.2631985056419568</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.2526445222047458</t>
+          <t>2.1909791018051936</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.697452980617661</t>
+          <t>0.669499356514482</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.20406420795604063</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.2269391912561094</t>
+          <t>1.2017886418064379</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.8237077486622641</t>
+          <t>1.7728316212051343</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.9130618617888904</t>
+          <t>0.8865416110424111</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.5046382062327719</t>
+          <t>0.4762182716319718</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.415401457863526</t>
+          <t>1.3459352255208303</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>4.15500567941239</t>
+          <t>3.9698017485872583</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>13.69424222519893</t>
+          <t>13.302815957583691</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>12.936232197600923</t>
+          <t>12.717734904993634</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.0359228708185535</t>
+          <t>1.0026059267128795</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.5155708917567594</t>
+          <t>1.507768181103991</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2.1976402625292804</t>
+          <t>2.0678751146127627</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>9.87862832132172</t>
+          <t>9.64023411225122</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>16.897474363627268</t>
+          <t>17.14457417283218</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.902779739225354</t>
+          <t>8.76280521373368</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9696405247681229</t>
+          <t>0.9210279361392871</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3363556919912636</t>
+          <t>0.3220764622142367</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.583256182213562</t>
+          <t>9.25397153834698</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.3221467538306406</t>
+          <t>3.1412134893653914</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.731965342242683</t>
+          <t>14.833200618667382</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.338853834689929</t>
+          <t>1.284531081068161</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>6.069158648410628</t>
+          <t>5.885514812355384</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>6.168635979486111</t>
+          <t>5.909646224369787</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.83956455307981</t>
+          <t>3.7719589676200442</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.775049198170643</t>
+          <t>0.7430655793817662</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.825339426919342</t>
+          <t>6.749957536909861</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.128503620959222</t>
+          <t>2.1597132017247134</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.286196856507119</t>
+          <t>1.332670442363417</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2.192114851256761</t>
+          <t>2.141847547276079</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20.40199745693254</t>
+          <t>20.532541978561213</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.747004414353853</t>
+          <t>4.7229196750035385</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>28.327318130090784</t>
+          <t>27.96191851288087</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.48445665772482194</t>
+          <t>0.45767787021238093</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6549000642264231</t>
+          <t>0.6086022366928662</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20.331271797015404</t>
+          <t>21.174326884024964</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>34.87960522860293</t>
+          <t>36.122396904432655</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>14.78858184090546</t>
+          <t>14.81571190601685</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.692631680723639</t>
+          <t>3.6001540415107707</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>3.234671240899309</t>
+          <t>2.270560833930396</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>9.817740380418144</t>
+          <t>10.29910176100357</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.923119974603203</t>
+          <t>5.853451382194352</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>8.238620545367597</t>
+          <t>8.030999234286531</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8995522045103117</t>
+          <t>0.8812199991118153</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.7486953926685231</t>
+          <t>1.3989187759885482</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.413734536074273</t>
+          <t>14.357247389356521</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2.4625650487410176</t>
+          <t>2.305059465215974</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.768974715486479</t>
+          <t>15.09423551739844</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>15.61766031403959</t>
+          <t>15.16108102752405</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>3.0089947735980087</t>
+          <t>2.8227637540510884</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.3978857132816422</t>
+          <t>2.32527717381633</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>10.09085633586806</t>
+          <t>9.738563412711196</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>46.49257034709279</t>
+          <t>44.829107071332</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>6.254476273804688</t>
+          <t>6.120719777042568</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>45.92158381916685</t>
+          <t>45.48565474710946</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>9.50337235124281</t>
+          <t>9.155166158495684</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2.293932364730086</t>
+          <t>2.106053891054453</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>13.951443255578354</t>
+          <t>14.52526626239721</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>15.36495582148302</t>
+          <t>14.68880936651485</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16.23546510025362</t>
+          <t>16.952557022349154</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>68.42421726234998</t>
+          <t>68.77515314466874</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.50629812370353</t>
+          <t>6.567365890619822</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.820029699286002</t>
+          <t>3.840883267139036</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.0007807959800024</t>
+          <t>7.399560684336539</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.308012939886482</t>
+          <t>5.316859533269996</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.37288312075800534</t>
+          <t>0.3631954639995352</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.500548572828365</t>
+          <t>2.4470932658060907</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.0047008131259638</t>
+          <t>1.006631885858916</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.09280428168829</t>
+          <t>10.142232652021915</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.7647119084402885</t>
+          <t>3.7906793077781504</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.049002408355414</t>
+          <t>2.0583133777425022</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.8707714080187134</t>
+          <t>5.717887101809826</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.1248353898633985</t>
+          <t>5.155682339573555</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.669276727776249</t>
+          <t>1.689181351879663</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.3807372224404304</t>
+          <t>3.3998070693176814</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.56598564364404</t>
+          <t>10.540727086949495</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.486706452554311</t>
+          <t>6.503141863575124</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.5162193558399446</t>
+          <t>2.5162459849857237</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.6364143980533206</t>
+          <t>0.6390282551100016</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.34577904470346404</t>
+          <t>0.3481920751567063</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.3660467426911325</t>
+          <t>3.3261145766249456</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5255700483687927</t>
+          <t>0.5263717063927938</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.5434152329344926</t>
+          <t>3.5610215015103615</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.27139048083418055</t>
+          <t>0.2719744602617623</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.2080959505300584</t>
+          <t>1.2087294186070423</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.2537146127145085</t>
+          <t>3.282375264530999</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5510855935534409</t>
+          <t>0.5502664131004331</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.147915549676676</t>
+          <t>4.890538940499048</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.210829913721223</t>
+          <t>4.2247356701169805</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.4044254366429247</t>
+          <t>1.4149945466345482</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.26676438026069516</t>
+          <t>0.2681403689383677</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.302815575810051</t>
+          <t>4.292681610796004</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.6751027782628762</t>
+          <t>1.679015253468748</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.733018700644969</t>
+          <t>2.718279232392293</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>5.775148758822553</t>
+          <t>5.743482639701555</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0023872501712248</t>
+          <t>0.9973890263167107</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.6894086679415352</t>
+          <t>0.6908290205761368</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2618339301868602</t>
+          <t>0.2623428576098803</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.22098448949347266</t>
+          <t>0.22066269207013126</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2155974206943565</t>
+          <t>0.21512087536466318</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.407427502453423</t>
+          <t>6.426830330573097</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.22000819456148113</t>
+          <t>0.21876276386671512</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.1446056315761142</t>
+          <t>1.1557788898005699</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2631985056419568</t>
+          <t>0.26321032178492615</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.1909791018051936</t>
+          <t>2.196088288351183</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.669499356514482</t>
+          <t>0.6644842526669912</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.2017886418064379</t>
+          <t>1.188918993259473</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.7728316212051343</t>
+          <t>1.785973915902711</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.8865416110424111</t>
+          <t>0.887025068524764</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.4762182716319718</t>
+          <t>0.47305049081120354</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.3459352255208303</t>
+          <t>1.3570070651590038</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.9698017485872583</t>
+          <t>3.989608793177702</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>13.302815957583691</t>
+          <t>13.2925170597739</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>12.717734904993634</t>
+          <t>12.6530615149711</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.0026059267128795</t>
+          <t>1.000156925783457</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.507768181103991</t>
+          <t>1.5173673154913008</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2.0678751146127627</t>
+          <t>2.036607759056171</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>9.64023411225122</t>
+          <t>9.69623307539505</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>17.14457417283218</t>
+          <t>15.579637358825984</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.76280521373368</t>
+          <t>8.966084708790737</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9210279361392871</t>
+          <t>0.9184473106799482</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3220764622142367</t>
+          <t>0.3211174721922099</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.25397153834698</t>
+          <t>9.27348348982756</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.1412134893653914</t>
+          <t>3.1229889020106594</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.833200618667382</t>
+          <t>14.82254789450073</t>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1.1828894969117507</t>
+          <t>0.3013517229519873</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.284531081068161</t>
+          <t>1.282519476859592</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.885514812355384</t>
+          <t>5.893002220472675</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>5.909646224369787</t>
+          <t>5.9227174245488055</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.7719589676200442</t>
+          <t>3.781608461746061</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7430655793817662</t>
+          <t>0.7462872963152858</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.749957536909861</t>
+          <t>6.758478296666723</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.1597132017247134</t>
+          <t>2.1555928427814592</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.332670442363417</t>
+          <t>1.311235520378759</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2.141847547276079</t>
+          <t>2.1585681630895994</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20.532541978561213</t>
+          <t>20.602017250254093</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.7229196750035385</t>
+          <t>4.5789669610743715</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>27.96191851288087</t>
+          <t>28.26302458634277</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.45767787021238093</t>
+          <t>0.45904573337771204</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6086022366928662</t>
+          <t>0.6082189650444401</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>21.174326884024964</t>
+          <t>20.996134908580487</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>36.122396904432655</t>
+          <t>35.97004709631308</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>14.81571190601685</t>
+          <t>14.847475818184755</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.6001540415107707</t>
+          <t>3.609308073530836</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2.270560833930396</t>
+          <t>2.26287067519835</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>10.29910176100357</t>
+          <t>10.529771200235288</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.853451382194352</t>
+          <t>5.855113127009801</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>8.030999234286531</t>
+          <t>8.032662810981996</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8812199991118153</t>
+          <t>0.8861308614115835</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.3989187759885482</t>
+          <t>1.3913942775725872</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.357247389356521</t>
+          <t>14.335001772784826</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2.305059465215974</t>
+          <t>2.3356602356669307</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.09423551739844</t>
+          <t>15.061593538994344</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>15.16108102752405</t>
+          <t>15.04087130796839</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.8227637540510884</t>
+          <t>2.847398958715218</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.32527717381633</t>
+          <t>2.2787474149735845</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.738563412711196</t>
+          <t>9.721883794567436</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>44.829107071332</t>
+          <t>44.96002805470685</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>6.120719777042568</t>
+          <t>6.1315153710031325</t>
         </is>
       </c>
     </row>
@@ -10011,12 +10011,12 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>45.48565474710946</t>
+          <t>12.99495732040063</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>9.155166158495684</t>
+          <t>9.205749449016322</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2.106053891054453</t>
+          <t>2.11410235875266</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>14.52526626239721</t>
+          <t>14.489858550788583</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>14.68880936651485</t>
+          <t>14.6191359450953</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16.952557022349154</t>
+          <t>16.884055313590295</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>68.77515314466874</t>
+          <t>68.97855801046069</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D447"/>
+  <dimension ref="A1:D451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>1.5817559830612324</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.567365890619822</t>
+          <t>3.6398810171913603</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.5778010619588624</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.281286886901235</t>
+          <t>2.5</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.840883267139036</t>
+          <t>2.9075357712304686</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.399560684336539</t>
+          <t>9.172995669443159</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.316859533269996</t>
+          <t>3.6762604704494857</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.3631954639995352</t>
+          <t>0.2435953859484799</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.4470932658060907</t>
+          <t>1.6368128395644845</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.9132272426127037</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.6666666666666665</t>
+          <t>1.8264544852254074</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.20817079441390107</t>
+          <t>0.22812868869012348</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.006631885858916</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.2663928094193209</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.2018746419228403</t>
+          <t>1.317101598251191</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.142232652021915</t>
+          <t>6.481921045393251</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.0817079441390107</t>
+          <t>2.281286886901235</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.7906793077781504</t>
+          <t>2.3427806541190304</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.0583133777425022</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.717887101809826</t>
+          <t>5.211417549523055</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.7991784282579633</t>
+          <t>4.1634158882780214</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.155682339573555</t>
+          <t>3.4043797654692343</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.689181351879663</t>
+          <t>1.078632835661727</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.3998070693176814</t>
+          <t>2.170984800424069</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.540727086949495</t>
+          <t>10.797557518585647</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>1.7334031858765866</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.503141863575124</t>
+          <t>4.675207713739483</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.5162459849857237</t>
+          <t>2.396190685182994</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.6390282551100016</t>
+          <t>0.4017974285145941</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.317101598251191</t>
+          <t>1.4433756729740645</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.1556021239177248</t>
+          <t>1.2663928094193209</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.3481920751567063</t>
+          <t>0.2561291962766023</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.4811252243246881</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6088181617418025</t>
+          <t>0.6671871973200014</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.3261145766249456</t>
+          <t>2.9203706729510515</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.6671871973200014</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.5263717063927938</t>
+          <t>0.4172413558420799</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.46260176536422465</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.5610215015103615</t>
+          <t>2.9821425362611507</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2719744602617623</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.2087294186070423</t>
+          <t>0.7508020083518118</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3.282375264530999</t>
+          <t>1.9316725454976897</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5502664131004331</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.2193456688254154</t>
+          <t>0.2403749283845681</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4.890538940499048</t>
+          <t>6.858463096673472</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2193456688254154</t>
+          <t>0.2403749283845681</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.2247356701169805</t>
+          <t>4.7874548967035055</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.4330127018922193</t>
+          <t>0.47452679491836974</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.4149945466345482</t>
+          <t>0.8724174166762576</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.46260176536422465</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2681403689383677</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4.292681610796004</t>
+          <t>2.6989278060858366</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.679015253468748</t>
+          <t>1.2453034168225101</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.3655761147090257</t>
+          <t>0.40062488064094687</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.21106546823655348</t>
+          <t>0.23130088268211232</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20817079441390107</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2.6964049558080228</t>
+          <t>2.954916555311748</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.718279232392293</t>
+          <t>2.279331562015056</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>5.743482639701555</t>
+          <t>6.691972758794009</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0.9973890263167107</t>
+          <t>1.0202038140282639</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.6908290205761368</t>
+          <t>0.42591925624548765</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2623428576098803</t>
+          <t>0.20473463598726038</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3515013295691628</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.22066269207013126</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.21512087536466318</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6.426830330573097</t>
+          <t>4.429130646691519</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.21876276386671512</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.6735753140545633</t>
+          <t>0.7381527920952418</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1.1557788898005699</t>
+          <t>0.6638835190267827</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.26321032178492615</t>
+          <t>0.23257889246026192</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2.196088288351183</t>
+          <t>1.4457232653914054</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.6644842526669912</t>
+          <t>0.438445811247858</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1.8695827763244182</t>
+          <t>2.0488247083907414</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1.188918993259473</t>
+          <t>0.7883715819572137</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.8695827763244182</t>
+          <t>2.0488247083907414</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.785973915902711</t>
+          <t>1.1274653842174829</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.887025068524764</t>
+          <t>0.6513598233271973</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.5118065605926359</t>
+          <t>0.5608748328973255</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.47305049081120354</t>
+          <t>0.42317035995244384</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.3570070651590038</t>
+          <t>0.997731095591797</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.989608793177702</t>
+          <t>2.3101817120121506</t>
         </is>
       </c>
     </row>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>13.2925170597739</t>
+          <t>2.2230939340300315</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>12.6530615149711</t>
+          <t>3.268911700880242</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1.000156925783457</t>
+          <t>0.7310232548772905</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.5173673154913008</t>
+          <t>0.9830518219966571</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2.036607759056171</t>
+          <t>1.6945082754133947</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>9.69623307539505</t>
+          <t>6.0713967780659575</t>
         </is>
       </c>
     </row>
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>15.579637358825984</t>
+          <t>10.80969259189834</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8.966084708790737</t>
+          <t>5.721302955327908</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.9184473106799482</t>
+          <t>0.59071155900973</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3211174721922099</t>
+          <t>0.20759023408254906</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>9.27348348982756</t>
+          <t>6.0604444003409945</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>3.1229889020106594</t>
+          <t>1.9595332394002103</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.82254789450073</t>
+          <t>14.266356756853819</t>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.3013517229519873</t>
+          <t>5.745055486062067</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.282519476859592</t>
+          <t>1.2962962962962958</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>5.893002220472675</t>
+          <t>4.489380556676227</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>5.9227174245488055</t>
+          <t>4.134050607010536</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.781608461746061</t>
+          <t>2.4623776148158214</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7462872963152858</t>
+          <t>0.5064227911703552</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>6.758478296666723</t>
+          <t>4.747534767716421</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.1555928427814592</t>
+          <t>2.2918670355201414</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.311235520378759</t>
+          <t>1.174480490551852</t>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2.1585681630895994</t>
+          <t>0.34736287874891936</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.9849721851039159</t>
+          <t>1.0794041191831907</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20.602017250254093</t>
+          <t>15.480177925821788</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>4.5789669610743715</t>
+          <t>1.6556706795416432</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>28.26302458634277</t>
+          <t>19.275810826835666</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.45904573337771204</t>
+          <t>0.3759649647274439</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.6082189650444401</t>
+          <t>0.5537156623428492</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20.996134908580487</t>
+          <t>24.609908598226973</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>35.97004709631308</t>
+          <t>36.54918215559326</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>14.847475818184755</t>
+          <t>10.924791816993443</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>3.609308073530836</t>
+          <t>2.089470261021128</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2.26287067519835</t>
+          <t>2.113179947040661</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>10.529771200235288</t>
+          <t>15.397655341040087</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>5.855113127009801</t>
+          <t>3.7817166974121617</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>8.032662810981996</t>
+          <t>5.884127837114169</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.8861308614115835</t>
+          <t>0.68382207617559</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2636261319337816</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.3913942775725872</t>
+          <t>2.676861673144785</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.335001772784826</t>
+          <t>13.930358730374756</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2.3356602356669307</t>
+          <t>1.512762873730088</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>0.2048824708390741</t>
+          <t>0.2245251046848544</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.061593538994344</t>
+          <t>13.908053351786407</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>15.04087130796839</t>
+          <t>10.58440689171503</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.847398958715218</t>
+          <t>1.7860272674584443</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2.2787474149735845</t>
+          <t>1.4326413319116025</t>
         </is>
       </c>
     </row>
@@ -9747,12 +9747,12 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>9.721883794567436</t>
+          <t>1.9284010233929154</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>44.96002805470685</t>
+          <t>32.79162973418425</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>6.1315153710031325</t>
+          <t>4.685943036389515</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>12.99495732040063</t>
+          <t>15.078765633309137</t>
         </is>
       </c>
     </row>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>9.205749449016322</t>
+          <t>3.972788337536712</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2.11410235875266</t>
+          <t>1.827947129323935</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>14.489858550788583</t>
+          <t>16.84381272270938</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>14.6191359450953</t>
+          <t>10.37333103961539</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16.884055313590295</t>
+          <t>17.901185283044157</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,95 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>68.97855801046069</t>
+          <t>54.19605495627985</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>F2P_AGL_Anni_Goku</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>BU_TEQ_Majin_Duu</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>10.033838166927339</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>CLR_TEQ_SS3_Vegeta_DAIMA</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>47.01711890209773</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>DFLR_STR_SS4_Goku_DAIMA</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>29.089950076458823</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -727,12 +727,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.172995669443159</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.429130646691519</t>
+          <t>2.8805854944093134</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.7883715819572137</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>6.0604444003409945</t>
+          <t>4.463748691492391</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>19.275810826835666</t>
+          <t>7.464323762752208</t>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2.113179947040661</t>
+          <t>1.2661916395954158</t>
         </is>
       </c>
     </row>
@@ -9527,12 +9527,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>0.2245251046848544</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>10.58440689171503</t>
+          <t>2.9184246520820896</t>
         </is>
       </c>
     </row>
@@ -9747,12 +9747,12 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.9284010233929154</t>
+          <t>1.3800472991305295</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>47.01711890209773</t>
+          <t>41.89917280411432</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.6398810171913603</t>
+          <t>4.466472600671301</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.9075357712304686</t>
+          <t>3.3514384452412265</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.6762604704494857</t>
+          <t>4.533627908267188</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.2435953859484799</t>
+          <t>0.2930186431141339</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.6368128395644845</t>
+          <t>1.9773242136529865</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.481921045393251</t>
+          <t>7.873231988734098</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.3427806541190304</t>
+          <t>2.87077635711918</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.700577841853358</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.211417549523055</t>
+          <t>5.546551989335376</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.4043797654692343</t>
+          <t>4.179825235863951</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.078632835661727</t>
+          <t>1.2903544730889507</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.170984800424069</t>
+          <t>2.648668570148782</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.797557518585647</t>
+          <t>10.73436377849643</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.675207713739483</t>
+          <t>5.495760345972292</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.396190685182994</t>
+          <t>2.668906846887444</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.4017974285145941</t>
+          <t>0.49439595648473145</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.2561291962766023</t>
+          <t>0.29059505630253235</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.9203706729510515</t>
+          <t>3.1925462588229294</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4172413558420799</t>
+          <t>0.45809166177549265</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.9821425362611507</t>
+          <t>3.472241768507491</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.207536133524335</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.7508020083518118</t>
+          <t>0.9101466944066381</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.9316725454976897</t>
+          <t>2.34333895431961</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.858463096673472</t>
+          <t>6.240890448270542</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.7874548967035055</t>
+          <t>4.741089868924704</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8724174166762576</t>
+          <t>1.0657716097705539</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20216786241533133</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.6989278060858366</t>
+          <t>3.2914091077864027</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.2453034168225101</t>
+          <t>1.4428539891696008</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.279331562015056</t>
+          <t>2.404718281356613</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.691972758794009</t>
+          <t>6.518181497519635</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0202038140282639</t>
+          <t>1.046519975382438</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.42591925624548765</t>
+          <t>0.522543714566837</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.20473463598726038</t>
+          <t>0.24844164572693295</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2.8805854944093134</t>
+          <t>3.3843772020567826</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.6638835190267827</t>
+          <t>0.8185003114266763</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23257889246026192</t>
+          <t>0.24611833527861388</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.4457232653914054</t>
+          <t>1.7685615169063635</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.438445811247858</t>
+          <t>0.5217332099676044</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.1274653842174829</t>
+          <t>1.370468758781921</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6513598233271973</t>
+          <t>0.741480717074015</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.42317035995244384</t>
+          <t>0.44323690750919387</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.997731095591797</t>
+          <t>1.1775773668495604</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.3101817120121506</t>
+          <t>2.858447029403092</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.2230939340300315</t>
+          <t>2.7956152001785526</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>3.268911700880242</t>
+          <t>3.89120620767153</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.7310232548772905</t>
+          <t>0.8487182980058131</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>0.9830518219966571</t>
+          <t>1.198880550857906</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.6945082754133947</t>
+          <t>1.8678134329504443</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>6.0713967780659575</t>
+          <t>7.488548093605437</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10.80969259189834</t>
+          <t>10.416528970764688</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>5.721302955327908</t>
+          <t>7.052577717344332</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.59071155900973</t>
+          <t>0.7108595616645838</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.20759023408254906</t>
+          <t>0.2454945818494938</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>4.463748691492391</t>
+          <t>5.466893199908068</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>1.9595332394002103</t>
+          <t>2.420693899945471</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.266356756853819</t>
+          <t>14.741001879122123</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>5.745055486062067</t>
+          <t>7.428256983547752</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.489380556676227</t>
+          <t>4.988781765119781</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.134050607010536</t>
+          <t>4.978645170453265</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.4623776148158214</t>
+          <t>2.9796683607062313</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.5064227911703552</t>
+          <t>0.5855201419645022</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>4.747534767716421</t>
+          <t>5.667653656465009</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.2918670355201414</t>
+          <t>2.34306839091866</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.174480490551852</t>
+          <t>1.189998191904056</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.34736287874891936</t>
+          <t>0.4287999408239891</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>15.480177925821788</t>
+          <t>17.78980442939843</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.6556706795416432</t>
+          <t>1.0956631759465267</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.464323762752208</t>
+          <t>7.605289990076173</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.3759649647274439</t>
+          <t>0.4143285517885209</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5537156623428492</t>
+          <t>0.5758558905221705</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.609908598226973</t>
+          <t>24.050312549064614</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>36.54918215559326</t>
+          <t>38.24398183829709</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>10.924791816993443</t>
+          <t>12.811288081129234</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.089470261021128</t>
+          <t>2.5781436438955017</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.2661916395954158</t>
+          <t>1.4490655056065287</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>15.397655341040087</t>
+          <t>13.980914770199886</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>3.7817166974121617</t>
+          <t>4.658835642673839</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>5.884127837114169</t>
+          <t>6.640837979360156</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.68382207617559</t>
+          <t>0.789330583937073</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2636261319337816</t>
+          <t>0.31583743927483265</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.676861673144785</t>
+          <t>2.073264877282327</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>13.930358730374756</t>
+          <t>14.52114988284984</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.512762873730088</t>
+          <t>1.859303560038776</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>13.908053351786407</t>
+          <t>15.065554557977755</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2.9184246520820896</t>
+          <t>3.58932297121196</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.7860272674584443</t>
+          <t>2.198403480015154</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.4326413319116025</t>
+          <t>1.6981128015170555</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.3800472991305295</t>
+          <t>1.6954954178526496</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>32.79162973418425</t>
+          <t>39.35271158179698</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>4.685943036389515</t>
+          <t>5.388575141667327</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>15.078765633309137</t>
+          <t>14.327230195809541</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.972788337536712</t>
+          <t>4.873961476226842</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.827947129323935</t>
+          <t>1.926828384509411</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>16.84381272270938</t>
+          <t>16.549226962144566</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>10.37333103961539</t>
+          <t>12.14948586478016</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17.901185283044157</t>
+          <t>16.713985910408397</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>54.19605495627985</t>
+          <t>61.22361562241233</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>10.033838166927339</t>
+          <t>11.665354373515996</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>41.89917280411432</t>
+          <t>43.53643062634067</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>29.089950076458823</t>
+          <t>25.55847411871501</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D451"/>
+  <dimension ref="A1:D453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.466472600671301</t>
+          <t>4.335986394789488</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.3514384452412265</t>
+          <t>3.2525068636623162</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.533627908267188</t>
+          <t>4.155413499850166</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.2930186431141339</t>
+          <t>0.2725823346224779</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.9773242136529865</t>
+          <t>1.8593173017201778</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.9132272426127037</t>
+          <t>4.178180538907891</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>11.699264609326555</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.873231988734098</t>
+          <t>7.588388867817622</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.87077635711918</t>
+          <t>2.7814821335930997</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.700577841853358</t>
+          <t>1.6309106890615386</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.546551989335376</t>
+          <t>5.503877193649479</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4.179825235863951</t>
+          <t>3.979269727004306</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.2903544730889507</t>
+          <t>1.2319029536710504</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.648668570148782</t>
+          <t>2.5643018180098416</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.73436377849643</t>
+          <t>10.898517859641196</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.495760345972292</t>
+          <t>5.320646992086697</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.668906846887444</t>
+          <t>2.6333716928830007</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.49439595648473145</t>
+          <t>0.47069058329711055</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.29059505630253235</t>
+          <t>0.271387435183374</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.1925462588229294</t>
+          <t>3.159869690957997</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.45809166177549265</t>
+          <t>0.4373247080201048</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.472241768507491</t>
+          <t>3.267939286819135</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.207536133524335</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.9101466944066381</t>
+          <t>0.8756195981274076</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.34333895431961</t>
+          <t>2.139105321287732</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.240890448270542</t>
+          <t>6.426639096588916</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.741089868924704</t>
+          <t>4.772793512964207</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0657716097705539</t>
+          <t>1.021466708565978</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.20216786241533133</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.2914091077864027</t>
+          <t>3.1304109776005475</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.4428539891696008</t>
+          <t>1.3677559686686833</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.404718281356613</t>
+          <t>2.301139754054248</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.518181497519635</t>
+          <t>6.582574911775559</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.046519975382438</t>
+          <t>1.0424362791785597</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.522543714566837</t>
+          <t>0.49309019015913486</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.24844164572693295</t>
+          <t>0.2364294475392299</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.3843772020567826</t>
+          <t>3.2733655601978384</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.8185003114266763</t>
+          <t>0.7661851039380605</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.24611833527861388</t>
+          <t>0.23290944917536932</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.7685615169063635</t>
+          <t>1.6994497516649067</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.5217332099676044</t>
+          <t>0.4849080628946352</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.370468758781921</t>
+          <t>1.3103418759854046</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.741480717074015</t>
+          <t>0.7041083795382632</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.44323690750919387</t>
+          <t>0.4192663557149131</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.1775773668495604</t>
+          <t>1.1105613315730474</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.858447029403092</t>
+          <t>2.694468314446139</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.7956152001785526</t>
+          <t>2.6480084214617765</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>3.89120620767153</t>
+          <t>3.7139871607751687</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.8487182980058131</t>
+          <t>0.7988088431038749</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.198880550857906</t>
+          <t>1.13449276318876</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.8678134329504443</t>
+          <t>1.7619721874735186</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>7.488548093605437</t>
+          <t>7.003369708544152</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10.416528970764688</t>
+          <t>10.59968758165595</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>7.052577717344332</t>
+          <t>6.5691358836561085</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.7108595616645838</t>
+          <t>0.656851793453701</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.2454945818494938</t>
+          <t>0.22749081762933798</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>5.466893199908068</t>
+          <t>5.156403361104797</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.420693899945471</t>
+          <t>2.254147144685991</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.741001879122123</t>
+          <t>14.77832883357677</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>7.428256983547752</t>
+          <t>6.9876544180696225</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.988781765119781</t>
+          <t>4.760320777461955</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.978645170453265</t>
+          <t>4.666634567560434</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.9796683607062313</t>
+          <t>2.8441451327840603</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.5855201419645022</t>
+          <t>0.5542491378241041</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.667653656465009</t>
+          <t>5.476959353150491</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.34306839091866</t>
+          <t>2.3343989628012096</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.189998191904056</t>
+          <t>1.131614574404482</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.4287999408239891</t>
+          <t>0.40468244386229024</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>17.78980442939843</t>
+          <t>17.44453855714124</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.0956631759465267</t>
+          <t>1.1495492483511356</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.605289990076173</t>
+          <t>7.640450179743681</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.4143285517885209</t>
+          <t>0.387077844088741</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5758558905221705</t>
+          <t>0.5436012846936897</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.050312549064614</t>
+          <t>24.409457440848495</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>38.24398183829709</t>
+          <t>38.25848392134649</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>12.811288081129234</t>
+          <t>12.356974864695317</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2.5781436438955017</t>
+          <t>2.4121905058527426</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.4490655056065287</t>
+          <t>1.354927873978903</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>13.980914770199886</t>
+          <t>14.382732278920175</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>4.658835642673839</t>
+          <t>4.277328449852669</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.640837979360156</t>
+          <t>6.34570207831217</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.789330583937073</t>
+          <t>0.7413657641009719</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.31583743927483265</t>
+          <t>0.2992823593866758</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.073264877282327</t>
+          <t>2.183018170077162</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.52114988284984</t>
+          <t>14.548503690918276</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.859303560038776</t>
+          <t>1.6986383527685844</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.065554557977755</t>
+          <t>14.892567083238248</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.58932297121196</t>
+          <t>3.3858853188076594</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.198403480015154</t>
+          <t>2.028521556875347</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.6981128015170555</t>
+          <t>1.5909448933483947</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.6954954178526496</t>
+          <t>1.6053921808590204</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>39.35271158179698</t>
+          <t>37.34305141431005</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.388575141667327</t>
+          <t>5.0917000583095975</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>14.327230195809541</t>
+          <t>14.768192092911733</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>4.873961476226842</t>
+          <t>4.599542732116043</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.926828384509411</t>
+          <t>1.796061368438495</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>16.549226962144566</t>
+          <t>16.779867070307198</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>12.14948586478016</t>
+          <t>11.49329957770675</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16.713985910408397</t>
+          <t>17.17797956653819</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>61.22361562241233</t>
+          <t>60.12097278147493</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>11.665354373515996</t>
+          <t>11.234336178471729</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>43.53643062634067</t>
+          <t>34.58882202323496</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,51 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>25.55847411871501</t>
+          <t>20.581863236903175</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>LR_PHY_SS_Sword_Trunks</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>12.441243178866523</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Majin_Kuu</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D453"/>
+  <dimension ref="A1:D456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.6189084256432587</t>
+          <t>4.30982261817819</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.935161679303848</t>
+          <t>3.347846263839125</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.492925085325443</t>
+          <t>4.237128636961418</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.2433723058740319</t>
+          <t>0.2869830875193282</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.6056230483694518</t>
+          <t>1.915879972691015</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.749738047705847</t>
+          <t>4.3090482917999315</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.467187820820207</t>
+          <t>2.2892604207703915</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.8181299415073662</t>
+          <t>2.184619160501915</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.258848217992341</t>
+          <t>2.697676941163399</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6350296745026545</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.21524632971217</t>
+          <t>5.528824232904632</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.2003028446175654</t>
+          <t>3.800229258082414</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.03463105737264</t>
+          <t>1.2044497537344423</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.18537054968613</t>
+          <t>2.592566705794681</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.821867344147087</t>
+          <t>10.789091190132895</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.685478722667127</t>
+          <t>5.411044592162347</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.394912618383143</t>
+          <t>2.654217567956063</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.3957657798228859</t>
+          <t>0.47555922500819997</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.2534869348722403</t>
+          <t>0.28066083054268276</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.9495516612093695</t>
+          <t>3.211803060341289</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.41145081970204783</t>
+          <t>0.44194241223509834</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.650094784396126</t>
+          <t>2.9806476029400923</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.20101105163865388</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.7604495023841481</t>
+          <t>0.9021480193585703</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.873422833727022</t>
+          <t>2.24792284293784</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>7.036894630079938</t>
+          <t>6.502620730847667</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.755079979698225</t>
+          <t>4.7546985407939495</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.8810727817673423</t>
+          <t>1.039795768584446</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.735781942450912</t>
+          <t>3.232516750339026</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.180205105536102</t>
+          <t>1.3328620571762622</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.219168256749705</t>
+          <t>2.285829654121476</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.719692008053329</t>
+          <t>6.548220703254913</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0119584012834508</t>
+          <t>1.056370441484205</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.43065669104558624</t>
+          <t>0.5133843197934596</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2047768956777576</t>
+          <t>0.2417261700627087</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2.904887681418238</t>
+          <t>3.3602643779963657</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.6331031443487983</t>
+          <t>0.7672426521811196</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.22921519719153993</t>
+          <t>0.23776948608738446</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.4681268061528976</t>
+          <t>1.74510183889338</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.4479233203297479</t>
+          <t>0.523523433385809</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.1403472547818734</t>
+          <t>1.3404492311628557</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6430214654581548</t>
+          <t>0.7105922285285162</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.41510463292129124</t>
+          <t>0.4254590798801524</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.9888949955580807</t>
+          <t>1.125419323875216</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.3130852266200304</t>
+          <t>2.8257499431752393</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.326213208977097</t>
+          <t>2.745896588911024</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.0687089394868927</t>
+          <t>1.281449273752191</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.7127017977139133</t>
+          <t>0.801754150987608</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.2461457974838952</t>
+          <t>1.31393530461445</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.6259409549620552</t>
+          <t>1.7510670673769635</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>6.046619564236102</t>
+          <t>7.229276335711776</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10.721274547450335</t>
+          <t>10.33674347651268</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.5745703450702223</t>
+          <t>0.6769461640028774</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.20089330998291954</t>
+          <t>0.23266742317394762</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>4.315767929725151</t>
+          <t>5.162700461837169</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>1.9774759936733464</t>
+          <t>2.3840079659203894</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.370096394889025</t>
+          <t>14.956589555022411</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>5.470742320493845</t>
+          <t>6.405049459017242</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.434445408046249</t>
+          <t>4.789564589755713</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.055538562667838</t>
+          <t>4.741406491520565</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.4719518495059702</t>
+          <t>2.9432453123150175</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.5126524395391558</t>
+          <t>0.570482488235323</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>4.70871445926052</t>
+          <t>5.562552750224889</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.276390457106295</t>
+          <t>2.350066513259172</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.160186562987866</t>
+          <t>1.167512756851789</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.34580027823312953</t>
+          <t>0.41646147842361003</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>15.722231523410581</t>
+          <t>17.82541396792793</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.6305999156221986</t>
+          <t>1.1251831607925027</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.529434397016729</t>
+          <t>7.726280528542965</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.366467590914896</t>
+          <t>0.3927103495842241</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5379814653016577</t>
+          <t>0.551380716091207</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.635553194605855</t>
+          <t>24.23625629002064</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>28.933492787274403</t>
+          <t>33.510157004355</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.3754571055697669</t>
+          <t>1.6786570626328785</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.203739612436104</t>
+          <t>1.29726117645653</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>15.08507428810308</t>
+          <t>13.779317755205625</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>3.7382002161607435</t>
+          <t>4.475382539221986</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>5.83724611124511</t>
+          <t>6.391963162153277</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.6637039662338919</t>
+          <t>0.7457077900390243</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2547082762548154</t>
+          <t>0.2971321431385361</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.6216562666622707</t>
+          <t>2.086961482338836</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.082222665876841</t>
+          <t>14.709392218948096</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.4484441630987184</t>
+          <t>1.7400769528151092</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.042980039558373</t>
+          <t>15.093580989180651</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2.894153070303096</t>
+          <t>3.4934163623209393</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.7665789363048745</t>
+          <t>2.1309610618887755</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.3943182301751031</t>
+          <t>1.615262749127865</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.393832548035311</t>
+          <t>1.6589590783032904</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>32.57537779901678</t>
+          <t>38.42139402188072</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>4.525917284752323</t>
+          <t>5.184064748411103</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>15.199652986887967</t>
+          <t>14.340037224514765</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.9152160841542365</t>
+          <t>4.66831932921339</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.7997417864253242</t>
+          <t>1.903145031492121</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>16.912469623791957</t>
+          <t>16.85710178996068</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>9.768363973311201</t>
+          <t>11.18917450967932</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17.759923925012153</t>
+          <t>16.845507121255295</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>53.38652648099045</t>
+          <t>59.7259804551319</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>10.249531281582659</t>
+          <t>11.413042588328892</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>35.03947874395172</t>
+          <t>35.36957375262423</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>21.810157205100126</t>
+          <t>19.38866486693088</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>11.724064056963833</t>
+          <t>12.438408696593985</t>
         </is>
       </c>
     </row>
@@ -10389,6 +10389,72 @@
         </is>
       </c>
       <c r="D453" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>F2P_PHY_Tamagami_3</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>F2P_TEQ_Tamagami_2</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>F2P_AGL_Tamagami_1</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D456"/>
+  <dimension ref="A1:D460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.30982261817819</t>
+          <t>4.28755028044265</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.347846263839125</t>
+          <t>3.23867066363952</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.237128636961418</t>
+          <t>3.7941030743331177</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.2869830875193282</t>
+          <t>0.25803028104965187</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.915879972691015</t>
+          <t>1.825673014980635</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.3090482917999315</t>
+          <t>4.69754621821748</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.2892604207703915</t>
+          <t>9.099419200086134</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.184619160501915</t>
+          <t>2.1222673789034645</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.697676941163399</t>
+          <t>2.3019642961449804</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6350296745026545</t>
+          <t>1.5596898075731822</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.528824232904632</t>
+          <t>5.569624501252605</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.800229258082414</t>
+          <t>3.8105502863629974</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.2044497537344423</t>
+          <t>1.165865245830375</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.592566705794681</t>
+          <t>2.5813499247359495</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.789091190132895</t>
+          <t>11.131526226866951</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.7334031858765866</t>
+          <t>9.755494402027226</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.411044592162347</t>
+          <t>5.333842942247284</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.654217567956063</t>
+          <t>2.6714441933556685</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.47555922500819997</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.28066083054268276</t>
+          <t>0.2471842372372613</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.211803060341289</t>
+          <t>3.200203135008799</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.44194241223509834</t>
+          <t>0.4199633666376798</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.9806476029400923</t>
+          <t>2.8301279313505274</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.20101105163865388</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.9021480193585703</t>
+          <t>0.887459202221322</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.24792284293784</t>
+          <t>1.9732509734463628</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.502620730847667</t>
+          <t>6.5342470249340705</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.7546985407939495</t>
+          <t>4.786881156613128</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.039795768584446</t>
+          <t>1.017050323776138</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.232516750339026</t>
+          <t>3.026164078380308</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3328620571762622</t>
+          <t>1.258366014764205</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.285829654121476</t>
+          <t>2.193954426258119</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.548220703254913</t>
+          <t>6.62007289158727</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.056370441484205</t>
+          <t>1.021571957992336</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.5133843197934596</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2417261700627087</t>
+          <t>0.23376534078408717</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.3602643779963657</t>
+          <t>3.2588736371990237</t>
         </is>
       </c>
     </row>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.7381527920952418</t>
+          <t>0.24909239792527116</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.7672426521811196</t>
+          <t>0.7365781034955258</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23776948608738446</t>
+          <t>0.21397956056319323</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.74510183889338</t>
+          <t>1.6931976473612917</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.523523433385809</t>
+          <t>0.46703934523814006</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3404492311628557</t>
+          <t>1.311957233125776</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7105922285285162</t>
+          <t>0.690516873543308</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.4254590798801524</t>
+          <t>0.38849075935245597</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.125419323875216</t>
+          <t>1.0609466799148697</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.8257499431752393</t>
+          <t>2.586290116982299</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.745896588911024</t>
+          <t>2.5903373006673425</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.281449273752191</t>
+          <t>1.4637885642892794</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.801754150987608</t>
+          <t>0.7472078987193504</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.31393530461445</t>
+          <t>1.0166121967654327</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.7510670673769635</t>
+          <t>1.6007638354151146</t>
         </is>
       </c>
     </row>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>7.229276335711776</t>
+          <t>11.756464036470842</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10.33674347651268</t>
+          <t>10.789891098437124</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6769461640028774</t>
+          <t>0.6263326217526188</t>
         </is>
       </c>
     </row>
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.23266742317394762</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>5.162700461837169</t>
+          <t>4.747161788227508</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.3840079659203894</t>
+          <t>2.1362568690624997</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.956589555022411</t>
+          <t>15.029954829926254</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>6.405049459017242</t>
+          <t>6.311048972625623</t>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>4.789564589755713</t>
+          <t>1.1375846640129748</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.741406491520565</t>
+          <t>4.416019046183307</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.9432453123150175</t>
+          <t>2.8032849122671983</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.570482488235323</t>
+          <t>0.5440008877531799</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.562552750224889</t>
+          <t>5.418856670201446</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.350066513259172</t>
+          <t>2.3507265321933843</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.167512756851789</t>
+          <t>1.614436412577731</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.41646147842361003</t>
+          <t>0.40006593917028965</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>17.82541396792793</t>
+          <t>17.904350163030273</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.1251831607925027</t>
+          <t>1.1689395545288193</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.726280528542965</t>
+          <t>7.750529398587055</t>
         </is>
       </c>
     </row>
@@ -8713,12 +8713,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.3927103495842241</t>
+          <t>0.5708613748923799</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.551380716091207</t>
+          <t>0.5010732042623538</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.23625629002064</t>
+          <t>24.89183805428351</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>33.510157004355</t>
+          <t>18.563091902572403</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.6786570626328785</t>
+          <t>1.5622062754168293</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.29726117645653</t>
+          <t>1.2587634343869318</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>13.779317755205625</t>
+          <t>14.363465644931807</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>4.475382539221986</t>
+          <t>4.020939838343255</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.391963162153277</t>
+          <t>6.239121339594775</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7457077900390243</t>
+          <t>0.7197825109570961</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2971321431385361</t>
+          <t>0.2867382291064562</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.086961482338836</t>
+          <t>2.258221930320474</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.709392218948096</t>
+          <t>14.791545502479098</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.7400769528151092</t>
+          <t>1.549425182390425</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>15.093580989180651</t>
+          <t>14.932224285756327</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.4934163623209393</t>
+          <t>3.2754877884620015</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2.1309610618887755</t>
+          <t>1.901263463652948</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.615262749127865</t>
+          <t>1.5322314294068957</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.6589590783032904</t>
+          <t>1.5955682060351801</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>38.42139402188072</t>
+          <t>36.30101614655761</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.184064748411103</t>
+          <t>5.043588295419466</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>14.340037224514765</t>
+          <t>15.020261512899685</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>4.66831932921339</t>
+          <t>4.470701308412828</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.903145031492121</t>
+          <t>1.6374786555429828</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>16.85710178996068</t>
+          <t>17.12935671532616</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>11.18917450967932</t>
+          <t>10.29851455434736</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>16.845507121255295</t>
+          <t>17.2520602584068</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>59.7259804551319</t>
+          <t>59.86137130224857</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>11.413042588328892</t>
+          <t>11.201634982349042</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>35.36957375262423</t>
+          <t>34.81275163420027</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>19.38866486693088</t>
+          <t>20.558452271595513</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>12.438408696593985</t>
+          <t>12.643766929864436</t>
         </is>
       </c>
     </row>
@@ -10457,6 +10457,94 @@
       <c r="D456" t="inlineStr">
         <is>
           <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>DF_INT_SSGSS_Vegeta</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>7.197052361782508</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>BU_AGL_Ledgic</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>13.15035559753548</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>DFLR_INT_SS4_Vegeta_Goku</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>5.546617136646006</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>CLR_PHY_UI_Goku_SSGSSE_Vegeta</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>3.6166851286845945</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.28755028044265</t>
+          <t>4.29364952903002</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.23867066363952</t>
+          <t>3.232798550619845</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.7941030743331177</t>
+          <t>3.745445956953797</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.25803028104965187</t>
+          <t>0.25613261219263656</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.825673014980635</t>
+          <t>1.8143433487562226</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.69754621821748</t>
+          <t>4.710144641812332</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.099419200086134</t>
+          <t>9.138843933514176</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.1222673789034645</t>
+          <t>2.1158760380931096</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.3019642961449804</t>
+          <t>2.30176585974459</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.5596898075731822</t>
+          <t>1.5539054958266156</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.569624501252605</t>
+          <t>5.5701248348182935</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.8105502863629974</t>
+          <t>3.7981585250229166</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.165865245830375</t>
+          <t>1.1552226421240246</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.5813499247359495</t>
+          <t>2.585602578025952</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.131526226866951</t>
+          <t>11.143966616693568</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9.755494402027226</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.333842942247284</t>
+          <t>5.335904733040408</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.6714441933556685</t>
+          <t>2.680161915043115</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.2471842372372613</t>
+          <t>0.2438711324665859</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.200203135008799</t>
+          <t>3.2062715862488673</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4199633666376798</t>
+          <t>0.41757943901815286</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.8301279313505274</t>
+          <t>2.815346531589526</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.887459202221322</t>
+          <t>0.8880085074636312</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.9732509734463628</t>
+          <t>1.9503961304106179</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.5342470249340705</t>
+          <t>6.5424563703360095</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.786881156613128</t>
+          <t>4.783953866381949</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.017050323776138</t>
+          <t>1.0176578665872087</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.026164078380308</t>
+          <t>3.0143201995008795</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.258366014764205</t>
+          <t>1.2556776184026508</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.193954426258119</t>
+          <t>2.177006704473293</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.62007289158727</t>
+          <t>6.6199991726165175</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.021571957992336</t>
+          <t>1.0189014927825397</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.23376534078408717</t>
+          <t>0.23314798321569175</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.2588736371990237</t>
+          <t>3.2576516675367766</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.24909239792527116</t>
+          <t>0.24696987795005387</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.7365781034955258</t>
+          <t>0.7308292484897656</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.21397956056319323</t>
+          <t>0.21149243357899922</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.6931976473612917</t>
+          <t>1.6877407961670667</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.46703934523814006</t>
+          <t>0.46187102956090964</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.311957233125776</t>
+          <t>1.311535368980942</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.690516873543308</t>
+          <t>0.686967028922123</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.38849075935245597</t>
+          <t>0.38473336911130857</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.0609466799148697</t>
+          <t>1.0523725185555146</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.586290116982299</t>
+          <t>2.5803579441555082</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.5903373006673425</t>
+          <t>2.5771775656909615</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.4637885642892794</t>
+          <t>1.4615733279690701</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.7472078987193504</t>
+          <t>0.7428343389700636</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.0166121967654327</t>
+          <t>1.014346541753051</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.6007638354151146</t>
+          <t>1.5847423417847073</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>11.756464036470842</t>
+          <t>11.731163414591418</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10.789891098437124</t>
+          <t>10.804316843179883</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6263326217526188</t>
+          <t>0.6205233939140311</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>4.747161788227508</t>
+          <t>4.7424222811569905</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.1362568690624997</t>
+          <t>2.131507177121634</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>15.029954829926254</t>
+          <t>15.066633340551517</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>6.311048972625623</t>
+          <t>6.289151668912931</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.1375846640129748</t>
+          <t>1.13504987286061</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.416019046183307</t>
+          <t>4.401799140891315</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.8032849122671983</t>
+          <t>2.7988003766854916</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.5440008877531799</t>
+          <t>0.5415909117961011</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.418856670201446</t>
+          <t>5.4105150240164726</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.3507265321933843</t>
+          <t>2.347467461894631</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.614436412577731</t>
+          <t>1.596513312364233</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.40006593917028965</t>
+          <t>0.39891350460971964</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>17.904350163030273</t>
+          <t>17.92935520260039</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.1689395545288193</t>
+          <t>1.1634229019816331</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.750529398587055</t>
+          <t>7.760123652344383</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.5708613748923799</t>
+          <t>0.5670171148717793</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.5010732042623538</t>
+          <t>0.4964463018982628</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.89183805428351</t>
+          <t>24.981352208787552</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>18.563091902572403</t>
+          <t>18.617745285087672</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.5622062754168293</t>
+          <t>1.5492970903976122</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.2587634343869318</t>
+          <t>1.250428670543292</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>14.363465644931807</t>
+          <t>14.388644602049014</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>4.020939838343255</t>
+          <t>3.988110952172838</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.239121339594775</t>
+          <t>6.216316434323618</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7197825109570961</t>
+          <t>0.7154274763177657</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2867382291064562</t>
+          <t>0.2850992994190502</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.258221930320474</t>
+          <t>2.2616332536734234</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.791545502479098</t>
+          <t>14.808653274076555</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.549425182390425</t>
+          <t>1.5343526683203126</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.932224285756327</t>
+          <t>14.933788211735752</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.2754877884620015</t>
+          <t>3.25799418229794</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.901263463652948</t>
+          <t>1.8883920238799379</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.5322314294068957</t>
+          <t>1.5224153521086525</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.5955682060351801</t>
+          <t>1.5936928278395097</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>36.30101614655761</t>
+          <t>36.18848923617806</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.043588295419466</t>
+          <t>5.015209191021998</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>15.020261512899685</t>
+          <t>15.072904163294368</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>4.470701308412828</t>
+          <t>4.4524821512956105</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.6374786555429828</t>
+          <t>1.613274279952369</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>17.12935671532616</t>
+          <t>17.186281082432778</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>10.29851455434736</t>
+          <t>10.210561339246519</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17.2520602584068</t>
+          <t>17.267547864281546</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>59.86137130224857</t>
+          <t>59.89929155574097</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>11.201634982349042</t>
+          <t>11.184215587816816</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>34.81275163420027</t>
+          <t>34.7935821145629</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20.558452271595513</t>
+          <t>20.645688799158904</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>12.643766929864436</t>
+          <t>12.650163530010948</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>7.197052361782508</t>
+          <t>7.2112181839308915</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>13.15035559753548</t>
+          <t>13.09907798524964</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>5.546617136646006</t>
+          <t>5.5759451809356335</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>3.6166851286845945</t>
+          <t>3.6123969253607697</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.29364952903002</t>
+          <t>4.561864422667938</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.232798550619845</t>
+          <t>3.3495175250452287</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.745445956953797</t>
+          <t>4.125742607422568</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.25613261219263656</t>
+          <t>0.23330442559462075</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.8143433487562226</t>
+          <t>1.7635048055488105</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.710144641812332</t>
+          <t>4.757974967749212</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.138843933514176</t>
+          <t>9.704570904924646</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.1158760380931096</t>
+          <t>2.1549230504458867</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.30176585974459</t>
+          <t>2.751451117712561</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.5539054958266156</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.5701248348182935</t>
+          <t>4.935064086518815</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.1634158882780214</t>
+          <t>26.00619731777872</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.7981585250229166</t>
+          <t>3.2360204665631223</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.1552226421240246</t>
+          <t>1.2532056111648242</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.585602578025952</t>
+          <t>2.4783633286333</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.143966616693568</t>
+          <t>10.867953946175845</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.335904733040408</t>
+          <t>4.745662496321012</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.680161915043115</t>
+          <t>2.315591121646609</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.2438711324665859</t>
+          <t>0.20725285275621178</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.2062715862488673</t>
+          <t>3.5596494432487944</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.41757943901815286</t>
+          <t>0.42990482948209113</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.815346531589526</t>
+          <t>3.433038680920488</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.8880085074636312</t>
+          <t>0.7659514588384404</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.9503961304106179</t>
+          <t>1.8790866583375148</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.5424563703360095</t>
+          <t>6.569891830119815</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4.783953866381949</t>
+          <t>5.578758764054655</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0176578665872087</t>
+          <t>1.0162682543310082</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.0143201995008795</t>
+          <t>2.8655422103526167</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.2556776184026508</t>
+          <t>1.3596930429847949</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.177006704473293</t>
+          <t>2.116006476834581</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.6199991726165175</t>
+          <t>6.9033494839548055</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0189014927825397</t>
+          <t>1.0374495814152098</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.23314798321569175</t>
+          <t>0.23140368461643757</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.2576516675367766</t>
+          <t>2.8804971704159783</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.24696987795005387</t>
+          <t>0.24745464154038443</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.7308292484897656</t>
+          <t>0.7053112780736239</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.21149243357899922</t>
+          <t>0.23168741312154345</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.6877407961670667</t>
+          <t>1.6719983192029975</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.46187102956090964</t>
+          <t>0.2663086274561781</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.311535368980942</t>
+          <t>1.2853857097142187</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.686967028922123</t>
+          <t>0.7019292171330971</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.38473336911130857</t>
+          <t>0.3831956781137306</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1.0523725185555146</t>
+          <t>0.9954061048607986</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.5803579441555082</t>
+          <t>2.808708727810389</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.5771775656909615</t>
+          <t>2.474444245288364</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.4615733279690701</t>
+          <t>1.3089894332946397</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.7428343389700636</t>
+          <t>0.7177916516520859</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.014346541753051</t>
+          <t>1.3513883360048844</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.5847423417847073</t>
+          <t>1.4116239336802452</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>11.731163414591418</t>
+          <t>9.979431637446169</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10.804316843179883</t>
+          <t>11.194766176909821</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6205233939140311</t>
+          <t>0.6085195921788156</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>4.7424222811569905</t>
+          <t>4.19416268230361</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.131507177121634</t>
+          <t>1.8702781239277328</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>15.066633340551517</t>
+          <t>14.8167467953039</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>6.289151668912931</t>
+          <t>6.251543379053039</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.13504987286061</t>
+          <t>1.1205599301908933</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.401799140891315</t>
+          <t>3.89674788644686</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.7988003766854916</t>
+          <t>2.660130739974221</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.5415909117961011</t>
+          <t>0.5424134788571333</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.4105150240164726</t>
+          <t>5.037513830125892</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.347467461894631</t>
+          <t>2.3151097357718697</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.596513312364233</t>
+          <t>1.6406575283910563</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.39891350460971964</t>
+          <t>0.38577028166568006</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>17.92935520260039</t>
+          <t>16.537748233254256</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.1634229019816331</t>
+          <t>1.2059468938078624</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.760123652344383</t>
+          <t>7.8046996422802195</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.5670171148717793</t>
+          <t>0.51077941261592</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.4964463018982628</t>
+          <t>0.47500719982930867</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>24.981352208787552</t>
+          <t>25.265372602417436</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>18.617745285087672</t>
+          <t>18.25087578605087</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.5492970903976122</t>
+          <t>1.448524044878821</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.250428670543292</t>
+          <t>1.8046089345931051</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>14.388644602049014</t>
+          <t>14.217431826619702</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>3.988110952172838</t>
+          <t>3.428423094800932</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.216316434323618</t>
+          <t>5.80661820269925</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7154274763177657</t>
+          <t>0.7141837538991003</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2850992994190502</t>
+          <t>0.32194833450314864</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.2616332536734234</t>
+          <t>2.3667078464052054</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.808653274076555</t>
+          <t>14.341076914726038</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.5343526683203126</t>
+          <t>1.3619164018722154</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.933788211735752</t>
+          <t>14.18259216769193</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.25799418229794</t>
+          <t>3.557052849125901</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.8883920238799379</t>
+          <t>1.6531858427079116</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.5224153521086525</t>
+          <t>1.7514576787626528</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.5936928278395097</t>
+          <t>1.5830224718401702</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>36.18848923617806</t>
+          <t>32.99809491619958</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>5.015209191021998</t>
+          <t>3.1380746771838766</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>15.072904163294368</t>
+          <t>13.311051066960985</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>4.4524821512956105</t>
+          <t>4.440319261094509</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.613274279952369</t>
+          <t>1.4702237119242</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>17.186281082432778</t>
+          <t>16.99387707780688</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>10.210561339246519</t>
+          <t>10.69407975310926</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17.267547864281546</t>
+          <t>17.53712498377474</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>59.89929155574097</t>
+          <t>11.960725415981564</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>11.184215587816816</t>
+          <t>12.27704591705109</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>34.7935821145629</t>
+          <t>31.671791438116617</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20.645688799158904</t>
+          <t>20.923236610192134</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>12.650163530010948</t>
+          <t>11.293893714861307</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>7.2112181839308915</t>
+          <t>7.157093707623624</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>13.09907798524964</t>
+          <t>12.28510953674136</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>5.5759451809356335</t>
+          <t>6.484132321458162</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>3.6123969253607697</t>
+          <t>3.2013388276932635</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.561864422667938</t>
+          <t>4.561874803446679</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.3495175250452287</t>
+          <t>3.349516295759591</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.125742607422568</t>
+          <t>4.125735874072862</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.23330442559462075</t>
+          <t>0.23330451480409561</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.7635048055488105</t>
+          <t>1.7635044785796359</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.757974967749212</t>
+          <t>4.7579706660211345</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.704570904924646</t>
+          <t>9.70456486137585</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.1549230504458867</t>
+          <t>2.1549214175724964</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.751451117712561</t>
+          <t>2.7514558844556287</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.935064086518815</t>
+          <t>4.935062597404264</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26.00619731777872</t>
+          <t>26.005440075594578</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.2360204665631223</t>
+          <t>3.236025891788948</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.2532056111648242</t>
+          <t>1.2532054412765448</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.4783633286333</t>
+          <t>2.4783679982596105</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.867953946175845</t>
+          <t>10.86795080049255</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.745662496321012</t>
+          <t>4.7456622789931115</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.315591121646609</t>
+          <t>2.3155924810815662</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.20725285275621178</t>
+          <t>0.20725280303512966</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.5596494432487944</t>
+          <t>3.5596496731201133</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.42990482948209113</t>
+          <t>0.4299054558115628</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.433038680920488</t>
+          <t>3.4330405838692153</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.7659514588384404</t>
+          <t>0.7659527384256924</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.8790866583375148</t>
+          <t>1.8790821704276746</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.569891830119815</t>
+          <t>6.5698904455131</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5.578758764054655</t>
+          <t>5.5787550460758295</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.0162682543310082</t>
+          <t>1.016270570767943</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.8655422103526167</t>
+          <t>2.865548789854242</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3596930429847949</t>
+          <t>1.3596951261571522</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.116006476834581</t>
+          <t>2.116008986673664</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.9033494839548055</t>
+          <t>6.903345296042076</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0374495814152098</t>
+          <t>1.0374482733690513</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.23140368461643757</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2.8804971704159783</t>
+          <t>2.880495804666179</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.24745464154038443</t>
+          <t>0.2474549336629778</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.7053112780736239</t>
+          <t>0.7053107045498049</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.23168741312154345</t>
+          <t>0.2316873613693221</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.6719983192029975</t>
+          <t>1.6719994689466546</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.2663086274561781</t>
+          <t>0.26630856169310224</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.2853857097142187</t>
+          <t>1.2853885922378716</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7019292171330971</t>
+          <t>0.7019306543297628</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.3831956781137306</t>
+          <t>0.3831959186919521</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.9954061048607986</t>
+          <t>0.9954072771682729</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.808708727810389</t>
+          <t>2.808706322501891</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.474444245288364</t>
+          <t>2.474446276206508</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.3089894332946397</t>
+          <t>1.308990127940639</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.7177916516520859</t>
+          <t>0.7177920521843664</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.3513883360048844</t>
+          <t>1.3513916924472502</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.4116239336802452</t>
+          <t>1.411623985077078</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>9.979431637446169</t>
+          <t>9.97943383143</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>11.194766176909821</t>
+          <t>11.194760647123474</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6085195921788156</t>
+          <t>0.6085197248416121</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>4.19416268230361</t>
+          <t>4.194170498387171</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>1.8702781239277328</t>
+          <t>1.8702760455295984</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.8167467953039</t>
+          <t>14.816745035209017</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>6.251543379053039</t>
+          <t>6.251553119363984</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.1205599301908933</t>
+          <t>1.1205621110531476</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>3.89674788644686</t>
+          <t>3.8967528559828124</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.660130739974221</t>
+          <t>2.660128626594638</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.5424134788571333</t>
+          <t>0.542414122088259</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.037513830125892</t>
+          <t>5.037511645580189</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.3151097357718697</t>
+          <t>2.315108383507564</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.6406575283910563</t>
+          <t>1.6406561636537222</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.38577028166568006</t>
+          <t>0.385770618301029</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>16.537748233254256</t>
+          <t>16.53776063871775</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.2059468938078624</t>
+          <t>1.2059440455812904</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.8046996422802195</t>
+          <t>7.804694556742412</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.51077941261592</t>
+          <t>0.510779992989852</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.47500719982930867</t>
+          <t>0.4750073270494181</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>25.265372602417436</t>
+          <t>25.265370352351113</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>18.25087578605087</t>
+          <t>18.25087464958201</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.448524044878821</t>
+          <t>1.4485221101801828</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.8046089345931051</t>
+          <t>1.804611463017265</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>14.217431826619702</t>
+          <t>14.217421601730946</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>3.428423094800932</t>
+          <t>3.4284195304460887</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>5.80661820269925</t>
+          <t>5.806629556000286</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7141837538991003</t>
+          <t>0.7141846717554521</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.32194833450314864</t>
+          <t>0.32194908369338293</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.3667078464052054</t>
+          <t>2.3667037844845993</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.341076914726038</t>
+          <t>14.341068070488006</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.3619164018722154</t>
+          <t>1.3619140094085909</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.18259216769193</t>
+          <t>14.182576778246428</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.557052849125901</t>
+          <t>3.5570544179123</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.6531858427079116</t>
+          <t>1.6531843568582143</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.7514576787626528</t>
+          <t>1.7514592208696584</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.5830224718401702</t>
+          <t>1.5830252018758397</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>32.99809491619958</t>
+          <t>32.99807866238464</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.1380746771838766</t>
+          <t>3.1380801550132684</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>13.311051066960985</t>
+          <t>13.31105797972377</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>4.440319261094509</t>
+          <t>4.440323393984105</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.4702237119242</t>
+          <t>1.470219739531221</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>16.99387707780688</t>
+          <t>16.993873920361096</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>10.69407975310926</t>
+          <t>10.69407420122494</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17.53712498377474</t>
+          <t>17.537111063873468</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>11.960725415981564</t>
+          <t>11.960738630193546</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>12.27704591705109</t>
+          <t>12.277041028680912</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>31.671791438116617</t>
+          <t>31.671781493361546</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20.923236610192134</t>
+          <t>20.923258825641938</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>11.293893714861307</t>
+          <t>11.293895974350166</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>7.157093707623624</t>
+          <t>7.157087672237003</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>12.28510953674136</t>
+          <t>12.28512776795946</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>6.484132321458162</t>
+          <t>6.484136388728216</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>3.2013388276932635</t>
+          <t>3.201333981128471</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>1.7334031858765866</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.561874803446679</t>
+          <t>4.952314620980141</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.5778010619588624</t>
+          <t>0.6331964047096604</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.349516295759591</t>
+          <t>3.4558250301612117</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.125735874072862</t>
+          <t>4.485238087100072</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.6666666666666665</t>
+          <t>1.8264544852254074</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.23330451480409561</t>
+          <t>0.23901434692247872</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.7635044785796359</t>
+          <t>2.3547873114782463</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.7579706660211345</t>
+          <t>4.56192391490669</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.70456486137585</t>
+          <t>8.839017265404578</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.22812868869012348</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.8780677321674606</t>
+          <t>0.9622504486493763</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.7604289623004117</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.317101598251191</t>
+          <t>1.4433756729740645</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.1549214175724964</t>
+          <t>2.1594169393842595</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.281286886901235</t>
+          <t>2.5</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.7514558844556287</t>
+          <t>2.9478745582627894</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.5208579246008234</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.935062597404264</t>
+          <t>6.057904066606328</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26.005440075594578</t>
+          <t>26.793366278564722</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.236025891788948</t>
+          <t>3.454872006895405</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.2532054412765448</t>
+          <t>1.3110398933830278</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.4783679982596105</t>
+          <t>2.693059565912403</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.86795080049255</t>
+          <t>11.131571221058953</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.7456622789931115</t>
+          <t>4.475514274157544</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.3155924810815662</t>
+          <t>2.2269268599825813</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>1.5817559830612324</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.2663928094193209</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.20725280303512966</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.4811252243246881</t>
+          <t>0.527251994353744</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.6671871973200014</t>
+          <t>0.7311522294180514</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.5596496731201133</t>
+          <t>3.557516755073614</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.8012497612818937</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4299054558115628</t>
+          <t>0.4337603705916653</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.4330405838692153</t>
+          <t>3.493579379601613</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.33340624724744394</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.7659527384256924</t>
+          <t>0.8592337042894796</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.693902648046337</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.8790821704276746</t>
+          <t>1.6549776853234575</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.8333333333333333</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.2403749283845681</t>
+          <t>0.2634203196502382</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.5698904455131</t>
+          <t>6.476756114397293</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2403749283845681</t>
+          <t>0.2634203196502382</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5.5787550460758295</t>
+          <t>5.629191584400591</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.47452679491836974</t>
+          <t>0.520020955762976</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.016270570767943</t>
+          <t>1.1003956633055718</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5069526415336075</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.865548789854242</t>
+          <t>2.99890425908716</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.3596951261571522</t>
+          <t>1.4089238748332131</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.40062488064094687</t>
+          <t>0.4390338660837303</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.23130088268211232</t>
+          <t>0.25347632076680376</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.20817079441390107</t>
+          <t>0.22812868869012348</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2.954916555311748</t>
+          <t>3.238212357549572</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.116008986673664</t>
+          <t>2.076289377051222</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.903345296042076</t>
+          <t>6.840421513633402</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1.0374482733690513</t>
+          <t>0.9807638791040604</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.3852007079725748</t>
+          <t>0.42213093647310695</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2.880495804666179</t>
+          <t>4.391507851617629</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.2474549336629778</t>
+          <t>0.2403011173814012</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.7053107045498049</t>
+          <t>0.7390308294774428</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2316873613693221</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.6719994689466546</t>
+          <t>1.5658129358579322</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.26630856169310224</t>
+          <t>0.4246226676617728</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.0488247083907414</t>
+          <t>2.2452510468485443</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.0488247083907414</t>
+          <t>2.2452510468485443</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.2853885922378716</t>
+          <t>1.3792583770458149</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7019306543297628</t>
+          <t>0.71840368679843</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.5608748328973255</t>
+          <t>0.6146474125172223</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.3831959186919521</t>
+          <t>0.3669132510680256</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.9954072771682729</t>
+          <t>0.9990984383625267</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.808706322501891</t>
+          <t>2.860041787855309</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.474446276206508</t>
+          <t>2.798000371567052</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.308990127940639</t>
+          <t>1.4986182763762983</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.7177920521843664</t>
+          <t>0.5493395544672325</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.3513916924472502</t>
+          <t>1.4766824489204282</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.411623985077078</t>
+          <t>1.3547169796604352</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>9.97943383143</t>
+          <t>10.840331846097772</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>11.194760647123474</t>
+          <t>10.184394489600678</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6085197248416121</t>
+          <t>0.6234167440361564</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>4.194170498387171</t>
+          <t>4.601581717834051</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>1.8702760455295984</t>
+          <t>1.9827343964380617</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>14.816745035209017</t>
+          <t>13.70839455575554</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>6.251553119363984</t>
+          <t>6.52910194903757</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.2962962962962958</t>
+          <t>1.4205757107308723</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.1205621110531476</t>
+          <t>1.1849363641921355</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>3.8967528559828124</t>
+          <t>4.011772167512062</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.660128626594638</t>
+          <t>2.849232232671369</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.542414122088259</t>
+          <t>0.563103163986796</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.037511645580189</t>
+          <t>5.639125386177021</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2.315108383507564</t>
+          <t>4.012180009516243</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.6406561636537222</t>
+          <t>1.557445099496081</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.385770618301029</t>
+          <t>0.4129512819912602</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>1.0794041191831907</t>
+          <t>1.1828894969117507</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>16.53776063871775</t>
+          <t>18.026192195771937</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.2059440455812904</t>
+          <t>1.0197857985061631</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.804694556742412</t>
+          <t>7.908897344514294</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.510779992989852</t>
+          <t>0.5441218868840588</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.4750073270494181</t>
+          <t>0.4505442357153466</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>25.265370352351113</t>
+          <t>25.835186114695226</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>18.25087464958201</t>
+          <t>18.69804525575301</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.4485221101801828</t>
+          <t>1.4805535444795028</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.804611463017265</t>
+          <t>1.7524906584082793</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>14.217421601730946</t>
+          <t>14.941924586360429</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>3.4284195304460887</t>
+          <t>3.654591517749436</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>5.806629556000286</t>
+          <t>5.941883371270137</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7141846717554521</t>
+          <t>0.7381494706441623</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.32194908369338293</t>
+          <t>0.3341980140784644</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.3667037844845993</t>
+          <t>2.140669487954284</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.341068070488006</t>
+          <t>14.319069651766263</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.3619140094085909</t>
+          <t>1.430926449609314</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.182576778246428</t>
+          <t>14.596493570951088</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.5570544179123</t>
+          <t>3.654704020379169</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.6531843568582143</t>
+          <t>1.735665651178464</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.7514592208696584</t>
+          <t>1.8068785235449636</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.5830252018758397</t>
+          <t>1.7054856849236</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>32.99807866238464</t>
+          <t>34.58123421150158</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.1380801550132684</t>
+          <t>3.258070053958848</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>13.31105797972377</t>
+          <t>13.061941185080272</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>4.440323393984105</t>
+          <t>4.183979927484203</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.470219739531221</t>
+          <t>1.379184056810845</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>16.993873920361096</t>
+          <t>17.540517895605312</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>10.69407420122494</t>
+          <t>10.63456096563458</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17.537111063873468</t>
+          <t>17.212470622612564</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>11.960738630193546</t>
+          <t>12.39381756151565</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>12.277041028680912</t>
+          <t>13.929388200328614</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>31.671781493361546</t>
+          <t>33.51480947617925</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20.923258825641938</t>
+          <t>19.709106453454027</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>11.293895974350166</t>
+          <t>11.884599361585714</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>7.157087672237003</t>
+          <t>6.88605698422062</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>12.28512776795946</t>
+          <t>12.74744831472148</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>6.484136388728216</t>
+          <t>5.739560661181159</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>3.201333981128471</t>
+          <t>2.3359047727832234</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D460"/>
+  <dimension ref="A1:D463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.952314620980141</t>
+          <t>4.5373933773505595</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.4558250301612117</t>
+          <t>3.366373122324899</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.485238087100072</t>
+          <t>1.4211486170404626</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.23901434692247872</t>
+          <t>0.25201120920720244</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.3547873114782463</t>
+          <t>2.401842303864301</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.56192391490669</t>
+          <t>5.836567035783441</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.839017265404578</t>
+          <t>6.439003772009604</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.1594169393842595</t>
+          <t>1.9925460074912045</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.9478745582627894</t>
+          <t>3.1197839532069302</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6666666666666665</t>
+          <t>1.8733149685941985</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6.057904066606328</t>
+          <t>7.654281685776174</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26.793366278564722</t>
+          <t>12.713426375035983</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.454872006895405</t>
+          <t>1.3696775056958161</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.3110398933830278</t>
+          <t>0.8098016813458584</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.693059565912403</t>
+          <t>2.9100403513602586</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.131571221058953</t>
+          <t>8.240460137777417</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.475514274157544</t>
+          <t>5.528785109137439</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.2269268599825813</t>
+          <t>1.6004455008951826</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.557516755073614</t>
+          <t>3.3990425664866493</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4337603705916653</t>
+          <t>0.4595994185994283</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3.493579379601613</t>
+          <t>1.4888564619077667</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.33340624724744394</t>
+          <t>0.46151494387686953</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.8592337042894796</t>
+          <t>0.8693991018659801</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.6549776853234575</t>
+          <t>1.0783846467002933</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.476756114397293</t>
+          <t>6.375169835743822</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5.629191584400591</t>
+          <t>10.59390656474744</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.1003956633055718</t>
+          <t>1.5876438765312355</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.99890425908716</t>
+          <t>2.911933849128296</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.4089238748332131</t>
+          <t>1.5828207520481072</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.076289377051222</t>
+          <t>2.290062990128732</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.840421513633402</t>
+          <t>6.84578237294366</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0.9807638791040604</t>
+          <t>0.907196294641416</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.391507851617629</t>
+          <t>4.018700902749259</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.2403011173814012</t>
+          <t>0.2875955488858465</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.7390308294774428</t>
+          <t>0.6721988674794598</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.5658129358579322</t>
+          <t>1.3882903356541638</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.4246226676617728</t>
+          <t>0.44096811358460114</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3792583770458149</t>
+          <t>1.414651804613345</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.71840368679843</t>
+          <t>0.7646782960405871</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.3669132510680256</t>
+          <t>0.40811243561810584</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.9990984383625267</t>
+          <t>0.20022325014331877</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.860041787855309</t>
+          <t>1.9179916722303698</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2.798000371567052</t>
+          <t>1.9767612683001383</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.4986182763762983</t>
+          <t>1.40534255544455</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.5493395544672325</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.4766824489204282</t>
+          <t>1.4526053396976915</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.3547169796604352</t>
+          <t>1.3222021125024392</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>10.840331846097772</t>
+          <t>3.259997177909449</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>10.184394489600678</t>
+          <t>9.944456345415064</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6234167440361564</t>
+          <t>0.6427303889872878</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>4.601581717834051</t>
+          <t>3.437550436612261</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>1.9827343964380617</t>
+          <t>2.2591889730482</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>13.70839455575554</t>
+          <t>13.580382838207804</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>6.52910194903757</t>
+          <t>3.910527149987851</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.1849363641921355</t>
+          <t>1.1956489868592035</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>4.011772167512062</t>
+          <t>2.686511932085389</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.849232232671369</t>
+          <t>2.2502294799688087</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.563103163986796</t>
+          <t>0.7841851967875364</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.639125386177021</t>
+          <t>5.396138440578857</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>4.012180009516243</t>
+          <t>3.684921183483098</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>1.557445099496081</t>
+          <t>2.274751695723469</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.4129512819912602</t>
+          <t>0.40410123804115017</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>18.026192195771937</t>
+          <t>11.376205793723948</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>1.0197857985061631</t>
+          <t>0.9371551433523136</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>7.908897344514294</t>
+          <t>9.425555253086095</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.5441218868840588</t>
+          <t>0.2540746158083268</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.4505442357153466</t>
+          <t>0.37522150874562854</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>25.835186114695226</t>
+          <t>21.065993706081237</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>18.69804525575301</t>
+          <t>13.806791466707342</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.4805535444795028</t>
+          <t>1.3188034479569666</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.7524906584082793</t>
+          <t>1.5938272176711499</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>14.941924586360429</t>
+          <t>15.502743218200175</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>3.654591517749436</t>
+          <t>1.2935127414785499</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>5.941883371270137</t>
+          <t>6.340654279812104</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7381494706441623</t>
+          <t>0.7443776285559229</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3341980140784644</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.140669487954284</t>
+          <t>2.012828243440964</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>14.319069651766263</t>
+          <t>13.572055476622399</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>1.430926449609314</t>
+          <t>0.5421105686698535</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>14.596493570951088</t>
+          <t>11.117194272307806</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.654704020379169</t>
+          <t>3.0984460862991003</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.735665651178464</t>
+          <t>1.2434106247437178</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.8068785235449636</t>
+          <t>1.8164132643089328</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.7054856849236</t>
+          <t>1.7243745890478088</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>34.58123421150158</t>
+          <t>18.94415563383503</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.258070053958848</t>
+          <t>3.3235164260973233</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>13.061941185080272</t>
+          <t>5.1139398853772775</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>4.183979927484203</t>
+          <t>3.6372851195674443</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>1.379184056810845</t>
+          <t>0.6829415694635803</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>17.540517895605312</t>
+          <t>14.32505588848148</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>10.63456096563458</t>
+          <t>4.531112033504467</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17.212470622612564</t>
+          <t>18.884953747907993</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>12.39381756151565</t>
+          <t>13.923699052962933</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>13.929388200328614</t>
+          <t>11.003232888903842</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>33.51480947617925</t>
+          <t>19.314597826013333</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>19.709106453454027</t>
+          <t>31.048056670846755</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>11.884599361585714</t>
+          <t>12.0862108482079</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>6.88605698422062</t>
+          <t>7.953030322261773</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>12.74744831472148</t>
+          <t>13.00694348007828</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>5.739560661181159</t>
+          <t>8.29142668706406</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,73 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2.3359047727832234</t>
+          <t>1.9625362295311817</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>DF_INT_UI_Goku</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>BU_STR_Yakon</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>21.21216525592952</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>DF_TEQ_Dabura</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>36.47121351709307</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.5373933773505595</t>
+          <t>4.1752687072844985</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.366373122324899</t>
+          <t>3.257995860158855</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.4211486170404626</t>
+          <t>1.397538459502134</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.25201120920720244</t>
+          <t>0.2525296902619156</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.401842303864301</t>
+          <t>2.327244898130253</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.836567035783441</t>
+          <t>5.886176749306498</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.439003772009604</t>
+          <t>6.796796700829065</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.9925460074912045</t>
+          <t>1.8621151978653336</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.1197839532069302</t>
+          <t>2.9555336172498805</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.8733149685941985</t>
+          <t>1.929784717152785</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.654281685776174</t>
+          <t>7.602550998653922</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.713426375035983</t>
+          <t>12.693673552072486</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.3696775056958161</t>
+          <t>1.412972662363643</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.8098016813458584</t>
+          <t>0.7482257005778452</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.9100403513602586</t>
+          <t>2.8813232630208603</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.240460137777417</t>
+          <t>8.13392589633917</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.528785109137439</t>
+          <t>5.328219961059762</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.6004455008951826</t>
+          <t>1.5418426636000544</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.3990425664866493</t>
+          <t>3.2906245376508636</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4595994185994283</t>
+          <t>0.43147557268463577</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.4888564619077667</t>
+          <t>1.4737476047536862</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.46151494387686953</t>
+          <t>0.4785750373475837</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.8693991018659801</t>
+          <t>0.8212763616059604</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.0783846467002933</t>
+          <t>1.0724043843931048</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.375169835743822</t>
+          <t>6.22244088107781</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10.59390656474744</t>
+          <t>10.234054679911354</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.5876438765312355</t>
+          <t>1.6270256367403206</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.911933849128296</t>
+          <t>2.9198149925532944</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.5828207520481072</t>
+          <t>1.5942202203971108</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.290062990128732</t>
+          <t>2.184136815274895</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.84578237294366</t>
+          <t>6.594353316535745</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0.907196294641416</t>
+          <t>0.8963312584684431</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.018700902749259</t>
+          <t>3.8505534271604485</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.2875955488858465</t>
+          <t>0.28984672682925117</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.6721988674794598</t>
+          <t>0.6131692990238453</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.3882903356541638</t>
+          <t>1.3698103387818341</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.44096811358460114</t>
+          <t>0.4238696572620002</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.414651804613345</t>
+          <t>1.293319575419819</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.7646782960405871</t>
+          <t>0.6984366555566672</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.40811243561810584</t>
+          <t>0.44037555903211967</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.20022325014331877</t>
+          <t>0.20026981789164022</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1.9179916722303698</t>
+          <t>2.0023163707983986</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>1.9767612683001383</t>
+          <t>1.8536864343688908</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.40534255544455</t>
+          <t>1.2545376323517594</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.4526053396976915</t>
+          <t>1.2716982019547256</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.3222021125024392</t>
+          <t>1.4005293038215887</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>3.259997177909449</t>
+          <t>3.0660820710683865</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>9.944456345415064</t>
+          <t>9.577648757812184</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6427303889872878</t>
+          <t>0.6202174252703178</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>3.437550436612261</t>
+          <t>3.714231621217241</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.2591889730482</t>
+          <t>2.40271552120352</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>13.580382838207804</t>
+          <t>13.067811222319037</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>3.910527149987851</t>
+          <t>4.092146718490477</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.1956489868592035</t>
+          <t>1.0624245230478184</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2.686511932085389</t>
+          <t>2.741013907987944</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.2502294799688087</t>
+          <t>2.0736177933475233</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7841851967875364</t>
+          <t>0.7807250216316026</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.396138440578857</t>
+          <t>5.03218245447178</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3.684921183483098</t>
+          <t>3.5898021351111424</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2.274751695723469</t>
+          <t>2.5374719918926716</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.40410123804115017</t>
+          <t>0.36448146409117044</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>11.376205793723948</t>
+          <t>10.665031507125441</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>0.9371551433523136</t>
+          <t>0.869142502206472</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>9.425555253086095</t>
+          <t>9.03916879058248</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.2540746158083268</t>
+          <t>0.23762165964454995</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.37522150874562854</t>
+          <t>0.36004851493526246</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>21.065993706081237</t>
+          <t>19.963295927420486</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>13.806791466707342</t>
+          <t>12.96141648901601</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.3188034479569666</t>
+          <t>1.166046944848671</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.5938272176711499</t>
+          <t>1.455457336109879</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>15.502743218200175</t>
+          <t>16.030619181049687</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>1.2935127414785499</t>
+          <t>1.2816605368133203</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>6.340654279812104</t>
+          <t>5.820007093274572</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.7443776285559229</t>
+          <t>0.6767659406626878</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2.012828243440964</t>
+          <t>1.8521144745101168</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>13.572055476622399</t>
+          <t>12.830132917869399</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.5421105686698535</t>
+          <t>0.5015331201556824</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>11.117194272307806</t>
+          <t>10.488789037782105</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.0984460862991003</t>
+          <t>2.7082086921139794</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.2434106247437178</t>
+          <t>1.2330771392117825</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.8164132643089328</t>
+          <t>1.6430208563743887</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.7243745890478088</t>
+          <t>1.5715264012588595</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>18.94415563383503</t>
+          <t>18.45647481956503</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.3235164260973233</t>
+          <t>3.266793641760378</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>5.1139398853772775</t>
+          <t>5.200262612295418</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.6372851195674443</t>
+          <t>3.2137625085419796</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>14.32505588848148</t>
+          <t>14.111188649979338</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>4.531112033504467</t>
+          <t>5.010617092246244</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>18.884953747907993</t>
+          <t>18.834313598761085</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>13.923699052962933</t>
+          <t>14.078657532111881</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>11.003232888903842</t>
+          <t>10.214106662142498</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>19.314597826013333</t>
+          <t>18.54970419017043</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>31.048056670846755</t>
+          <t>30.19705249794349</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>12.0862108482079</t>
+          <t>10.878365945873897</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>7.953030322261773</t>
+          <t>7.717997354398528</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>13.00694348007828</t>
+          <t>11.63999600175544</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>8.29142668706406</t>
+          <t>7.647959343530275</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>1.9625362295311817</t>
+          <t>1.8399286228341083</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>21.21216525592952</t>
+          <t>18.71497823069525</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>36.47121351709307</t>
+          <t>32.45671126440489</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.1752687072844985</t>
+          <t>4.200276053503051</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.257995860158855</t>
+          <t>3.2576384221378714</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.397538459502134</t>
+          <t>1.3978933973169436</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.2525296902619156</t>
+          <t>0.2530378195119672</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.327244898130253</t>
+          <t>2.3207565346937744</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.886176749306498</t>
+          <t>5.878315604562223</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.796796700829065</t>
+          <t>6.794843154804299</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.8621151978653336</t>
+          <t>1.8553421709609927</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.9555336172498805</t>
+          <t>2.9663552850011214</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.929784717152785</t>
+          <t>1.9406698462495795</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.602550998653922</t>
+          <t>7.609529987461181</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.693673552072486</t>
+          <t>12.743614720969116</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.412972662363643</t>
+          <t>1.4178626111971713</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.7482257005778452</t>
+          <t>0.7503767892981414</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.8813232630208603</t>
+          <t>2.8871999202216188</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.13392589633917</t>
+          <t>8.096536714807668</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.328219961059762</t>
+          <t>5.329017015622243</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.5418426636000544</t>
+          <t>1.5446439211140117</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.2906245376508636</t>
+          <t>3.2959685885821552</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.43147557268463577</t>
+          <t>0.4332541228027679</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.4737476047536862</t>
+          <t>1.479921858374792</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.4785750373475837</t>
+          <t>0.4772065107651129</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.8212763616059604</t>
+          <t>0.8225605877078194</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.0724043843931048</t>
+          <t>1.0624789563628363</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.22244088107781</t>
+          <t>6.225404904263184</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10.234054679911354</t>
+          <t>10.227534041965988</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.6270256367403206</t>
+          <t>1.632455757368762</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.9198149925532944</t>
+          <t>2.9332472488780086</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.5942202203971108</t>
+          <t>1.596711913375989</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.184136815274895</t>
+          <t>2.187574670230299</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.594353316535745</t>
+          <t>6.584088874272197</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0.8963312584684431</t>
+          <t>0.8941104882675148</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.8505534271604485</t>
+          <t>3.8426720411122304</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.28984672682925117</t>
+          <t>0.29136423998243455</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.6131692990238453</t>
+          <t>0.6118917172346404</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.3698103387818341</t>
+          <t>1.3725943495463213</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.4238696572620002</t>
+          <t>0.42402154103489975</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.293319575419819</t>
+          <t>1.3018968151425676</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.6984366555566672</t>
+          <t>0.702349359315277</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.44037555903211967</t>
+          <t>0.44044623120211657</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.20026981789164022</t>
+          <t>0.20062682669280996</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.0023163707983986</t>
+          <t>1.9930909392492602</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>1.8536864343688908</t>
+          <t>1.8547179947591381</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.2545376323517594</t>
+          <t>1.2571973185720804</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.2716982019547256</t>
+          <t>1.2830536055997968</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.4005293038215887</t>
+          <t>1.401539343479127</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>3.0660820710683865</t>
+          <t>3.0650509010129703</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>9.577648757812184</t>
+          <t>9.566533752618327</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6202174252703178</t>
+          <t>0.6206197352093962</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>3.714231621217241</t>
+          <t>3.723746284885411</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.40271552120352</t>
+          <t>2.39435840081261</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>13.067811222319037</t>
+          <t>13.059402866775521</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>4.092146718490477</t>
+          <t>4.11442176708323</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.0624245230478184</t>
+          <t>1.0685367703886541</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2.741013907987944</t>
+          <t>2.7538130499849665</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.0736177933475233</t>
+          <t>2.073579687029639</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7807250216316026</t>
+          <t>0.7815552871467437</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.03218245447178</t>
+          <t>5.030149223187301</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3.5898021351111424</t>
+          <t>3.5847689950325474</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2.5374719918926716</t>
+          <t>2.534065023991858</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.36448146409117044</t>
+          <t>0.3654596803026102</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>10.665031507125441</t>
+          <t>10.66586161195867</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>0.869142502206472</t>
+          <t>0.8627907195006799</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>9.03916879058248</t>
+          <t>9.018878700725153</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.23762165964454995</t>
+          <t>0.23816976208741703</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.36004851493526246</t>
+          <t>0.36139178037962444</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>19.963295927420486</t>
+          <t>20.00198625882544</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>12.96141648901601</t>
+          <t>12.868105397397997</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.166046944848671</t>
+          <t>1.1603503666384798</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.455457336109879</t>
+          <t>1.4572737942590501</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>16.030619181049687</t>
+          <t>15.998168513761895</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>1.2816605368133203</t>
+          <t>1.2760658082252823</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>5.820007093274572</t>
+          <t>5.851249587458519</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.6767659406626878</t>
+          <t>0.6774883305796466</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.8521144745101168</t>
+          <t>1.8423680720508315</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>12.830132917869399</t>
+          <t>12.81107638399293</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.5015331201556824</t>
+          <t>0.49791887905844995</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>10.488789037782105</t>
+          <t>10.444950946988897</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2.7082086921139794</t>
+          <t>2.713484105289787</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.2330771392117825</t>
+          <t>1.2281144801088206</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.6430208563743887</t>
+          <t>1.6489503734034763</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.5715264012588595</t>
+          <t>1.5785844977531909</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>18.45647481956503</t>
+          <t>18.39126311653206</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.266793641760378</t>
+          <t>3.281380057838288</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>5.200262612295418</t>
+          <t>5.194912700877978</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.2137625085419796</t>
+          <t>3.2254197386338426</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>14.111188649979338</t>
+          <t>14.084102366754493</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>5.010617092246244</t>
+          <t>4.987924607109049</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>18.834313598761085</t>
+          <t>18.78592193807156</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>14.078657532111881</t>
+          <t>14.110006234533952</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>10.214106662142498</t>
+          <t>10.184241699193908</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>18.54970419017043</t>
+          <t>18.46667725308745</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>30.19705249794349</t>
+          <t>30.215058956017188</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>10.878365945873897</t>
+          <t>10.878324217797797</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>7.717997354398528</t>
+          <t>7.700494932997023</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>11.63999600175544</t>
+          <t>11.71445364545764</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>7.647959343530275</t>
+          <t>7.660768037199162</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>1.8399286228341083</t>
+          <t>1.8281941253528375</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>18.71497823069525</t>
+          <t>15.0114102759968</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>32.45671126440489</t>
+          <t>44.71819490181953</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.7334031858765866</t>
+          <t>0.24267644602272212</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.200276053503051</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>0.08864749665935245</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.35000000000000003</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.08523454264385234</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.2576384221378714</t>
+          <t>0.5142857142857143</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.3978933973169436</t>
+          <t>0.1285714285714286</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>0.13471506281091267</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.11666666666666665</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>0.255703627931557</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.2530378195119672</t>
+          <t>0.17142857142857143</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.3207565346937744</t>
+          <t>0.21428571428571427</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.04285714285714286</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.878315604562223</t>
+          <t>0.34285714285714286</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.794843154804299</t>
+          <t>0.7714285714285714</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>0.13471506281091267</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>0.13471506281091267</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>0.10646005472205765</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>0.202072594216369</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.8553421709609927</t>
+          <t>0.21428571428571427</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.35000000000000003</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.9663552850011214</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.9406698462495795</t>
+          <t>0.2333333333333333</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.609529987461181</t>
+          <t>0.2571428571428572</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.743614720969116</t>
+          <t>0.7714285714285714</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.4178626111971713</t>
+          <t>0.08571428571428572</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.7503767892981414</t>
+          <t>0.04285714285714286</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.8871999202216188</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.096536714807668</t>
+          <t>0.2571428571428572</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.329017015622243</t>
+          <t>0.21428571428571427</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.5446439211140117</t>
+          <t>0.2571428571428572</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>0.22144583762857253</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>0.19429274145297434</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.046703103812400094</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>0.07381527920952417</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>0.09340620762480019</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.2959685885821552</t>
+          <t>0.6000000000000001</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.043869133765083085</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.043869133765083085</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3070839363555815</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>0.11217496657946512</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.4332541228027679</t>
+          <t>0.11217496657946512</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.06476424715099145</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.479921858374792</t>
+          <t>0.17142857142857143</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.07381527920952417</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.03466806371753174</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.03163511966122464</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.4772065107651129</t>
+          <t>0.08571428571428572</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.8225605877078194</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02142857142857143</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>0.09714637072648717</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.0624789563628363</t>
+          <t>0.08571428571428572</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.03333333333333333</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.07777777777777778</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.061464741251722244</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.08864749665935245</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>0.11666666666666665</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.2634203196502382</t>
+          <t>0.05268406393004763</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.08864749665935245</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6.225404904263184</t>
+          <t>0.2571428571428572</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.04097649416781483</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2634203196502382</t>
+          <t>0.05268406393004763</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10.227534041965988</t>
+          <t>0.5142857142857143</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.520020955762976</t>
+          <t>0.10400419115259521</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1.632455757368762</t>
+          <t>0.17142857142857143</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.07777777777777778</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.9332472488780086</t>
+          <t>0.30000000000000004</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1.596711913375989</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.061464741251722244</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.25347632076680376</t>
+          <t>0.03548668490735253</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.17142857142857143</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.03163511966122464</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.10400419115259521</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.05268406393004763</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>8.623264432486668</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.22812868869012348</t>
+          <t>0.045625737738024696</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.026342031965023816</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.05268406393004763</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.04285714285714286</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>3.238212357549572</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2.187574670230299</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4533497300569401</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>6.584088874272197</t>
+          <t>0.7000000000000001</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.032382123575495726</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0.8941104882675148</t>
+          <t>0.35000000000000003</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.05909833110623497</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.023112042478354484</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.026964049558080228</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.04285714285714286</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.8426720411122304</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.026964049558080228</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.29136423998243455</t>
+          <t>0.023112042478354484</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.026964049558080228</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0.6118917172346404</t>
+          <t>0.1285714285714286</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.3725943495463213</t>
+          <t>0.17142857142857143</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>0.42402154103489975</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.2452510468485443</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.2452510468485443</t>
+          <t>0.3143351465587962</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1.3018968151425676</t>
+          <t>0.2571428571428572</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>0.702349359315277</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.6146474125172223</t>
+          <t>0.12292948250344447</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.44044623120211657</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.20062682669280996</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1.9930909392492602</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>1.8547179947591381</t>
+          <t>0.30000000000000004</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1.2571973185720804</t>
+          <t>0.15000000000000002</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1.2830536055997968</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1.401539343479127</t>
+          <t>0.03412043737284239</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>3.0650509010129703</t>
+          <t>0.15000000000000002</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>9.566533752618327</t>
+          <t>0.7000000000000001</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.6206197352093962</t>
+          <t>0.04285714285714286</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>3.723746284885411</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2.39435840081261</t>
+          <t>0.15000000000000002</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>13.059402866775521</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>4.11442176708323</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.4205757107308723</t>
+          <t>2.8</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1.0685367703886541</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2.7538130499849665</t>
+          <t>0.30000000000000004</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2.073579687029639</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>0.7815552871467437</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5.030149223187301</t>
+          <t>0.7000000000000001</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3.5847689950325474</t>
+          <t>0.35000000000000003</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2.534065023991858</t>
+          <t>2.0999999999999996</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0.3654596803026102</t>
+          <t>0.15000000000000002</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>1.1828894969117507</t>
+          <t>0.16560452956764513</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>10.66586161195867</t>
+          <t>0.6000000000000001</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>0.8627907195006799</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>9.018878700725153</t>
+          <t>0.30000000000000004</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0.23816976208741703</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.36139178037962444</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20.00198625882544</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>12.868105397397997</t>
+          <t>0.6000000000000001</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>1.1603503666384798</t>
+          <t>0.0642857142857143</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1.4572737942590501</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>15.998168513761895</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>1.2760658082252823</t>
+          <t>0.08571428571428572</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>5.851249587458519</t>
+          <t>1.4</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.08571428571428572</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.6774883305796466</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>1.8423680720508315</t>
+          <t>0.45</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>12.81107638399293</t>
+          <t>0.30000000000000004</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.49791887905844995</t>
+          <t>0.04285714285714286</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>10.444950946988897</t>
+          <t>0.7000000000000001</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2.713484105289787</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>1.2281144801088206</t>
+          <t>0.0642857142857143</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>1.6489503734034763</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>1.5785844977531909</t>
+          <t>0.30000000000000004</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>18.39126311653206</t>
+          <t>4.8999999999999995</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.281380057838288</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>5.194912700877978</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.2254197386338426</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>0.6829415694635803</t>
+          <t>2.8</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>14.084102366754493</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>4.987924607109049</t>
+          <t>4.199999999999999</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>18.78592193807156</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>14.110006234533952</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>10.184241699193908</t>
+          <t>0.6000000000000001</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>18.46667725308745</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>30.215058956017188</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>10.878324217797797</t>
+          <t>0.10714285714285714</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>7.700494932997023</t>
+          <t>0.1285714285714286</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>11.71445364545764</t>
+          <t>2.8</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>7.660768037199162</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>1.8281941253528375</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>15.0114102759968</t>
+          <t>2.8</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>44.71819490181953</t>
+          <t>7.0</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.24267644602272212</t>
+          <t>0.22644485162471262</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.08864749665935245</t>
+          <t>0.0829675914145261</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.08523454264385234</t>
+          <t>0.08001378653035493</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.13471506281091267</t>
+          <t>0.12608347341863527</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.11666666666666665</t>
+          <t>0.10886332998468887</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.255703627931557</t>
+          <t>0.24076494769911352</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.13471506281091267</t>
+          <t>0.12608347341863527</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04665571285058094</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.13471506281091267</t>
+          <t>0.12608347341863527</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.10646005472205765</t>
+          <t>0.09963884661164767</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.202072594216369</t>
+          <t>0.18912521012795291</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.35000000000000003</t>
+          <t>0.32658998995406663</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.2333333333333333</t>
+          <t>0.21772665996937773</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.22144583762857253</t>
+          <t>0.20663426824710107</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.19429274145297434</t>
+          <t>0.18129732708364268</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.046703103812400094</t>
+          <t>0.04357933201404422</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.07381527920952417</t>
+          <t>0.06887808941570034</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.09340620762480019</t>
+          <t>0.08715866402808845</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.043869133765083085</t>
+          <t>0.04093491415894882</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.043869133765083085</t>
+          <t>0.04093491415894882</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.3070839363555815</t>
+          <t>0.28654439911264173</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.11217496657946512</t>
+          <t>0.10498758729608514</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.11217496657946512</t>
+          <t>0.10498758729608514</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.06476424715099145</t>
+          <t>0.060432442361214235</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.07381527920952417</t>
+          <t>0.06887808941570034</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.03466806371753174</t>
+          <t>0.03234926451781609</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.03163511966122464</t>
+          <t>0.02951918117815729</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.09714637072648717</t>
+          <t>0.09064866354182134</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.03333333333333333</t>
+          <t>0.03110380856705396</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.07777777777777778</t>
+          <t>0.0725755533231259</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0.061464741251722244</t>
+          <t>0.0573536263655122</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0.08864749665935245</t>
+          <t>0.0829675914145261</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.11666666666666665</t>
+          <t>0.10886332998468887</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.05268406393004763</t>
+          <t>0.04916025117043903</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.08864749665935245</t>
+          <t>0.0829675914145261</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.04097649416781483</t>
+          <t>0.03823575091034147</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.05268406393004763</t>
+          <t>0.04916025117043903</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.10400419115259521</t>
+          <t>0.09704779355344828</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.07777777777777778</t>
+          <t>0.0725755533231259</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.061464741251722244</t>
+          <t>0.0573536263655122</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.03548668490735253</t>
+          <t>0.03321294887054921</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.03163511966122464</t>
+          <t>0.02951918117815729</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.10400419115259521</t>
+          <t>0.09704779355344828</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.05268406393004763</t>
+          <t>0.04916025117043903</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>8.623264432486668</t>
+          <t>0.35000000000000003</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.045625737738024696</t>
+          <t>0.04270236283356329</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.026342031965023816</t>
+          <t>0.024580125585219516</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0.05268406393004763</t>
+          <t>0.04916025117043903</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0.4533497300569401</t>
+          <t>0.4230270965284996</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0.032382123575495726</t>
+          <t>0.030216221180607118</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.05909833110623497</t>
+          <t>0.05531172760968407</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.023112042478354484</t>
+          <t>0.02156617634521072</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.026964049558080228</t>
+          <t>0.025160539069412503</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.026964049558080228</t>
+          <t>0.025160539069412503</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0.023112042478354484</t>
+          <t>0.02156617634521072</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0.026964049558080228</t>
+          <t>0.025160539069412503</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>0.3143351465587962</t>
+          <t>0.2941947713101489</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.12292948250344447</t>
+          <t>0.11470725273102439</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.03412043737284239</t>
+          <t>0.0318382665680713</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>0.16560452956764513</t>
+          <t>0.1549937613958963</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.7334031858765866</t>
+          <t>3.466806371753173</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6331964047096604</t>
+          <t>1.2663928094193209</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.9245008972987525</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.8264544852254074</t>
+          <t>3.652908970450815</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.9245008972987525</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.9622504486493763</t>
+          <t>1.9245008972987525</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.7604289623004117</t>
+          <t>1.5208579246008234</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.4433756729740645</t>
+          <t>2.886751345948129</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.9406698462495795</t>
+          <t>3.333333333333333</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.5817559830612324</t>
+          <t>3.163511966122465</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.387805296092674</t>
+          <t>2.775610592185348</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.527251994353744</t>
+          <t>1.054503988707488</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.7311522294180514</t>
+          <t>1.4623044588361027</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.8012497612818937</t>
+          <t>1.6024995225637875</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>1.1111111111111112</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3466806371753174</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3163511966122465</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.693902648046337</t>
+          <t>1.387805296092674</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>1.1111111111111112</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0.8333333333333333</t>
+          <t>1.6666666666666665</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0.2634203196502382</t>
+          <t>0.5268406393004764</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2634203196502382</t>
+          <t>0.5268406393004764</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.520020955762976</t>
+          <t>1.040041911525952</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>1.1111111111111112</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.4390338660837303</t>
+          <t>0.8780677321674606</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0.25347632076680376</t>
+          <t>0.5069526415336075</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2634203196502382</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.22812868869012348</t>
+          <t>0.45625737738024696</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.2634203196502382</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>3.238212357549572</t>
+          <t>2.064991017880133</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.42213093647310695</t>
+          <t>0.8442618729462139</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.23112042478354483</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3852007079725748</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.2452510468485443</t>
+          <t>1.2830005981991683</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2.2452510468485443</t>
+          <t>1.2830005981991683</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.6146474125172223</t>
+          <t>0.3512270928669842</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0.20062682669280996</t>
+          <t>0.2926892440558202</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1.4205757107308723</t>
+          <t>0.8117575489890699</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>1.1828894969117507</t>
+          <t>0.6759368553781434</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>0.6829415694635803</t>
+          <t>0.3902523254077602</t>
         </is>
       </c>
     </row>

--- a/SummonRating.xlsx
+++ b/SummonRating.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.22644485162471262</t>
+          <t>0.3396672774370689</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0829675914145261</t>
+          <t>0.12445138712178914</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.35000000000000003</t>
+          <t>0.525</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.08001378653035493</t>
+          <t>0.16002757306070986</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.5142857142857143</t>
+          <t>1.0285714285714287</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.1285714285714286</t>
+          <t>0.19285714285714284</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.12608347341863527</t>
+          <t>0.25216694683727053</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.10886332998468887</t>
+          <t>0.1632949949770333</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.24076494769911352</t>
+          <t>0.48152989539822705</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.17142857142857143</t>
+          <t>0.2571428571428571</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.21428571428571427</t>
+          <t>0.3214285714285714</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.04285714285714286</t>
+          <t>0.06428571428571428</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.34285714285714286</t>
+          <t>0.5142857142857142</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.7714285714285714</t>
+          <t>1.5428571428571427</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.12608347341863527</t>
+          <t>0.25216694683727053</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.04665571285058094</t>
+          <t>0.0699835692758714</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.12608347341863527</t>
+          <t>0.25216694683727053</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.09963884661164767</t>
+          <t>0.1494582699174715</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.18912521012795291</t>
+          <t>0.2836878151919293</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.21428571428571427</t>
+          <t>0.3214285714285714</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.32658998995406663</t>
+          <t>0.4898849849310999</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.21772665996937773</t>
+          <t>0.43545331993875547</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.2571428571428572</t>
+          <t>0.3857142857142857</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.7714285714285714</t>
+          <t>1.5428571428571427</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.08571428571428572</t>
+          <t>0.12857142857142856</t